--- a/public/data/@Liste GROUPE B.xlsx
+++ b/public/data/@Liste GROUPE B.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="553">
   <si>
     <t xml:space="preserve">Équipe </t>
   </si>
@@ -362,10 +362,10 @@
     <t>OLOMMY</t>
   </si>
   <si>
-    <t>KHALIL</t>
-  </si>
-  <si>
-    <t>ZRELLI</t>
+    <t>FUNDI REHANI</t>
+  </si>
+  <si>
+    <t>JUMAINE</t>
   </si>
   <si>
     <t>REPOSE</t>
@@ -956,7 +956,10 @@
     <t>PAULIN</t>
   </si>
   <si>
-    <t>NOEL</t>
+    <t xml:space="preserve">AXEL </t>
+  </si>
+  <si>
+    <t>ALIMASI</t>
   </si>
   <si>
     <t>MARC-ARTHUR</t>
@@ -989,10 +992,10 @@
     <t>SALOMON</t>
   </si>
   <si>
-    <t>RIDDELL</t>
-  </si>
-  <si>
-    <t>ACHELUS</t>
+    <t>RYSDAEL C.</t>
+  </si>
+  <si>
+    <t>DUVELSAINT</t>
   </si>
   <si>
     <t>TEVINSON</t>
@@ -1007,10 +1010,10 @@
     <t>SAINT-PREUX</t>
   </si>
   <si>
-    <t>JEAN HK</t>
-  </si>
-  <si>
-    <t>LEVEILLÉ</t>
+    <t xml:space="preserve">RÉGINALD </t>
+  </si>
+  <si>
+    <t>CADET</t>
   </si>
   <si>
     <t>DARLENS</t>
@@ -1040,28 +1043,25 @@
     <t>CLIFORD</t>
   </si>
   <si>
-    <t>HANS JUNIOR</t>
-  </si>
-  <si>
-    <t>JEAN-PIERRE</t>
-  </si>
-  <si>
-    <t>DALSON</t>
-  </si>
-  <si>
-    <t>LAMOUR</t>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>TEIKEU</t>
+  </si>
+  <si>
+    <t>SYLVESTRE STALONNE</t>
+  </si>
+  <si>
+    <t>SECHOUAM</t>
+  </si>
+  <si>
+    <t>CEBATIEN</t>
+  </si>
+  <si>
+    <t>PIERRE-LOUIS</t>
   </si>
   <si>
     <t>YVES-MARY</t>
-  </si>
-  <si>
-    <t>BEAUBLANC</t>
-  </si>
-  <si>
-    <t>CEBATIEN</t>
-  </si>
-  <si>
-    <t>PIERRE-LOUIS</t>
   </si>
   <si>
     <t>BEAUBRUN</t>
@@ -1875,7 +1875,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1928,6 +1928,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF6F8F9"/>
         <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -2004,7 +2010,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="117">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2084,6 +2090,12 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -2099,7 +2111,7 @@
     <xf borderId="1" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2190,14 +2202,23 @@
     <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -2918,10 +2939,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -2971,25 +2992,25 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="66">
+      <c r="A8" s="68">
         <v>1.0</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="69" t="s">
         <v>359</v>
       </c>
-      <c r="E8" s="67" t="s">
+      <c r="E8" s="69" t="s">
         <v>506</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="39">
         <v>26.0</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="40" t="s">
         <v>507</v>
       </c>
       <c r="H8" s="28"/>
@@ -3007,25 +3028,25 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="68">
+      <c r="A9" s="70">
         <v>2.0</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="D9" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="67" t="s">
+      <c r="E9" s="69" t="s">
         <v>508</v>
       </c>
-      <c r="F9" s="103">
+      <c r="F9" s="108">
         <v>22.0</v>
       </c>
-      <c r="G9" s="104" t="s">
+      <c r="G9" s="109" t="s">
         <v>509</v>
       </c>
       <c r="H9" s="31"/>
@@ -3043,7 +3064,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="66">
+      <c r="A10" s="68">
         <v>3.0</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -3052,16 +3073,16 @@
       <c r="C10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="69" t="s">
         <v>510</v>
       </c>
-      <c r="E10" s="67" t="s">
+      <c r="E10" s="69" t="s">
         <v>511</v>
       </c>
-      <c r="F10" s="103">
+      <c r="F10" s="108">
         <v>30.0</v>
       </c>
-      <c r="G10" s="104" t="s">
+      <c r="G10" s="109" t="s">
         <v>512</v>
       </c>
       <c r="H10" s="28"/>
@@ -3079,25 +3100,25 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="66">
+      <c r="A11" s="68">
         <v>4.0</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="104" t="s">
+      <c r="C11" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="69" t="s">
         <v>513</v>
       </c>
-      <c r="E11" s="67" t="s">
+      <c r="E11" s="69" t="s">
         <v>514</v>
       </c>
-      <c r="F11" s="103">
+      <c r="F11" s="108">
         <v>25.0</v>
       </c>
-      <c r="G11" s="104" t="s">
+      <c r="G11" s="109" t="s">
         <v>515</v>
       </c>
       <c r="H11" s="28"/>
@@ -3115,23 +3136,23 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="66">
+      <c r="A12" s="68">
         <v>5.0</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="104" t="s">
+      <c r="C12" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="69" t="s">
         <v>516</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="69" t="s">
         <v>517</v>
       </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="38" t="s">
+      <c r="F12" s="39"/>
+      <c r="G12" s="40" t="s">
         <v>518</v>
       </c>
       <c r="H12" s="28"/>
@@ -3149,25 +3170,25 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="66">
+      <c r="A13" s="68">
         <v>6.0</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="104" t="s">
+      <c r="C13" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="69" t="s">
         <v>389</v>
       </c>
-      <c r="E13" s="67" t="s">
+      <c r="E13" s="69" t="s">
         <v>519</v>
       </c>
-      <c r="F13" s="103">
+      <c r="F13" s="108">
         <v>25.0</v>
       </c>
-      <c r="G13" s="104" t="s">
+      <c r="G13" s="109" t="s">
         <v>520</v>
       </c>
       <c r="H13" s="28"/>
@@ -3185,25 +3206,25 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="66">
+      <c r="A14" s="68">
         <v>7.0</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="104" t="s">
+      <c r="C14" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="D14" s="69" t="s">
         <v>389</v>
       </c>
-      <c r="E14" s="67" t="s">
+      <c r="E14" s="69" t="s">
         <v>521</v>
       </c>
-      <c r="F14" s="103">
+      <c r="F14" s="108">
         <v>30.0</v>
       </c>
-      <c r="G14" s="104" t="s">
+      <c r="G14" s="109" t="s">
         <v>520</v>
       </c>
       <c r="H14" s="28"/>
@@ -3221,7 +3242,7 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="66">
+      <c r="A15" s="68">
         <v>8.0</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3230,16 +3251,16 @@
       <c r="C15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="D15" s="69" t="s">
         <v>522</v>
       </c>
-      <c r="E15" s="67" t="s">
+      <c r="E15" s="69" t="s">
         <v>519</v>
       </c>
-      <c r="F15" s="103">
+      <c r="F15" s="108">
         <v>22.0</v>
       </c>
-      <c r="G15" s="104" t="s">
+      <c r="G15" s="109" t="s">
         <v>520</v>
       </c>
       <c r="H15" s="28"/>
@@ -3257,23 +3278,23 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="66">
+      <c r="A16" s="68">
         <v>9.0</v>
       </c>
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="69" t="s">
         <v>358</v>
       </c>
-      <c r="E16" s="67" t="s">
+      <c r="E16" s="69" t="s">
         <v>523</v>
       </c>
-      <c r="F16" s="37"/>
-      <c r="G16" s="38" t="s">
+      <c r="F16" s="39"/>
+      <c r="G16" s="40" t="s">
         <v>524</v>
       </c>
       <c r="H16" s="28"/>
@@ -3291,25 +3312,25 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="68">
+      <c r="A17" s="70">
         <v>10.0</v>
       </c>
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="67" t="s">
+      <c r="D17" s="69" t="s">
         <v>525</v>
       </c>
-      <c r="E17" s="67" t="s">
+      <c r="E17" s="69" t="s">
         <v>526</v>
       </c>
-      <c r="F17" s="103">
+      <c r="F17" s="108">
         <v>27.0</v>
       </c>
-      <c r="G17" s="104" t="s">
+      <c r="G17" s="109" t="s">
         <v>512</v>
       </c>
       <c r="H17" s="31"/>
@@ -3327,25 +3348,25 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="66">
+      <c r="A18" s="68">
         <v>11.0</v>
       </c>
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="104" t="s">
+      <c r="C18" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="67" t="s">
+      <c r="D18" s="69" t="s">
         <v>527</v>
       </c>
-      <c r="E18" s="67" t="s">
+      <c r="E18" s="69" t="s">
         <v>528</v>
       </c>
-      <c r="F18" s="103">
+      <c r="F18" s="108">
         <v>23.0</v>
       </c>
-      <c r="G18" s="104" t="s">
+      <c r="G18" s="109" t="s">
         <v>520</v>
       </c>
       <c r="H18" s="28"/>
@@ -3363,25 +3384,25 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="68">
+      <c r="A19" s="70">
         <v>12.0</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="104" t="s">
+      <c r="C19" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="D19" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="E19" s="67" t="s">
+      <c r="E19" s="69" t="s">
         <v>529</v>
       </c>
-      <c r="F19" s="103">
+      <c r="F19" s="108">
         <v>30.0</v>
       </c>
-      <c r="G19" s="104" t="s">
+      <c r="G19" s="109" t="s">
         <v>512</v>
       </c>
       <c r="H19" s="31"/>
@@ -3399,23 +3420,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="68">
+      <c r="A20" s="70">
         <v>13.0</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="104" t="s">
+      <c r="C20" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="67" t="s">
+      <c r="D20" s="69" t="s">
         <v>530</v>
       </c>
-      <c r="E20" s="67" t="s">
+      <c r="E20" s="69" t="s">
         <v>531</v>
       </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="104" t="s">
+      <c r="G20" s="109" t="s">
         <v>520</v>
       </c>
       <c r="H20" s="31"/>
@@ -3433,25 +3454,25 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="68">
+      <c r="A21" s="70">
         <v>14.0</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="104" t="s">
+      <c r="C21" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="67" t="s">
+      <c r="D21" s="69" t="s">
         <v>532</v>
       </c>
-      <c r="E21" s="67" t="s">
+      <c r="E21" s="69" t="s">
         <v>533</v>
       </c>
-      <c r="F21" s="103">
+      <c r="F21" s="108">
         <v>18.0</v>
       </c>
-      <c r="G21" s="104" t="s">
+      <c r="G21" s="109" t="s">
         <v>518</v>
       </c>
       <c r="H21" s="31"/>
@@ -3469,25 +3490,25 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="66">
+      <c r="A22" s="68">
         <v>15.0</v>
       </c>
-      <c r="B22" s="105" t="s">
+      <c r="B22" s="110" t="s">
         <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="67" t="s">
+      <c r="D22" s="69" t="s">
         <v>358</v>
       </c>
-      <c r="E22" s="67" t="s">
+      <c r="E22" s="69" t="s">
         <v>534</v>
       </c>
-      <c r="F22" s="103">
+      <c r="F22" s="108">
         <v>23.0</v>
       </c>
-      <c r="G22" s="104" t="s">
+      <c r="G22" s="109" t="s">
         <v>520</v>
       </c>
       <c r="H22" s="28"/>
@@ -3505,25 +3526,25 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="68">
+      <c r="A23" s="70">
         <v>16.0</v>
       </c>
-      <c r="B23" s="105" t="s">
+      <c r="B23" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="104" t="s">
+      <c r="C23" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="67" t="s">
+      <c r="D23" s="69" t="s">
         <v>535</v>
       </c>
-      <c r="E23" s="67" t="s">
+      <c r="E23" s="69" t="s">
         <v>511</v>
       </c>
-      <c r="F23" s="103">
+      <c r="F23" s="108">
         <v>22.0</v>
       </c>
-      <c r="G23" s="104" t="s">
+      <c r="G23" s="109" t="s">
         <v>520</v>
       </c>
       <c r="H23" s="31"/>
@@ -3541,25 +3562,25 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="106">
+      <c r="A24" s="111">
         <v>17.0</v>
       </c>
-      <c r="B24" s="107" t="s">
+      <c r="B24" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C24" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="109" t="s">
+      <c r="D24" s="114" t="s">
         <v>536</v>
       </c>
-      <c r="E24" s="109" t="s">
+      <c r="E24" s="114" t="s">
         <v>537</v>
       </c>
-      <c r="F24" s="103">
+      <c r="F24" s="108">
         <v>30.0</v>
       </c>
-      <c r="G24" s="104" t="s">
+      <c r="G24" s="109" t="s">
         <v>512</v>
       </c>
       <c r="H24" s="28"/>
@@ -3577,25 +3598,25 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="66">
+      <c r="A25" s="68">
         <v>18.0</v>
       </c>
-      <c r="B25" s="67" t="s">
+      <c r="B25" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="104" t="s">
+      <c r="C25" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="69" t="s">
         <v>353</v>
       </c>
-      <c r="E25" s="67" t="s">
+      <c r="E25" s="69" t="s">
         <v>538</v>
       </c>
-      <c r="F25" s="103">
+      <c r="F25" s="108">
         <v>19.0</v>
       </c>
-      <c r="G25" s="104" t="s">
+      <c r="G25" s="109" t="s">
         <v>520</v>
       </c>
       <c r="H25" s="28"/>
@@ -3613,23 +3634,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="68">
+      <c r="A26" s="70">
         <v>19.0</v>
       </c>
-      <c r="B26" s="67" t="s">
+      <c r="B26" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="104" t="s">
+      <c r="C26" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="67" t="s">
+      <c r="D26" s="69" t="s">
         <v>539</v>
       </c>
-      <c r="E26" s="67" t="s">
+      <c r="E26" s="69" t="s">
         <v>540</v>
       </c>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38" t="s">
+      <c r="F26" s="39"/>
+      <c r="G26" s="40" t="s">
         <v>518</v>
       </c>
       <c r="H26" s="31"/>
@@ -3647,25 +3668,25 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="68">
+      <c r="A27" s="70">
         <v>20.0</v>
       </c>
-      <c r="B27" s="67" t="s">
+      <c r="B27" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="104" t="s">
+      <c r="C27" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="67" t="s">
+      <c r="D27" s="69" t="s">
         <v>541</v>
       </c>
-      <c r="E27" s="67" t="s">
+      <c r="E27" s="69" t="s">
         <v>537</v>
       </c>
-      <c r="F27" s="103">
+      <c r="F27" s="108">
         <v>22.0</v>
       </c>
-      <c r="G27" s="104" t="s">
+      <c r="G27" s="109" t="s">
         <v>518</v>
       </c>
       <c r="H27" s="31"/>
@@ -3683,61 +3704,61 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="106">
+      <c r="A28" s="111">
         <v>21.0</v>
       </c>
-      <c r="B28" s="107" t="s">
+      <c r="B28" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="108" t="s">
+      <c r="C28" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="109" t="s">
+      <c r="D28" s="114" t="s">
         <v>542</v>
       </c>
-      <c r="E28" s="109" t="s">
+      <c r="E28" s="114" t="s">
         <v>543</v>
       </c>
-      <c r="F28" s="89">
+      <c r="F28" s="94">
         <v>23.0</v>
       </c>
-      <c r="G28" s="90" t="s">
+      <c r="G28" s="95" t="s">
         <v>518</v>
       </c>
-      <c r="H28" s="60"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="61"/>
-      <c r="O28" s="61"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="60">
+      <c r="H28" s="62"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="63"/>
+      <c r="M28" s="63"/>
+      <c r="N28" s="63"/>
+      <c r="O28" s="63"/>
+      <c r="P28" s="63"/>
+      <c r="Q28" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="68">
+      <c r="A29" s="70">
         <v>22.0</v>
       </c>
-      <c r="B29" s="67" t="s">
+      <c r="B29" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="67" t="s">
+      <c r="D29" s="69" t="s">
         <v>544</v>
       </c>
-      <c r="E29" s="67" t="s">
+      <c r="E29" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="F29" s="37">
+      <c r="F29" s="39">
         <v>22.0</v>
       </c>
-      <c r="G29" s="38" t="s">
+      <c r="G29" s="40" t="s">
         <v>518</v>
       </c>
       <c r="H29" s="31"/>
@@ -3755,25 +3776,25 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="68">
+      <c r="A30" s="70">
         <v>23.0</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="104" t="s">
+      <c r="C30" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="67" t="s">
+      <c r="D30" s="69" t="s">
         <v>545</v>
       </c>
-      <c r="E30" s="67" t="s">
+      <c r="E30" s="69" t="s">
         <v>546</v>
       </c>
-      <c r="F30" s="103">
+      <c r="F30" s="108">
         <v>21.0</v>
       </c>
-      <c r="G30" s="104" t="s">
+      <c r="G30" s="109" t="s">
         <v>547</v>
       </c>
       <c r="H30" s="31"/>
@@ -3791,25 +3812,25 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="68">
+      <c r="A31" s="70">
         <v>24.0</v>
       </c>
-      <c r="B31" s="67" t="s">
+      <c r="B31" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="67" t="s">
+      <c r="D31" s="69" t="s">
         <v>548</v>
       </c>
-      <c r="E31" s="67" t="s">
+      <c r="E31" s="69" t="s">
         <v>511</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="39">
         <v>30.0</v>
       </c>
-      <c r="G31" s="38" t="s">
+      <c r="G31" s="40" t="s">
         <v>507</v>
       </c>
       <c r="H31" s="31"/>
@@ -3827,59 +3848,59 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="68">
+      <c r="A32" s="70">
         <v>25.0</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="104" t="s">
+      <c r="C32" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="67" t="s">
+      <c r="D32" s="69" t="s">
         <v>549</v>
       </c>
-      <c r="E32" s="67" t="s">
+      <c r="E32" s="69" t="s">
         <v>550</v>
       </c>
-      <c r="F32" s="110">
+      <c r="F32" s="115">
         <v>23.0</v>
       </c>
-      <c r="G32" s="111" t="s">
+      <c r="G32" s="116" t="s">
         <v>551</v>
       </c>
-      <c r="H32" s="60"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="61"/>
-      <c r="N32" s="61"/>
-      <c r="O32" s="61"/>
-      <c r="P32" s="61"/>
-      <c r="Q32" s="60">
+      <c r="H32" s="62"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="63"/>
+      <c r="O32" s="63"/>
+      <c r="P32" s="63"/>
+      <c r="Q32" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="68">
+      <c r="A33" s="70">
         <v>26.0</v>
       </c>
-      <c r="B33" s="67" t="s">
+      <c r="B33" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="C33" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="67" t="s">
+      <c r="D33" s="69" t="s">
         <v>552</v>
       </c>
-      <c r="E33" s="67" t="s">
+      <c r="E33" s="69" t="s">
         <v>528</v>
       </c>
       <c r="F33" s="3"/>
-      <c r="G33" s="104" t="s">
+      <c r="G33" s="109" t="s">
         <v>518</v>
       </c>
       <c r="H33" s="31"/>
@@ -4620,10 +4641,10 @@
       <c r="C21" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="36" t="s">
         <v>109</v>
       </c>
       <c r="F21" s="26"/>
@@ -5229,10 +5250,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>140</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -5291,14 +5312,14 @@
       <c r="C8" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="38" t="s">
         <v>141</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -5329,8 +5350,8 @@
       <c r="E9" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="38"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -5361,8 +5382,8 @@
       <c r="E10" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="38"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -5393,8 +5414,8 @@
       <c r="E11" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="38"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -5425,8 +5446,8 @@
       <c r="E12" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="38"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="40"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -5457,8 +5478,8 @@
       <c r="E13" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="F13" s="37"/>
-      <c r="G13" s="38"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -5489,8 +5510,8 @@
       <c r="E14" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="F14" s="37"/>
-      <c r="G14" s="38"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="40"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -5521,8 +5542,8 @@
       <c r="E15" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="F15" s="37"/>
-      <c r="G15" s="38"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -5538,7 +5559,7 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="39">
+      <c r="A16" s="41">
         <v>9.0</v>
       </c>
       <c r="B16" s="23" t="s">
@@ -5547,14 +5568,14 @@
       <c r="C16" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="E16" s="40" t="s">
+      <c r="E16" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="F16" s="37"/>
-      <c r="G16" s="38"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
       <c r="H16" s="31"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
@@ -5585,8 +5606,8 @@
       <c r="E17" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="F17" s="37"/>
-      <c r="G17" s="38"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -5617,8 +5638,8 @@
       <c r="E18" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -5649,8 +5670,8 @@
       <c r="E19" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="F19" s="37"/>
-      <c r="G19" s="38"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="40"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -5678,11 +5699,11 @@
       <c r="D20" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -5713,8 +5734,8 @@
       <c r="E21" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -5745,8 +5766,8 @@
       <c r="E22" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="40"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -5771,8 +5792,8 @@
       <c r="C23" s="26"/>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="38"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="40"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -5803,8 +5824,8 @@
       <c r="E24" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -5835,8 +5856,8 @@
       <c r="E25" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="F25" s="37"/>
-      <c r="G25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -5867,8 +5888,8 @@
       <c r="E26" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -5884,7 +5905,7 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="42">
+      <c r="A27" s="44">
         <v>20.0</v>
       </c>
       <c r="B27" s="23" t="s">
@@ -5899,8 +5920,8 @@
       <c r="E27" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
       <c r="H27" s="28"/>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
@@ -5931,8 +5952,8 @@
       <c r="E28" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -5963,8 +5984,8 @@
       <c r="E29" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -5995,8 +6016,8 @@
       <c r="E30" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="40"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -6021,14 +6042,14 @@
       <c r="C31" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="40" t="s">
+      <c r="D31" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="E31" s="40" t="s">
+      <c r="E31" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="F31" s="37"/>
-      <c r="G31" s="38"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -6059,8 +6080,8 @@
       <c r="E32" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="40"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -6085,8 +6106,8 @@
       <c r="C33" s="26"/>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="40"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -6249,13 +6270,13 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="45" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="20" t="s">
@@ -6302,23 +6323,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="44">
+      <c r="A8" s="46">
         <v>1.0</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="49" t="s">
         <v>187</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="49" t="s">
+      <c r="F8" s="50"/>
+      <c r="G8" s="51" t="s">
         <v>189</v>
       </c>
       <c r="H8" s="28"/>
@@ -6336,23 +6357,23 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="50">
+      <c r="A9" s="52">
         <v>2.0</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52" t="s">
+      <c r="F9" s="54"/>
+      <c r="G9" s="54" t="s">
         <v>182</v>
       </c>
       <c r="H9" s="28"/>
@@ -6370,23 +6391,23 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="50">
+      <c r="A10" s="52">
         <v>3.0</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="53" t="s">
         <v>192</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="F10" s="48"/>
-      <c r="G10" s="49" t="s">
+      <c r="F10" s="50"/>
+      <c r="G10" s="51" t="s">
         <v>182</v>
       </c>
       <c r="H10" s="28"/>
@@ -6404,23 +6425,23 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="44">
+      <c r="A11" s="46">
         <v>4.0</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="49" t="s">
         <v>194</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E11" s="49" t="s">
         <v>195</v>
       </c>
-      <c r="F11" s="53"/>
-      <c r="G11" s="52" t="s">
+      <c r="F11" s="55"/>
+      <c r="G11" s="54" t="s">
         <v>182</v>
       </c>
       <c r="H11" s="31"/>
@@ -6438,23 +6459,23 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="44">
+      <c r="A12" s="46">
         <v>5.0</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D12" s="49" t="s">
         <v>196</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="E12" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="F12" s="48"/>
-      <c r="G12" s="49" t="s">
+      <c r="F12" s="50"/>
+      <c r="G12" s="51" t="s">
         <v>182</v>
       </c>
       <c r="H12" s="28"/>
@@ -6472,23 +6493,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="44">
+      <c r="A13" s="46">
         <v>6.0</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="47" t="s">
+      <c r="D13" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="E13" s="47" t="s">
+      <c r="E13" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="53"/>
-      <c r="G13" s="52" t="s">
+      <c r="F13" s="55"/>
+      <c r="G13" s="54" t="s">
         <v>119</v>
       </c>
       <c r="H13" s="31"/>
@@ -6506,23 +6527,23 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="50">
+      <c r="A14" s="52">
         <v>7.0</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="E14" s="51" t="s">
+      <c r="E14" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="F14" s="53"/>
-      <c r="G14" s="52" t="s">
+      <c r="F14" s="55"/>
+      <c r="G14" s="54" t="s">
         <v>182</v>
       </c>
       <c r="H14" s="31"/>
@@ -6540,23 +6561,23 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="44">
+      <c r="A15" s="46">
         <v>8.0</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="E15" s="47" t="s">
+      <c r="E15" s="49" t="s">
         <v>203</v>
       </c>
-      <c r="F15" s="53"/>
-      <c r="G15" s="52" t="s">
+      <c r="F15" s="55"/>
+      <c r="G15" s="54" t="s">
         <v>182</v>
       </c>
       <c r="H15" s="31"/>
@@ -6574,23 +6595,23 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="44">
+      <c r="A16" s="46">
         <v>9.0</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="49" t="s">
         <v>204</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="E16" s="49" t="s">
         <v>205</v>
       </c>
-      <c r="F16" s="54"/>
-      <c r="G16" s="55" t="s">
+      <c r="F16" s="56"/>
+      <c r="G16" s="57" t="s">
         <v>182</v>
       </c>
       <c r="H16" s="31"/>
@@ -6608,23 +6629,23 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="44">
+      <c r="A17" s="46">
         <v>10.0</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="49" t="s">
         <v>206</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E17" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49" t="s">
+      <c r="F17" s="50"/>
+      <c r="G17" s="51" t="s">
         <v>182</v>
       </c>
       <c r="H17" s="28"/>
@@ -6642,23 +6663,23 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="56">
+      <c r="A18" s="58">
         <v>11.0</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="53" t="s">
         <v>208</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49" t="s">
+      <c r="F18" s="50"/>
+      <c r="G18" s="51" t="s">
         <v>182</v>
       </c>
       <c r="H18" s="28"/>
@@ -6676,23 +6697,23 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="44">
+      <c r="A19" s="46">
         <v>12.0</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="49" t="s">
         <v>210</v>
       </c>
-      <c r="E19" s="47" t="s">
+      <c r="E19" s="49" t="s">
         <v>211</v>
       </c>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49" t="s">
+      <c r="F19" s="50"/>
+      <c r="G19" s="51" t="s">
         <v>182</v>
       </c>
       <c r="H19" s="28"/>
@@ -6710,23 +6731,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="57">
+      <c r="A20" s="59">
         <v>13.0</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="49" t="s">
         <v>212</v>
       </c>
-      <c r="E20" s="47" t="s">
+      <c r="E20" s="49" t="s">
         <v>213</v>
       </c>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49" t="s">
+      <c r="F20" s="50"/>
+      <c r="G20" s="51" t="s">
         <v>182</v>
       </c>
       <c r="H20" s="28"/>
@@ -6744,57 +6765,57 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="56">
+      <c r="A21" s="58">
         <v>14.0</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="E21" s="51" t="s">
+      <c r="E21" s="53" t="s">
         <v>215</v>
       </c>
-      <c r="F21" s="58"/>
-      <c r="G21" s="59" t="s">
+      <c r="F21" s="60"/>
+      <c r="G21" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="H21" s="60"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="61"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="61"/>
-      <c r="O21" s="61"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="60">
+      <c r="H21" s="62"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="63"/>
+      <c r="P21" s="63"/>
+      <c r="Q21" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="50">
+      <c r="A22" s="52">
         <v>15.0</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="51" t="s">
+      <c r="D22" s="53" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="53" t="s">
         <v>217</v>
       </c>
-      <c r="F22" s="53"/>
-      <c r="G22" s="52" t="s">
+      <c r="F22" s="55"/>
+      <c r="G22" s="54" t="s">
         <v>182</v>
       </c>
       <c r="H22" s="31"/>
@@ -6812,23 +6833,23 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="44">
+      <c r="A23" s="46">
         <v>16.0</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="F23" s="53"/>
-      <c r="G23" s="52" t="s">
+      <c r="F23" s="55"/>
+      <c r="G23" s="54" t="s">
         <v>182</v>
       </c>
       <c r="H23" s="31"/>
@@ -6846,23 +6867,23 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="56">
+      <c r="A24" s="58">
         <v>17.0</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="51" t="s">
+      <c r="D24" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="E24" s="51" t="s">
+      <c r="E24" s="53" t="s">
         <v>220</v>
       </c>
-      <c r="F24" s="48"/>
-      <c r="G24" s="49" t="s">
+      <c r="F24" s="50"/>
+      <c r="G24" s="51" t="s">
         <v>182</v>
       </c>
       <c r="H24" s="31"/>
@@ -6880,23 +6901,23 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="57">
+      <c r="A25" s="59">
         <v>18.0</v>
       </c>
-      <c r="B25" s="45" t="s">
+      <c r="B25" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="47" t="s">
+      <c r="D25" s="49" t="s">
         <v>221</v>
       </c>
-      <c r="E25" s="47" t="s">
+      <c r="E25" s="49" t="s">
         <v>222</v>
       </c>
-      <c r="F25" s="53"/>
-      <c r="G25" s="52" t="s">
+      <c r="F25" s="55"/>
+      <c r="G25" s="54" t="s">
         <v>182</v>
       </c>
       <c r="H25" s="28"/>
@@ -6914,23 +6935,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="57">
+      <c r="A26" s="59">
         <v>19.0</v>
       </c>
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="47" t="s">
+      <c r="D26" s="49" t="s">
         <v>223</v>
       </c>
-      <c r="E26" s="47" t="s">
+      <c r="E26" s="49" t="s">
         <v>224</v>
       </c>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49" t="s">
+      <c r="F26" s="51"/>
+      <c r="G26" s="51" t="s">
         <v>225</v>
       </c>
       <c r="H26" s="31"/>
@@ -6948,23 +6969,23 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="44">
+      <c r="A27" s="46">
         <v>20.0</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="47" t="s">
+      <c r="D27" s="49" t="s">
         <v>226</v>
       </c>
-      <c r="E27" s="47" t="s">
+      <c r="E27" s="49" t="s">
         <v>227</v>
       </c>
-      <c r="F27" s="48"/>
-      <c r="G27" s="49" t="s">
+      <c r="F27" s="50"/>
+      <c r="G27" s="51" t="s">
         <v>182</v>
       </c>
       <c r="H27" s="28"/>
@@ -6982,23 +7003,23 @@
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
-      <c r="A28" s="50">
+      <c r="A28" s="52">
         <v>21.0</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="46" t="s">
+      <c r="C28" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="51" t="s">
+      <c r="D28" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="E28" s="51" t="s">
+      <c r="E28" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="F28" s="62"/>
-      <c r="G28" s="55"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="57"/>
       <c r="H28" s="31"/>
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
@@ -7011,23 +7032,23 @@
       <c r="Q28" s="31"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="57">
+      <c r="A29" s="59">
         <v>22.0</v>
       </c>
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C29" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="49" t="s">
         <v>230</v>
       </c>
-      <c r="E29" s="47" t="s">
+      <c r="E29" s="49" t="s">
         <v>231</v>
       </c>
-      <c r="F29" s="62"/>
-      <c r="G29" s="55" t="s">
+      <c r="F29" s="64"/>
+      <c r="G29" s="57" t="s">
         <v>232</v>
       </c>
       <c r="H29" s="28"/>
@@ -7045,23 +7066,23 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="56">
+      <c r="A30" s="58">
         <v>23.0</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="51" t="s">
+      <c r="D30" s="53" t="s">
         <v>233</v>
       </c>
-      <c r="E30" s="51" t="s">
+      <c r="E30" s="53" t="s">
         <v>234</v>
       </c>
-      <c r="F30" s="62"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="57"/>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
@@ -7077,23 +7098,23 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="57">
+      <c r="A31" s="59">
         <v>24.0</v>
       </c>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="47" t="s">
+      <c r="D31" s="49" t="s">
         <v>235</v>
       </c>
-      <c r="E31" s="47" t="s">
+      <c r="E31" s="49" t="s">
         <v>236</v>
       </c>
-      <c r="F31" s="62"/>
-      <c r="G31" s="55"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="57"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
       <c r="J31" s="29"/>
@@ -7109,23 +7130,23 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="57">
+      <c r="A32" s="59">
         <v>25.0</v>
       </c>
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="47" t="s">
+      <c r="D32" s="49" t="s">
         <v>237</v>
       </c>
-      <c r="E32" s="47" t="s">
+      <c r="E32" s="49" t="s">
         <v>238</v>
       </c>
-      <c r="F32" s="62"/>
-      <c r="G32" s="55"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="57"/>
       <c r="H32" s="31"/>
       <c r="I32" s="32"/>
       <c r="J32" s="32"/>
@@ -7141,23 +7162,23 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="44">
+      <c r="A33" s="46">
         <v>26.0</v>
       </c>
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="63" t="s">
+      <c r="D33" s="65" t="s">
         <v>239</v>
       </c>
-      <c r="E33" s="47" t="s">
+      <c r="E33" s="49" t="s">
         <v>240</v>
       </c>
-      <c r="F33" s="53"/>
-      <c r="G33" s="52" t="s">
+      <c r="F33" s="55"/>
+      <c r="G33" s="54" t="s">
         <v>182</v>
       </c>
       <c r="H33" s="31"/>
@@ -7175,13 +7196,13 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="57"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="65"/>
+      <c r="A34" s="59"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="66"/>
+      <c r="G34" s="67"/>
       <c r="H34" s="31"/>
       <c r="I34" s="32"/>
       <c r="J34" s="32"/>
@@ -7331,10 +7352,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -7384,23 +7405,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="66">
+      <c r="A8" s="68">
         <v>1.0</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="69" t="s">
         <v>241</v>
       </c>
-      <c r="E8" s="67" t="s">
+      <c r="E8" s="69" t="s">
         <v>242</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -7416,21 +7437,21 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="68">
+      <c r="A9" s="70">
         <v>2.0</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="67" t="s">
+      <c r="C9" s="40"/>
+      <c r="D9" s="69" t="s">
         <v>243</v>
       </c>
-      <c r="E9" s="67" t="s">
+      <c r="E9" s="69" t="s">
         <v>244</v>
       </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="38"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -7446,21 +7467,21 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="66">
+      <c r="A10" s="68">
         <v>3.0</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="67" t="s">
+      <c r="C10" s="40"/>
+      <c r="D10" s="69" t="s">
         <v>245</v>
       </c>
-      <c r="E10" s="67" t="s">
+      <c r="E10" s="69" t="s">
         <v>246</v>
       </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="38"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -7476,21 +7497,21 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="68">
+      <c r="A11" s="70">
         <v>4.0</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="67" t="s">
+      <c r="C11" s="40"/>
+      <c r="D11" s="69" t="s">
         <v>247</v>
       </c>
-      <c r="E11" s="67" t="s">
+      <c r="E11" s="69" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="38"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -7506,21 +7527,21 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="66">
+      <c r="A12" s="68">
         <v>5.0</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="67" t="s">
+      <c r="C12" s="40"/>
+      <c r="D12" s="69" t="s">
         <v>249</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="69" t="s">
         <v>250</v>
       </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="38"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="40"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -7536,21 +7557,21 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="68">
+      <c r="A13" s="70">
         <v>6.0</v>
       </c>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="67" t="s">
+      <c r="C13" s="40"/>
+      <c r="D13" s="69" t="s">
         <v>251</v>
       </c>
-      <c r="E13" s="67" t="s">
+      <c r="E13" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="F13" s="37"/>
-      <c r="G13" s="38"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -7566,21 +7587,21 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="66">
+      <c r="A14" s="68">
         <v>7.0</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="38"/>
-      <c r="D14" s="67" t="s">
+      <c r="C14" s="40"/>
+      <c r="D14" s="69" t="s">
         <v>253</v>
       </c>
-      <c r="E14" s="67" t="s">
+      <c r="E14" s="69" t="s">
         <v>254</v>
       </c>
-      <c r="F14" s="37"/>
-      <c r="G14" s="38"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="40"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -7596,21 +7617,21 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="68">
+      <c r="A15" s="70">
         <v>8.0</v>
       </c>
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="38"/>
-      <c r="D15" s="67" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="69" t="s">
         <v>255</v>
       </c>
-      <c r="E15" s="67" t="s">
+      <c r="E15" s="69" t="s">
         <v>256</v>
       </c>
-      <c r="F15" s="37"/>
-      <c r="G15" s="38"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -7626,21 +7647,21 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="66">
+      <c r="A16" s="68">
         <v>9.0</v>
       </c>
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="67" t="s">
+      <c r="C16" s="40"/>
+      <c r="D16" s="69" t="s">
         <v>257</v>
       </c>
-      <c r="E16" s="67" t="s">
+      <c r="E16" s="69" t="s">
         <v>250</v>
       </c>
-      <c r="F16" s="37"/>
-      <c r="G16" s="38"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
       <c r="J16" s="29"/>
@@ -7656,21 +7677,21 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="68">
+      <c r="A17" s="70">
         <v>10.0</v>
       </c>
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="67" t="s">
+      <c r="C17" s="40"/>
+      <c r="D17" s="69" t="s">
         <v>258</v>
       </c>
-      <c r="E17" s="67" t="s">
+      <c r="E17" s="69" t="s">
         <v>259</v>
       </c>
-      <c r="F17" s="37"/>
-      <c r="G17" s="38"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -7686,21 +7707,21 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="66">
+      <c r="A18" s="68">
         <v>11.0</v>
       </c>
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="67" t="s">
+      <c r="C18" s="40"/>
+      <c r="D18" s="69" t="s">
         <v>260</v>
       </c>
-      <c r="E18" s="67" t="s">
+      <c r="E18" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -7716,21 +7737,21 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="68">
+      <c r="A19" s="70">
         <v>12.0</v>
       </c>
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="67" t="s">
+      <c r="C19" s="40"/>
+      <c r="D19" s="69" t="s">
         <v>261</v>
       </c>
-      <c r="E19" s="67" t="s">
+      <c r="E19" s="69" t="s">
         <v>262</v>
       </c>
-      <c r="F19" s="37"/>
-      <c r="G19" s="38"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="40"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -7746,21 +7767,21 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="66">
+      <c r="A20" s="68">
         <v>13.0</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="67" t="s">
+      <c r="C20" s="40"/>
+      <c r="D20" s="69" t="s">
         <v>263</v>
       </c>
-      <c r="E20" s="69" t="s">
+      <c r="E20" s="71" t="s">
         <v>264</v>
       </c>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -7776,21 +7797,21 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="68">
+      <c r="A21" s="70">
         <v>14.0</v>
       </c>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="67" t="s">
+      <c r="C21" s="40"/>
+      <c r="D21" s="69" t="s">
         <v>265</v>
       </c>
-      <c r="E21" s="67" t="s">
+      <c r="E21" s="69" t="s">
         <v>266</v>
       </c>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -7806,21 +7827,21 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="66">
+      <c r="A22" s="68">
         <v>15.0</v>
       </c>
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="67" t="s">
+      <c r="C22" s="40"/>
+      <c r="D22" s="69" t="s">
         <v>267</v>
       </c>
-      <c r="E22" s="67" t="s">
+      <c r="E22" s="69" t="s">
         <v>268</v>
       </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="40"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -7836,21 +7857,21 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="68">
+      <c r="A23" s="70">
         <v>16.0</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="67" t="s">
+      <c r="C23" s="40"/>
+      <c r="D23" s="69" t="s">
         <v>269</v>
       </c>
-      <c r="E23" s="69" t="s">
+      <c r="E23" s="71" t="s">
         <v>270</v>
       </c>
-      <c r="F23" s="37"/>
-      <c r="G23" s="38"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="40"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -7866,21 +7887,21 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="66">
+      <c r="A24" s="68">
         <v>17.0</v>
       </c>
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="67" t="s">
+      <c r="C24" s="40"/>
+      <c r="D24" s="69" t="s">
         <v>271</v>
       </c>
-      <c r="E24" s="67" t="s">
+      <c r="E24" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -7896,21 +7917,21 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="68">
+      <c r="A25" s="70">
         <v>18.0</v>
       </c>
-      <c r="B25" s="67" t="s">
+      <c r="B25" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="67" t="s">
+      <c r="C25" s="40"/>
+      <c r="D25" s="69" t="s">
         <v>272</v>
       </c>
-      <c r="E25" s="67" t="s">
+      <c r="E25" s="69" t="s">
         <v>273</v>
       </c>
-      <c r="F25" s="37"/>
-      <c r="G25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -7926,21 +7947,21 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="66">
+      <c r="A26" s="68">
         <v>19.0</v>
       </c>
-      <c r="B26" s="67" t="s">
+      <c r="B26" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="67" t="s">
+      <c r="C26" s="40"/>
+      <c r="D26" s="69" t="s">
         <v>274</v>
       </c>
-      <c r="E26" s="67" t="s">
+      <c r="E26" s="69" t="s">
         <v>275</v>
       </c>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -7956,21 +7977,21 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="68">
+      <c r="A27" s="70">
         <v>20.0</v>
       </c>
-      <c r="B27" s="67" t="s">
+      <c r="B27" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="38"/>
-      <c r="D27" s="67" t="s">
+      <c r="C27" s="40"/>
+      <c r="D27" s="69" t="s">
         <v>276</v>
       </c>
-      <c r="E27" s="67" t="s">
+      <c r="E27" s="69" t="s">
         <v>277</v>
       </c>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
@@ -7986,21 +8007,21 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="66">
+      <c r="A28" s="68">
         <v>21.0</v>
       </c>
-      <c r="B28" s="67" t="s">
+      <c r="B28" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="67" t="s">
+      <c r="C28" s="40"/>
+      <c r="D28" s="69" t="s">
         <v>278</v>
       </c>
-      <c r="E28" s="67" t="s">
+      <c r="E28" s="69" t="s">
         <v>279</v>
       </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -8016,21 +8037,21 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="68">
+      <c r="A29" s="70">
         <v>22.0</v>
       </c>
-      <c r="B29" s="67" t="s">
+      <c r="B29" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="38"/>
-      <c r="D29" s="67" t="s">
+      <c r="C29" s="40"/>
+      <c r="D29" s="69" t="s">
         <v>280</v>
       </c>
-      <c r="E29" s="67" t="s">
+      <c r="E29" s="69" t="s">
         <v>281</v>
       </c>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -8046,21 +8067,21 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="66">
+      <c r="A30" s="68">
         <v>23.0</v>
       </c>
-      <c r="B30" s="67" t="s">
+      <c r="B30" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="38"/>
-      <c r="D30" s="67" t="s">
+      <c r="C30" s="40"/>
+      <c r="D30" s="69" t="s">
         <v>267</v>
       </c>
-      <c r="E30" s="67" t="s">
+      <c r="E30" s="69" t="s">
         <v>282</v>
       </c>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="40"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -8076,21 +8097,21 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="68">
+      <c r="A31" s="70">
         <v>24.0</v>
       </c>
-      <c r="B31" s="67" t="s">
+      <c r="B31" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="38"/>
-      <c r="D31" s="67" t="s">
+      <c r="C31" s="40"/>
+      <c r="D31" s="69" t="s">
         <v>283</v>
       </c>
-      <c r="E31" s="69" t="s">
+      <c r="E31" s="71" t="s">
         <v>284</v>
       </c>
-      <c r="F31" s="37"/>
-      <c r="G31" s="38"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -8106,21 +8127,21 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="66">
+      <c r="A32" s="68">
         <v>25.0</v>
       </c>
-      <c r="B32" s="67" t="s">
+      <c r="B32" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="67" t="s">
+      <c r="C32" s="40"/>
+      <c r="D32" s="69" t="s">
         <v>285</v>
       </c>
-      <c r="E32" s="67" t="s">
+      <c r="E32" s="69" t="s">
         <v>286</v>
       </c>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="40"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -8136,21 +8157,21 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="68">
+      <c r="A33" s="70">
         <v>26.0</v>
       </c>
-      <c r="B33" s="67" t="s">
+      <c r="B33" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="38"/>
-      <c r="D33" s="67" t="s">
+      <c r="C33" s="40"/>
+      <c r="D33" s="69" t="s">
         <v>257</v>
       </c>
-      <c r="E33" s="67" t="s">
+      <c r="E33" s="69" t="s">
         <v>287</v>
       </c>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="40"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -8267,7 +8288,7 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="70" t="s">
+      <c r="E3" s="72" t="s">
         <v>290</v>
       </c>
       <c r="F3" s="5"/>
@@ -8313,10 +8334,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -8366,25 +8387,25 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="66">
+      <c r="A8" s="68">
         <v>1.0</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="69" t="s">
         <v>293</v>
       </c>
-      <c r="E8" s="67" t="s">
+      <c r="E8" s="69" t="s">
         <v>294</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="39">
         <v>37.0</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H8" s="28"/>
@@ -8402,25 +8423,25 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="68">
+      <c r="A9" s="70">
         <v>2.0</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="73" t="s">
         <v>295</v>
       </c>
-      <c r="E9" s="72" t="s">
+      <c r="E9" s="74" t="s">
         <v>296</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="39">
         <v>32.0</v>
       </c>
-      <c r="G9" s="38" t="s">
+      <c r="G9" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H9" s="31"/>
@@ -8438,25 +8459,25 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="66">
+      <c r="A10" s="68">
         <v>3.0</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="69" t="s">
         <v>297</v>
       </c>
-      <c r="E10" s="67" t="s">
+      <c r="E10" s="69" t="s">
         <v>298</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="39">
         <v>25.0</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H10" s="28"/>
@@ -8474,25 +8495,25 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="66">
+      <c r="A11" s="68">
         <v>4.0</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="69" t="s">
         <v>299</v>
       </c>
-      <c r="E11" s="67" t="s">
+      <c r="E11" s="69" t="s">
         <v>300</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="39">
         <v>29.0</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H11" s="28"/>
@@ -8510,25 +8531,25 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="68">
+      <c r="A12" s="70">
         <v>5.0</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="69" t="s">
         <v>301</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="69" t="s">
         <v>302</v>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="39">
         <v>27.0</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="40" t="s">
         <v>303</v>
       </c>
       <c r="H12" s="31"/>
@@ -8546,23 +8567,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="68">
+      <c r="A13" s="70">
         <v>6.0</v>
       </c>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="75" t="s">
         <v>304</v>
       </c>
-      <c r="E13" s="67" t="s">
+      <c r="E13" s="69" t="s">
         <v>305</v>
       </c>
-      <c r="F13" s="37"/>
-      <c r="G13" s="38" t="s">
+      <c r="F13" s="39"/>
+      <c r="G13" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H13" s="31"/>
@@ -8580,25 +8601,25 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="66">
+      <c r="A14" s="68">
         <v>7.0</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="67" t="s">
-        <v>304</v>
-      </c>
-      <c r="E14" s="67" t="s">
+      <c r="D14" s="76" t="s">
         <v>306</v>
       </c>
-      <c r="F14" s="37">
+      <c r="E14" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="F14" s="39">
         <v>23.0</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H14" s="28"/>
@@ -8616,25 +8637,25 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="68">
+      <c r="A15" s="70">
         <v>8.0</v>
       </c>
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="67" t="s">
-        <v>307</v>
-      </c>
-      <c r="E15" s="67" t="s">
+      <c r="D15" s="69" t="s">
         <v>308</v>
       </c>
-      <c r="F15" s="37">
+      <c r="E15" s="69" t="s">
+        <v>309</v>
+      </c>
+      <c r="F15" s="39">
         <v>28.0</v>
       </c>
-      <c r="G15" s="38" t="s">
+      <c r="G15" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H15" s="31"/>
@@ -8652,25 +8673,25 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="66">
+      <c r="A16" s="68">
         <v>9.0</v>
       </c>
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="67" t="s">
-        <v>309</v>
-      </c>
-      <c r="E16" s="67" t="s">
+      <c r="D16" s="69" t="s">
         <v>310</v>
       </c>
-      <c r="F16" s="37">
+      <c r="E16" s="69" t="s">
+        <v>311</v>
+      </c>
+      <c r="F16" s="39">
         <v>40.0</v>
       </c>
-      <c r="G16" s="38" t="s">
+      <c r="G16" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H16" s="28"/>
@@ -8688,25 +8709,25 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="66">
+      <c r="A17" s="68">
         <v>10.0</v>
       </c>
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="67" t="s">
-        <v>311</v>
-      </c>
-      <c r="E17" s="67" t="s">
+      <c r="D17" s="69" t="s">
         <v>312</v>
       </c>
-      <c r="F17" s="37">
+      <c r="E17" s="69" t="s">
+        <v>313</v>
+      </c>
+      <c r="F17" s="39">
         <v>37.0</v>
       </c>
-      <c r="G17" s="38" t="s">
+      <c r="G17" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H17" s="28"/>
@@ -8724,25 +8745,25 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="68">
+      <c r="A18" s="70">
         <v>11.0</v>
       </c>
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="67" t="s">
-        <v>313</v>
-      </c>
-      <c r="E18" s="67" t="s">
+      <c r="D18" s="69" t="s">
         <v>314</v>
       </c>
-      <c r="F18" s="37">
+      <c r="E18" s="69" t="s">
+        <v>315</v>
+      </c>
+      <c r="F18" s="39">
         <v>32.0</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="G18" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H18" s="31"/>
@@ -8760,25 +8781,25 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="68">
+      <c r="A19" s="70">
         <v>12.0</v>
       </c>
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="73" t="s">
-        <v>315</v>
-      </c>
-      <c r="E19" s="67" t="s">
+      <c r="D19" s="75" t="s">
         <v>316</v>
       </c>
-      <c r="F19" s="37">
+      <c r="E19" s="69" t="s">
+        <v>317</v>
+      </c>
+      <c r="F19" s="39">
         <v>20.0</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H19" s="31"/>
@@ -8796,23 +8817,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="66">
+      <c r="A20" s="68">
         <v>13.0</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="73" t="s">
-        <v>317</v>
-      </c>
-      <c r="E20" s="67" t="s">
+      <c r="D20" s="77" t="s">
         <v>318</v>
       </c>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38" t="s">
+      <c r="E20" s="77" t="s">
+        <v>319</v>
+      </c>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H20" s="28"/>
@@ -8830,25 +8851,25 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="68">
+      <c r="A21" s="70">
         <v>14.0</v>
       </c>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="67" t="s">
-        <v>319</v>
-      </c>
-      <c r="E21" s="67" t="s">
+      <c r="D21" s="69" t="s">
         <v>320</v>
       </c>
-      <c r="F21" s="37">
+      <c r="E21" s="69" t="s">
+        <v>321</v>
+      </c>
+      <c r="F21" s="39">
         <v>33.0</v>
       </c>
-      <c r="G21" s="38" t="s">
+      <c r="G21" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H21" s="31"/>
@@ -8866,25 +8887,25 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="66">
+      <c r="A22" s="68">
         <v>15.0</v>
       </c>
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="67" t="s">
-        <v>321</v>
-      </c>
-      <c r="E22" s="67" t="s">
+      <c r="D22" s="69" t="s">
         <v>322</v>
       </c>
-      <c r="F22" s="37">
+      <c r="E22" s="69" t="s">
+        <v>323</v>
+      </c>
+      <c r="F22" s="39">
         <v>33.0</v>
       </c>
-      <c r="G22" s="38" t="s">
+      <c r="G22" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H22" s="28"/>
@@ -8902,25 +8923,25 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="68">
+      <c r="A23" s="70">
         <v>16.0</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="73" t="s">
-        <v>323</v>
-      </c>
-      <c r="E23" s="67" t="s">
+      <c r="C23" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="77" t="s">
         <v>324</v>
       </c>
-      <c r="F23" s="37">
+      <c r="E23" s="77" t="s">
+        <v>325</v>
+      </c>
+      <c r="F23" s="39">
         <v>41.0</v>
       </c>
-      <c r="G23" s="38" t="s">
+      <c r="G23" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H23" s="31"/>
@@ -8938,25 +8959,25 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="66">
+      <c r="A24" s="68">
         <v>17.0</v>
       </c>
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="73" t="s">
-        <v>325</v>
-      </c>
-      <c r="E24" s="67" t="s">
+      <c r="D24" s="75" t="s">
         <v>326</v>
       </c>
-      <c r="F24" s="37">
+      <c r="E24" s="69" t="s">
+        <v>327</v>
+      </c>
+      <c r="F24" s="39">
         <v>20.0</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="G24" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H24" s="28"/>
@@ -8974,25 +8995,25 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="68">
+      <c r="A25" s="70">
         <v>18.0</v>
       </c>
-      <c r="B25" s="67" t="s">
+      <c r="B25" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="73" t="s">
-        <v>327</v>
-      </c>
-      <c r="E25" s="67" t="s">
+      <c r="D25" s="75" t="s">
         <v>328</v>
       </c>
-      <c r="F25" s="37">
+      <c r="E25" s="69" t="s">
+        <v>329</v>
+      </c>
+      <c r="F25" s="39">
         <v>34.0</v>
       </c>
-      <c r="G25" s="38" t="s">
+      <c r="G25" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H25" s="31"/>
@@ -9010,23 +9031,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="66">
+      <c r="A26" s="68">
         <v>19.0</v>
       </c>
-      <c r="B26" s="67" t="s">
+      <c r="B26" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="73" t="s">
-        <v>329</v>
-      </c>
-      <c r="E26" s="67" t="s">
+      <c r="D26" s="75" t="s">
         <v>330</v>
       </c>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38" t="s">
+      <c r="E26" s="69" t="s">
+        <v>331</v>
+      </c>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H26" s="28"/>
@@ -9044,25 +9065,25 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="68">
+      <c r="A27" s="70">
         <v>20.0</v>
       </c>
-      <c r="B27" s="67" t="s">
+      <c r="B27" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="73" t="s">
-        <v>331</v>
-      </c>
-      <c r="E27" s="67" t="s">
+      <c r="D27" s="75" t="s">
+        <v>332</v>
+      </c>
+      <c r="E27" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="39">
         <v>27.0</v>
       </c>
-      <c r="G27" s="38" t="s">
+      <c r="G27" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H27" s="31"/>
@@ -9080,25 +9101,25 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="68">
+      <c r="A28" s="70">
         <v>21.0</v>
       </c>
-      <c r="B28" s="67" t="s">
+      <c r="B28" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="67" t="s">
-        <v>332</v>
-      </c>
-      <c r="E28" s="67" t="s">
+      <c r="D28" s="69" t="s">
         <v>333</v>
       </c>
-      <c r="F28" s="37">
+      <c r="E28" s="69" t="s">
+        <v>334</v>
+      </c>
+      <c r="F28" s="39">
         <v>32.0</v>
       </c>
-      <c r="G28" s="38" t="s">
+      <c r="G28" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H28" s="31"/>
@@ -9116,25 +9137,25 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="68">
+      <c r="A29" s="70">
         <v>22.0</v>
       </c>
-      <c r="B29" s="67" t="s">
+      <c r="B29" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="73" t="s">
-        <v>334</v>
-      </c>
-      <c r="E29" s="67" t="s">
+      <c r="D29" s="77" t="s">
         <v>335</v>
       </c>
-      <c r="F29" s="37">
+      <c r="E29" s="77" t="s">
+        <v>336</v>
+      </c>
+      <c r="F29" s="39">
         <v>28.0</v>
       </c>
-      <c r="G29" s="38" t="s">
+      <c r="G29" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H29" s="31"/>
@@ -9152,25 +9173,25 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="66">
+      <c r="A30" s="68">
         <v>23.0</v>
       </c>
-      <c r="B30" s="67" t="s">
+      <c r="B30" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="73" t="s">
-        <v>336</v>
-      </c>
-      <c r="E30" s="67" t="s">
+      <c r="D30" s="77" t="s">
         <v>337</v>
       </c>
-      <c r="F30" s="37">
+      <c r="E30" s="77" t="s">
+        <v>338</v>
+      </c>
+      <c r="F30" s="39">
         <v>41.0</v>
       </c>
-      <c r="G30" s="38" t="s">
+      <c r="G30" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H30" s="28"/>
@@ -9188,25 +9209,21 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="66">
+      <c r="A31" s="68">
         <v>24.0</v>
       </c>
-      <c r="B31" s="67" t="s">
+      <c r="B31" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="73" t="s">
-        <v>338</v>
-      </c>
-      <c r="E31" s="67" t="s">
-        <v>339</v>
-      </c>
-      <c r="F31" s="37">
+      <c r="D31" s="75"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="39">
         <v>36.0</v>
       </c>
-      <c r="G31" s="38" t="s">
+      <c r="G31" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H31" s="28"/>
@@ -9224,25 +9241,25 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="66">
+      <c r="A32" s="68">
         <v>25.0</v>
       </c>
-      <c r="B32" s="67" t="s">
+      <c r="B32" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="67" t="s">
+      <c r="D32" s="69" t="s">
+        <v>339</v>
+      </c>
+      <c r="E32" s="69" t="s">
         <v>340</v>
       </c>
-      <c r="E32" s="67" t="s">
-        <v>341</v>
-      </c>
-      <c r="F32" s="37">
+      <c r="F32" s="39">
         <v>19.0</v>
       </c>
-      <c r="G32" s="38"/>
+      <c r="G32" s="40"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -9258,25 +9275,25 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="68">
+      <c r="A33" s="70">
         <v>26.0</v>
       </c>
-      <c r="B33" s="67" t="s">
+      <c r="B33" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="C33" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="E33" s="67" t="s">
+      <c r="D33" s="69" t="s">
+        <v>341</v>
+      </c>
+      <c r="E33" s="69" t="s">
         <v>342</v>
       </c>
-      <c r="F33" s="37">
+      <c r="F33" s="39">
         <v>19.0</v>
       </c>
-      <c r="G33" s="38"/>
+      <c r="G33" s="40"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -9356,12 +9373,12 @@
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="74" t="s">
+      <c r="F1" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="75"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="77" t="s">
+      <c r="G1" s="80"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="82" t="s">
         <v>42</v>
       </c>
       <c r="J1" s="10"/>
@@ -9417,21 +9434,21 @@
       <c r="H4" s="6"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="83" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="79" t="s">
+      <c r="F5" s="84" t="s">
         <v>346</v>
       </c>
-      <c r="G5" s="80"/>
-      <c r="H5" s="81"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="86"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="82"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -9441,13 +9458,13 @@
       <c r="H6" s="16"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
         <v>347</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>348</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="37" t="s">
         <v>349</v>
       </c>
       <c r="D7" s="20" t="s">
@@ -9497,26 +9514,26 @@
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1">
-      <c r="A8" s="83">
+      <c r="A8" s="88">
         <v>1.0</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="84" t="s">
+      <c r="D8" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="90" t="s">
         <v>350</v>
       </c>
-      <c r="F8" s="85" t="s">
+      <c r="F8" s="90" t="s">
         <v>351</v>
       </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="86" t="s">
+      <c r="G8" s="39"/>
+      <c r="H8" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I8" s="28"/>
@@ -9534,26 +9551,26 @@
       </c>
     </row>
     <row r="9" ht="21.0" customHeight="1">
-      <c r="A9" s="83">
+      <c r="A9" s="88">
         <v>2.0</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="83" t="s">
+      <c r="C9" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="84" t="s">
+      <c r="D9" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="85" t="s">
+      <c r="E9" s="90" t="s">
         <v>352</v>
       </c>
-      <c r="F9" s="85" t="s">
+      <c r="F9" s="90" t="s">
         <v>353</v>
       </c>
-      <c r="G9" s="37"/>
-      <c r="H9" s="86" t="s">
+      <c r="G9" s="39"/>
+      <c r="H9" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I9" s="31"/>
@@ -9571,26 +9588,26 @@
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1">
-      <c r="A10" s="83">
+      <c r="A10" s="88">
         <v>3.0</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="84" t="s">
+      <c r="D10" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="87" t="s">
+      <c r="E10" s="92" t="s">
         <v>354</v>
       </c>
-      <c r="F10" s="87" t="s">
+      <c r="F10" s="92" t="s">
         <v>355</v>
       </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="86" t="s">
+      <c r="G10" s="39"/>
+      <c r="H10" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I10" s="31"/>
@@ -9608,26 +9625,26 @@
       </c>
     </row>
     <row r="11" ht="21.0" customHeight="1">
-      <c r="A11" s="83">
+      <c r="A11" s="88">
         <v>4.0</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="83" t="s">
+      <c r="C11" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="84" t="s">
+      <c r="D11" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="85" t="s">
+      <c r="E11" s="90" t="s">
         <v>356</v>
       </c>
-      <c r="F11" s="85" t="s">
+      <c r="F11" s="90" t="s">
         <v>357</v>
       </c>
-      <c r="G11" s="37"/>
-      <c r="H11" s="86" t="s">
+      <c r="G11" s="39"/>
+      <c r="H11" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I11" s="31"/>
@@ -9645,26 +9662,26 @@
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="83">
+      <c r="A12" s="88">
         <v>5.0</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="83" t="s">
+      <c r="C12" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="84" t="s">
+      <c r="D12" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="85" t="s">
+      <c r="E12" s="90" t="s">
         <v>358</v>
       </c>
-      <c r="F12" s="85" t="s">
+      <c r="F12" s="90" t="s">
         <v>351</v>
       </c>
-      <c r="G12" s="37"/>
-      <c r="H12" s="86" t="s">
+      <c r="G12" s="39"/>
+      <c r="H12" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I12" s="28"/>
@@ -9682,26 +9699,26 @@
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1">
-      <c r="A13" s="83">
+      <c r="A13" s="88">
         <v>6.0</v>
       </c>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="83" t="s">
+      <c r="C13" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="84" t="s">
+      <c r="D13" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="85" t="s">
+      <c r="E13" s="90" t="s">
         <v>359</v>
       </c>
-      <c r="F13" s="85" t="s">
+      <c r="F13" s="90" t="s">
         <v>179</v>
       </c>
-      <c r="G13" s="37"/>
-      <c r="H13" s="86" t="s">
+      <c r="G13" s="39"/>
+      <c r="H13" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I13" s="31"/>
@@ -9719,26 +9736,26 @@
       </c>
     </row>
     <row r="14" ht="24.75" customHeight="1">
-      <c r="A14" s="83">
+      <c r="A14" s="88">
         <v>7.0</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="84" t="s">
+      <c r="D14" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="85" t="s">
+      <c r="E14" s="90" t="s">
         <v>223</v>
       </c>
-      <c r="F14" s="85" t="s">
+      <c r="F14" s="90" t="s">
         <v>179</v>
       </c>
-      <c r="G14" s="37"/>
-      <c r="H14" s="86" t="s">
+      <c r="G14" s="39"/>
+      <c r="H14" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I14" s="28"/>
@@ -9756,26 +9773,26 @@
       </c>
     </row>
     <row r="15" ht="21.0" customHeight="1">
-      <c r="A15" s="83">
+      <c r="A15" s="88">
         <v>8.0</v>
       </c>
-      <c r="B15" s="83" t="s">
+      <c r="B15" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="83" t="s">
+      <c r="C15" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="84" t="s">
+      <c r="D15" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="85" t="s">
+      <c r="E15" s="90" t="s">
         <v>360</v>
       </c>
-      <c r="F15" s="85" t="s">
+      <c r="F15" s="90" t="s">
         <v>179</v>
       </c>
-      <c r="G15" s="37"/>
-      <c r="H15" s="86" t="s">
+      <c r="G15" s="39"/>
+      <c r="H15" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I15" s="31"/>
@@ -9793,26 +9810,26 @@
       </c>
     </row>
     <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="83">
+      <c r="A16" s="88">
         <v>9.0</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="83" t="s">
+      <c r="C16" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="84" t="s">
+      <c r="D16" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="85" t="s">
+      <c r="E16" s="90" t="s">
         <v>361</v>
       </c>
-      <c r="F16" s="85" t="s">
+      <c r="F16" s="90" t="s">
         <v>362</v>
       </c>
-      <c r="G16" s="37"/>
-      <c r="H16" s="86" t="s">
+      <c r="G16" s="39"/>
+      <c r="H16" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I16" s="28"/>
@@ -9830,26 +9847,26 @@
       </c>
     </row>
     <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="83">
+      <c r="A17" s="88">
         <v>10.0</v>
       </c>
-      <c r="B17" s="83" t="s">
+      <c r="B17" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="84" t="s">
+      <c r="D17" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="85" t="s">
+      <c r="E17" s="90" t="s">
         <v>363</v>
       </c>
-      <c r="F17" s="85" t="s">
+      <c r="F17" s="90" t="s">
         <v>364</v>
       </c>
-      <c r="G17" s="37"/>
-      <c r="H17" s="86" t="s">
+      <c r="G17" s="39"/>
+      <c r="H17" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I17" s="31"/>
@@ -9867,26 +9884,26 @@
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="83">
+      <c r="A18" s="88">
         <v>11.0</v>
       </c>
-      <c r="B18" s="83" t="s">
+      <c r="B18" s="88" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="83" t="s">
+      <c r="C18" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="84" t="s">
+      <c r="D18" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="85" t="s">
+      <c r="E18" s="90" t="s">
         <v>365</v>
       </c>
-      <c r="F18" s="85" t="s">
+      <c r="F18" s="90" t="s">
         <v>366</v>
       </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="86" t="s">
+      <c r="G18" s="39"/>
+      <c r="H18" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I18" s="28"/>
@@ -9904,26 +9921,26 @@
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1">
-      <c r="A19" s="83">
+      <c r="A19" s="88">
         <v>12.0</v>
       </c>
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="88" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="84" t="s">
+      <c r="D19" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="85" t="s">
+      <c r="E19" s="90" t="s">
         <v>367</v>
       </c>
-      <c r="F19" s="85" t="s">
+      <c r="F19" s="90" t="s">
         <v>368</v>
       </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="86" t="s">
+      <c r="G19" s="39"/>
+      <c r="H19" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I19" s="31"/>
@@ -9941,26 +9958,26 @@
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1">
-      <c r="A20" s="83">
+      <c r="A20" s="88">
         <v>13.0</v>
       </c>
-      <c r="B20" s="83" t="s">
+      <c r="B20" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="83" t="s">
+      <c r="C20" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="84" t="s">
+      <c r="D20" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="85" t="s">
+      <c r="E20" s="90" t="s">
         <v>369</v>
       </c>
-      <c r="F20" s="85" t="s">
+      <c r="F20" s="90" t="s">
         <v>370</v>
       </c>
-      <c r="G20" s="37"/>
-      <c r="H20" s="86" t="s">
+      <c r="G20" s="39"/>
+      <c r="H20" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I20" s="28"/>
@@ -9978,26 +9995,26 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="83">
+      <c r="A21" s="88">
         <v>14.0</v>
       </c>
-      <c r="B21" s="83" t="s">
+      <c r="B21" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="83" t="s">
+      <c r="C21" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="84" t="s">
+      <c r="D21" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="85" t="s">
+      <c r="E21" s="90" t="s">
         <v>371</v>
       </c>
-      <c r="F21" s="85" t="s">
+      <c r="F21" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="G21" s="37"/>
-      <c r="H21" s="86" t="s">
+      <c r="G21" s="39"/>
+      <c r="H21" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I21" s="31"/>
@@ -10015,26 +10032,26 @@
       </c>
     </row>
     <row r="22" ht="23.25" customHeight="1">
-      <c r="A22" s="83">
+      <c r="A22" s="88">
         <v>15.0</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="83" t="s">
+      <c r="C22" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="84" t="s">
+      <c r="D22" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="85" t="s">
+      <c r="E22" s="90" t="s">
         <v>372</v>
       </c>
-      <c r="F22" s="85" t="s">
+      <c r="F22" s="90" t="s">
         <v>373</v>
       </c>
-      <c r="G22" s="37"/>
-      <c r="H22" s="86" t="s">
+      <c r="G22" s="39"/>
+      <c r="H22" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I22" s="28"/>
@@ -10052,26 +10069,26 @@
       </c>
     </row>
     <row r="23" ht="21.75" customHeight="1">
-      <c r="A23" s="83">
+      <c r="A23" s="88">
         <v>16.0</v>
       </c>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="83" t="s">
+      <c r="C23" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="84" t="s">
+      <c r="D23" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="85" t="s">
+      <c r="E23" s="90" t="s">
         <v>374</v>
       </c>
-      <c r="F23" s="85" t="s">
+      <c r="F23" s="90" t="s">
         <v>375</v>
       </c>
-      <c r="G23" s="37"/>
-      <c r="H23" s="88" t="s">
+      <c r="G23" s="39"/>
+      <c r="H23" s="93" t="s">
         <v>71</v>
       </c>
       <c r="I23" s="31"/>
@@ -10089,26 +10106,26 @@
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1">
-      <c r="A24" s="83">
+      <c r="A24" s="88">
         <v>17.0</v>
       </c>
-      <c r="B24" s="83" t="s">
+      <c r="B24" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="83" t="s">
+      <c r="C24" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="84" t="s">
+      <c r="D24" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="85" t="s">
+      <c r="E24" s="90" t="s">
         <v>376</v>
       </c>
-      <c r="F24" s="85" t="s">
+      <c r="F24" s="90" t="s">
         <v>377</v>
       </c>
-      <c r="G24" s="37"/>
-      <c r="H24" s="86" t="s">
+      <c r="G24" s="39"/>
+      <c r="H24" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I24" s="31"/>
@@ -10126,26 +10143,26 @@
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="83">
+      <c r="A25" s="88">
         <v>18.0</v>
       </c>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="83" t="s">
+      <c r="C25" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="84" t="s">
+      <c r="D25" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="85" t="s">
+      <c r="E25" s="90" t="s">
         <v>378</v>
       </c>
-      <c r="F25" s="85" t="s">
+      <c r="F25" s="90" t="s">
         <v>379</v>
       </c>
-      <c r="G25" s="37"/>
-      <c r="H25" s="86" t="s">
+      <c r="G25" s="39"/>
+      <c r="H25" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I25" s="28"/>
@@ -10163,26 +10180,26 @@
       </c>
     </row>
     <row r="26" ht="24.0" customHeight="1">
-      <c r="A26" s="83">
+      <c r="A26" s="88">
         <v>19.0</v>
       </c>
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="83" t="s">
+      <c r="C26" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="84" t="s">
+      <c r="D26" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="85" t="s">
+      <c r="E26" s="90" t="s">
         <v>380</v>
       </c>
-      <c r="F26" s="85" t="s">
+      <c r="F26" s="90" t="s">
         <v>381</v>
       </c>
-      <c r="G26" s="37"/>
-      <c r="H26" s="86" t="s">
+      <c r="G26" s="39"/>
+      <c r="H26" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I26" s="28"/>
@@ -10200,26 +10217,26 @@
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1">
-      <c r="A27" s="83">
+      <c r="A27" s="88">
         <v>20.0</v>
       </c>
-      <c r="B27" s="83" t="s">
+      <c r="B27" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="83" t="s">
+      <c r="C27" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="84" t="s">
+      <c r="D27" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="85" t="s">
+      <c r="E27" s="90" t="s">
         <v>382</v>
       </c>
-      <c r="F27" s="85" t="s">
+      <c r="F27" s="90" t="s">
         <v>357</v>
       </c>
-      <c r="G27" s="37"/>
-      <c r="H27" s="86" t="s">
+      <c r="G27" s="39"/>
+      <c r="H27" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I27" s="28"/>
@@ -10237,26 +10254,26 @@
       </c>
     </row>
     <row r="28" ht="20.25" customHeight="1">
-      <c r="A28" s="83">
+      <c r="A28" s="88">
         <v>21.0</v>
       </c>
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="83" t="s">
+      <c r="C28" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="84" t="s">
+      <c r="D28" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="85" t="s">
+      <c r="E28" s="90" t="s">
         <v>383</v>
       </c>
-      <c r="F28" s="85" t="s">
+      <c r="F28" s="90" t="s">
         <v>384</v>
       </c>
-      <c r="G28" s="37"/>
-      <c r="H28" s="86" t="s">
+      <c r="G28" s="39"/>
+      <c r="H28" s="91" t="s">
         <v>99</v>
       </c>
       <c r="I28" s="31"/>
@@ -10274,26 +10291,26 @@
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="83">
+      <c r="A29" s="88">
         <v>22.0</v>
       </c>
-      <c r="B29" s="83" t="s">
+      <c r="B29" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="84" t="s">
+      <c r="D29" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="85" t="s">
+      <c r="E29" s="90" t="s">
         <v>385</v>
       </c>
-      <c r="F29" s="85" t="s">
+      <c r="F29" s="90" t="s">
         <v>386</v>
       </c>
-      <c r="G29" s="37"/>
-      <c r="H29" s="86" t="s">
+      <c r="G29" s="39"/>
+      <c r="H29" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I29" s="28"/>
@@ -10311,26 +10328,26 @@
       </c>
     </row>
     <row r="30" ht="20.25" customHeight="1">
-      <c r="A30" s="83">
+      <c r="A30" s="88">
         <v>23.0</v>
       </c>
-      <c r="B30" s="83" t="s">
+      <c r="B30" s="88" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="83" t="s">
+      <c r="C30" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="84" t="s">
+      <c r="D30" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="85" t="s">
+      <c r="E30" s="90" t="s">
         <v>387</v>
       </c>
-      <c r="F30" s="85" t="s">
+      <c r="F30" s="90" t="s">
         <v>388</v>
       </c>
-      <c r="G30" s="37"/>
-      <c r="H30" s="86" t="s">
+      <c r="G30" s="39"/>
+      <c r="H30" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I30" s="31"/>
@@ -10348,26 +10365,26 @@
       </c>
     </row>
     <row r="31" ht="21.0" customHeight="1">
-      <c r="A31" s="83">
+      <c r="A31" s="88">
         <v>24.0</v>
       </c>
-      <c r="B31" s="83" t="s">
+      <c r="B31" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="83" t="s">
+      <c r="C31" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="84" t="s">
+      <c r="D31" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="85" t="s">
+      <c r="E31" s="90" t="s">
         <v>389</v>
       </c>
-      <c r="F31" s="85" t="s">
+      <c r="F31" s="90" t="s">
         <v>390</v>
       </c>
-      <c r="G31" s="37"/>
-      <c r="H31" s="86" t="s">
+      <c r="G31" s="39"/>
+      <c r="H31" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I31" s="28"/>
@@ -10385,26 +10402,26 @@
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="83">
+      <c r="A32" s="88">
         <v>25.0</v>
       </c>
-      <c r="B32" s="83" t="s">
+      <c r="B32" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="83" t="s">
+      <c r="C32" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="84" t="s">
+      <c r="D32" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="85" t="s">
+      <c r="E32" s="90" t="s">
         <v>391</v>
       </c>
-      <c r="F32" s="85" t="s">
+      <c r="F32" s="90" t="s">
         <v>392</v>
       </c>
-      <c r="G32" s="37"/>
-      <c r="H32" s="86" t="s">
+      <c r="G32" s="39"/>
+      <c r="H32" s="91" t="s">
         <v>71</v>
       </c>
       <c r="I32" s="31"/>
@@ -10422,26 +10439,26 @@
       </c>
     </row>
     <row r="33" ht="21.0" customHeight="1">
-      <c r="A33" s="83">
+      <c r="A33" s="88">
         <v>26.0</v>
       </c>
-      <c r="B33" s="83" t="s">
+      <c r="B33" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="83" t="s">
+      <c r="C33" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="84" t="s">
+      <c r="D33" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="85" t="s">
+      <c r="E33" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="85" t="s">
+      <c r="F33" s="90" t="s">
         <v>393</v>
       </c>
-      <c r="G33" s="37"/>
-      <c r="H33" s="86" t="s">
+      <c r="G33" s="39"/>
+      <c r="H33" s="91" t="s">
         <v>394</v>
       </c>
       <c r="I33" s="28"/>
@@ -10604,10 +10621,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -10672,8 +10689,8 @@
       <c r="E8" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38" t="s">
+      <c r="F8" s="39"/>
+      <c r="G8" s="40" t="s">
         <v>85</v>
       </c>
       <c r="H8" s="28"/>
@@ -10706,8 +10723,8 @@
       <c r="E9" s="23" t="s">
         <v>403</v>
       </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="38" t="s">
+      <c r="F9" s="39"/>
+      <c r="G9" s="40" t="s">
         <v>404</v>
       </c>
       <c r="H9" s="31"/>
@@ -10740,8 +10757,8 @@
       <c r="E10" s="23" t="s">
         <v>406</v>
       </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="38" t="s">
+      <c r="F10" s="39"/>
+      <c r="G10" s="40" t="s">
         <v>407</v>
       </c>
       <c r="H10" s="28"/>
@@ -10774,8 +10791,8 @@
       <c r="E11" s="23" t="s">
         <v>409</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="38" t="s">
+      <c r="F11" s="39"/>
+      <c r="G11" s="40" t="s">
         <v>395</v>
       </c>
       <c r="H11" s="31"/>
@@ -10808,8 +10825,8 @@
       <c r="E12" s="23" t="s">
         <v>411</v>
       </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="38" t="s">
+      <c r="F12" s="39"/>
+      <c r="G12" s="40" t="s">
         <v>395</v>
       </c>
       <c r="H12" s="28"/>
@@ -10842,8 +10859,8 @@
       <c r="E13" s="23" t="s">
         <v>413</v>
       </c>
-      <c r="F13" s="37"/>
-      <c r="G13" s="38" t="s">
+      <c r="F13" s="39"/>
+      <c r="G13" s="40" t="s">
         <v>395</v>
       </c>
       <c r="H13" s="31"/>
@@ -10876,8 +10893,8 @@
       <c r="E14" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="F14" s="37"/>
-      <c r="G14" s="38" t="s">
+      <c r="F14" s="39"/>
+      <c r="G14" s="40" t="s">
         <v>75</v>
       </c>
       <c r="H14" s="28"/>
@@ -10910,8 +10927,8 @@
       <c r="E15" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="F15" s="37"/>
-      <c r="G15" s="38" t="s">
+      <c r="F15" s="39"/>
+      <c r="G15" s="40" t="s">
         <v>71</v>
       </c>
       <c r="H15" s="31"/>
@@ -10944,8 +10961,8 @@
       <c r="E16" s="23" t="s">
         <v>418</v>
       </c>
-      <c r="F16" s="37"/>
-      <c r="G16" s="38" t="s">
+      <c r="F16" s="39"/>
+      <c r="G16" s="40" t="s">
         <v>288</v>
       </c>
       <c r="H16" s="28"/>
@@ -10978,8 +10995,8 @@
       <c r="E17" s="23" t="s">
         <v>420</v>
       </c>
-      <c r="F17" s="37"/>
-      <c r="G17" s="38" t="s">
+      <c r="F17" s="39"/>
+      <c r="G17" s="40" t="s">
         <v>395</v>
       </c>
       <c r="H17" s="31"/>
@@ -11012,20 +11029,20 @@
       <c r="E18" s="23" t="s">
         <v>422</v>
       </c>
-      <c r="F18" s="89"/>
-      <c r="G18" s="90" t="s">
+      <c r="F18" s="94"/>
+      <c r="G18" s="95" t="s">
         <v>423</v>
       </c>
-      <c r="H18" s="60"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="91"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="60">
+      <c r="H18" s="62"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="96"/>
+      <c r="O18" s="96"/>
+      <c r="P18" s="96"/>
+      <c r="Q18" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11046,20 +11063,20 @@
       <c r="E19" s="23" t="s">
         <v>425</v>
       </c>
-      <c r="F19" s="89"/>
-      <c r="G19" s="90" t="s">
+      <c r="F19" s="94"/>
+      <c r="G19" s="95" t="s">
         <v>395</v>
       </c>
-      <c r="H19" s="60"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="61"/>
-      <c r="P19" s="61"/>
-      <c r="Q19" s="60">
+      <c r="H19" s="62"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="63"/>
+      <c r="P19" s="63"/>
+      <c r="Q19" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11080,20 +11097,20 @@
       <c r="E20" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="F20" s="89"/>
-      <c r="G20" s="90" t="s">
+      <c r="F20" s="94"/>
+      <c r="G20" s="95" t="s">
         <v>395</v>
       </c>
-      <c r="H20" s="60"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="91"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="91"/>
-      <c r="P20" s="91"/>
-      <c r="Q20" s="60">
+      <c r="H20" s="62"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="96"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="96"/>
+      <c r="P20" s="96"/>
+      <c r="Q20" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11114,10 +11131,10 @@
       <c r="E21" s="23" t="s">
         <v>429</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="39">
         <v>20.0</v>
       </c>
-      <c r="G21" s="38" t="s">
+      <c r="G21" s="40" t="s">
         <v>430</v>
       </c>
       <c r="H21" s="31"/>
@@ -11150,8 +11167,8 @@
       <c r="E22" s="23" t="s">
         <v>432</v>
       </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38" t="s">
+      <c r="F22" s="39"/>
+      <c r="G22" s="40" t="s">
         <v>303</v>
       </c>
       <c r="H22" s="28"/>
@@ -11184,18 +11201,18 @@
       <c r="E23" s="23" t="s">
         <v>434</v>
       </c>
-      <c r="F23" s="89"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="91"/>
-      <c r="Q23" s="60">
+      <c r="F23" s="94"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="96"/>
+      <c r="L23" s="96"/>
+      <c r="M23" s="96"/>
+      <c r="N23" s="96"/>
+      <c r="O23" s="96"/>
+      <c r="P23" s="96"/>
+      <c r="Q23" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11216,8 +11233,8 @@
       <c r="E24" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38" t="s">
+      <c r="F24" s="39"/>
+      <c r="G24" s="40" t="s">
         <v>75</v>
       </c>
       <c r="H24" s="28"/>
@@ -11250,20 +11267,20 @@
       <c r="E25" s="23" t="s">
         <v>437</v>
       </c>
-      <c r="F25" s="89"/>
-      <c r="G25" s="90" t="s">
+      <c r="F25" s="94"/>
+      <c r="G25" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="H25" s="60"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="91"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="91"/>
-      <c r="M25" s="91"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="91"/>
-      <c r="P25" s="91"/>
-      <c r="Q25" s="60">
+      <c r="H25" s="62"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="96"/>
+      <c r="L25" s="96"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="96"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="96"/>
+      <c r="Q25" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11284,8 +11301,8 @@
       <c r="E26" s="23" t="s">
         <v>439</v>
       </c>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38" t="s">
+      <c r="F26" s="39"/>
+      <c r="G26" s="40" t="s">
         <v>99</v>
       </c>
       <c r="H26" s="28"/>
@@ -11318,8 +11335,8 @@
       <c r="E27" s="23" t="s">
         <v>441</v>
       </c>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38" t="s">
+      <c r="F27" s="39"/>
+      <c r="G27" s="40" t="s">
         <v>395</v>
       </c>
       <c r="H27" s="31"/>
@@ -11352,8 +11369,8 @@
       <c r="E28" s="23" t="s">
         <v>443</v>
       </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -11384,8 +11401,8 @@
       <c r="E29" s="23" t="s">
         <v>445</v>
       </c>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38" t="s">
+      <c r="F29" s="39"/>
+      <c r="G29" s="40" t="s">
         <v>395</v>
       </c>
       <c r="H29" s="31"/>
@@ -11418,8 +11435,8 @@
       <c r="E30" s="23" t="s">
         <v>447</v>
       </c>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38" t="s">
+      <c r="F30" s="39"/>
+      <c r="G30" s="40" t="s">
         <v>448</v>
       </c>
       <c r="H30" s="28"/>
@@ -11452,52 +11469,52 @@
       <c r="E31" s="23" t="s">
         <v>425</v>
       </c>
-      <c r="F31" s="89"/>
-      <c r="G31" s="90" t="s">
+      <c r="F31" s="94"/>
+      <c r="G31" s="95" t="s">
         <v>395</v>
       </c>
-      <c r="H31" s="60"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="91"/>
-      <c r="K31" s="91"/>
-      <c r="L31" s="91"/>
-      <c r="M31" s="91"/>
-      <c r="N31" s="91"/>
-      <c r="O31" s="91"/>
-      <c r="P31" s="91"/>
-      <c r="Q31" s="60">
+      <c r="H31" s="62"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="96"/>
+      <c r="L31" s="96"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="96"/>
+      <c r="O31" s="96"/>
+      <c r="P31" s="96"/>
+      <c r="Q31" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="92">
+      <c r="A32" s="97">
         <v>25.0</v>
       </c>
-      <c r="B32" s="93" t="s">
+      <c r="B32" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="94" t="s">
+      <c r="C32" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="93" t="s">
+      <c r="D32" s="98" t="s">
         <v>450</v>
       </c>
-      <c r="E32" s="93" t="s">
+      <c r="E32" s="98" t="s">
         <v>451</v>
       </c>
-      <c r="F32" s="89"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="91"/>
-      <c r="K32" s="91"/>
-      <c r="L32" s="91"/>
-      <c r="M32" s="91"/>
-      <c r="N32" s="91"/>
-      <c r="O32" s="91"/>
-      <c r="P32" s="91"/>
-      <c r="Q32" s="60">
+      <c r="F32" s="94"/>
+      <c r="G32" s="95"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="96"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="96"/>
+      <c r="O32" s="96"/>
+      <c r="P32" s="96"/>
+      <c r="Q32" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11518,8 +11535,8 @@
       <c r="E33" s="23" t="s">
         <v>453</v>
       </c>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38" t="s">
+      <c r="F33" s="39"/>
+      <c r="G33" s="40" t="s">
         <v>454</v>
       </c>
       <c r="H33" s="31"/>
@@ -11599,7 +11616,7 @@
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="95" t="s">
+      <c r="E1" s="100" t="s">
         <v>37</v>
       </c>
       <c r="F1" s="5"/>
@@ -11624,7 +11641,7 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="95"/>
+      <c r="E2" s="100"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="13"/>
@@ -11636,7 +11653,7 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="95" t="s">
+      <c r="E3" s="100" t="s">
         <v>455</v>
       </c>
       <c r="F3" s="5"/>
@@ -11650,7 +11667,7 @@
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
-      <c r="E4" s="96" t="s">
+      <c r="E4" s="101" t="s">
         <v>456</v>
       </c>
       <c r="F4" s="5"/>
@@ -11664,7 +11681,7 @@
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="95" t="s">
+      <c r="E5" s="100" t="s">
         <v>457</v>
       </c>
       <c r="F5" s="5"/>
@@ -11682,10 +11699,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -11735,23 +11752,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="66">
+      <c r="A8" s="68">
         <v>1.0</v>
       </c>
-      <c r="B8" s="97" t="s">
+      <c r="B8" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="98" t="s">
+      <c r="C8" s="103" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="99" t="s">
+      <c r="D8" s="104" t="s">
         <v>458</v>
       </c>
-      <c r="E8" s="99" t="s">
+      <c r="E8" s="104" t="s">
         <v>235</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -11767,23 +11784,23 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="68">
+      <c r="A9" s="70">
         <v>2.0</v>
       </c>
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="98" t="s">
+      <c r="C9" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="99" t="s">
+      <c r="D9" s="104" t="s">
         <v>459</v>
       </c>
-      <c r="E9" s="99" t="s">
+      <c r="E9" s="104" t="s">
         <v>460</v>
       </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="38"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -11799,23 +11816,23 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="66">
+      <c r="A10" s="68">
         <v>3.0</v>
       </c>
-      <c r="B10" s="97" t="s">
+      <c r="B10" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="98" t="s">
+      <c r="C10" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="100" t="s">
+      <c r="D10" s="105" t="s">
         <v>461</v>
       </c>
-      <c r="E10" s="100" t="s">
+      <c r="E10" s="105" t="s">
         <v>462</v>
       </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="38"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -11831,23 +11848,23 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="68">
+      <c r="A11" s="70">
         <v>4.0</v>
       </c>
-      <c r="B11" s="97" t="s">
+      <c r="B11" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="100" t="s">
+      <c r="D11" s="105" t="s">
         <v>463</v>
       </c>
-      <c r="E11" s="100" t="s">
+      <c r="E11" s="105" t="s">
         <v>464</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="38"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -11863,23 +11880,23 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="66">
+      <c r="A12" s="68">
         <v>5.0</v>
       </c>
-      <c r="B12" s="97" t="s">
+      <c r="B12" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="98" t="s">
+      <c r="C12" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="101" t="s">
+      <c r="D12" s="106" t="s">
         <v>465</v>
       </c>
-      <c r="E12" s="99" t="s">
+      <c r="E12" s="104" t="s">
         <v>466</v>
       </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="38"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="40"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -11895,23 +11912,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="68">
+      <c r="A13" s="70">
         <v>6.0</v>
       </c>
-      <c r="B13" s="97" t="s">
+      <c r="B13" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="102" t="s">
+      <c r="C13" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="101" t="s">
+      <c r="D13" s="106" t="s">
         <v>467</v>
       </c>
-      <c r="E13" s="101" t="s">
+      <c r="E13" s="106" t="s">
         <v>468</v>
       </c>
-      <c r="F13" s="37"/>
-      <c r="G13" s="38"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -11927,23 +11944,23 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="66">
+      <c r="A14" s="68">
         <v>7.0</v>
       </c>
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="102" t="s">
+      <c r="C14" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="101" t="s">
+      <c r="D14" s="106" t="s">
         <v>469</v>
       </c>
-      <c r="E14" s="101" t="s">
+      <c r="E14" s="106" t="s">
         <v>470</v>
       </c>
-      <c r="F14" s="37"/>
-      <c r="G14" s="38"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="40"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -11959,23 +11976,23 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="68">
+      <c r="A15" s="70">
         <v>8.0</v>
       </c>
-      <c r="B15" s="97" t="s">
+      <c r="B15" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="102" t="s">
+      <c r="C15" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="101" t="s">
+      <c r="D15" s="106" t="s">
         <v>471</v>
       </c>
-      <c r="E15" s="101" t="s">
+      <c r="E15" s="106" t="s">
         <v>472</v>
       </c>
-      <c r="F15" s="37"/>
-      <c r="G15" s="38"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -11991,23 +12008,23 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="66">
+      <c r="A16" s="68">
         <v>9.0</v>
       </c>
-      <c r="B16" s="97" t="s">
+      <c r="B16" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="102" t="s">
+      <c r="C16" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="101" t="s">
+      <c r="D16" s="106" t="s">
         <v>473</v>
       </c>
-      <c r="E16" s="101" t="s">
+      <c r="E16" s="106" t="s">
         <v>474</v>
       </c>
-      <c r="F16" s="37"/>
-      <c r="G16" s="38"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
       <c r="J16" s="29"/>
@@ -12023,23 +12040,23 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="68">
+      <c r="A17" s="70">
         <v>10.0</v>
       </c>
-      <c r="B17" s="97" t="s">
+      <c r="B17" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="102" t="s">
+      <c r="C17" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="101" t="s">
+      <c r="D17" s="106" t="s">
         <v>475</v>
       </c>
-      <c r="E17" s="101" t="s">
+      <c r="E17" s="106" t="s">
         <v>466</v>
       </c>
-      <c r="F17" s="37"/>
-      <c r="G17" s="38"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -12055,23 +12072,23 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="66">
+      <c r="A18" s="68">
         <v>12.0</v>
       </c>
-      <c r="B18" s="97" t="s">
+      <c r="B18" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="102" t="s">
+      <c r="C18" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="101" t="s">
+      <c r="D18" s="106" t="s">
         <v>476</v>
       </c>
-      <c r="E18" s="101" t="s">
+      <c r="E18" s="106" t="s">
         <v>477</v>
       </c>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -12087,23 +12104,23 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="68">
+      <c r="A19" s="70">
         <v>11.0</v>
       </c>
-      <c r="B19" s="97" t="s">
+      <c r="B19" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="102" t="s">
+      <c r="C19" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="101" t="s">
+      <c r="D19" s="106" t="s">
         <v>478</v>
       </c>
-      <c r="E19" s="101" t="s">
+      <c r="E19" s="106" t="s">
         <v>479</v>
       </c>
-      <c r="F19" s="37"/>
-      <c r="G19" s="38"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="40"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -12119,23 +12136,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="66">
+      <c r="A20" s="68">
         <v>13.0</v>
       </c>
-      <c r="B20" s="97" t="s">
+      <c r="B20" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="102" t="s">
+      <c r="C20" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="101" t="s">
+      <c r="D20" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="101" t="s">
+      <c r="E20" s="106" t="s">
         <v>480</v>
       </c>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -12151,23 +12168,23 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="68">
+      <c r="A21" s="70">
         <v>14.0</v>
       </c>
-      <c r="B21" s="97" t="s">
+      <c r="B21" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="102" t="s">
+      <c r="C21" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="101" t="s">
+      <c r="D21" s="106" t="s">
         <v>469</v>
       </c>
-      <c r="E21" s="101" t="s">
+      <c r="E21" s="106" t="s">
         <v>481</v>
       </c>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -12183,23 +12200,23 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="66">
+      <c r="A22" s="68">
         <v>15.0</v>
       </c>
-      <c r="B22" s="97" t="s">
+      <c r="B22" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="98" t="s">
+      <c r="C22" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="99" t="s">
+      <c r="D22" s="104" t="s">
         <v>482</v>
       </c>
-      <c r="E22" s="99" t="s">
+      <c r="E22" s="104" t="s">
         <v>483</v>
       </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="40"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -12215,23 +12232,23 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="68">
+      <c r="A23" s="70">
         <v>16.0</v>
       </c>
-      <c r="B23" s="97" t="s">
+      <c r="B23" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="98" t="s">
+      <c r="C23" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="99" t="s">
+      <c r="D23" s="104" t="s">
         <v>484</v>
       </c>
-      <c r="E23" s="99" t="s">
+      <c r="E23" s="104" t="s">
         <v>485</v>
       </c>
-      <c r="F23" s="37"/>
-      <c r="G23" s="38"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="40"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -12247,23 +12264,23 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="66">
+      <c r="A24" s="68">
         <v>17.0</v>
       </c>
-      <c r="B24" s="97" t="s">
+      <c r="B24" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="98" t="s">
+      <c r="C24" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="99" t="s">
+      <c r="D24" s="104" t="s">
         <v>486</v>
       </c>
-      <c r="E24" s="99" t="s">
+      <c r="E24" s="104" t="s">
         <v>487</v>
       </c>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -12279,23 +12296,23 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="66">
+      <c r="A25" s="68">
         <v>18.0</v>
       </c>
-      <c r="B25" s="97" t="s">
+      <c r="B25" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="98" t="s">
+      <c r="C25" s="103" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="99" t="s">
+      <c r="D25" s="104" t="s">
         <v>488</v>
       </c>
-      <c r="E25" s="99" t="s">
+      <c r="E25" s="104" t="s">
         <v>489</v>
       </c>
-      <c r="F25" s="37"/>
-      <c r="G25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -12311,23 +12328,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="66">
+      <c r="A26" s="68">
         <v>19.0</v>
       </c>
-      <c r="B26" s="97" t="s">
+      <c r="B26" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="98" t="s">
+      <c r="C26" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="99" t="s">
+      <c r="D26" s="104" t="s">
         <v>490</v>
       </c>
-      <c r="E26" s="99" t="s">
+      <c r="E26" s="104" t="s">
         <v>466</v>
       </c>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -12343,23 +12360,23 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="66">
+      <c r="A27" s="68">
         <v>20.0</v>
       </c>
-      <c r="B27" s="97" t="s">
+      <c r="B27" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="98" t="s">
+      <c r="C27" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="99" t="s">
+      <c r="D27" s="104" t="s">
         <v>491</v>
       </c>
-      <c r="E27" s="99" t="s">
+      <c r="E27" s="104" t="s">
         <v>481</v>
       </c>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
@@ -12375,23 +12392,23 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="66">
+      <c r="A28" s="68">
         <v>21.0</v>
       </c>
-      <c r="B28" s="97" t="s">
+      <c r="B28" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="98" t="s">
+      <c r="C28" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="99" t="s">
+      <c r="D28" s="104" t="s">
         <v>492</v>
       </c>
-      <c r="E28" s="99" t="s">
+      <c r="E28" s="104" t="s">
         <v>493</v>
       </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -12407,23 +12424,23 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="66">
+      <c r="A29" s="68">
         <v>22.0</v>
       </c>
-      <c r="B29" s="97" t="s">
+      <c r="B29" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="98" t="s">
+      <c r="C29" s="103" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="99" t="s">
+      <c r="D29" s="104" t="s">
         <v>494</v>
       </c>
-      <c r="E29" s="99" t="s">
+      <c r="E29" s="104" t="s">
         <v>179</v>
       </c>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -12439,23 +12456,23 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="66">
+      <c r="A30" s="68">
         <v>23.0</v>
       </c>
-      <c r="B30" s="97" t="s">
+      <c r="B30" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="98" t="s">
+      <c r="C30" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="99" t="s">
+      <c r="D30" s="104" t="s">
         <v>495</v>
       </c>
-      <c r="E30" s="99" t="s">
+      <c r="E30" s="104" t="s">
         <v>496</v>
       </c>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="40"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -12471,23 +12488,23 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="68">
+      <c r="A31" s="70">
         <v>24.0</v>
       </c>
-      <c r="B31" s="97" t="s">
+      <c r="B31" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="98" t="s">
+      <c r="C31" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="99" t="s">
+      <c r="D31" s="104" t="s">
         <v>276</v>
       </c>
-      <c r="E31" s="99" t="s">
+      <c r="E31" s="104" t="s">
         <v>497</v>
       </c>
-      <c r="F31" s="37"/>
-      <c r="G31" s="38"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -12503,23 +12520,23 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="66">
+      <c r="A32" s="68">
         <v>25.0</v>
       </c>
-      <c r="B32" s="97" t="s">
+      <c r="B32" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="98" t="s">
+      <c r="C32" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="99" t="s">
+      <c r="D32" s="104" t="s">
         <v>498</v>
       </c>
-      <c r="E32" s="99" t="s">
+      <c r="E32" s="104" t="s">
         <v>483</v>
       </c>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="40"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -12535,23 +12552,23 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="68">
+      <c r="A33" s="70">
         <v>26.0</v>
       </c>
-      <c r="B33" s="97" t="s">
+      <c r="B33" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="98" t="s">
+      <c r="C33" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="99" t="s">
+      <c r="D33" s="104" t="s">
         <v>499</v>
       </c>
-      <c r="E33" s="99" t="s">
+      <c r="E33" s="104" t="s">
         <v>500</v>
       </c>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="40"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>

--- a/public/data/@Liste GROUPE B.xlsx
+++ b/public/data/@Liste GROUPE B.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="556">
   <si>
     <t xml:space="preserve">Équipe </t>
   </si>
@@ -278,10 +278,10 @@
     <t>RCA</t>
   </si>
   <si>
-    <t>MAMADOU</t>
-  </si>
-  <si>
-    <t>KALILOU BARRY</t>
+    <t>ANTWI BOATENG</t>
+  </si>
+  <si>
+    <t>ENOCH</t>
   </si>
   <si>
     <t>Côte D'Ivoire</t>
@@ -314,10 +314,10 @@
     <t>MOSA</t>
   </si>
   <si>
-    <t>JEANCY</t>
-  </si>
-  <si>
-    <t>KAYOLO KIMBUTA</t>
+    <t>DAN MWIMBA</t>
+  </si>
+  <si>
+    <t>MULEDI</t>
   </si>
   <si>
     <t>4-ATTAQUANT</t>
@@ -401,10 +401,10 @@
     <t>2XL</t>
   </si>
   <si>
-    <t>SILVIO</t>
-  </si>
-  <si>
-    <t>BIABO NZOUENGUE</t>
+    <t>DAVID ALEXANDRE</t>
+  </si>
+  <si>
+    <t>SIMOES</t>
   </si>
   <si>
     <t>LÉO EMILIEN</t>
@@ -413,10 +413,10 @@
     <t>NKOA</t>
   </si>
   <si>
-    <t>FRANÇOIS</t>
-  </si>
-  <si>
-    <t>ECA MSEKE</t>
+    <t>ESPOIR</t>
+  </si>
+  <si>
+    <t>ASDJIM</t>
   </si>
   <si>
     <t>AFONSO ALMEIDA</t>
@@ -539,6 +539,12 @@
     <t>FAYE</t>
   </si>
   <si>
+    <t xml:space="preserve">MOUSTAPHA </t>
+  </si>
+  <si>
+    <t>DIOP</t>
+  </si>
+  <si>
     <t>PAPE IBRAHIMA</t>
   </si>
   <si>
@@ -584,6 +590,12 @@
     <t>MBODJ</t>
   </si>
   <si>
+    <t>SOULEYMANE</t>
+  </si>
+  <si>
+    <t>DIALLO</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -707,970 +719,967 @@
     <t>DEKASSI</t>
   </si>
   <si>
+    <t>EMMANUEL BORIS</t>
+  </si>
+  <si>
+    <t>OLÉ OBALÉ</t>
+  </si>
+  <si>
+    <t>guinée</t>
+  </si>
+  <si>
+    <t>KOUTAO RAKOU</t>
+  </si>
+  <si>
+    <t>TALMANTA</t>
+  </si>
+  <si>
+    <t>ALOGNISSO</t>
+  </si>
+  <si>
+    <t>RONALD</t>
+  </si>
+  <si>
+    <t>PETERSON</t>
+  </si>
+  <si>
+    <t>AUGUSTE</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>LOCHINA</t>
+  </si>
+  <si>
+    <t>DJAFAROU</t>
+  </si>
+  <si>
+    <t>KONATÉ</t>
+  </si>
+  <si>
+    <t>MANSOUR</t>
+  </si>
+  <si>
+    <t>KOMLAN AMEN</t>
+  </si>
+  <si>
+    <t>AKAMA</t>
+  </si>
+  <si>
+    <t>ESSODONA</t>
+  </si>
+  <si>
+    <t>HALAOUI</t>
+  </si>
+  <si>
+    <t>ADONIS</t>
+  </si>
+  <si>
+    <t>KALENGA</t>
+  </si>
+  <si>
+    <t>MKOLE</t>
+  </si>
+  <si>
+    <t>RAMADHANI</t>
+  </si>
+  <si>
+    <t>DESIRE</t>
+  </si>
+  <si>
+    <t>BICUKA</t>
+  </si>
+  <si>
+    <t>ABEDI</t>
+  </si>
+  <si>
+    <t>SAIDI</t>
+  </si>
+  <si>
+    <t>ATAMBA</t>
+  </si>
+  <si>
+    <t>SHAURI</t>
+  </si>
+  <si>
+    <t>JONAS</t>
+  </si>
+  <si>
+    <t>KISUBI</t>
+  </si>
+  <si>
+    <t>PATIENT</t>
+  </si>
+  <si>
+    <t>ECA MBOKO</t>
+  </si>
+  <si>
+    <t>SALEH</t>
+  </si>
+  <si>
+    <t>ECA</t>
+  </si>
+  <si>
+    <t>UWEZO</t>
+  </si>
+  <si>
+    <t>JUMAPILI</t>
+  </si>
+  <si>
+    <t>NDIKUMANA</t>
+  </si>
+  <si>
+    <t>JANVIER</t>
+  </si>
+  <si>
+    <t>REUBEN</t>
+  </si>
+  <si>
+    <t>MLONGEKA</t>
+  </si>
+  <si>
+    <t>AMURI</t>
+  </si>
+  <si>
+    <t>NDUME</t>
+  </si>
+  <si>
+    <t>OMARI</t>
+  </si>
+  <si>
+    <t>KASHINDI</t>
+  </si>
+  <si>
+    <t>WILONDJA</t>
+  </si>
+  <si>
+    <t>LWAMAGENA</t>
+  </si>
+  <si>
+    <t>SADIKI</t>
+  </si>
+  <si>
+    <t>SHOKU MAJEGEZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGAZINI </t>
+  </si>
+  <si>
+    <t>LWABOSHI MAJEGEZA</t>
+  </si>
+  <si>
+    <t>ERICK</t>
+  </si>
+  <si>
+    <t>NISHIMWE</t>
+  </si>
+  <si>
+    <t>ASENDE</t>
+  </si>
+  <si>
+    <t>ABANGWA</t>
+  </si>
+  <si>
+    <t>OLIVIER</t>
+  </si>
+  <si>
+    <t>RIPHIN</t>
+  </si>
+  <si>
+    <t>HONNEUR</t>
+  </si>
+  <si>
+    <t>JEAN MARIE</t>
+  </si>
+  <si>
+    <t>ELIAZERI</t>
+  </si>
+  <si>
+    <t>NIYOGUSENGA</t>
+  </si>
+  <si>
+    <t>BYAOMBE</t>
+  </si>
+  <si>
+    <t>BAHOME</t>
+  </si>
+  <si>
+    <t>YAMUNGU MLENBA</t>
+  </si>
+  <si>
+    <t>ZAKARIA</t>
+  </si>
+  <si>
+    <t>RÉMY</t>
+  </si>
+  <si>
+    <t>MILAMBO</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>soccerangranmoun@gmail.com; flounes37@gmail.com</t>
+  </si>
+  <si>
+    <t>4189563785 / 4388384936</t>
+  </si>
+  <si>
+    <t>Lounès Félicin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hans Raldy Saint-Preux </t>
+  </si>
+  <si>
+    <t>MAQUINGSON</t>
+  </si>
+  <si>
+    <t>MAIGNAN</t>
+  </si>
+  <si>
+    <t>AMILICA</t>
+  </si>
+  <si>
+    <t>MADI BOUKARI</t>
+  </si>
+  <si>
+    <t>MICHAEL PERSHINGSON</t>
+  </si>
+  <si>
+    <t>PIERRE</t>
+  </si>
+  <si>
+    <t>JEFFERSON</t>
+  </si>
+  <si>
+    <t>ANTOINE</t>
+  </si>
+  <si>
+    <t>GREGORY</t>
+  </si>
+  <si>
+    <t>ANNAY</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>JERRY</t>
+  </si>
+  <si>
+    <t>PAULIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXEL </t>
+  </si>
+  <si>
+    <t>ALIMASI</t>
+  </si>
+  <si>
+    <t>MARC-ARTHUR</t>
+  </si>
+  <si>
+    <t>REGISTRE</t>
+  </si>
+  <si>
+    <t>MARC-DONALD</t>
+  </si>
+  <si>
+    <t>SIMEUS</t>
+  </si>
+  <si>
+    <t>EVEDERSON</t>
+  </si>
+  <si>
+    <t>PREVILON</t>
+  </si>
+  <si>
+    <t>WOODSON</t>
+  </si>
+  <si>
+    <t>SAINT-LOUIS</t>
+  </si>
+  <si>
+    <t>ROMAIN</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>RYSDAEL C.</t>
+  </si>
+  <si>
+    <t>DUVELSAINT</t>
+  </si>
+  <si>
+    <t>TEVINSON</t>
+  </si>
+  <si>
+    <t>GARCON</t>
+  </si>
+  <si>
+    <t>HANS RALDY</t>
+  </si>
+  <si>
+    <t>SAINT-PREUX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RÉGINALD </t>
+  </si>
+  <si>
+    <t>CADET</t>
+  </si>
+  <si>
+    <t>DARLENS</t>
+  </si>
+  <si>
+    <t>CEPOUDY</t>
+  </si>
+  <si>
+    <t>HUGGUENS</t>
+  </si>
+  <si>
+    <t>VEILLARD</t>
+  </si>
+  <si>
+    <t>OMRA VALDJY WOODLEY</t>
+  </si>
+  <si>
+    <t>BARTHELUS</t>
+  </si>
+  <si>
+    <t>KENLEY</t>
+  </si>
+  <si>
+    <t>MAXI</t>
+  </si>
+  <si>
+    <t>CLIFORD</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>TEIKEU</t>
+  </si>
+  <si>
+    <t>SYLVESTRE STALONNE</t>
+  </si>
+  <si>
+    <t>SECHOUAM</t>
+  </si>
+  <si>
+    <t>CEBATIEN</t>
+  </si>
+  <si>
+    <t>PIERRE-LOUIS</t>
+  </si>
+  <si>
+    <t>YVES-MARY</t>
+  </si>
+  <si>
+    <t>BEAUBRUN</t>
+  </si>
+  <si>
+    <t>oudoucis@yahoo.com</t>
+  </si>
+  <si>
+    <t>418 953 6873</t>
+  </si>
+  <si>
+    <t>ABDRAHAMANE TRAORE</t>
+  </si>
+  <si>
+    <t>Mohamed Coulibaly</t>
+  </si>
+  <si>
+    <t>NUMBER</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>SHORT</t>
+  </si>
+  <si>
+    <t>JACOB</t>
+  </si>
+  <si>
+    <t>DEMBÉLÉ</t>
+  </si>
+  <si>
+    <t>HAMED</t>
+  </si>
+  <si>
+    <t>OUSMANE</t>
+  </si>
+  <si>
+    <t>ABDOULAYE</t>
+  </si>
+  <si>
+    <t>DAO</t>
+  </si>
+  <si>
+    <t>NAMAKÉ FALAYE</t>
+  </si>
+  <si>
+    <t>SISSOKO</t>
+  </si>
+  <si>
+    <t>MOUSSA</t>
+  </si>
+  <si>
     <t>MOHAMED</t>
   </si>
   <si>
+    <t>KALILOU</t>
+  </si>
+  <si>
+    <t>SALIM</t>
+  </si>
+  <si>
+    <t>NIMAGA</t>
+  </si>
+  <si>
+    <t>SIDY MAHAMANE</t>
+  </si>
+  <si>
+    <t>TOURÉ</t>
+  </si>
+  <si>
+    <t>MAHAMOUDOU</t>
+  </si>
+  <si>
+    <t>KONÉ</t>
+  </si>
+  <si>
+    <t>IDRISSA DADYS</t>
+  </si>
+  <si>
+    <t>SIDIBÉ</t>
+  </si>
+  <si>
+    <t>ABOUBAKRINE</t>
+  </si>
+  <si>
+    <t>INTALLA</t>
+  </si>
+  <si>
+    <t>SEKOU SOULEYMANE</t>
+  </si>
+  <si>
+    <t>MAMADOU BAZAN</t>
+  </si>
+  <si>
+    <t>TOGOLA</t>
+  </si>
+  <si>
+    <t>DJIMÉ</t>
+  </si>
+  <si>
+    <t>KÉBÉ</t>
+  </si>
+  <si>
+    <t>MOULAYE MOHAMED</t>
+  </si>
+  <si>
+    <t>DICKO</t>
+  </si>
+  <si>
+    <t>HAROUNA</t>
+  </si>
+  <si>
+    <t>BACHIR</t>
+  </si>
+  <si>
+    <t>BASSIROU</t>
+  </si>
+  <si>
+    <t>HAIDARA</t>
+  </si>
+  <si>
+    <t>GUESSOUMA</t>
+  </si>
+  <si>
+    <t>PATRICK STÉPHANE</t>
+  </si>
+  <si>
+    <t>KAMDEM WAKAM</t>
+  </si>
+  <si>
+    <t>MALIK</t>
+  </si>
+  <si>
+    <t>DIARRA</t>
+  </si>
+  <si>
+    <t>IBRAHIM</t>
+  </si>
+  <si>
+    <t>ISSAKA</t>
+  </si>
+  <si>
+    <t>OUMAR</t>
+  </si>
+  <si>
+    <t>CISSÉ</t>
+  </si>
+  <si>
+    <t>ALMAMY</t>
+  </si>
+  <si>
+    <t>GUINDO</t>
+  </si>
+  <si>
+    <t>KOULBÉ</t>
+  </si>
+  <si>
+    <t>Tchad</t>
+  </si>
+  <si>
+    <t>Gabon</t>
+  </si>
+  <si>
+    <t>georgesarmel1@hotmail.fr</t>
+  </si>
+  <si>
+    <t>(581)849-3674</t>
+  </si>
+  <si>
+    <t>Georges armel Nguimbi</t>
+  </si>
+  <si>
+    <t>Cedrick essockamba</t>
+  </si>
+  <si>
+    <t>DROLET</t>
+  </si>
+  <si>
+    <t>DIEUDONNÉ</t>
+  </si>
+  <si>
+    <t>CIZA</t>
+  </si>
+  <si>
+    <t>Rwanda</t>
+  </si>
+  <si>
+    <t>STEPHANE</t>
+  </si>
+  <si>
+    <t>PREDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada </t>
+  </si>
+  <si>
+    <t>CEDRIC</t>
+  </si>
+  <si>
+    <t>ESSOCKAMBA</t>
+  </si>
+  <si>
+    <t>JEAN-THERRY</t>
+  </si>
+  <si>
+    <t>YAMA</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>BAMBA</t>
+  </si>
+  <si>
+    <t>FARAJA</t>
+  </si>
+  <si>
+    <t>DIEU BENIT</t>
+  </si>
+  <si>
+    <t>SOUMAI</t>
+  </si>
+  <si>
+    <t>FEDSON</t>
+  </si>
+  <si>
+    <t>ROSIER</t>
+  </si>
+  <si>
+    <t>YANNICK</t>
+  </si>
+  <si>
+    <t>KAYILOU</t>
+  </si>
+  <si>
+    <t>ESTEBAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cote d'ivoire </t>
+  </si>
+  <si>
+    <t>JEAN DANIEL</t>
+  </si>
+  <si>
+    <t>POTTEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE </t>
+  </si>
+  <si>
+    <t>KOKORA</t>
+  </si>
+  <si>
+    <t>ABDELAZIZ</t>
+  </si>
+  <si>
+    <t>KAPATA</t>
+  </si>
+  <si>
+    <t>Centre-afrique</t>
+  </si>
+  <si>
+    <t>VINCENT</t>
+  </si>
+  <si>
+    <t>CORNEAU</t>
+  </si>
+  <si>
+    <t>DEMOYER</t>
+  </si>
+  <si>
+    <t>KOUASSI</t>
+  </si>
+  <si>
+    <t>BENONI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÉMILE </t>
+  </si>
+  <si>
+    <t>FRANCK NELSON</t>
+  </si>
+  <si>
+    <t>VOUFO</t>
+  </si>
+  <si>
+    <t>SAMUEL</t>
+  </si>
+  <si>
+    <t>POATY</t>
+  </si>
+  <si>
+    <t>DYLAN</t>
+  </si>
+  <si>
+    <t>POTE</t>
+  </si>
+  <si>
+    <t>ARGI</t>
+  </si>
+  <si>
+    <t>PASCAL</t>
+  </si>
+  <si>
+    <t>BIENVENUE</t>
+  </si>
+  <si>
+    <t>STANY</t>
+  </si>
+  <si>
+    <t>Burundi</t>
+  </si>
+  <si>
+    <t>MARC</t>
+  </si>
+  <si>
+    <t>ÉRISA</t>
+  </si>
+  <si>
+    <t>NSHIMIYIMANA</t>
+  </si>
+  <si>
+    <t>JUNIOR</t>
+  </si>
+  <si>
+    <t>POKOU</t>
+  </si>
+  <si>
+    <t>Cote d'ivoire</t>
+  </si>
+  <si>
+    <t>418-554-0364</t>
+  </si>
+  <si>
+    <t>ABDOUL-AZIZ</t>
+  </si>
+  <si>
+    <t>Hamidou Ouédraogo</t>
+  </si>
+  <si>
+    <t>FAAROOQ</t>
+  </si>
+  <si>
+    <t>CHEIK OMAR</t>
+  </si>
+  <si>
+    <t>BOUSSIM FADEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORESTE </t>
+  </si>
+  <si>
+    <t>TOMPOUDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAPI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KANE </t>
+  </si>
+  <si>
+    <t>HAMED-TIDJANI</t>
+  </si>
+  <si>
+    <t>OUEDRAOGO</t>
+  </si>
+  <si>
+    <t>ABDOUL-FATAHOU</t>
+  </si>
+  <si>
+    <t>COMPAORÉ</t>
+  </si>
+  <si>
+    <t>YACOUBA</t>
+  </si>
+  <si>
+    <t>DARGA</t>
+  </si>
+  <si>
+    <t>RAOUF</t>
+  </si>
+  <si>
+    <t>KRIGAH</t>
+  </si>
+  <si>
+    <t>HANS</t>
+  </si>
+  <si>
+    <t>KOUAKOU</t>
+  </si>
+  <si>
+    <t>HAMIDOU</t>
+  </si>
+  <si>
+    <t>KEVIN ESPÉRAT</t>
+  </si>
+  <si>
+    <t>SAWADOGO</t>
+  </si>
+  <si>
+    <t>ABDOUL-HAKIM</t>
+  </si>
+  <si>
+    <t>BANCÉ</t>
+  </si>
+  <si>
+    <t>SIMPORE</t>
+  </si>
+  <si>
+    <t>ZONGO</t>
+  </si>
+  <si>
+    <t>ELVIS</t>
+  </si>
+  <si>
+    <t>KABORÉ</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>NDJIEUNDE</t>
+  </si>
+  <si>
+    <t>MAX ILDEVER WENDPOUIRÉ</t>
+  </si>
+  <si>
+    <t>SOUILI</t>
+  </si>
+  <si>
+    <t>CHATELAIN</t>
+  </si>
+  <si>
+    <t>YADJUI</t>
+  </si>
+  <si>
+    <t>SOUHOUDOU</t>
+  </si>
+  <si>
+    <t>MICHEL DONALD</t>
+  </si>
+  <si>
+    <t>MAT-JUNIOR</t>
+  </si>
+  <si>
+    <t>SOBJANG NDJATOU</t>
+  </si>
+  <si>
+    <t>LASSINA</t>
+  </si>
+  <si>
+    <t>WILFREID</t>
+  </si>
+  <si>
+    <t>KINDO</t>
+  </si>
+  <si>
+    <t>ASSAGOU</t>
+  </si>
+  <si>
+    <t>VÉRON</t>
+  </si>
+  <si>
+    <t>FAHMAN</t>
+  </si>
+  <si>
+    <t>GUIRO</t>
+  </si>
+  <si>
+    <t>NOM DE L'ÉQUIPE :GUINÉE 🇬🇳</t>
+  </si>
+  <si>
+    <t>ADRESSE  COURRIEL :aboubabacarpapikeita@gmail.com</t>
+  </si>
+  <si>
+    <t>TÉL D'URGENCE : 4182658413</t>
+  </si>
+  <si>
+    <t>NOM DU COACH : Frédérick</t>
+  </si>
+  <si>
+    <t>NOM DU CAPITAINE : Moustapha Donzo</t>
+  </si>
+  <si>
+    <t>BAH</t>
+  </si>
+  <si>
+    <t>Guinéen</t>
+  </si>
+  <si>
+    <t>SY SAVANÉ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malien </t>
+  </si>
+  <si>
+    <t>THIERNO OUSMANE</t>
+  </si>
+  <si>
+    <t>SOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guinée </t>
+  </si>
+  <si>
+    <t>NAZIF</t>
+  </si>
+  <si>
+    <t>AGBEDOH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Togolaise </t>
+  </si>
+  <si>
+    <t>ISMAEL</t>
+  </si>
+  <si>
+    <t>BARRY</t>
+  </si>
+  <si>
+    <t>Guinée</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guinéen </t>
+  </si>
+  <si>
+    <t>DIANÉ</t>
+  </si>
+  <si>
+    <t>ABOUBACAR</t>
+  </si>
+  <si>
+    <t>AKHYAR</t>
+  </si>
+  <si>
+    <t>Mauritanien</t>
+  </si>
+  <si>
+    <t>MOHAMED DAYE</t>
+  </si>
+  <si>
+    <t>KEBE</t>
+  </si>
+  <si>
+    <t>MALICK</t>
+  </si>
+  <si>
+    <t>TRAORE</t>
+  </si>
+  <si>
+    <t>DONZO</t>
+  </si>
+  <si>
+    <t>VICTOR</t>
+  </si>
+  <si>
+    <t>LENO</t>
+  </si>
+  <si>
+    <t>PIERRE DENIS</t>
+  </si>
+  <si>
+    <t>SAGNO</t>
+  </si>
+  <si>
+    <t>HAROU</t>
+  </si>
+  <si>
+    <t>THIERNO NOUHOU</t>
+  </si>
+  <si>
+    <t>ELHADJ OUSMANE</t>
+  </si>
+  <si>
+    <t>BERETE</t>
+  </si>
+  <si>
+    <t>MAMADY</t>
+  </si>
+  <si>
+    <t>DIANE</t>
+  </si>
+  <si>
+    <t>MAMADOU KINDY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEVE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DABIRÉ </t>
+  </si>
+  <si>
+    <t>AMADOU</t>
+  </si>
+  <si>
     <t>CHERIF</t>
-  </si>
-  <si>
-    <t>guinée</t>
-  </si>
-  <si>
-    <t>KOUTAO RAKOU</t>
-  </si>
-  <si>
-    <t>TALMANTA</t>
-  </si>
-  <si>
-    <t>ALOGNISSO</t>
-  </si>
-  <si>
-    <t>RONALD</t>
-  </si>
-  <si>
-    <t>PETERSON</t>
-  </si>
-  <si>
-    <t>AUGUSTE</t>
-  </si>
-  <si>
-    <t>CI</t>
-  </si>
-  <si>
-    <t>LOCHINA</t>
-  </si>
-  <si>
-    <t>DJAFAROU</t>
-  </si>
-  <si>
-    <t>KONATÉ</t>
-  </si>
-  <si>
-    <t>MANSOUR</t>
-  </si>
-  <si>
-    <t>KOMLAN AMEN</t>
-  </si>
-  <si>
-    <t>AKAMA</t>
-  </si>
-  <si>
-    <t>ESSODONA</t>
-  </si>
-  <si>
-    <t>HALAOUI</t>
-  </si>
-  <si>
-    <t>ADONIS</t>
-  </si>
-  <si>
-    <t>KALENGA</t>
-  </si>
-  <si>
-    <t>MKOLE</t>
-  </si>
-  <si>
-    <t>RAMADHANI</t>
-  </si>
-  <si>
-    <t>DESIRE</t>
-  </si>
-  <si>
-    <t>BICUKA</t>
-  </si>
-  <si>
-    <t>ABEDI</t>
-  </si>
-  <si>
-    <t>SAIDI</t>
-  </si>
-  <si>
-    <t>ATAMBA</t>
-  </si>
-  <si>
-    <t>SHAURI</t>
-  </si>
-  <si>
-    <t>JONAS</t>
-  </si>
-  <si>
-    <t>KISUBI</t>
-  </si>
-  <si>
-    <t>PATIENT</t>
-  </si>
-  <si>
-    <t>ECA MBOKO</t>
-  </si>
-  <si>
-    <t>SALEH</t>
-  </si>
-  <si>
-    <t>ECA</t>
-  </si>
-  <si>
-    <t>UWEZO</t>
-  </si>
-  <si>
-    <t>JUMAPILI</t>
-  </si>
-  <si>
-    <t>NDIKUMANA</t>
-  </si>
-  <si>
-    <t>JANVIER</t>
-  </si>
-  <si>
-    <t>REUBEN</t>
-  </si>
-  <si>
-    <t>MLONGEKA</t>
-  </si>
-  <si>
-    <t>AMURI</t>
-  </si>
-  <si>
-    <t>NDUME</t>
-  </si>
-  <si>
-    <t>OMARI</t>
-  </si>
-  <si>
-    <t>KASHINDI</t>
-  </si>
-  <si>
-    <t>WILONDJA</t>
-  </si>
-  <si>
-    <t>LWAMAGENA</t>
-  </si>
-  <si>
-    <t>SADIKI</t>
-  </si>
-  <si>
-    <t>SHOKU MAJEGEZA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>ERICK</t>
-  </si>
-  <si>
-    <t>NISHIMWE</t>
-  </si>
-  <si>
-    <t>MISES</t>
-  </si>
-  <si>
-    <t>BASA</t>
-  </si>
-  <si>
-    <t>OLIVIER</t>
-  </si>
-  <si>
-    <t>RIPHIN</t>
-  </si>
-  <si>
-    <t>HONNEUR</t>
-  </si>
-  <si>
-    <t>JEAN MARIE</t>
-  </si>
-  <si>
-    <t>ELIAZERI</t>
-  </si>
-  <si>
-    <t>NIYOGUSENGA</t>
-  </si>
-  <si>
-    <t>BYAOMBE</t>
-  </si>
-  <si>
-    <t>BAHOME</t>
-  </si>
-  <si>
-    <t>YAMUNGU MLENBA</t>
-  </si>
-  <si>
-    <t>ZAKARIA</t>
-  </si>
-  <si>
-    <t>RÉMY</t>
-  </si>
-  <si>
-    <t>MILAMBO</t>
-  </si>
-  <si>
-    <t>Haiti</t>
-  </si>
-  <si>
-    <t>soccerangranmoun@gmail.com; flounes37@gmail.com</t>
-  </si>
-  <si>
-    <t>4189563785 / 4388384936</t>
-  </si>
-  <si>
-    <t>Lounès Félicin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hans Raldy Saint-Preux </t>
-  </si>
-  <si>
-    <t>MAQUINGSON</t>
-  </si>
-  <si>
-    <t>MAIGNAN</t>
-  </si>
-  <si>
-    <t>AMILICA</t>
-  </si>
-  <si>
-    <t>MADI BOUKARI</t>
-  </si>
-  <si>
-    <t>MICHAEL PERSHINGSON</t>
-  </si>
-  <si>
-    <t>PIERRE</t>
-  </si>
-  <si>
-    <t>JEFFERSON</t>
-  </si>
-  <si>
-    <t>ANTOINE</t>
-  </si>
-  <si>
-    <t>GREGORY</t>
-  </si>
-  <si>
-    <t>ANNAY</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>JERRY</t>
-  </si>
-  <si>
-    <t>PAULIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AXEL </t>
-  </si>
-  <si>
-    <t>ALIMASI</t>
-  </si>
-  <si>
-    <t>MARC-ARTHUR</t>
-  </si>
-  <si>
-    <t>REGISTRE</t>
-  </si>
-  <si>
-    <t>MARC-DONALD</t>
-  </si>
-  <si>
-    <t>SIMEUS</t>
-  </si>
-  <si>
-    <t>EVEDERSON</t>
-  </si>
-  <si>
-    <t>PREVILON</t>
-  </si>
-  <si>
-    <t>WOODSON</t>
-  </si>
-  <si>
-    <t>SAINT-LOUIS</t>
-  </si>
-  <si>
-    <t>ROMAIN</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>RYSDAEL C.</t>
-  </si>
-  <si>
-    <t>DUVELSAINT</t>
-  </si>
-  <si>
-    <t>TEVINSON</t>
-  </si>
-  <si>
-    <t>GARCON</t>
-  </si>
-  <si>
-    <t>HANS RALDY</t>
-  </si>
-  <si>
-    <t>SAINT-PREUX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RÉGINALD </t>
-  </si>
-  <si>
-    <t>CADET</t>
-  </si>
-  <si>
-    <t>DARLENS</t>
-  </si>
-  <si>
-    <t>CEPOUDY</t>
-  </si>
-  <si>
-    <t>HUGGUENS</t>
-  </si>
-  <si>
-    <t>VEILLARD</t>
-  </si>
-  <si>
-    <t>OMRA VALDJY WOODLEY</t>
-  </si>
-  <si>
-    <t>BARTHELUS</t>
-  </si>
-  <si>
-    <t>KENLEY</t>
-  </si>
-  <si>
-    <t>MAXI</t>
-  </si>
-  <si>
-    <t>CLIFORD</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>TEIKEU</t>
-  </si>
-  <si>
-    <t>SYLVESTRE STALONNE</t>
-  </si>
-  <si>
-    <t>SECHOUAM</t>
-  </si>
-  <si>
-    <t>CEBATIEN</t>
-  </si>
-  <si>
-    <t>PIERRE-LOUIS</t>
-  </si>
-  <si>
-    <t>YVES-MARY</t>
-  </si>
-  <si>
-    <t>BEAUBRUN</t>
-  </si>
-  <si>
-    <t>oudoucis@yahoo.com</t>
-  </si>
-  <si>
-    <t>418 953 6873</t>
-  </si>
-  <si>
-    <t>ABDRAHAMANE TRAORE</t>
-  </si>
-  <si>
-    <t>Mohamed Coulibaly</t>
-  </si>
-  <si>
-    <t>NUMBER</t>
-  </si>
-  <si>
-    <t>TOP</t>
-  </si>
-  <si>
-    <t>SHORT</t>
-  </si>
-  <si>
-    <t>JACOB</t>
-  </si>
-  <si>
-    <t>DEMBÉLÉ</t>
-  </si>
-  <si>
-    <t>HAMED</t>
-  </si>
-  <si>
-    <t>OUSMANE</t>
-  </si>
-  <si>
-    <t>ABDOULAYE</t>
-  </si>
-  <si>
-    <t>DAO</t>
-  </si>
-  <si>
-    <t>NAMAKÉ FALAYE</t>
-  </si>
-  <si>
-    <t>SISSOKO</t>
-  </si>
-  <si>
-    <t>MOUSSA</t>
-  </si>
-  <si>
-    <t>SOULEYMANE</t>
-  </si>
-  <si>
-    <t>KALILOU</t>
-  </si>
-  <si>
-    <t>SALIM</t>
-  </si>
-  <si>
-    <t>NIMAGA</t>
-  </si>
-  <si>
-    <t>SIDY MAHAMANE</t>
-  </si>
-  <si>
-    <t>TOURÉ</t>
-  </si>
-  <si>
-    <t>MAHAMOUDOU</t>
-  </si>
-  <si>
-    <t>KONÉ</t>
-  </si>
-  <si>
-    <t>IDRISSA DADYS</t>
-  </si>
-  <si>
-    <t>SIDIBÉ</t>
-  </si>
-  <si>
-    <t>ABOUBAKRINE</t>
-  </si>
-  <si>
-    <t>INTALLA</t>
-  </si>
-  <si>
-    <t>SEKOU SOULEYMANE</t>
-  </si>
-  <si>
-    <t>MAMADOU BAZAN</t>
-  </si>
-  <si>
-    <t>TOGOLA</t>
-  </si>
-  <si>
-    <t>DJIMÉ</t>
-  </si>
-  <si>
-    <t>KÉBÉ</t>
-  </si>
-  <si>
-    <t>MOULAYE MOHAMED</t>
-  </si>
-  <si>
-    <t>DICKO</t>
-  </si>
-  <si>
-    <t>HAROUNA</t>
-  </si>
-  <si>
-    <t>BACHIR</t>
-  </si>
-  <si>
-    <t>BASSIROU</t>
-  </si>
-  <si>
-    <t>HAIDARA</t>
-  </si>
-  <si>
-    <t>GUESSOUMA</t>
-  </si>
-  <si>
-    <t>PATRICK STÉPHANE</t>
-  </si>
-  <si>
-    <t>KAMDEM WAKAM</t>
-  </si>
-  <si>
-    <t>MALIK</t>
-  </si>
-  <si>
-    <t>DIARRA</t>
-  </si>
-  <si>
-    <t>IBRAHIM</t>
-  </si>
-  <si>
-    <t>ISSAKA</t>
-  </si>
-  <si>
-    <t>OUMAR</t>
-  </si>
-  <si>
-    <t>CISSÉ</t>
-  </si>
-  <si>
-    <t>ALMAMY</t>
-  </si>
-  <si>
-    <t>GUINDO</t>
-  </si>
-  <si>
-    <t>KOULBÉ</t>
-  </si>
-  <si>
-    <t>Tchad</t>
-  </si>
-  <si>
-    <t>Gabon</t>
-  </si>
-  <si>
-    <t>georgesarmel1@hotmail.fr</t>
-  </si>
-  <si>
-    <t>(581)849-3674</t>
-  </si>
-  <si>
-    <t>Georges armel Nguimbi</t>
-  </si>
-  <si>
-    <t>Cedrick essockamba</t>
-  </si>
-  <si>
-    <t>TAHA</t>
-  </si>
-  <si>
-    <t>ESSIBA</t>
-  </si>
-  <si>
-    <t>DIEUDONNÉ</t>
-  </si>
-  <si>
-    <t>CIZA</t>
-  </si>
-  <si>
-    <t>Rwanda</t>
-  </si>
-  <si>
-    <t>STEPHANE</t>
-  </si>
-  <si>
-    <t>PREDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada </t>
-  </si>
-  <si>
-    <t>CEDRIC</t>
-  </si>
-  <si>
-    <t>ESSOCKAMBA</t>
-  </si>
-  <si>
-    <t>JEAN-THERRY</t>
-  </si>
-  <si>
-    <t>YAMA</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>BAMBA</t>
-  </si>
-  <si>
-    <t>FARAJA</t>
-  </si>
-  <si>
-    <t>DIEU BENIT</t>
-  </si>
-  <si>
-    <t>SOUMAI</t>
-  </si>
-  <si>
-    <t>FEDSON</t>
-  </si>
-  <si>
-    <t>ROSIER</t>
-  </si>
-  <si>
-    <t>YANNICK</t>
-  </si>
-  <si>
-    <t>KAYILOU</t>
-  </si>
-  <si>
-    <t>ESTEBAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cote d'ivoire </t>
-  </si>
-  <si>
-    <t>JEAN DANIEL</t>
-  </si>
-  <si>
-    <t>POTTEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALEXANDRE </t>
-  </si>
-  <si>
-    <t>KOKORA</t>
-  </si>
-  <si>
-    <t>ABDELAZIZ</t>
-  </si>
-  <si>
-    <t>KAPATA</t>
-  </si>
-  <si>
-    <t>Centre-afrique</t>
-  </si>
-  <si>
-    <t>VINCENT</t>
-  </si>
-  <si>
-    <t>CORNEAU</t>
-  </si>
-  <si>
-    <t>DEMOYER</t>
-  </si>
-  <si>
-    <t>KOUASSI</t>
-  </si>
-  <si>
-    <t>BENONI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ÉMILE </t>
-  </si>
-  <si>
-    <t>DROLET</t>
-  </si>
-  <si>
-    <t>FRANCK NELSON</t>
-  </si>
-  <si>
-    <t>VOUFO</t>
-  </si>
-  <si>
-    <t>SAMUEL</t>
-  </si>
-  <si>
-    <t>POATY</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>POTE</t>
-  </si>
-  <si>
-    <t>ARGI</t>
-  </si>
-  <si>
-    <t>PASCAL</t>
-  </si>
-  <si>
-    <t>BIENVENUE</t>
-  </si>
-  <si>
-    <t>STANY</t>
-  </si>
-  <si>
-    <t>Burundi</t>
-  </si>
-  <si>
-    <t>MARC</t>
-  </si>
-  <si>
-    <t>ÉRISA</t>
-  </si>
-  <si>
-    <t>NSHIMIYIMANA</t>
-  </si>
-  <si>
-    <t>JUNIOR</t>
-  </si>
-  <si>
-    <t>POKOU</t>
-  </si>
-  <si>
-    <t>Cote d'ivoire</t>
-  </si>
-  <si>
-    <t>418-554-0364</t>
-  </si>
-  <si>
-    <t>ABDOUL-AZIZ</t>
-  </si>
-  <si>
-    <t>Hamidou Ouédraogo</t>
-  </si>
-  <si>
-    <t>FAAROOQ</t>
-  </si>
-  <si>
-    <t>CHEIK OMAR</t>
-  </si>
-  <si>
-    <t>BOUSSIM FADEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORESTE </t>
-  </si>
-  <si>
-    <t>TOMPOUDI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KANE </t>
-  </si>
-  <si>
-    <t>HAMED-TIDJANI</t>
-  </si>
-  <si>
-    <t>OUEDRAOGO</t>
-  </si>
-  <si>
-    <t>ABDOUL-FATAHOU</t>
-  </si>
-  <si>
-    <t>COMPAORÉ</t>
-  </si>
-  <si>
-    <t>YACOUBA</t>
-  </si>
-  <si>
-    <t>DARGA</t>
-  </si>
-  <si>
-    <t>RAOUF</t>
-  </si>
-  <si>
-    <t>KRIGAH</t>
-  </si>
-  <si>
-    <t>HANS</t>
-  </si>
-  <si>
-    <t>KOUAKOU</t>
-  </si>
-  <si>
-    <t>HAMIDOU</t>
-  </si>
-  <si>
-    <t>KEVIN ESPÉRAT</t>
-  </si>
-  <si>
-    <t>SAWADOGO</t>
-  </si>
-  <si>
-    <t>ABDOUL-HAKIM</t>
-  </si>
-  <si>
-    <t>BANCÉ</t>
-  </si>
-  <si>
-    <t>SIMPORE</t>
-  </si>
-  <si>
-    <t>ZONGO</t>
-  </si>
-  <si>
-    <t>ELVIS</t>
-  </si>
-  <si>
-    <t>KABORÉ</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>NDJIEUNDE</t>
-  </si>
-  <si>
-    <t>MAX ILDEVER WENDPOUIRÉ</t>
-  </si>
-  <si>
-    <t>SOUILI</t>
-  </si>
-  <si>
-    <t>CHATELAIN</t>
-  </si>
-  <si>
-    <t>YADJUI</t>
-  </si>
-  <si>
-    <t>SOUHOUDOU</t>
-  </si>
-  <si>
-    <t>MICHEL DONALD</t>
-  </si>
-  <si>
-    <t>MAT-JUNIOR</t>
-  </si>
-  <si>
-    <t>SOBJANG NDJATOU</t>
-  </si>
-  <si>
-    <t>LASSINA</t>
-  </si>
-  <si>
-    <t>WILFREID</t>
-  </si>
-  <si>
-    <t>KINDO</t>
-  </si>
-  <si>
-    <t>ASSAGOU</t>
-  </si>
-  <si>
-    <t>VÉRON</t>
-  </si>
-  <si>
-    <t>FAHMAN</t>
-  </si>
-  <si>
-    <t>GUIRO</t>
-  </si>
-  <si>
-    <t>NOM DE L'ÉQUIPE :GUINÉE 🇬🇳</t>
-  </si>
-  <si>
-    <t>ADRESSE  COURRIEL :aboubabacarpapikeita@gmail.com</t>
-  </si>
-  <si>
-    <t>TÉL D'URGENCE : 4182658413</t>
-  </si>
-  <si>
-    <t>NOM DU COACH : Frédérick</t>
-  </si>
-  <si>
-    <t>NOM DU CAPITAINE : Moustapha Donzo</t>
-  </si>
-  <si>
-    <t>BAH</t>
-  </si>
-  <si>
-    <t>Guinéen</t>
-  </si>
-  <si>
-    <t>SY SAVANÉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malien </t>
-  </si>
-  <si>
-    <t>THIERNO OUSMANE</t>
-  </si>
-  <si>
-    <t>SOW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guinée </t>
-  </si>
-  <si>
-    <t>NAZIF</t>
-  </si>
-  <si>
-    <t>AGBEDOH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Togolaise </t>
-  </si>
-  <si>
-    <t>ISMAEL</t>
-  </si>
-  <si>
-    <t>BARRY</t>
-  </si>
-  <si>
-    <t>Guinée</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guinéen </t>
-  </si>
-  <si>
-    <t>DIANÉ</t>
-  </si>
-  <si>
-    <t>ABOUBACAR</t>
-  </si>
-  <si>
-    <t>AKHYAR</t>
-  </si>
-  <si>
-    <t>Mauritanien</t>
-  </si>
-  <si>
-    <t>MOHAMED DAYE</t>
-  </si>
-  <si>
-    <t>KEBE</t>
-  </si>
-  <si>
-    <t>MALICK</t>
-  </si>
-  <si>
-    <t>TRAORE</t>
-  </si>
-  <si>
-    <t>DONZO</t>
-  </si>
-  <si>
-    <t>VICTOR</t>
-  </si>
-  <si>
-    <t>LENO</t>
-  </si>
-  <si>
-    <t>PIERRE DENIS</t>
-  </si>
-  <si>
-    <t>SAGNO</t>
-  </si>
-  <si>
-    <t>HAROU</t>
-  </si>
-  <si>
-    <t>THIERNO NOUHOU</t>
-  </si>
-  <si>
-    <t>ELHADJ OUSMANE</t>
-  </si>
-  <si>
-    <t>DIALLO</t>
-  </si>
-  <si>
-    <t>BERETE</t>
-  </si>
-  <si>
-    <t>MAMADY</t>
-  </si>
-  <si>
-    <t>DIANE</t>
-  </si>
-  <si>
-    <t>MAMADOU KINDY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEVE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DABIRÉ </t>
-  </si>
-  <si>
-    <t>AMADOU</t>
   </si>
   <si>
     <t>DARSY</t>
@@ -1701,7 +1710,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1829,6 +1838,11 @@
     </font>
     <font>
       <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Comic Sans MS"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
@@ -1875,7 +1889,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1916,6 +1930,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE7F9EF"/>
         <bgColor rgb="FFE7F9EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF00FF"/>
+        <bgColor rgb="FFFF00FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -2010,7 +2030,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="124">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2089,11 +2109,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2111,10 +2136,13 @@
     <xf borderId="1" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2144,17 +2172,17 @@
     <xf borderId="1" fillId="7" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="21" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="9" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2175,6 +2203,12 @@
     <xf borderId="0" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2184,7 +2218,7 @@
     <xf borderId="0" fillId="3" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="10" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2199,28 +2233,34 @@
     <xf borderId="1" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="10" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="11" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2232,38 +2272,44 @@
     <xf borderId="6" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="8" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
@@ -2271,14 +2317,14 @@
     <xf borderId="1" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2294,7 +2340,7 @@
     <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2312,17 +2358,14 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -2859,7 +2902,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2882,7 +2925,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2894,7 +2937,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2906,7 +2949,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -2918,7 +2961,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2939,10 +2982,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="38" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -2992,26 +3035,26 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="68">
+      <c r="A8" s="72">
         <v>1.0</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="69" t="s">
-        <v>359</v>
-      </c>
-      <c r="E8" s="69" t="s">
-        <v>506</v>
-      </c>
-      <c r="F8" s="39">
+      <c r="D8" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="73" t="s">
+        <v>509</v>
+      </c>
+      <c r="F8" s="40">
         <v>26.0</v>
       </c>
-      <c r="G8" s="40" t="s">
-        <v>507</v>
+      <c r="G8" s="41" t="s">
+        <v>510</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -3028,26 +3071,26 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="70">
+      <c r="A9" s="74">
         <v>2.0</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="73" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="69" t="s">
-        <v>508</v>
-      </c>
-      <c r="F9" s="108">
+      <c r="E9" s="73" t="s">
+        <v>511</v>
+      </c>
+      <c r="F9" s="116">
         <v>22.0</v>
       </c>
-      <c r="G9" s="109" t="s">
-        <v>509</v>
+      <c r="G9" s="117" t="s">
+        <v>512</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -3064,7 +3107,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="68">
+      <c r="A10" s="72">
         <v>3.0</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -3073,17 +3116,17 @@
       <c r="C10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="69" t="s">
-        <v>510</v>
-      </c>
-      <c r="E10" s="69" t="s">
-        <v>511</v>
-      </c>
-      <c r="F10" s="108">
+      <c r="D10" s="73" t="s">
+        <v>513</v>
+      </c>
+      <c r="E10" s="73" t="s">
+        <v>514</v>
+      </c>
+      <c r="F10" s="116">
         <v>30.0</v>
       </c>
-      <c r="G10" s="109" t="s">
-        <v>512</v>
+      <c r="G10" s="117" t="s">
+        <v>515</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -3100,26 +3143,26 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="68">
+      <c r="A11" s="72">
         <v>4.0</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="109" t="s">
+      <c r="C11" s="117" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="69" t="s">
-        <v>513</v>
-      </c>
-      <c r="E11" s="69" t="s">
-        <v>514</v>
-      </c>
-      <c r="F11" s="108">
+      <c r="D11" s="73" t="s">
+        <v>516</v>
+      </c>
+      <c r="E11" s="73" t="s">
+        <v>517</v>
+      </c>
+      <c r="F11" s="116">
         <v>25.0</v>
       </c>
-      <c r="G11" s="109" t="s">
-        <v>515</v>
+      <c r="G11" s="117" t="s">
+        <v>518</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11" s="29"/>
@@ -3136,24 +3179,24 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="68">
+      <c r="A12" s="72">
         <v>5.0</v>
       </c>
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="109" t="s">
+      <c r="C12" s="117" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="69" t="s">
-        <v>516</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>517</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40" t="s">
-        <v>518</v>
+      <c r="D12" s="73" t="s">
+        <v>519</v>
+      </c>
+      <c r="E12" s="73" t="s">
+        <v>520</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41" t="s">
+        <v>521</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -3170,26 +3213,26 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="68">
+      <c r="A13" s="72">
         <v>6.0</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="109" t="s">
+      <c r="C13" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="69" t="s">
-        <v>389</v>
-      </c>
-      <c r="E13" s="69" t="s">
-        <v>519</v>
-      </c>
-      <c r="F13" s="108">
+      <c r="D13" s="73" t="s">
+        <v>394</v>
+      </c>
+      <c r="E13" s="73" t="s">
+        <v>522</v>
+      </c>
+      <c r="F13" s="116">
         <v>25.0</v>
       </c>
-      <c r="G13" s="109" t="s">
-        <v>520</v>
+      <c r="G13" s="117" t="s">
+        <v>523</v>
       </c>
       <c r="H13" s="28"/>
       <c r="I13" s="29"/>
@@ -3206,26 +3249,26 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="68">
+      <c r="A14" s="72">
         <v>7.0</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="109" t="s">
+      <c r="C14" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="69" t="s">
-        <v>389</v>
-      </c>
-      <c r="E14" s="69" t="s">
-        <v>521</v>
-      </c>
-      <c r="F14" s="108">
+      <c r="D14" s="73" t="s">
+        <v>394</v>
+      </c>
+      <c r="E14" s="73" t="s">
+        <v>524</v>
+      </c>
+      <c r="F14" s="116">
         <v>30.0</v>
       </c>
-      <c r="G14" s="109" t="s">
-        <v>520</v>
+      <c r="G14" s="117" t="s">
+        <v>523</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
@@ -3242,7 +3285,7 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="68">
+      <c r="A15" s="72">
         <v>8.0</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3251,17 +3294,17 @@
       <c r="C15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="69" t="s">
+      <c r="D15" s="73" t="s">
+        <v>525</v>
+      </c>
+      <c r="E15" s="73" t="s">
         <v>522</v>
       </c>
-      <c r="E15" s="69" t="s">
-        <v>519</v>
-      </c>
-      <c r="F15" s="108">
+      <c r="F15" s="116">
         <v>22.0</v>
       </c>
-      <c r="G15" s="109" t="s">
-        <v>520</v>
+      <c r="G15" s="117" t="s">
+        <v>523</v>
       </c>
       <c r="H15" s="28"/>
       <c r="I15" s="29"/>
@@ -3278,24 +3321,24 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="68">
+      <c r="A16" s="72">
         <v>9.0</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="69" t="s">
-        <v>358</v>
-      </c>
-      <c r="E16" s="69" t="s">
-        <v>523</v>
-      </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40" t="s">
-        <v>524</v>
+      <c r="D16" s="73" t="s">
+        <v>363</v>
+      </c>
+      <c r="E16" s="73" t="s">
+        <v>526</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41" t="s">
+        <v>527</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -3312,26 +3355,26 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="70">
+      <c r="A17" s="74">
         <v>10.0</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="109" t="s">
+      <c r="C17" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="69" t="s">
-        <v>525</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>526</v>
-      </c>
-      <c r="F17" s="108">
+      <c r="D17" s="73" t="s">
+        <v>528</v>
+      </c>
+      <c r="E17" s="73" t="s">
+        <v>529</v>
+      </c>
+      <c r="F17" s="116">
         <v>27.0</v>
       </c>
-      <c r="G17" s="109" t="s">
-        <v>512</v>
+      <c r="G17" s="117" t="s">
+        <v>515</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
@@ -3348,26 +3391,26 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="68">
+      <c r="A18" s="72">
         <v>11.0</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="109" t="s">
+      <c r="C18" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="69" t="s">
-        <v>527</v>
-      </c>
-      <c r="E18" s="69" t="s">
-        <v>528</v>
-      </c>
-      <c r="F18" s="108">
+      <c r="D18" s="73" t="s">
+        <v>530</v>
+      </c>
+      <c r="E18" s="73" t="s">
+        <v>531</v>
+      </c>
+      <c r="F18" s="116">
         <v>23.0</v>
       </c>
-      <c r="G18" s="109" t="s">
-        <v>520</v>
+      <c r="G18" s="117" t="s">
+        <v>523</v>
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
@@ -3384,26 +3427,26 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="70">
+      <c r="A19" s="74">
         <v>12.0</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="109" t="s">
+      <c r="C19" s="117" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E19" s="69" t="s">
-        <v>529</v>
-      </c>
-      <c r="F19" s="108">
+      <c r="D19" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" s="73" t="s">
+        <v>532</v>
+      </c>
+      <c r="F19" s="116">
         <v>30.0</v>
       </c>
-      <c r="G19" s="109" t="s">
-        <v>512</v>
+      <c r="G19" s="117" t="s">
+        <v>515</v>
       </c>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
@@ -3420,24 +3463,24 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="70">
+      <c r="A20" s="74">
         <v>13.0</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="109" t="s">
+      <c r="C20" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="69" t="s">
-        <v>530</v>
-      </c>
-      <c r="E20" s="69" t="s">
-        <v>531</v>
+      <c r="D20" s="73" t="s">
+        <v>533</v>
+      </c>
+      <c r="E20" s="73" t="s">
+        <v>534</v>
       </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="109" t="s">
-        <v>520</v>
+      <c r="G20" s="117" t="s">
+        <v>523</v>
       </c>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
@@ -3454,26 +3497,26 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="70">
+      <c r="A21" s="74">
         <v>14.0</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="109" t="s">
+      <c r="C21" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="69" t="s">
-        <v>532</v>
-      </c>
-      <c r="E21" s="69" t="s">
-        <v>533</v>
-      </c>
-      <c r="F21" s="108">
+      <c r="D21" s="73" t="s">
+        <v>535</v>
+      </c>
+      <c r="E21" s="73" t="s">
+        <v>536</v>
+      </c>
+      <c r="F21" s="116">
         <v>18.0</v>
       </c>
-      <c r="G21" s="109" t="s">
-        <v>518</v>
+      <c r="G21" s="117" t="s">
+        <v>521</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -3490,26 +3533,26 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="68">
+      <c r="A22" s="72">
         <v>15.0</v>
       </c>
-      <c r="B22" s="110" t="s">
+      <c r="B22" s="118" t="s">
         <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="69" t="s">
-        <v>358</v>
-      </c>
-      <c r="E22" s="69" t="s">
-        <v>534</v>
-      </c>
-      <c r="F22" s="108">
+      <c r="D22" s="73" t="s">
+        <v>363</v>
+      </c>
+      <c r="E22" s="73" t="s">
+        <v>537</v>
+      </c>
+      <c r="F22" s="116">
         <v>23.0</v>
       </c>
-      <c r="G22" s="109" t="s">
-        <v>520</v>
+      <c r="G22" s="117" t="s">
+        <v>523</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -3526,26 +3569,26 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="70">
+      <c r="A23" s="74">
         <v>16.0</v>
       </c>
-      <c r="B23" s="110" t="s">
+      <c r="B23" s="118" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="109" t="s">
+      <c r="C23" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="69" t="s">
-        <v>535</v>
-      </c>
-      <c r="E23" s="69" t="s">
-        <v>511</v>
-      </c>
-      <c r="F23" s="108">
+      <c r="D23" s="73" t="s">
+        <v>538</v>
+      </c>
+      <c r="E23" s="73" t="s">
+        <v>514</v>
+      </c>
+      <c r="F23" s="116">
         <v>22.0</v>
       </c>
-      <c r="G23" s="109" t="s">
-        <v>520</v>
+      <c r="G23" s="117" t="s">
+        <v>523</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -3562,26 +3605,26 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="111">
+      <c r="A24" s="119">
         <v>17.0</v>
       </c>
-      <c r="B24" s="112" t="s">
+      <c r="B24" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="113" t="s">
+      <c r="C24" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="114" t="s">
-        <v>536</v>
-      </c>
-      <c r="E24" s="114" t="s">
-        <v>537</v>
-      </c>
-      <c r="F24" s="108">
+      <c r="D24" s="82" t="s">
+        <v>539</v>
+      </c>
+      <c r="E24" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="F24" s="116">
         <v>30.0</v>
       </c>
-      <c r="G24" s="109" t="s">
-        <v>512</v>
+      <c r="G24" s="117" t="s">
+        <v>515</v>
       </c>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
@@ -3598,26 +3641,26 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="68">
+      <c r="A25" s="72">
         <v>18.0</v>
       </c>
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="109" t="s">
+      <c r="C25" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="69" t="s">
-        <v>353</v>
-      </c>
-      <c r="E25" s="69" t="s">
-        <v>538</v>
-      </c>
-      <c r="F25" s="108">
+      <c r="D25" s="73" t="s">
+        <v>358</v>
+      </c>
+      <c r="E25" s="73" t="s">
+        <v>540</v>
+      </c>
+      <c r="F25" s="116">
         <v>19.0</v>
       </c>
-      <c r="G25" s="109" t="s">
-        <v>520</v>
+      <c r="G25" s="117" t="s">
+        <v>523</v>
       </c>
       <c r="H25" s="28"/>
       <c r="I25" s="29"/>
@@ -3634,24 +3677,24 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="70">
+      <c r="A26" s="74">
         <v>19.0</v>
       </c>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="109" t="s">
+      <c r="C26" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="69" t="s">
-        <v>539</v>
-      </c>
-      <c r="E26" s="69" t="s">
-        <v>540</v>
-      </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40" t="s">
-        <v>518</v>
+      <c r="D26" s="73" t="s">
+        <v>541</v>
+      </c>
+      <c r="E26" s="73" t="s">
+        <v>542</v>
+      </c>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41" t="s">
+        <v>521</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="32"/>
@@ -3668,26 +3711,26 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="70">
+      <c r="A27" s="74">
         <v>20.0</v>
       </c>
-      <c r="B27" s="69" t="s">
+      <c r="B27" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="109" t="s">
+      <c r="C27" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="69" t="s">
-        <v>541</v>
-      </c>
-      <c r="E27" s="69" t="s">
-        <v>537</v>
-      </c>
-      <c r="F27" s="108">
+      <c r="D27" s="73" t="s">
+        <v>543</v>
+      </c>
+      <c r="E27" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="F27" s="116">
         <v>22.0</v>
       </c>
-      <c r="G27" s="109" t="s">
-        <v>518</v>
+      <c r="G27" s="117" t="s">
+        <v>521</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -3704,62 +3747,62 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="111">
+      <c r="A28" s="119">
         <v>21.0</v>
       </c>
-      <c r="B28" s="112" t="s">
+      <c r="B28" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="113" t="s">
+      <c r="C28" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="114" t="s">
-        <v>542</v>
-      </c>
-      <c r="E28" s="114" t="s">
-        <v>543</v>
-      </c>
-      <c r="F28" s="94">
+      <c r="D28" s="82" t="s">
+        <v>544</v>
+      </c>
+      <c r="E28" s="82" t="s">
+        <v>545</v>
+      </c>
+      <c r="F28" s="102">
         <v>23.0</v>
       </c>
-      <c r="G28" s="95" t="s">
-        <v>518</v>
-      </c>
-      <c r="H28" s="62"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="63"/>
-      <c r="M28" s="63"/>
-      <c r="N28" s="63"/>
-      <c r="O28" s="63"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="62">
+      <c r="G28" s="103" t="s">
+        <v>521</v>
+      </c>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="65"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="70">
+      <c r="A29" s="74">
         <v>22.0</v>
       </c>
-      <c r="B29" s="69" t="s">
+      <c r="B29" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="69" t="s">
-        <v>544</v>
-      </c>
-      <c r="E29" s="69" t="s">
-        <v>224</v>
-      </c>
-      <c r="F29" s="39">
+      <c r="D29" s="73" t="s">
+        <v>546</v>
+      </c>
+      <c r="E29" s="73" t="s">
+        <v>547</v>
+      </c>
+      <c r="F29" s="40">
         <v>22.0</v>
       </c>
-      <c r="G29" s="40" t="s">
-        <v>518</v>
+      <c r="G29" s="41" t="s">
+        <v>521</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -3776,26 +3819,26 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="70">
+      <c r="A30" s="74">
         <v>23.0</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="109" t="s">
+      <c r="C30" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="69" t="s">
-        <v>545</v>
-      </c>
-      <c r="E30" s="69" t="s">
-        <v>546</v>
-      </c>
-      <c r="F30" s="108">
+      <c r="D30" s="73" t="s">
+        <v>548</v>
+      </c>
+      <c r="E30" s="73" t="s">
+        <v>549</v>
+      </c>
+      <c r="F30" s="116">
         <v>21.0</v>
       </c>
-      <c r="G30" s="109" t="s">
-        <v>547</v>
+      <c r="G30" s="117" t="s">
+        <v>550</v>
       </c>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
@@ -3812,26 +3855,26 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="70">
+      <c r="A31" s="74">
         <v>24.0</v>
       </c>
-      <c r="B31" s="69" t="s">
+      <c r="B31" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="69" t="s">
-        <v>548</v>
-      </c>
-      <c r="E31" s="69" t="s">
-        <v>511</v>
-      </c>
-      <c r="F31" s="39">
+      <c r="D31" s="73" t="s">
+        <v>551</v>
+      </c>
+      <c r="E31" s="73" t="s">
+        <v>514</v>
+      </c>
+      <c r="F31" s="40">
         <v>30.0</v>
       </c>
-      <c r="G31" s="40" t="s">
-        <v>507</v>
+      <c r="G31" s="41" t="s">
+        <v>510</v>
       </c>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
@@ -3848,60 +3891,60 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="70">
+      <c r="A32" s="74">
         <v>25.0</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="109" t="s">
+      <c r="C32" s="117" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="69" t="s">
-        <v>549</v>
-      </c>
-      <c r="E32" s="69" t="s">
-        <v>550</v>
-      </c>
-      <c r="F32" s="115">
+      <c r="D32" s="73" t="s">
+        <v>552</v>
+      </c>
+      <c r="E32" s="73" t="s">
+        <v>553</v>
+      </c>
+      <c r="F32" s="122">
         <v>23.0</v>
       </c>
-      <c r="G32" s="116" t="s">
-        <v>551</v>
-      </c>
-      <c r="H32" s="62"/>
-      <c r="I32" s="63"/>
-      <c r="J32" s="63"/>
-      <c r="K32" s="63"/>
-      <c r="L32" s="63"/>
-      <c r="M32" s="63"/>
-      <c r="N32" s="63"/>
-      <c r="O32" s="63"/>
-      <c r="P32" s="63"/>
-      <c r="Q32" s="62">
+      <c r="G32" s="123" t="s">
+        <v>554</v>
+      </c>
+      <c r="H32" s="64"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="65"/>
+      <c r="L32" s="65"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="65"/>
+      <c r="O32" s="65"/>
+      <c r="P32" s="65"/>
+      <c r="Q32" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="70">
+      <c r="A33" s="74">
         <v>26.0</v>
       </c>
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="69" t="s">
-        <v>552</v>
-      </c>
-      <c r="E33" s="69" t="s">
-        <v>528</v>
+      <c r="D33" s="73" t="s">
+        <v>555</v>
+      </c>
+      <c r="E33" s="73" t="s">
+        <v>531</v>
       </c>
       <c r="F33" s="3"/>
-      <c r="G33" s="109" t="s">
-        <v>518</v>
+      <c r="G33" s="117" t="s">
+        <v>521</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -4271,10 +4314,10 @@
       <c r="C11" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="34" t="s">
         <v>81</v>
       </c>
       <c r="F11" s="26"/>
@@ -4419,10 +4462,10 @@
       <c r="C15" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="35" t="s">
         <v>93</v>
       </c>
       <c r="F15" s="26"/>
@@ -4641,10 +4684,10 @@
       <c r="C21" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="37" t="s">
         <v>109</v>
       </c>
       <c r="F21" s="26"/>
@@ -4863,10 +4906,10 @@
       <c r="C27" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="E27" s="34" t="s">
         <v>122</v>
       </c>
       <c r="F27" s="26"/>
@@ -4937,10 +4980,10 @@
       <c r="C29" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="E29" s="34" t="s">
         <v>126</v>
       </c>
       <c r="F29" s="26"/>
@@ -5250,10 +5293,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="38" t="s">
         <v>140</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -5312,14 +5355,14 @@
       <c r="C8" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="39" t="s">
         <v>141</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -5350,8 +5393,8 @@
       <c r="E9" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -5382,8 +5425,8 @@
       <c r="E10" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -5414,8 +5457,8 @@
       <c r="E11" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -5446,8 +5489,8 @@
       <c r="E12" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -5478,8 +5521,8 @@
       <c r="E13" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -5510,8 +5553,8 @@
       <c r="E14" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="F14" s="39"/>
-      <c r="G14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -5542,8 +5585,8 @@
       <c r="E15" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -5559,7 +5602,7 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="41">
+      <c r="A16" s="42">
         <v>9.0</v>
       </c>
       <c r="B16" s="23" t="s">
@@ -5568,14 +5611,14 @@
       <c r="C16" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
       <c r="H16" s="31"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
@@ -5606,8 +5649,8 @@
       <c r="E17" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -5638,8 +5681,8 @@
       <c r="E18" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="41"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -5670,8 +5713,8 @@
       <c r="E19" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="41"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -5699,11 +5742,11 @@
       <c r="D20" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -5734,8 +5777,8 @@
       <c r="E21" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -5766,8 +5809,8 @@
       <c r="E22" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="41"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -5789,11 +5832,17 @@
       <c r="B23" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
+      <c r="C23" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="40"/>
+      <c r="G23" s="41"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -5819,13 +5868,13 @@
         <v>76</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
+        <v>170</v>
+      </c>
+      <c r="F24" s="40"/>
+      <c r="G24" s="41"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -5851,13 +5900,13 @@
         <v>94</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
+        <v>172</v>
+      </c>
+      <c r="F25" s="40"/>
+      <c r="G25" s="41"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -5883,13 +5932,13 @@
         <v>94</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40"/>
+        <v>174</v>
+      </c>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -5905,7 +5954,7 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="44">
+      <c r="A27" s="46">
         <v>20.0</v>
       </c>
       <c r="B27" s="23" t="s">
@@ -5915,13 +5964,13 @@
         <v>94</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
+        <v>176</v>
+      </c>
+      <c r="F27" s="40"/>
+      <c r="G27" s="41"/>
       <c r="H27" s="28"/>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
@@ -5947,13 +5996,13 @@
         <v>86</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E28" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -5979,13 +6028,13 @@
         <v>94</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
+        <v>178</v>
+      </c>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -6011,13 +6060,13 @@
         <v>76</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E30" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="41"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -6042,14 +6091,14 @@
       <c r="C31" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="E31" s="42" t="s">
-        <v>179</v>
-      </c>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40"/>
+      <c r="D31" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" s="40"/>
+      <c r="G31" s="41"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -6075,13 +6124,13 @@
         <v>86</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
+        <v>183</v>
+      </c>
+      <c r="F32" s="40"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -6103,11 +6152,17 @@
       <c r="B33" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
+      <c r="C33" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -6186,7 +6241,7 @@
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="6"/>
@@ -6211,7 +6266,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="11" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
@@ -6225,7 +6280,7 @@
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
       <c r="E3" s="11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -6239,7 +6294,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -6253,7 +6308,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="11" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -6270,13 +6325,13 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="47" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="20" t="s">
@@ -6323,24 +6378,24 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="46">
+      <c r="A8" s="48">
         <v>1.0</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="E8" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51" t="s">
-        <v>189</v>
+      <c r="D8" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" s="52"/>
+      <c r="G8" s="53" t="s">
+        <v>193</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -6357,24 +6412,24 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="52">
+      <c r="A9" s="54">
         <v>2.0</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>191</v>
-      </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54" t="s">
-        <v>182</v>
+      <c r="D9" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56" t="s">
+        <v>186</v>
       </c>
       <c r="H9" s="28"/>
       <c r="I9" s="29"/>
@@ -6391,24 +6446,24 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="52">
+      <c r="A10" s="54">
         <v>3.0</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="53" t="s">
-        <v>192</v>
-      </c>
-      <c r="E10" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="51" t="s">
-        <v>182</v>
+      <c r="D10" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>197</v>
+      </c>
+      <c r="F10" s="52"/>
+      <c r="G10" s="53" t="s">
+        <v>186</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -6425,24 +6480,24 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="46">
+      <c r="A11" s="48">
         <v>4.0</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="E11" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="F11" s="55"/>
-      <c r="G11" s="54" t="s">
-        <v>182</v>
+      <c r="D11" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="F11" s="57"/>
+      <c r="G11" s="56" t="s">
+        <v>186</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
@@ -6459,24 +6514,24 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="46">
+      <c r="A12" s="48">
         <v>5.0</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="51" t="s">
-        <v>182</v>
+      <c r="D12" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="F12" s="52"/>
+      <c r="G12" s="53" t="s">
+        <v>186</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -6493,23 +6548,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="46">
+      <c r="A13" s="48">
         <v>6.0</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="E13" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="F13" s="55"/>
-      <c r="G13" s="54" t="s">
+      <c r="D13" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="F13" s="57"/>
+      <c r="G13" s="56" t="s">
         <v>119</v>
       </c>
       <c r="H13" s="31"/>
@@ -6527,24 +6582,24 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="52">
+      <c r="A14" s="54">
         <v>7.0</v>
       </c>
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="53" t="s">
-        <v>200</v>
-      </c>
-      <c r="E14" s="53" t="s">
-        <v>201</v>
-      </c>
-      <c r="F14" s="55"/>
-      <c r="G14" s="54" t="s">
-        <v>182</v>
+      <c r="D14" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="F14" s="57"/>
+      <c r="G14" s="56" t="s">
+        <v>186</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="32"/>
@@ -6561,24 +6616,24 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="46">
+      <c r="A15" s="48">
         <v>8.0</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="E15" s="49" t="s">
-        <v>203</v>
-      </c>
-      <c r="F15" s="55"/>
-      <c r="G15" s="54" t="s">
-        <v>182</v>
+      <c r="D15" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="F15" s="57"/>
+      <c r="G15" s="56" t="s">
+        <v>186</v>
       </c>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
@@ -6595,24 +6650,24 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="46">
+      <c r="A16" s="48">
         <v>9.0</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="E16" s="49" t="s">
-        <v>205</v>
-      </c>
-      <c r="F16" s="56"/>
-      <c r="G16" s="57" t="s">
-        <v>182</v>
+      <c r="D16" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="51" t="s">
+        <v>209</v>
+      </c>
+      <c r="F16" s="58"/>
+      <c r="G16" s="59" t="s">
+        <v>186</v>
       </c>
       <c r="H16" s="31"/>
       <c r="I16" s="32"/>
@@ -6629,24 +6684,24 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="46">
+      <c r="A17" s="48">
         <v>10.0</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="E17" s="49" t="s">
-        <v>207</v>
-      </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="51" t="s">
-        <v>182</v>
+      <c r="D17" s="51" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="F17" s="52"/>
+      <c r="G17" s="53" t="s">
+        <v>186</v>
       </c>
       <c r="H17" s="28"/>
       <c r="I17" s="29"/>
@@ -6663,24 +6718,24 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="58">
+      <c r="A18" s="60">
         <v>11.0</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="53" t="s">
-        <v>208</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="F18" s="50"/>
-      <c r="G18" s="51" t="s">
-        <v>182</v>
+      <c r="D18" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="E18" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="F18" s="52"/>
+      <c r="G18" s="53" t="s">
+        <v>186</v>
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
@@ -6697,24 +6752,24 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="46">
+      <c r="A19" s="48">
         <v>12.0</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="49" t="s">
-        <v>210</v>
-      </c>
-      <c r="E19" s="49" t="s">
-        <v>211</v>
-      </c>
-      <c r="F19" s="50"/>
-      <c r="G19" s="51" t="s">
-        <v>182</v>
+      <c r="D19" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="F19" s="52"/>
+      <c r="G19" s="53" t="s">
+        <v>186</v>
       </c>
       <c r="H19" s="28"/>
       <c r="I19" s="29"/>
@@ -6731,24 +6786,24 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="59">
+      <c r="A20" s="61">
         <v>13.0</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="49" t="s">
-        <v>212</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>213</v>
-      </c>
-      <c r="F20" s="50"/>
-      <c r="G20" s="51" t="s">
-        <v>182</v>
+      <c r="D20" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="F20" s="52"/>
+      <c r="G20" s="53" t="s">
+        <v>186</v>
       </c>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
@@ -6765,58 +6820,58 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="58">
+      <c r="A21" s="60">
         <v>14.0</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="53" t="s">
-        <v>214</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>215</v>
-      </c>
-      <c r="F21" s="60"/>
-      <c r="G21" s="61" t="s">
-        <v>182</v>
-      </c>
-      <c r="H21" s="62"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="63"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="63"/>
-      <c r="M21" s="63"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="63"/>
-      <c r="P21" s="63"/>
-      <c r="Q21" s="62">
+      <c r="D21" s="55" t="s">
+        <v>218</v>
+      </c>
+      <c r="E21" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="F21" s="62"/>
+      <c r="G21" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="52">
+      <c r="A22" s="54">
         <v>15.0</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="53" t="s">
-        <v>216</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>217</v>
-      </c>
-      <c r="F22" s="55"/>
-      <c r="G22" s="54" t="s">
-        <v>182</v>
+      <c r="D22" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="E22" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="F22" s="57"/>
+      <c r="G22" s="56" t="s">
+        <v>186</v>
       </c>
       <c r="H22" s="31"/>
       <c r="I22" s="32"/>
@@ -6833,24 +6888,24 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="46">
+      <c r="A23" s="48">
         <v>16.0</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="49" t="s">
-        <v>218</v>
-      </c>
-      <c r="E23" s="49" t="s">
-        <v>219</v>
-      </c>
-      <c r="F23" s="55"/>
-      <c r="G23" s="54" t="s">
-        <v>182</v>
+      <c r="D23" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="F23" s="57"/>
+      <c r="G23" s="56" t="s">
+        <v>186</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -6867,24 +6922,24 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="58">
+      <c r="A24" s="60">
         <v>17.0</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="53" t="s">
+      <c r="D24" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="E24" s="53" t="s">
-        <v>220</v>
-      </c>
-      <c r="F24" s="50"/>
-      <c r="G24" s="51" t="s">
-        <v>182</v>
+      <c r="E24" s="55" t="s">
+        <v>224</v>
+      </c>
+      <c r="F24" s="52"/>
+      <c r="G24" s="53" t="s">
+        <v>186</v>
       </c>
       <c r="H24" s="31"/>
       <c r="I24" s="32"/>
@@ -6901,24 +6956,24 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="59">
+      <c r="A25" s="61">
         <v>18.0</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="48" t="s">
+      <c r="C25" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="E25" s="49" t="s">
-        <v>222</v>
-      </c>
-      <c r="F25" s="55"/>
-      <c r="G25" s="54" t="s">
-        <v>182</v>
+      <c r="D25" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="F25" s="57"/>
+      <c r="G25" s="56" t="s">
+        <v>186</v>
       </c>
       <c r="H25" s="28"/>
       <c r="I25" s="29"/>
@@ -6935,24 +6990,24 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="59">
+      <c r="A26" s="61">
         <v>19.0</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="48" t="s">
+      <c r="C26" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="49" t="s">
-        <v>223</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>224</v>
-      </c>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51" t="s">
-        <v>225</v>
+      <c r="D26" s="67" t="s">
+        <v>227</v>
+      </c>
+      <c r="E26" s="67" t="s">
+        <v>228</v>
+      </c>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53" t="s">
+        <v>229</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="32"/>
@@ -6969,24 +7024,24 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="46">
+      <c r="A27" s="48">
         <v>20.0</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="48" t="s">
+      <c r="C27" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="49" t="s">
-        <v>226</v>
-      </c>
-      <c r="E27" s="49" t="s">
-        <v>227</v>
-      </c>
-      <c r="F27" s="50"/>
-      <c r="G27" s="51" t="s">
-        <v>182</v>
+      <c r="D27" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>231</v>
+      </c>
+      <c r="F27" s="52"/>
+      <c r="G27" s="53" t="s">
+        <v>186</v>
       </c>
       <c r="H27" s="28"/>
       <c r="I27" s="29"/>
@@ -7003,23 +7058,23 @@
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
-      <c r="A28" s="52">
+      <c r="A28" s="54">
         <v>21.0</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="48" t="s">
+      <c r="C28" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="53" t="s">
-        <v>228</v>
-      </c>
-      <c r="E28" s="53" t="s">
-        <v>229</v>
-      </c>
-      <c r="F28" s="64"/>
-      <c r="G28" s="57"/>
+      <c r="D28" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="E28" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="F28" s="68"/>
+      <c r="G28" s="59"/>
       <c r="H28" s="31"/>
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
@@ -7032,24 +7087,24 @@
       <c r="Q28" s="31"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="59">
+      <c r="A29" s="61">
         <v>22.0</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="48" t="s">
+      <c r="C29" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="49" t="s">
-        <v>230</v>
-      </c>
-      <c r="E29" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="57" t="s">
-        <v>232</v>
+      <c r="D29" s="51" t="s">
+        <v>234</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="F29" s="68"/>
+      <c r="G29" s="59" t="s">
+        <v>236</v>
       </c>
       <c r="H29" s="28"/>
       <c r="I29" s="29"/>
@@ -7066,23 +7121,23 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="58">
+      <c r="A30" s="60">
         <v>23.0</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="E30" s="53" t="s">
-        <v>234</v>
-      </c>
-      <c r="F30" s="64"/>
-      <c r="G30" s="57"/>
+      <c r="D30" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="E30" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="F30" s="68"/>
+      <c r="G30" s="59"/>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
@@ -7098,23 +7153,23 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="59">
+      <c r="A31" s="61">
         <v>24.0</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="C31" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="49" t="s">
-        <v>235</v>
-      </c>
-      <c r="E31" s="49" t="s">
-        <v>236</v>
-      </c>
-      <c r="F31" s="64"/>
-      <c r="G31" s="57"/>
+      <c r="D31" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="F31" s="68"/>
+      <c r="G31" s="59"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
       <c r="J31" s="29"/>
@@ -7130,23 +7185,23 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="59">
+      <c r="A32" s="61">
         <v>25.0</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="48" t="s">
+      <c r="C32" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="E32" s="49" t="s">
-        <v>238</v>
-      </c>
-      <c r="F32" s="64"/>
-      <c r="G32" s="57"/>
+      <c r="D32" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="F32" s="68"/>
+      <c r="G32" s="59"/>
       <c r="H32" s="31"/>
       <c r="I32" s="32"/>
       <c r="J32" s="32"/>
@@ -7162,24 +7217,24 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="46">
+      <c r="A33" s="48">
         <v>26.0</v>
       </c>
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="65" t="s">
-        <v>239</v>
-      </c>
-      <c r="E33" s="49" t="s">
-        <v>240</v>
-      </c>
-      <c r="F33" s="55"/>
-      <c r="G33" s="54" t="s">
-        <v>182</v>
+      <c r="D33" s="69" t="s">
+        <v>243</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>244</v>
+      </c>
+      <c r="F33" s="57"/>
+      <c r="G33" s="56" t="s">
+        <v>186</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -7196,13 +7251,13 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="59"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="66"/>
-      <c r="G34" s="67"/>
+      <c r="A34" s="61"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="71"/>
       <c r="H34" s="31"/>
       <c r="I34" s="32"/>
       <c r="J34" s="32"/>
@@ -7262,7 +7317,7 @@
     <col customWidth="1" hidden="1" min="2" max="2" width="11.75"/>
     <col customWidth="1" hidden="1" min="3" max="3" width="15.25"/>
     <col customWidth="1" min="4" max="4" width="13.5"/>
-    <col customWidth="1" min="5" max="5" width="19.88"/>
+    <col customWidth="1" min="5" max="5" width="26.75"/>
     <col customWidth="1" hidden="1" min="6" max="6" width="16.75"/>
     <col customWidth="1" hidden="1" min="7" max="7" width="16.63"/>
     <col customWidth="1" hidden="1" min="8" max="8" width="7.88"/>
@@ -7352,10 +7407,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="38" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -7405,23 +7460,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="68">
+      <c r="A8" s="72">
         <v>1.0</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="69" t="s">
-        <v>241</v>
-      </c>
-      <c r="E8" s="69" t="s">
-        <v>242</v>
-      </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="D8" s="73" t="s">
+        <v>245</v>
+      </c>
+      <c r="E8" s="73" t="s">
+        <v>246</v>
+      </c>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -7437,21 +7492,21 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="70">
+      <c r="A9" s="74">
         <v>2.0</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="69" t="s">
-        <v>243</v>
-      </c>
-      <c r="E9" s="69" t="s">
-        <v>244</v>
-      </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="73" t="s">
+        <v>247</v>
+      </c>
+      <c r="E9" s="73" t="s">
+        <v>248</v>
+      </c>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -7467,21 +7522,21 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="68">
+      <c r="A10" s="72">
         <v>3.0</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="69" t="s">
-        <v>245</v>
-      </c>
-      <c r="E10" s="69" t="s">
-        <v>246</v>
-      </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="73" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" s="73" t="s">
+        <v>250</v>
+      </c>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -7497,21 +7552,21 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="70">
+      <c r="A11" s="74">
         <v>4.0</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="69" t="s">
-        <v>247</v>
-      </c>
-      <c r="E11" s="69" t="s">
-        <v>248</v>
-      </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="73" t="s">
+        <v>251</v>
+      </c>
+      <c r="E11" s="73" t="s">
+        <v>252</v>
+      </c>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -7527,21 +7582,21 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="68">
+      <c r="A12" s="72">
         <v>5.0</v>
       </c>
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="69" t="s">
-        <v>249</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>250</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="73" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" s="73" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -7557,21 +7612,21 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="70">
+      <c r="A13" s="74">
         <v>6.0</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="E13" s="69" t="s">
-        <v>252</v>
-      </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="73" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="73" t="s">
+        <v>256</v>
+      </c>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -7587,21 +7642,21 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="68">
+      <c r="A14" s="72">
         <v>7.0</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="69" t="s">
-        <v>253</v>
-      </c>
-      <c r="E14" s="69" t="s">
-        <v>254</v>
-      </c>
-      <c r="F14" s="39"/>
-      <c r="G14" s="40"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="73" t="s">
+        <v>257</v>
+      </c>
+      <c r="E14" s="73" t="s">
+        <v>258</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -7617,21 +7672,21 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="70">
+      <c r="A15" s="74">
         <v>8.0</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="E15" s="69" t="s">
-        <v>256</v>
-      </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="73" t="s">
+        <v>259</v>
+      </c>
+      <c r="E15" s="73" t="s">
+        <v>260</v>
+      </c>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -7647,21 +7702,21 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="68">
+      <c r="A16" s="72">
         <v>9.0</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="69" t="s">
-        <v>257</v>
-      </c>
-      <c r="E16" s="69" t="s">
-        <v>250</v>
-      </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="E16" s="73" t="s">
+        <v>254</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
       <c r="J16" s="29"/>
@@ -7677,21 +7732,21 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="70">
+      <c r="A17" s="74">
         <v>10.0</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="69" t="s">
-        <v>258</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>259</v>
-      </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="73" t="s">
+        <v>262</v>
+      </c>
+      <c r="E17" s="73" t="s">
+        <v>263</v>
+      </c>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -7707,21 +7762,21 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="68">
+      <c r="A18" s="72">
         <v>11.0</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="69" t="s">
-        <v>260</v>
-      </c>
-      <c r="E18" s="69" t="s">
-        <v>252</v>
-      </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="73" t="s">
+        <v>264</v>
+      </c>
+      <c r="E18" s="73" t="s">
+        <v>256</v>
+      </c>
+      <c r="F18" s="40"/>
+      <c r="G18" s="41"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -7737,21 +7792,21 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="70">
+      <c r="A19" s="74">
         <v>12.0</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="69" t="s">
-        <v>261</v>
-      </c>
-      <c r="E19" s="69" t="s">
-        <v>262</v>
-      </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="73" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" s="73" t="s">
+        <v>266</v>
+      </c>
+      <c r="F19" s="40"/>
+      <c r="G19" s="41"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -7767,21 +7822,21 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="68">
+      <c r="A20" s="72">
         <v>13.0</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="69" t="s">
-        <v>263</v>
-      </c>
-      <c r="E20" s="71" t="s">
-        <v>264</v>
-      </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="73" t="s">
+        <v>267</v>
+      </c>
+      <c r="E20" s="75" t="s">
+        <v>268</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -7797,21 +7852,21 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="70">
+      <c r="A21" s="74">
         <v>14.0</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="69" t="s">
-        <v>265</v>
-      </c>
-      <c r="E21" s="69" t="s">
-        <v>266</v>
-      </c>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="73" t="s">
+        <v>269</v>
+      </c>
+      <c r="E21" s="73" t="s">
+        <v>270</v>
+      </c>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -7827,21 +7882,21 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="68">
+      <c r="A22" s="72">
         <v>15.0</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="69" t="s">
-        <v>267</v>
-      </c>
-      <c r="E22" s="69" t="s">
-        <v>268</v>
-      </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="73" t="s">
+        <v>271</v>
+      </c>
+      <c r="E22" s="73" t="s">
+        <v>272</v>
+      </c>
+      <c r="F22" s="40"/>
+      <c r="G22" s="41"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -7857,21 +7912,21 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="70">
+      <c r="A23" s="74">
         <v>16.0</v>
       </c>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="69" t="s">
-        <v>269</v>
-      </c>
-      <c r="E23" s="71" t="s">
-        <v>270</v>
-      </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="73" t="s">
+        <v>273</v>
+      </c>
+      <c r="E23" s="75" t="s">
+        <v>274</v>
+      </c>
+      <c r="F23" s="40"/>
+      <c r="G23" s="41"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -7887,21 +7942,21 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="68">
+      <c r="A24" s="72">
         <v>17.0</v>
       </c>
-      <c r="B24" s="69" t="s">
+      <c r="B24" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="E24" s="69" t="s">
-        <v>252</v>
-      </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="76" t="s">
+        <v>275</v>
+      </c>
+      <c r="E24" s="76" t="s">
+        <v>276</v>
+      </c>
+      <c r="F24" s="40"/>
+      <c r="G24" s="41"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -7917,21 +7972,21 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="70">
+      <c r="A25" s="74">
         <v>18.0</v>
       </c>
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="69" t="s">
-        <v>272</v>
-      </c>
-      <c r="E25" s="69" t="s">
-        <v>273</v>
-      </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="73" t="s">
+        <v>277</v>
+      </c>
+      <c r="E25" s="73" t="s">
+        <v>278</v>
+      </c>
+      <c r="F25" s="40"/>
+      <c r="G25" s="41"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -7947,21 +8002,21 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="68">
+      <c r="A26" s="72">
         <v>19.0</v>
       </c>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="69" t="s">
-        <v>274</v>
-      </c>
-      <c r="E26" s="69" t="s">
-        <v>275</v>
-      </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="77" t="s">
+        <v>279</v>
+      </c>
+      <c r="E26" s="77" t="s">
+        <v>280</v>
+      </c>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -7977,21 +8032,21 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="70">
+      <c r="A27" s="74">
         <v>20.0</v>
       </c>
-      <c r="B27" s="69" t="s">
+      <c r="B27" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="69" t="s">
-        <v>276</v>
-      </c>
-      <c r="E27" s="69" t="s">
-        <v>277</v>
-      </c>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="73" t="s">
+        <v>281</v>
+      </c>
+      <c r="E27" s="73" t="s">
+        <v>282</v>
+      </c>
+      <c r="F27" s="40"/>
+      <c r="G27" s="41"/>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
@@ -8007,21 +8062,21 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="68">
+      <c r="A28" s="72">
         <v>21.0</v>
       </c>
-      <c r="B28" s="69" t="s">
+      <c r="B28" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E28" s="69" t="s">
-        <v>279</v>
-      </c>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="73" t="s">
+        <v>283</v>
+      </c>
+      <c r="E28" s="73" t="s">
+        <v>284</v>
+      </c>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -8037,21 +8092,21 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="70">
+      <c r="A29" s="74">
         <v>22.0</v>
       </c>
-      <c r="B29" s="69" t="s">
+      <c r="B29" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="69" t="s">
-        <v>280</v>
-      </c>
-      <c r="E29" s="69" t="s">
-        <v>281</v>
-      </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="73" t="s">
+        <v>285</v>
+      </c>
+      <c r="E29" s="73" t="s">
+        <v>286</v>
+      </c>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -8067,21 +8122,21 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="68">
+      <c r="A30" s="72">
         <v>23.0</v>
       </c>
-      <c r="B30" s="69" t="s">
+      <c r="B30" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="69" t="s">
-        <v>267</v>
-      </c>
-      <c r="E30" s="69" t="s">
-        <v>282</v>
-      </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="73" t="s">
+        <v>271</v>
+      </c>
+      <c r="E30" s="73" t="s">
+        <v>287</v>
+      </c>
+      <c r="F30" s="40"/>
+      <c r="G30" s="41"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -8097,21 +8152,21 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="70">
+      <c r="A31" s="74">
         <v>24.0</v>
       </c>
-      <c r="B31" s="69" t="s">
+      <c r="B31" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="69" t="s">
-        <v>283</v>
-      </c>
-      <c r="E31" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="E31" s="75" t="s">
+        <v>289</v>
+      </c>
+      <c r="F31" s="40"/>
+      <c r="G31" s="41"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -8127,21 +8182,21 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="68">
+      <c r="A32" s="72">
         <v>25.0</v>
       </c>
-      <c r="B32" s="69" t="s">
+      <c r="B32" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="40"/>
-      <c r="D32" s="69" t="s">
-        <v>285</v>
-      </c>
-      <c r="E32" s="69" t="s">
-        <v>286</v>
-      </c>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="73" t="s">
+        <v>290</v>
+      </c>
+      <c r="E32" s="73" t="s">
+        <v>291</v>
+      </c>
+      <c r="F32" s="40"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -8157,21 +8212,21 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="70">
+      <c r="A33" s="74">
         <v>26.0</v>
       </c>
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="40"/>
-      <c r="D33" s="69" t="s">
-        <v>257</v>
-      </c>
-      <c r="E33" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="E33" s="73" t="s">
+        <v>292</v>
+      </c>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -8250,7 +8305,7 @@
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="11" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="6"/>
@@ -8275,7 +8330,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="11" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
@@ -8288,8 +8343,8 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="72" t="s">
-        <v>290</v>
+      <c r="E3" s="78" t="s">
+        <v>295</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -8303,7 +8358,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -8317,7 +8372,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="11" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -8334,10 +8389,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="38" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -8387,26 +8442,26 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="68">
+      <c r="A8" s="72">
         <v>1.0</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="73" t="s">
+        <v>298</v>
+      </c>
+      <c r="E8" s="73" t="s">
+        <v>299</v>
+      </c>
+      <c r="F8" s="40">
+        <v>37.0</v>
+      </c>
+      <c r="G8" s="41" t="s">
         <v>293</v>
-      </c>
-      <c r="E8" s="69" t="s">
-        <v>294</v>
-      </c>
-      <c r="F8" s="39">
-        <v>37.0</v>
-      </c>
-      <c r="G8" s="40" t="s">
-        <v>288</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -8423,26 +8478,26 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="70">
+      <c r="A9" s="74">
         <v>2.0</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="73" t="s">
-        <v>295</v>
-      </c>
-      <c r="E9" s="74" t="s">
-        <v>296</v>
-      </c>
-      <c r="F9" s="39">
+      <c r="D9" s="79" t="s">
+        <v>300</v>
+      </c>
+      <c r="E9" s="80" t="s">
+        <v>301</v>
+      </c>
+      <c r="F9" s="40">
         <v>32.0</v>
       </c>
-      <c r="G9" s="40" t="s">
-        <v>288</v>
+      <c r="G9" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -8459,26 +8514,26 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="68">
+      <c r="A10" s="72">
         <v>3.0</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="69" t="s">
-        <v>297</v>
-      </c>
-      <c r="E10" s="69" t="s">
-        <v>298</v>
-      </c>
-      <c r="F10" s="39">
+      <c r="D10" s="73" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" s="73" t="s">
+        <v>303</v>
+      </c>
+      <c r="F10" s="40">
         <v>25.0</v>
       </c>
-      <c r="G10" s="40" t="s">
-        <v>288</v>
+      <c r="G10" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -8495,26 +8550,26 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="68">
+      <c r="A11" s="72">
         <v>4.0</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="69" t="s">
-        <v>299</v>
-      </c>
-      <c r="E11" s="69" t="s">
-        <v>300</v>
-      </c>
-      <c r="F11" s="39">
+      <c r="D11" s="73" t="s">
+        <v>304</v>
+      </c>
+      <c r="E11" s="73" t="s">
+        <v>305</v>
+      </c>
+      <c r="F11" s="40">
         <v>29.0</v>
       </c>
-      <c r="G11" s="40" t="s">
-        <v>288</v>
+      <c r="G11" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11" s="29"/>
@@ -8531,26 +8586,26 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="70">
+      <c r="A12" s="74">
         <v>5.0</v>
       </c>
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="69" t="s">
-        <v>301</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>302</v>
-      </c>
-      <c r="F12" s="39">
+      <c r="D12" s="73" t="s">
+        <v>306</v>
+      </c>
+      <c r="E12" s="73" t="s">
+        <v>307</v>
+      </c>
+      <c r="F12" s="40">
         <v>27.0</v>
       </c>
-      <c r="G12" s="40" t="s">
-        <v>303</v>
+      <c r="G12" s="41" t="s">
+        <v>308</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="32"/>
@@ -8567,24 +8622,24 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="70">
+      <c r="A13" s="74">
         <v>6.0</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="75" t="s">
-        <v>304</v>
-      </c>
-      <c r="E13" s="69" t="s">
-        <v>305</v>
-      </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40" t="s">
-        <v>288</v>
+      <c r="D13" s="81" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" s="73" t="s">
+        <v>310</v>
+      </c>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
@@ -8601,26 +8656,26 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="68">
+      <c r="A14" s="72">
         <v>7.0</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="76" t="s">
-        <v>306</v>
-      </c>
-      <c r="E14" s="76" t="s">
-        <v>307</v>
-      </c>
-      <c r="F14" s="39">
+      <c r="D14" s="82" t="s">
+        <v>311</v>
+      </c>
+      <c r="E14" s="82" t="s">
+        <v>312</v>
+      </c>
+      <c r="F14" s="40">
         <v>23.0</v>
       </c>
-      <c r="G14" s="40" t="s">
-        <v>288</v>
+      <c r="G14" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
@@ -8637,26 +8692,26 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="70">
+      <c r="A15" s="74">
         <v>8.0</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="69" t="s">
-        <v>308</v>
-      </c>
-      <c r="E15" s="69" t="s">
-        <v>309</v>
-      </c>
-      <c r="F15" s="39">
+      <c r="D15" s="73" t="s">
+        <v>313</v>
+      </c>
+      <c r="E15" s="73" t="s">
+        <v>314</v>
+      </c>
+      <c r="F15" s="40">
         <v>28.0</v>
       </c>
-      <c r="G15" s="40" t="s">
-        <v>288</v>
+      <c r="G15" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
@@ -8673,26 +8728,26 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="68">
+      <c r="A16" s="72">
         <v>9.0</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="69" t="s">
-        <v>310</v>
-      </c>
-      <c r="E16" s="69" t="s">
-        <v>311</v>
-      </c>
-      <c r="F16" s="39">
+      <c r="D16" s="73" t="s">
+        <v>315</v>
+      </c>
+      <c r="E16" s="73" t="s">
+        <v>316</v>
+      </c>
+      <c r="F16" s="40">
         <v>40.0</v>
       </c>
-      <c r="G16" s="40" t="s">
-        <v>288</v>
+      <c r="G16" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -8709,26 +8764,26 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="68">
+      <c r="A17" s="72">
         <v>10.0</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="69" t="s">
-        <v>312</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>313</v>
-      </c>
-      <c r="F17" s="39">
+      <c r="D17" s="73" t="s">
+        <v>317</v>
+      </c>
+      <c r="E17" s="73" t="s">
+        <v>318</v>
+      </c>
+      <c r="F17" s="40">
         <v>37.0</v>
       </c>
-      <c r="G17" s="40" t="s">
-        <v>288</v>
+      <c r="G17" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H17" s="28"/>
       <c r="I17" s="29"/>
@@ -8745,26 +8800,26 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="70">
+      <c r="A18" s="74">
         <v>11.0</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="69" t="s">
-        <v>314</v>
-      </c>
-      <c r="E18" s="69" t="s">
-        <v>315</v>
-      </c>
-      <c r="F18" s="39">
+      <c r="D18" s="73" t="s">
+        <v>319</v>
+      </c>
+      <c r="E18" s="73" t="s">
+        <v>320</v>
+      </c>
+      <c r="F18" s="40">
         <v>32.0</v>
       </c>
-      <c r="G18" s="40" t="s">
-        <v>288</v>
+      <c r="G18" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H18" s="31"/>
       <c r="I18" s="32"/>
@@ -8781,26 +8836,26 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="70">
+      <c r="A19" s="74">
         <v>12.0</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="73" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="75" t="s">
-        <v>316</v>
-      </c>
-      <c r="E19" s="69" t="s">
-        <v>317</v>
-      </c>
-      <c r="F19" s="39">
+      <c r="D19" s="81" t="s">
+        <v>321</v>
+      </c>
+      <c r="E19" s="73" t="s">
+        <v>322</v>
+      </c>
+      <c r="F19" s="40">
         <v>20.0</v>
       </c>
-      <c r="G19" s="40" t="s">
-        <v>288</v>
+      <c r="G19" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
@@ -8817,24 +8872,24 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="68">
+      <c r="A20" s="72">
         <v>13.0</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="77" t="s">
-        <v>318</v>
-      </c>
-      <c r="E20" s="77" t="s">
-        <v>319</v>
-      </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40" t="s">
-        <v>288</v>
+      <c r="D20" s="82" t="s">
+        <v>323</v>
+      </c>
+      <c r="E20" s="82" t="s">
+        <v>324</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
@@ -8851,26 +8906,26 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="70">
+      <c r="A21" s="74">
         <v>14.0</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="69" t="s">
-        <v>320</v>
-      </c>
-      <c r="E21" s="69" t="s">
-        <v>321</v>
-      </c>
-      <c r="F21" s="39">
+      <c r="D21" s="73" t="s">
+        <v>325</v>
+      </c>
+      <c r="E21" s="73" t="s">
+        <v>326</v>
+      </c>
+      <c r="F21" s="40">
         <v>33.0</v>
       </c>
-      <c r="G21" s="40" t="s">
-        <v>288</v>
+      <c r="G21" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -8887,26 +8942,26 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="68">
+      <c r="A22" s="72">
         <v>15.0</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="69" t="s">
-        <v>322</v>
-      </c>
-      <c r="E22" s="69" t="s">
-        <v>323</v>
-      </c>
-      <c r="F22" s="39">
+      <c r="D22" s="73" t="s">
+        <v>327</v>
+      </c>
+      <c r="E22" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="F22" s="40">
         <v>33.0</v>
       </c>
-      <c r="G22" s="40" t="s">
-        <v>288</v>
+      <c r="G22" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -8923,26 +8978,26 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="70">
+      <c r="A23" s="74">
         <v>16.0</v>
       </c>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="78" t="s">
+      <c r="C23" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="77" t="s">
-        <v>324</v>
-      </c>
-      <c r="E23" s="77" t="s">
-        <v>325</v>
-      </c>
-      <c r="F23" s="39">
+      <c r="D23" s="84" t="s">
+        <v>329</v>
+      </c>
+      <c r="E23" s="84" t="s">
+        <v>330</v>
+      </c>
+      <c r="F23" s="40">
         <v>41.0</v>
       </c>
-      <c r="G23" s="40" t="s">
-        <v>288</v>
+      <c r="G23" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -8959,26 +9014,26 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="68">
+      <c r="A24" s="72">
         <v>17.0</v>
       </c>
-      <c r="B24" s="69" t="s">
+      <c r="B24" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="75" t="s">
-        <v>326</v>
-      </c>
-      <c r="E24" s="69" t="s">
-        <v>327</v>
-      </c>
-      <c r="F24" s="39">
+      <c r="D24" s="81" t="s">
+        <v>331</v>
+      </c>
+      <c r="E24" s="73" t="s">
+        <v>332</v>
+      </c>
+      <c r="F24" s="40">
         <v>20.0</v>
       </c>
-      <c r="G24" s="40" t="s">
-        <v>288</v>
+      <c r="G24" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
@@ -8995,26 +9050,26 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="70">
+      <c r="A25" s="74">
         <v>18.0</v>
       </c>
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="75" t="s">
-        <v>328</v>
-      </c>
-      <c r="E25" s="69" t="s">
-        <v>329</v>
-      </c>
-      <c r="F25" s="39">
+      <c r="D25" s="81" t="s">
+        <v>333</v>
+      </c>
+      <c r="E25" s="73" t="s">
+        <v>334</v>
+      </c>
+      <c r="F25" s="40">
         <v>34.0</v>
       </c>
-      <c r="G25" s="40" t="s">
-        <v>288</v>
+      <c r="G25" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
@@ -9031,24 +9086,24 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="68">
+      <c r="A26" s="72">
         <v>19.0</v>
       </c>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="75" t="s">
-        <v>330</v>
-      </c>
-      <c r="E26" s="69" t="s">
-        <v>331</v>
-      </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40" t="s">
-        <v>288</v>
+      <c r="D26" s="81" t="s">
+        <v>335</v>
+      </c>
+      <c r="E26" s="73" t="s">
+        <v>336</v>
+      </c>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
@@ -9065,26 +9120,26 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="70">
+      <c r="A27" s="74">
         <v>20.0</v>
       </c>
-      <c r="B27" s="69" t="s">
+      <c r="B27" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="75" t="s">
-        <v>332</v>
-      </c>
-      <c r="E27" s="69" t="s">
+      <c r="D27" s="81" t="s">
+        <v>337</v>
+      </c>
+      <c r="E27" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="F27" s="39">
+      <c r="F27" s="40">
         <v>27.0</v>
       </c>
-      <c r="G27" s="40" t="s">
-        <v>288</v>
+      <c r="G27" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -9101,26 +9156,26 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="70">
+      <c r="A28" s="74">
         <v>21.0</v>
       </c>
-      <c r="B28" s="69" t="s">
+      <c r="B28" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C28" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="69" t="s">
-        <v>333</v>
-      </c>
-      <c r="E28" s="69" t="s">
-        <v>334</v>
-      </c>
-      <c r="F28" s="39">
+      <c r="D28" s="73" t="s">
+        <v>338</v>
+      </c>
+      <c r="E28" s="73" t="s">
+        <v>339</v>
+      </c>
+      <c r="F28" s="40">
         <v>32.0</v>
       </c>
-      <c r="G28" s="40" t="s">
-        <v>288</v>
+      <c r="G28" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H28" s="31"/>
       <c r="I28" s="32"/>
@@ -9137,26 +9192,26 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="70">
+      <c r="A29" s="74">
         <v>22.0</v>
       </c>
-      <c r="B29" s="69" t="s">
+      <c r="B29" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="77" t="s">
-        <v>335</v>
-      </c>
-      <c r="E29" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="F29" s="39">
+      <c r="D29" s="84" t="s">
+        <v>340</v>
+      </c>
+      <c r="E29" s="84" t="s">
+        <v>341</v>
+      </c>
+      <c r="F29" s="40">
         <v>28.0</v>
       </c>
-      <c r="G29" s="40" t="s">
-        <v>288</v>
+      <c r="G29" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -9173,26 +9228,26 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="68">
+      <c r="A30" s="72">
         <v>23.0</v>
       </c>
-      <c r="B30" s="69" t="s">
+      <c r="B30" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="77" t="s">
-        <v>337</v>
-      </c>
-      <c r="E30" s="77" t="s">
-        <v>338</v>
-      </c>
-      <c r="F30" s="39">
+      <c r="D30" s="84" t="s">
+        <v>342</v>
+      </c>
+      <c r="E30" s="84" t="s">
+        <v>343</v>
+      </c>
+      <c r="F30" s="40">
         <v>41.0</v>
       </c>
-      <c r="G30" s="40" t="s">
-        <v>288</v>
+      <c r="G30" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
@@ -9209,22 +9264,22 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="68">
+      <c r="A31" s="72">
         <v>24.0</v>
       </c>
-      <c r="B31" s="69" t="s">
+      <c r="B31" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="75"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="39">
+      <c r="D31" s="81"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="40">
         <v>36.0</v>
       </c>
-      <c r="G31" s="40" t="s">
-        <v>288</v>
+      <c r="G31" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
@@ -9241,25 +9296,25 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="68">
+      <c r="A32" s="72">
         <v>25.0</v>
       </c>
-      <c r="B32" s="69" t="s">
+      <c r="B32" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="69" t="s">
-        <v>339</v>
-      </c>
-      <c r="E32" s="69" t="s">
-        <v>340</v>
-      </c>
-      <c r="F32" s="39">
+      <c r="D32" s="73" t="s">
+        <v>344</v>
+      </c>
+      <c r="E32" s="73" t="s">
+        <v>345</v>
+      </c>
+      <c r="F32" s="40">
         <v>19.0</v>
       </c>
-      <c r="G32" s="40"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -9275,25 +9330,25 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="70">
+      <c r="A33" s="74">
         <v>26.0</v>
       </c>
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="73" t="s">
         <v>120</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="69" t="s">
-        <v>341</v>
-      </c>
-      <c r="E33" s="69" t="s">
-        <v>342</v>
-      </c>
-      <c r="F33" s="39">
+      <c r="D33" s="73" t="s">
+        <v>346</v>
+      </c>
+      <c r="E33" s="73" t="s">
+        <v>347</v>
+      </c>
+      <c r="F33" s="40">
         <v>19.0</v>
       </c>
-      <c r="G33" s="40"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -9373,12 +9428,12 @@
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="82" t="s">
+      <c r="G1" s="86"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="88" t="s">
         <v>42</v>
       </c>
       <c r="J1" s="10"/>
@@ -9400,7 +9455,7 @@
       <c r="D2" s="5"/>
       <c r="E2" s="6"/>
       <c r="F2" s="11" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="6"/>
@@ -9414,7 +9469,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="6"/>
       <c r="F3" s="11" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="6"/>
@@ -9428,27 +9483,27 @@
       <c r="D4" s="5"/>
       <c r="E4" s="6"/>
       <c r="F4" s="11" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="6"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="89" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="84" t="s">
-        <v>346</v>
-      </c>
-      <c r="G5" s="85"/>
-      <c r="H5" s="86"/>
+      <c r="F5" s="90" t="s">
+        <v>351</v>
+      </c>
+      <c r="G5" s="91"/>
+      <c r="H5" s="92"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="87"/>
+      <c r="A6" s="93"/>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -9458,14 +9513,14 @@
       <c r="H6" s="16"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="37" t="s">
-        <v>347</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>348</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>349</v>
+      <c r="A7" s="38" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>353</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>354</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>52</v>
@@ -9514,26 +9569,26 @@
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1">
-      <c r="A8" s="88">
+      <c r="A8" s="94">
         <v>1.0</v>
       </c>
-      <c r="B8" s="88" t="s">
+      <c r="B8" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="88" t="s">
+      <c r="C8" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="89" t="s">
+      <c r="D8" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="90" t="s">
-        <v>350</v>
-      </c>
-      <c r="F8" s="90" t="s">
-        <v>351</v>
-      </c>
-      <c r="G8" s="39"/>
-      <c r="H8" s="91" t="s">
+      <c r="E8" s="96" t="s">
+        <v>355</v>
+      </c>
+      <c r="F8" s="96" t="s">
+        <v>356</v>
+      </c>
+      <c r="G8" s="40"/>
+      <c r="H8" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I8" s="28"/>
@@ -9551,26 +9606,26 @@
       </c>
     </row>
     <row r="9" ht="21.0" customHeight="1">
-      <c r="A9" s="88">
+      <c r="A9" s="94">
         <v>2.0</v>
       </c>
-      <c r="B9" s="88" t="s">
+      <c r="B9" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="89" t="s">
+      <c r="D9" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="90" t="s">
-        <v>352</v>
-      </c>
-      <c r="F9" s="90" t="s">
-        <v>353</v>
-      </c>
-      <c r="G9" s="39"/>
-      <c r="H9" s="91" t="s">
+      <c r="E9" s="96" t="s">
+        <v>357</v>
+      </c>
+      <c r="F9" s="96" t="s">
+        <v>358</v>
+      </c>
+      <c r="G9" s="40"/>
+      <c r="H9" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I9" s="31"/>
@@ -9588,26 +9643,26 @@
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1">
-      <c r="A10" s="88">
+      <c r="A10" s="94">
         <v>3.0</v>
       </c>
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="89" t="s">
+      <c r="D10" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="92" t="s">
-        <v>354</v>
-      </c>
-      <c r="F10" s="92" t="s">
-        <v>355</v>
-      </c>
-      <c r="G10" s="39"/>
-      <c r="H10" s="91" t="s">
+      <c r="E10" s="98" t="s">
+        <v>359</v>
+      </c>
+      <c r="F10" s="98" t="s">
+        <v>360</v>
+      </c>
+      <c r="G10" s="40"/>
+      <c r="H10" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I10" s="31"/>
@@ -9625,26 +9680,26 @@
       </c>
     </row>
     <row r="11" ht="21.0" customHeight="1">
-      <c r="A11" s="88">
+      <c r="A11" s="94">
         <v>4.0</v>
       </c>
-      <c r="B11" s="88" t="s">
+      <c r="B11" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="88" t="s">
+      <c r="C11" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="89" t="s">
+      <c r="D11" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="90" t="s">
-        <v>356</v>
-      </c>
-      <c r="F11" s="90" t="s">
-        <v>357</v>
-      </c>
-      <c r="G11" s="39"/>
-      <c r="H11" s="91" t="s">
+      <c r="E11" s="96" t="s">
+        <v>361</v>
+      </c>
+      <c r="F11" s="96" t="s">
+        <v>362</v>
+      </c>
+      <c r="G11" s="40"/>
+      <c r="H11" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I11" s="31"/>
@@ -9662,26 +9717,26 @@
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="88">
+      <c r="A12" s="94">
         <v>5.0</v>
       </c>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="89" t="s">
+      <c r="D12" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="90" t="s">
-        <v>358</v>
-      </c>
-      <c r="F12" s="90" t="s">
-        <v>351</v>
-      </c>
-      <c r="G12" s="39"/>
-      <c r="H12" s="91" t="s">
+      <c r="E12" s="96" t="s">
+        <v>363</v>
+      </c>
+      <c r="F12" s="96" t="s">
+        <v>356</v>
+      </c>
+      <c r="G12" s="40"/>
+      <c r="H12" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I12" s="28"/>
@@ -9699,26 +9754,26 @@
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1">
-      <c r="A13" s="88">
+      <c r="A13" s="94">
         <v>6.0</v>
       </c>
-      <c r="B13" s="88" t="s">
+      <c r="B13" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="89" t="s">
+      <c r="D13" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="90" t="s">
-        <v>359</v>
-      </c>
-      <c r="F13" s="90" t="s">
-        <v>179</v>
-      </c>
-      <c r="G13" s="39"/>
-      <c r="H13" s="91" t="s">
+      <c r="E13" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="96" t="s">
+        <v>181</v>
+      </c>
+      <c r="G13" s="40"/>
+      <c r="H13" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I13" s="31"/>
@@ -9736,26 +9791,26 @@
       </c>
     </row>
     <row r="14" ht="24.75" customHeight="1">
-      <c r="A14" s="88">
+      <c r="A14" s="94">
         <v>7.0</v>
       </c>
-      <c r="B14" s="88" t="s">
+      <c r="B14" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="89" t="s">
+      <c r="D14" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="90" t="s">
-        <v>223</v>
-      </c>
-      <c r="F14" s="90" t="s">
-        <v>179</v>
-      </c>
-      <c r="G14" s="39"/>
-      <c r="H14" s="91" t="s">
+      <c r="E14" s="96" t="s">
+        <v>364</v>
+      </c>
+      <c r="F14" s="96" t="s">
+        <v>181</v>
+      </c>
+      <c r="G14" s="40"/>
+      <c r="H14" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I14" s="28"/>
@@ -9773,26 +9828,26 @@
       </c>
     </row>
     <row r="15" ht="21.0" customHeight="1">
-      <c r="A15" s="88">
+      <c r="A15" s="94">
         <v>8.0</v>
       </c>
-      <c r="B15" s="88" t="s">
+      <c r="B15" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="88" t="s">
+      <c r="C15" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="89" t="s">
+      <c r="D15" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="90" t="s">
-        <v>360</v>
-      </c>
-      <c r="F15" s="90" t="s">
-        <v>179</v>
-      </c>
-      <c r="G15" s="39"/>
-      <c r="H15" s="91" t="s">
+      <c r="E15" s="96" t="s">
+        <v>365</v>
+      </c>
+      <c r="F15" s="96" t="s">
+        <v>181</v>
+      </c>
+      <c r="G15" s="40"/>
+      <c r="H15" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I15" s="31"/>
@@ -9810,26 +9865,26 @@
       </c>
     </row>
     <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="88">
+      <c r="A16" s="94">
         <v>9.0</v>
       </c>
-      <c r="B16" s="88" t="s">
+      <c r="B16" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="89" t="s">
+      <c r="D16" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="90" t="s">
-        <v>361</v>
-      </c>
-      <c r="F16" s="90" t="s">
-        <v>362</v>
-      </c>
-      <c r="G16" s="39"/>
-      <c r="H16" s="91" t="s">
+      <c r="E16" s="96" t="s">
+        <v>366</v>
+      </c>
+      <c r="F16" s="96" t="s">
+        <v>367</v>
+      </c>
+      <c r="G16" s="40"/>
+      <c r="H16" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I16" s="28"/>
@@ -9847,26 +9902,26 @@
       </c>
     </row>
     <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="88">
+      <c r="A17" s="94">
         <v>10.0</v>
       </c>
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="88" t="s">
+      <c r="C17" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="89" t="s">
+      <c r="D17" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="90" t="s">
-        <v>363</v>
-      </c>
-      <c r="F17" s="90" t="s">
-        <v>364</v>
-      </c>
-      <c r="G17" s="39"/>
-      <c r="H17" s="91" t="s">
+      <c r="E17" s="96" t="s">
+        <v>368</v>
+      </c>
+      <c r="F17" s="96" t="s">
+        <v>369</v>
+      </c>
+      <c r="G17" s="40"/>
+      <c r="H17" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I17" s="31"/>
@@ -9884,26 +9939,26 @@
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="88">
+      <c r="A18" s="94">
         <v>11.0</v>
       </c>
-      <c r="B18" s="88" t="s">
+      <c r="B18" s="94" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="89" t="s">
+      <c r="D18" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="90" t="s">
-        <v>365</v>
-      </c>
-      <c r="F18" s="90" t="s">
-        <v>366</v>
-      </c>
-      <c r="G18" s="39"/>
-      <c r="H18" s="91" t="s">
+      <c r="E18" s="96" t="s">
+        <v>370</v>
+      </c>
+      <c r="F18" s="96" t="s">
+        <v>371</v>
+      </c>
+      <c r="G18" s="40"/>
+      <c r="H18" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I18" s="28"/>
@@ -9921,26 +9976,26 @@
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1">
-      <c r="A19" s="88">
+      <c r="A19" s="94">
         <v>12.0</v>
       </c>
-      <c r="B19" s="88" t="s">
+      <c r="B19" s="94" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="88" t="s">
+      <c r="C19" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="89" t="s">
+      <c r="D19" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="90" t="s">
-        <v>367</v>
-      </c>
-      <c r="F19" s="90" t="s">
-        <v>368</v>
-      </c>
-      <c r="G19" s="39"/>
-      <c r="H19" s="91" t="s">
+      <c r="E19" s="96" t="s">
+        <v>372</v>
+      </c>
+      <c r="F19" s="96" t="s">
+        <v>373</v>
+      </c>
+      <c r="G19" s="40"/>
+      <c r="H19" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I19" s="31"/>
@@ -9958,26 +10013,26 @@
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1">
-      <c r="A20" s="88">
+      <c r="A20" s="94">
         <v>13.0</v>
       </c>
-      <c r="B20" s="88" t="s">
+      <c r="B20" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="88" t="s">
+      <c r="C20" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="89" t="s">
+      <c r="D20" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="90" t="s">
-        <v>369</v>
-      </c>
-      <c r="F20" s="90" t="s">
-        <v>370</v>
-      </c>
-      <c r="G20" s="39"/>
-      <c r="H20" s="91" t="s">
+      <c r="E20" s="96" t="s">
+        <v>374</v>
+      </c>
+      <c r="F20" s="96" t="s">
+        <v>375</v>
+      </c>
+      <c r="G20" s="40"/>
+      <c r="H20" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I20" s="28"/>
@@ -9995,26 +10050,26 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="88">
+      <c r="A21" s="94">
         <v>14.0</v>
       </c>
-      <c r="B21" s="88" t="s">
+      <c r="B21" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="88" t="s">
+      <c r="C21" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="89" t="s">
+      <c r="D21" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="90" t="s">
-        <v>371</v>
-      </c>
-      <c r="F21" s="90" t="s">
+      <c r="E21" s="96" t="s">
+        <v>376</v>
+      </c>
+      <c r="F21" s="96" t="s">
         <v>146</v>
       </c>
-      <c r="G21" s="39"/>
-      <c r="H21" s="91" t="s">
+      <c r="G21" s="40"/>
+      <c r="H21" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I21" s="31"/>
@@ -10032,26 +10087,26 @@
       </c>
     </row>
     <row r="22" ht="23.25" customHeight="1">
-      <c r="A22" s="88">
+      <c r="A22" s="94">
         <v>15.0</v>
       </c>
-      <c r="B22" s="88" t="s">
+      <c r="B22" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="88" t="s">
+      <c r="C22" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="89" t="s">
+      <c r="D22" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="90" t="s">
-        <v>372</v>
-      </c>
-      <c r="F22" s="90" t="s">
-        <v>373</v>
-      </c>
-      <c r="G22" s="39"/>
-      <c r="H22" s="91" t="s">
+      <c r="E22" s="96" t="s">
+        <v>377</v>
+      </c>
+      <c r="F22" s="96" t="s">
+        <v>378</v>
+      </c>
+      <c r="G22" s="40"/>
+      <c r="H22" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I22" s="28"/>
@@ -10069,26 +10124,26 @@
       </c>
     </row>
     <row r="23" ht="21.75" customHeight="1">
-      <c r="A23" s="88">
+      <c r="A23" s="94">
         <v>16.0</v>
       </c>
-      <c r="B23" s="88" t="s">
+      <c r="B23" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="88" t="s">
+      <c r="C23" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="89" t="s">
+      <c r="D23" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="90" t="s">
-        <v>374</v>
-      </c>
-      <c r="F23" s="90" t="s">
-        <v>375</v>
-      </c>
-      <c r="G23" s="39"/>
-      <c r="H23" s="93" t="s">
+      <c r="E23" s="96" t="s">
+        <v>379</v>
+      </c>
+      <c r="F23" s="96" t="s">
+        <v>380</v>
+      </c>
+      <c r="G23" s="40"/>
+      <c r="H23" s="99" t="s">
         <v>71</v>
       </c>
       <c r="I23" s="31"/>
@@ -10106,26 +10161,26 @@
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1">
-      <c r="A24" s="88">
+      <c r="A24" s="94">
         <v>17.0</v>
       </c>
-      <c r="B24" s="88" t="s">
+      <c r="B24" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="89" t="s">
+      <c r="D24" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="90" t="s">
-        <v>376</v>
-      </c>
-      <c r="F24" s="90" t="s">
-        <v>377</v>
-      </c>
-      <c r="G24" s="39"/>
-      <c r="H24" s="91" t="s">
+      <c r="E24" s="96" t="s">
+        <v>381</v>
+      </c>
+      <c r="F24" s="96" t="s">
+        <v>382</v>
+      </c>
+      <c r="G24" s="40"/>
+      <c r="H24" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I24" s="31"/>
@@ -10143,26 +10198,26 @@
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="88">
+      <c r="A25" s="94">
         <v>18.0</v>
       </c>
-      <c r="B25" s="88" t="s">
+      <c r="B25" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="88" t="s">
+      <c r="C25" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="89" t="s">
+      <c r="D25" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="90" t="s">
-        <v>378</v>
-      </c>
-      <c r="F25" s="90" t="s">
-        <v>379</v>
-      </c>
-      <c r="G25" s="39"/>
-      <c r="H25" s="91" t="s">
+      <c r="E25" s="96" t="s">
+        <v>383</v>
+      </c>
+      <c r="F25" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="G25" s="40"/>
+      <c r="H25" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I25" s="28"/>
@@ -10180,26 +10235,26 @@
       </c>
     </row>
     <row r="26" ht="24.0" customHeight="1">
-      <c r="A26" s="88">
+      <c r="A26" s="94">
         <v>19.0</v>
       </c>
-      <c r="B26" s="88" t="s">
+      <c r="B26" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="88" t="s">
+      <c r="C26" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="89" t="s">
+      <c r="D26" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="90" t="s">
-        <v>380</v>
-      </c>
-      <c r="F26" s="90" t="s">
-        <v>381</v>
-      </c>
-      <c r="G26" s="39"/>
-      <c r="H26" s="91" t="s">
+      <c r="E26" s="96" t="s">
+        <v>385</v>
+      </c>
+      <c r="F26" s="96" t="s">
+        <v>386</v>
+      </c>
+      <c r="G26" s="40"/>
+      <c r="H26" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I26" s="28"/>
@@ -10217,26 +10272,26 @@
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1">
-      <c r="A27" s="88">
+      <c r="A27" s="94">
         <v>20.0</v>
       </c>
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="89" t="s">
+      <c r="D27" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="90" t="s">
-        <v>382</v>
-      </c>
-      <c r="F27" s="90" t="s">
-        <v>357</v>
-      </c>
-      <c r="G27" s="39"/>
-      <c r="H27" s="91" t="s">
+      <c r="E27" s="96" t="s">
+        <v>387</v>
+      </c>
+      <c r="F27" s="96" t="s">
+        <v>362</v>
+      </c>
+      <c r="G27" s="40"/>
+      <c r="H27" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I27" s="28"/>
@@ -10254,26 +10309,26 @@
       </c>
     </row>
     <row r="28" ht="20.25" customHeight="1">
-      <c r="A28" s="88">
+      <c r="A28" s="94">
         <v>21.0</v>
       </c>
-      <c r="B28" s="88" t="s">
+      <c r="B28" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="88" t="s">
+      <c r="C28" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="89" t="s">
+      <c r="D28" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="90" t="s">
-        <v>383</v>
-      </c>
-      <c r="F28" s="90" t="s">
-        <v>384</v>
-      </c>
-      <c r="G28" s="39"/>
-      <c r="H28" s="91" t="s">
+      <c r="E28" s="96" t="s">
+        <v>388</v>
+      </c>
+      <c r="F28" s="96" t="s">
+        <v>389</v>
+      </c>
+      <c r="G28" s="40"/>
+      <c r="H28" s="97" t="s">
         <v>99</v>
       </c>
       <c r="I28" s="31"/>
@@ -10291,26 +10346,26 @@
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="88">
+      <c r="A29" s="94">
         <v>22.0</v>
       </c>
-      <c r="B29" s="88" t="s">
+      <c r="B29" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="88" t="s">
+      <c r="C29" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="89" t="s">
+      <c r="D29" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="90" t="s">
-        <v>385</v>
-      </c>
-      <c r="F29" s="90" t="s">
-        <v>386</v>
-      </c>
-      <c r="G29" s="39"/>
-      <c r="H29" s="91" t="s">
+      <c r="E29" s="96" t="s">
+        <v>390</v>
+      </c>
+      <c r="F29" s="96" t="s">
+        <v>391</v>
+      </c>
+      <c r="G29" s="40"/>
+      <c r="H29" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I29" s="28"/>
@@ -10328,26 +10383,26 @@
       </c>
     </row>
     <row r="30" ht="20.25" customHeight="1">
-      <c r="A30" s="88">
+      <c r="A30" s="94">
         <v>23.0</v>
       </c>
-      <c r="B30" s="88" t="s">
+      <c r="B30" s="94" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="88" t="s">
+      <c r="C30" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="89" t="s">
+      <c r="D30" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="90" t="s">
-        <v>387</v>
-      </c>
-      <c r="F30" s="90" t="s">
-        <v>388</v>
-      </c>
-      <c r="G30" s="39"/>
-      <c r="H30" s="91" t="s">
+      <c r="E30" s="96" t="s">
+        <v>392</v>
+      </c>
+      <c r="F30" s="96" t="s">
+        <v>393</v>
+      </c>
+      <c r="G30" s="40"/>
+      <c r="H30" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I30" s="31"/>
@@ -10365,26 +10420,26 @@
       </c>
     </row>
     <row r="31" ht="21.0" customHeight="1">
-      <c r="A31" s="88">
+      <c r="A31" s="94">
         <v>24.0</v>
       </c>
-      <c r="B31" s="88" t="s">
+      <c r="B31" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="88" t="s">
+      <c r="C31" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="89" t="s">
+      <c r="D31" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="90" t="s">
-        <v>389</v>
-      </c>
-      <c r="F31" s="90" t="s">
-        <v>390</v>
-      </c>
-      <c r="G31" s="39"/>
-      <c r="H31" s="91" t="s">
+      <c r="E31" s="96" t="s">
+        <v>394</v>
+      </c>
+      <c r="F31" s="96" t="s">
+        <v>395</v>
+      </c>
+      <c r="G31" s="40"/>
+      <c r="H31" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I31" s="28"/>
@@ -10402,26 +10457,26 @@
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="88">
+      <c r="A32" s="94">
         <v>25.0</v>
       </c>
-      <c r="B32" s="88" t="s">
+      <c r="B32" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="88" t="s">
+      <c r="C32" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="89" t="s">
+      <c r="D32" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="90" t="s">
-        <v>391</v>
-      </c>
-      <c r="F32" s="90" t="s">
-        <v>392</v>
-      </c>
-      <c r="G32" s="39"/>
-      <c r="H32" s="91" t="s">
+      <c r="E32" s="96" t="s">
+        <v>396</v>
+      </c>
+      <c r="F32" s="96" t="s">
+        <v>397</v>
+      </c>
+      <c r="G32" s="40"/>
+      <c r="H32" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I32" s="31"/>
@@ -10439,27 +10494,27 @@
       </c>
     </row>
     <row r="33" ht="21.0" customHeight="1">
-      <c r="A33" s="88">
+      <c r="A33" s="94">
         <v>26.0</v>
       </c>
-      <c r="B33" s="88" t="s">
+      <c r="B33" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="88" t="s">
+      <c r="C33" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="89" t="s">
+      <c r="D33" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="90" t="s">
+      <c r="E33" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="90" t="s">
-        <v>393</v>
-      </c>
-      <c r="G33" s="39"/>
-      <c r="H33" s="91" t="s">
-        <v>394</v>
+      <c r="F33" s="96" t="s">
+        <v>398</v>
+      </c>
+      <c r="G33" s="40"/>
+      <c r="H33" s="97" t="s">
+        <v>399</v>
       </c>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
@@ -10537,7 +10592,7 @@
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="7" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="6"/>
@@ -10562,7 +10617,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="11" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
@@ -10576,7 +10631,7 @@
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
       <c r="E3" s="11" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -10590,7 +10645,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -10604,7 +10659,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="11" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -10621,10 +10676,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="38" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -10674,23 +10729,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="22">
-        <v>1.0</v>
+      <c r="A8" s="46">
+        <v>3.0</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>400</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40" t="s">
+      <c r="C8" s="100" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="101" t="s">
+        <v>305</v>
+      </c>
+      <c r="E8" s="101" t="s">
+        <v>405</v>
+      </c>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41" t="s">
         <v>85</v>
       </c>
       <c r="H8" s="28"/>
@@ -10718,14 +10773,14 @@
         <v>76</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>403</v>
-      </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40" t="s">
-        <v>404</v>
+        <v>407</v>
+      </c>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41" t="s">
+        <v>408</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -10742,8 +10797,8 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="22">
-        <v>3.0</v>
+      <c r="A10" s="46">
+        <v>1.0</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>67</v>
@@ -10752,14 +10807,14 @@
         <v>68</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>406</v>
-      </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40" t="s">
-        <v>407</v>
+        <v>410</v>
+      </c>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41" t="s">
+        <v>411</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -10786,14 +10841,14 @@
         <v>76</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40" t="s">
-        <v>395</v>
+        <v>413</v>
+      </c>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41" t="s">
+        <v>400</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
@@ -10820,14 +10875,14 @@
         <v>86</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>411</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40" t="s">
-        <v>395</v>
+        <v>415</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41" t="s">
+        <v>400</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -10854,14 +10909,14 @@
         <v>86</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>413</v>
-      </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40" t="s">
-        <v>395</v>
+        <v>417</v>
+      </c>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41" t="s">
+        <v>400</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
@@ -10888,13 +10943,13 @@
         <v>94</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="F14" s="39"/>
-      <c r="G14" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41" t="s">
         <v>75</v>
       </c>
       <c r="H14" s="28"/>
@@ -10922,13 +10977,13 @@
         <v>86</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>416</v>
-      </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40" t="s">
+        <v>420</v>
+      </c>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41" t="s">
         <v>71</v>
       </c>
       <c r="H15" s="31"/>
@@ -10956,14 +11011,14 @@
         <v>94</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>418</v>
-      </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40" t="s">
-        <v>288</v>
+        <v>422</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -10990,14 +11045,14 @@
         <v>94</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>420</v>
-      </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40" t="s">
-        <v>395</v>
+        <v>424</v>
+      </c>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41" t="s">
+        <v>400</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
@@ -11024,25 +11079,25 @@
         <v>94</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>422</v>
-      </c>
-      <c r="F18" s="94"/>
-      <c r="G18" s="95" t="s">
-        <v>423</v>
-      </c>
-      <c r="H18" s="62"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="96"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="96"/>
-      <c r="Q18" s="62">
+        <v>426</v>
+      </c>
+      <c r="F18" s="102"/>
+      <c r="G18" s="103" t="s">
+        <v>427</v>
+      </c>
+      <c r="H18" s="64"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="104"/>
+      <c r="N18" s="104"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="104"/>
+      <c r="Q18" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11058,25 +11113,25 @@
         <v>76</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>425</v>
-      </c>
-      <c r="F19" s="94"/>
-      <c r="G19" s="95" t="s">
-        <v>395</v>
-      </c>
-      <c r="H19" s="62"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="63"/>
-      <c r="O19" s="63"/>
-      <c r="P19" s="63"/>
-      <c r="Q19" s="62">
+        <v>429</v>
+      </c>
+      <c r="F19" s="102"/>
+      <c r="G19" s="103" t="s">
+        <v>400</v>
+      </c>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="65"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11092,25 +11147,25 @@
         <v>76</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="95" t="s">
-        <v>395</v>
-      </c>
-      <c r="H20" s="62"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="96"/>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="96"/>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="62">
+        <v>431</v>
+      </c>
+      <c r="F20" s="102"/>
+      <c r="G20" s="103" t="s">
+        <v>400</v>
+      </c>
+      <c r="H20" s="64"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="104"/>
+      <c r="O20" s="104"/>
+      <c r="P20" s="104"/>
+      <c r="Q20" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11126,16 +11181,16 @@
         <v>76</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>429</v>
-      </c>
-      <c r="F21" s="39">
+        <v>433</v>
+      </c>
+      <c r="F21" s="40">
         <v>20.0</v>
       </c>
-      <c r="G21" s="40" t="s">
-        <v>430</v>
+      <c r="G21" s="41" t="s">
+        <v>434</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -11162,14 +11217,14 @@
         <v>86</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40" t="s">
-        <v>303</v>
+        <v>436</v>
+      </c>
+      <c r="F22" s="40"/>
+      <c r="G22" s="41" t="s">
+        <v>308</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -11196,23 +11251,23 @@
         <v>86</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="F23" s="94"/>
-      <c r="G23" s="95"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96"/>
-      <c r="K23" s="96"/>
-      <c r="L23" s="96"/>
-      <c r="M23" s="96"/>
-      <c r="N23" s="96"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="96"/>
-      <c r="Q23" s="62">
+        <v>438</v>
+      </c>
+      <c r="F23" s="102"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="104"/>
+      <c r="N23" s="104"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="104"/>
+      <c r="Q23" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11228,13 +11283,13 @@
         <v>86</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E24" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40" t="s">
+      <c r="F24" s="40"/>
+      <c r="G24" s="41" t="s">
         <v>75</v>
       </c>
       <c r="H24" s="28"/>
@@ -11262,25 +11317,25 @@
         <v>86</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>437</v>
-      </c>
-      <c r="F25" s="94"/>
-      <c r="G25" s="95" t="s">
+        <v>405</v>
+      </c>
+      <c r="F25" s="102"/>
+      <c r="G25" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="H25" s="62"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96"/>
-      <c r="K25" s="96"/>
-      <c r="L25" s="96"/>
-      <c r="M25" s="96"/>
-      <c r="N25" s="96"/>
-      <c r="O25" s="96"/>
-      <c r="P25" s="96"/>
-      <c r="Q25" s="62">
+      <c r="H25" s="64"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="104"/>
+      <c r="N25" s="104"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="104"/>
+      <c r="Q25" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11296,13 +11351,13 @@
         <v>94</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>439</v>
-      </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40" t="s">
+        <v>442</v>
+      </c>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41" t="s">
         <v>99</v>
       </c>
       <c r="H26" s="28"/>
@@ -11330,14 +11385,14 @@
         <v>76</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>441</v>
-      </c>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40" t="s">
-        <v>395</v>
+        <v>444</v>
+      </c>
+      <c r="F27" s="40"/>
+      <c r="G27" s="41" t="s">
+        <v>400</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -11364,13 +11419,13 @@
         <v>86</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
+        <v>446</v>
+      </c>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -11396,14 +11451,14 @@
         <v>94</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40" t="s">
-        <v>395</v>
+        <v>448</v>
+      </c>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41" t="s">
+        <v>400</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -11430,14 +11485,14 @@
         <v>76</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>447</v>
-      </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40" t="s">
-        <v>448</v>
+        <v>450</v>
+      </c>
+      <c r="F30" s="40"/>
+      <c r="G30" s="41" t="s">
+        <v>451</v>
       </c>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
@@ -11464,57 +11519,57 @@
         <v>94</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>425</v>
-      </c>
-      <c r="F31" s="94"/>
-      <c r="G31" s="95" t="s">
-        <v>395</v>
-      </c>
-      <c r="H31" s="62"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="96"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="96"/>
-      <c r="P31" s="96"/>
-      <c r="Q31" s="62">
+        <v>429</v>
+      </c>
+      <c r="F31" s="102"/>
+      <c r="G31" s="103" t="s">
+        <v>400</v>
+      </c>
+      <c r="H31" s="64"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="104"/>
+      <c r="N31" s="104"/>
+      <c r="O31" s="104"/>
+      <c r="P31" s="104"/>
+      <c r="Q31" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="97">
+      <c r="A32" s="105">
         <v>25.0</v>
       </c>
-      <c r="B32" s="98" t="s">
+      <c r="B32" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="99" t="s">
+      <c r="C32" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="98" t="s">
-        <v>450</v>
-      </c>
-      <c r="E32" s="98" t="s">
-        <v>451</v>
-      </c>
-      <c r="F32" s="94"/>
-      <c r="G32" s="95"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="96"/>
-      <c r="O32" s="96"/>
-      <c r="P32" s="96"/>
-      <c r="Q32" s="62">
+      <c r="D32" s="106" t="s">
+        <v>453</v>
+      </c>
+      <c r="E32" s="106" t="s">
+        <v>454</v>
+      </c>
+      <c r="F32" s="102"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="104"/>
+      <c r="N32" s="104"/>
+      <c r="O32" s="104"/>
+      <c r="P32" s="104"/>
+      <c r="Q32" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11530,14 +11585,14 @@
         <v>76</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>453</v>
-      </c>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40" t="s">
-        <v>454</v>
+        <v>456</v>
+      </c>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41" t="s">
+        <v>457</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -11616,7 +11671,7 @@
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="100" t="s">
+      <c r="E1" s="108" t="s">
         <v>37</v>
       </c>
       <c r="F1" s="5"/>
@@ -11641,7 +11696,7 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="100"/>
+      <c r="E2" s="108"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="13"/>
@@ -11653,8 +11708,8 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="100" t="s">
-        <v>455</v>
+      <c r="E3" s="108" t="s">
+        <v>458</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -11667,8 +11722,8 @@
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
-      <c r="E4" s="101" t="s">
-        <v>456</v>
+      <c r="E4" s="109" t="s">
+        <v>459</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -11681,8 +11736,8 @@
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="100" t="s">
-        <v>457</v>
+      <c r="E5" s="108" t="s">
+        <v>460</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -11699,10 +11754,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="38" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -11752,23 +11807,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="68">
+      <c r="A8" s="72">
         <v>1.0</v>
       </c>
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="104" t="s">
-        <v>458</v>
-      </c>
-      <c r="E8" s="104" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="D8" s="112" t="s">
+        <v>461</v>
+      </c>
+      <c r="E8" s="112" t="s">
+        <v>239</v>
+      </c>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -11784,23 +11839,23 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="70">
+      <c r="A9" s="74">
         <v>2.0</v>
       </c>
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="104" t="s">
-        <v>459</v>
-      </c>
-      <c r="E9" s="104" t="s">
-        <v>460</v>
-      </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="D9" s="112" t="s">
+        <v>462</v>
+      </c>
+      <c r="E9" s="112" t="s">
+        <v>463</v>
+      </c>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -11816,23 +11871,23 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="68">
+      <c r="A10" s="72">
         <v>3.0</v>
       </c>
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="C10" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="105" t="s">
-        <v>461</v>
-      </c>
-      <c r="E10" s="105" t="s">
-        <v>462</v>
-      </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="D10" s="113" t="s">
+        <v>464</v>
+      </c>
+      <c r="E10" s="113" t="s">
+        <v>465</v>
+      </c>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -11848,23 +11903,23 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="70">
+      <c r="A11" s="74">
         <v>4.0</v>
       </c>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="103" t="s">
+      <c r="C11" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="105" t="s">
-        <v>463</v>
-      </c>
-      <c r="E11" s="105" t="s">
-        <v>464</v>
-      </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
+      <c r="D11" s="113" t="s">
+        <v>466</v>
+      </c>
+      <c r="E11" s="113" t="s">
+        <v>467</v>
+      </c>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -11880,23 +11935,23 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="68">
+      <c r="A12" s="72">
         <v>5.0</v>
       </c>
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="103" t="s">
+      <c r="C12" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="106" t="s">
-        <v>465</v>
-      </c>
-      <c r="E12" s="104" t="s">
-        <v>466</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
+      <c r="D12" s="114" t="s">
+        <v>468</v>
+      </c>
+      <c r="E12" s="112" t="s">
+        <v>469</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -11912,23 +11967,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="70">
+      <c r="A13" s="74">
         <v>6.0</v>
       </c>
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="107" t="s">
+      <c r="C13" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="E13" s="106" t="s">
-        <v>468</v>
-      </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40"/>
+      <c r="D13" s="114" t="s">
+        <v>470</v>
+      </c>
+      <c r="E13" s="114" t="s">
+        <v>471</v>
+      </c>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -11944,23 +11999,23 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="68">
+      <c r="A14" s="72">
         <v>7.0</v>
       </c>
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="107" t="s">
+      <c r="C14" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="106" t="s">
-        <v>469</v>
-      </c>
-      <c r="E14" s="106" t="s">
-        <v>470</v>
-      </c>
-      <c r="F14" s="39"/>
-      <c r="G14" s="40"/>
+      <c r="D14" s="114" t="s">
+        <v>472</v>
+      </c>
+      <c r="E14" s="114" t="s">
+        <v>473</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -11976,23 +12031,23 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="70">
+      <c r="A15" s="74">
         <v>8.0</v>
       </c>
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="107" t="s">
+      <c r="C15" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="106" t="s">
-        <v>471</v>
-      </c>
-      <c r="E15" s="106" t="s">
-        <v>472</v>
-      </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
+      <c r="D15" s="114" t="s">
+        <v>474</v>
+      </c>
+      <c r="E15" s="114" t="s">
+        <v>475</v>
+      </c>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -12008,23 +12063,23 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="68">
+      <c r="A16" s="72">
         <v>9.0</v>
       </c>
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="107" t="s">
+      <c r="C16" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="106" t="s">
-        <v>473</v>
-      </c>
-      <c r="E16" s="106" t="s">
-        <v>474</v>
-      </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="D16" s="114" t="s">
+        <v>476</v>
+      </c>
+      <c r="E16" s="114" t="s">
+        <v>477</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
       <c r="J16" s="29"/>
@@ -12040,23 +12095,23 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="70">
+      <c r="A17" s="74">
         <v>10.0</v>
       </c>
-      <c r="B17" s="102" t="s">
+      <c r="B17" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="107" t="s">
+      <c r="C17" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="106" t="s">
-        <v>475</v>
-      </c>
-      <c r="E17" s="106" t="s">
-        <v>466</v>
-      </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40"/>
+      <c r="D17" s="114" t="s">
+        <v>478</v>
+      </c>
+      <c r="E17" s="114" t="s">
+        <v>469</v>
+      </c>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -12072,23 +12127,23 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="68">
+      <c r="A18" s="72">
         <v>12.0</v>
       </c>
-      <c r="B18" s="102" t="s">
+      <c r="B18" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="107" t="s">
+      <c r="C18" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="106" t="s">
-        <v>476</v>
-      </c>
-      <c r="E18" s="106" t="s">
-        <v>477</v>
-      </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40"/>
+      <c r="D18" s="114" t="s">
+        <v>479</v>
+      </c>
+      <c r="E18" s="114" t="s">
+        <v>480</v>
+      </c>
+      <c r="F18" s="40"/>
+      <c r="G18" s="41"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -12104,23 +12159,23 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="70">
+      <c r="A19" s="74">
         <v>11.0</v>
       </c>
-      <c r="B19" s="102" t="s">
+      <c r="B19" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="107" t="s">
+      <c r="C19" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="106" t="s">
-        <v>478</v>
-      </c>
-      <c r="E19" s="106" t="s">
-        <v>479</v>
-      </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40"/>
+      <c r="D19" s="114" t="s">
+        <v>481</v>
+      </c>
+      <c r="E19" s="114" t="s">
+        <v>482</v>
+      </c>
+      <c r="F19" s="40"/>
+      <c r="G19" s="41"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -12136,23 +12191,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="68">
+      <c r="A20" s="72">
         <v>13.0</v>
       </c>
-      <c r="B20" s="102" t="s">
+      <c r="B20" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="107" t="s">
+      <c r="C20" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="106" t="s">
+      <c r="D20" s="114" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="106" t="s">
-        <v>480</v>
-      </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40"/>
+      <c r="E20" s="114" t="s">
+        <v>483</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -12168,23 +12223,23 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="70">
+      <c r="A21" s="74">
         <v>14.0</v>
       </c>
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="107" t="s">
+      <c r="C21" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="106" t="s">
-        <v>469</v>
-      </c>
-      <c r="E21" s="106" t="s">
-        <v>481</v>
-      </c>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40"/>
+      <c r="D21" s="114" t="s">
+        <v>472</v>
+      </c>
+      <c r="E21" s="114" t="s">
+        <v>484</v>
+      </c>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -12200,23 +12255,23 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="68">
+      <c r="A22" s="72">
         <v>15.0</v>
       </c>
-      <c r="B22" s="102" t="s">
+      <c r="B22" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="103" t="s">
+      <c r="C22" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="104" t="s">
-        <v>482</v>
-      </c>
-      <c r="E22" s="104" t="s">
-        <v>483</v>
-      </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40"/>
+      <c r="D22" s="112" t="s">
+        <v>485</v>
+      </c>
+      <c r="E22" s="112" t="s">
+        <v>486</v>
+      </c>
+      <c r="F22" s="40"/>
+      <c r="G22" s="41"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -12232,23 +12287,23 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="70">
+      <c r="A23" s="74">
         <v>16.0</v>
       </c>
-      <c r="B23" s="102" t="s">
+      <c r="B23" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="103" t="s">
+      <c r="C23" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="104" t="s">
-        <v>484</v>
-      </c>
-      <c r="E23" s="104" t="s">
-        <v>485</v>
-      </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
+      <c r="D23" s="112" t="s">
+        <v>487</v>
+      </c>
+      <c r="E23" s="112" t="s">
+        <v>488</v>
+      </c>
+      <c r="F23" s="40"/>
+      <c r="G23" s="41"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -12264,23 +12319,23 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="68">
+      <c r="A24" s="72">
         <v>17.0</v>
       </c>
-      <c r="B24" s="102" t="s">
+      <c r="B24" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="103" t="s">
+      <c r="C24" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="104" t="s">
-        <v>486</v>
-      </c>
-      <c r="E24" s="104" t="s">
-        <v>487</v>
-      </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
+      <c r="D24" s="112" t="s">
+        <v>489</v>
+      </c>
+      <c r="E24" s="112" t="s">
+        <v>490</v>
+      </c>
+      <c r="F24" s="40"/>
+      <c r="G24" s="41"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -12296,23 +12351,23 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="68">
+      <c r="A25" s="72">
         <v>18.0</v>
       </c>
-      <c r="B25" s="102" t="s">
+      <c r="B25" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="103" t="s">
+      <c r="C25" s="111" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="104" t="s">
-        <v>488</v>
-      </c>
-      <c r="E25" s="104" t="s">
-        <v>489</v>
-      </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
+      <c r="D25" s="112" t="s">
+        <v>491</v>
+      </c>
+      <c r="E25" s="112" t="s">
+        <v>492</v>
+      </c>
+      <c r="F25" s="40"/>
+      <c r="G25" s="41"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -12328,23 +12383,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="68">
+      <c r="A26" s="72">
         <v>19.0</v>
       </c>
-      <c r="B26" s="102" t="s">
+      <c r="B26" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="103" t="s">
+      <c r="C26" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="104" t="s">
-        <v>490</v>
-      </c>
-      <c r="E26" s="104" t="s">
-        <v>466</v>
-      </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40"/>
+      <c r="D26" s="112" t="s">
+        <v>493</v>
+      </c>
+      <c r="E26" s="112" t="s">
+        <v>469</v>
+      </c>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -12360,23 +12415,23 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="68">
+      <c r="A27" s="72">
         <v>20.0</v>
       </c>
-      <c r="B27" s="102" t="s">
+      <c r="B27" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="103" t="s">
+      <c r="C27" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="104" t="s">
-        <v>491</v>
-      </c>
-      <c r="E27" s="104" t="s">
-        <v>481</v>
-      </c>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
+      <c r="D27" s="112" t="s">
+        <v>494</v>
+      </c>
+      <c r="E27" s="112" t="s">
+        <v>484</v>
+      </c>
+      <c r="F27" s="40"/>
+      <c r="G27" s="41"/>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
@@ -12392,23 +12447,23 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="68">
+      <c r="A28" s="72">
         <v>21.0</v>
       </c>
-      <c r="B28" s="102" t="s">
+      <c r="B28" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="103" t="s">
+      <c r="C28" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="104" t="s">
-        <v>492</v>
-      </c>
-      <c r="E28" s="104" t="s">
-        <v>493</v>
-      </c>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
+      <c r="D28" s="112" t="s">
+        <v>495</v>
+      </c>
+      <c r="E28" s="112" t="s">
+        <v>496</v>
+      </c>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -12424,23 +12479,23 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="68">
+      <c r="A29" s="72">
         <v>22.0</v>
       </c>
-      <c r="B29" s="102" t="s">
+      <c r="B29" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="103" t="s">
+      <c r="C29" s="111" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="104" t="s">
-        <v>494</v>
-      </c>
-      <c r="E29" s="104" t="s">
-        <v>179</v>
-      </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
+      <c r="D29" s="112" t="s">
+        <v>497</v>
+      </c>
+      <c r="E29" s="112" t="s">
+        <v>181</v>
+      </c>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -12456,23 +12511,23 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="68">
+      <c r="A30" s="72">
         <v>23.0</v>
       </c>
-      <c r="B30" s="102" t="s">
+      <c r="B30" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="103" t="s">
+      <c r="C30" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="104" t="s">
-        <v>495</v>
-      </c>
-      <c r="E30" s="104" t="s">
-        <v>496</v>
-      </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40"/>
+      <c r="D30" s="112" t="s">
+        <v>498</v>
+      </c>
+      <c r="E30" s="112" t="s">
+        <v>499</v>
+      </c>
+      <c r="F30" s="40"/>
+      <c r="G30" s="41"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -12488,23 +12543,23 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="70">
+      <c r="A31" s="74">
         <v>24.0</v>
       </c>
-      <c r="B31" s="102" t="s">
+      <c r="B31" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="103" t="s">
+      <c r="C31" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="104" t="s">
-        <v>276</v>
-      </c>
-      <c r="E31" s="104" t="s">
-        <v>497</v>
-      </c>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40"/>
+      <c r="D31" s="112" t="s">
+        <v>281</v>
+      </c>
+      <c r="E31" s="112" t="s">
+        <v>500</v>
+      </c>
+      <c r="F31" s="40"/>
+      <c r="G31" s="41"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -12520,23 +12575,23 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="68">
+      <c r="A32" s="72">
         <v>25.0</v>
       </c>
-      <c r="B32" s="102" t="s">
+      <c r="B32" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="103" t="s">
+      <c r="C32" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="104" t="s">
-        <v>498</v>
-      </c>
-      <c r="E32" s="104" t="s">
-        <v>483</v>
-      </c>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
+      <c r="D32" s="112" t="s">
+        <v>501</v>
+      </c>
+      <c r="E32" s="112" t="s">
+        <v>486</v>
+      </c>
+      <c r="F32" s="40"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -12552,23 +12607,23 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="70">
+      <c r="A33" s="74">
         <v>26.0</v>
       </c>
-      <c r="B33" s="102" t="s">
+      <c r="B33" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="103" t="s">
+      <c r="C33" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="104" t="s">
-        <v>499</v>
-      </c>
-      <c r="E33" s="104" t="s">
-        <v>500</v>
-      </c>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
+      <c r="D33" s="112" t="s">
+        <v>502</v>
+      </c>
+      <c r="E33" s="112" t="s">
+        <v>503</v>
+      </c>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>

--- a/public/data/@Liste GROUPE B.xlsx
+++ b/public/data/@Liste GROUPE B.xlsx
@@ -941,7 +941,7 @@
     <t>AMILICA</t>
   </si>
   <si>
-    <t>MADI BOUKARI</t>
+    <t>BOUKARI BOURDJA</t>
   </si>
   <si>
     <t>MICHAEL PERSHINGSON</t>
@@ -2246,7 +2246,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="11" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>

--- a/public/data/@Liste GROUPE B.xlsx
+++ b/public/data/@Liste GROUPE B.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="555">
   <si>
     <t xml:space="preserve">Équipe </t>
   </si>
@@ -401,10 +401,10 @@
     <t>2XL</t>
   </si>
   <si>
-    <t>DAVID ALEXANDRE</t>
-  </si>
-  <si>
-    <t>SIMOES</t>
+    <t xml:space="preserve">MULLER </t>
+  </si>
+  <si>
+    <t>TITINGUERA</t>
   </si>
   <si>
     <t>LÉO EMILIEN</t>
@@ -1544,10 +1544,7 @@
     <t>VÉRON</t>
   </si>
   <si>
-    <t>FAHMAN</t>
-  </si>
-  <si>
-    <t>GUIRO</t>
+    <t>MANA</t>
   </si>
   <si>
     <t>NOM DE L'ÉQUIPE :GUINÉE 🇬🇳</t>
@@ -2030,7 +2027,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2349,6 +2346,9 @@
     <xf borderId="1" fillId="3" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
@@ -2902,7 +2902,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2949,7 +2949,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3048,13 +3048,13 @@
         <v>184</v>
       </c>
       <c r="E8" s="73" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F8" s="40">
         <v>26.0</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -3084,13 +3084,13 @@
         <v>141</v>
       </c>
       <c r="E9" s="73" t="s">
+        <v>510</v>
+      </c>
+      <c r="F9" s="117">
+        <v>22.0</v>
+      </c>
+      <c r="G9" s="118" t="s">
         <v>511</v>
-      </c>
-      <c r="F9" s="116">
-        <v>22.0</v>
-      </c>
-      <c r="G9" s="117" t="s">
-        <v>512</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -3117,16 +3117,16 @@
         <v>76</v>
       </c>
       <c r="D10" s="73" t="s">
+        <v>512</v>
+      </c>
+      <c r="E10" s="73" t="s">
         <v>513</v>
       </c>
-      <c r="E10" s="73" t="s">
+      <c r="F10" s="117">
+        <v>30.0</v>
+      </c>
+      <c r="G10" s="118" t="s">
         <v>514</v>
-      </c>
-      <c r="F10" s="116">
-        <v>30.0</v>
-      </c>
-      <c r="G10" s="117" t="s">
-        <v>515</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -3149,20 +3149,20 @@
       <c r="B11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="118" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="73" t="s">
+        <v>515</v>
+      </c>
+      <c r="E11" s="73" t="s">
         <v>516</v>
       </c>
-      <c r="E11" s="73" t="s">
+      <c r="F11" s="117">
+        <v>25.0</v>
+      </c>
+      <c r="G11" s="118" t="s">
         <v>517</v>
-      </c>
-      <c r="F11" s="116">
-        <v>25.0</v>
-      </c>
-      <c r="G11" s="117" t="s">
-        <v>518</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11" s="29"/>
@@ -3185,18 +3185,18 @@
       <c r="B12" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="118" t="s">
         <v>76</v>
       </c>
       <c r="D12" s="73" t="s">
+        <v>518</v>
+      </c>
+      <c r="E12" s="73" t="s">
         <v>519</v>
-      </c>
-      <c r="E12" s="73" t="s">
-        <v>520</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="41" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -3219,20 +3219,20 @@
       <c r="B13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="118" t="s">
         <v>86</v>
       </c>
       <c r="D13" s="73" t="s">
         <v>394</v>
       </c>
       <c r="E13" s="73" t="s">
+        <v>521</v>
+      </c>
+      <c r="F13" s="117">
+        <v>25.0</v>
+      </c>
+      <c r="G13" s="118" t="s">
         <v>522</v>
-      </c>
-      <c r="F13" s="116">
-        <v>25.0</v>
-      </c>
-      <c r="G13" s="117" t="s">
-        <v>523</v>
       </c>
       <c r="H13" s="28"/>
       <c r="I13" s="29"/>
@@ -3255,20 +3255,20 @@
       <c r="B14" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="118" t="s">
         <v>94</v>
       </c>
       <c r="D14" s="73" t="s">
         <v>394</v>
       </c>
       <c r="E14" s="73" t="s">
-        <v>524</v>
-      </c>
-      <c r="F14" s="116">
+        <v>523</v>
+      </c>
+      <c r="F14" s="117">
         <v>30.0</v>
       </c>
-      <c r="G14" s="117" t="s">
-        <v>523</v>
+      <c r="G14" s="118" t="s">
+        <v>522</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
@@ -3295,16 +3295,16 @@
         <v>86</v>
       </c>
       <c r="D15" s="73" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E15" s="73" t="s">
+        <v>521</v>
+      </c>
+      <c r="F15" s="117">
+        <v>22.0</v>
+      </c>
+      <c r="G15" s="118" t="s">
         <v>522</v>
-      </c>
-      <c r="F15" s="116">
-        <v>22.0</v>
-      </c>
-      <c r="G15" s="117" t="s">
-        <v>523</v>
       </c>
       <c r="H15" s="28"/>
       <c r="I15" s="29"/>
@@ -3334,11 +3334,11 @@
         <v>363</v>
       </c>
       <c r="E16" s="73" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -3361,20 +3361,20 @@
       <c r="B17" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="118" t="s">
         <v>86</v>
       </c>
       <c r="D17" s="73" t="s">
+        <v>527</v>
+      </c>
+      <c r="E17" s="73" t="s">
         <v>528</v>
       </c>
-      <c r="E17" s="73" t="s">
-        <v>529</v>
-      </c>
-      <c r="F17" s="116">
+      <c r="F17" s="117">
         <v>27.0</v>
       </c>
-      <c r="G17" s="117" t="s">
-        <v>515</v>
+      <c r="G17" s="118" t="s">
+        <v>514</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
@@ -3397,20 +3397,20 @@
       <c r="B18" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="118" t="s">
         <v>94</v>
       </c>
       <c r="D18" s="73" t="s">
+        <v>529</v>
+      </c>
+      <c r="E18" s="73" t="s">
         <v>530</v>
       </c>
-      <c r="E18" s="73" t="s">
-        <v>531</v>
-      </c>
-      <c r="F18" s="116">
+      <c r="F18" s="117">
         <v>23.0</v>
       </c>
-      <c r="G18" s="117" t="s">
-        <v>523</v>
+      <c r="G18" s="118" t="s">
+        <v>522</v>
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
@@ -3433,20 +3433,20 @@
       <c r="B19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="118" t="s">
         <v>76</v>
       </c>
       <c r="D19" s="73" t="s">
         <v>179</v>
       </c>
       <c r="E19" s="73" t="s">
-        <v>532</v>
-      </c>
-      <c r="F19" s="116">
+        <v>531</v>
+      </c>
+      <c r="F19" s="117">
         <v>30.0</v>
       </c>
-      <c r="G19" s="117" t="s">
-        <v>515</v>
+      <c r="G19" s="118" t="s">
+        <v>514</v>
       </c>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
@@ -3469,18 +3469,18 @@
       <c r="B20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="117" t="s">
+      <c r="C20" s="118" t="s">
         <v>86</v>
       </c>
       <c r="D20" s="73" t="s">
+        <v>532</v>
+      </c>
+      <c r="E20" s="73" t="s">
         <v>533</v>
       </c>
-      <c r="E20" s="73" t="s">
-        <v>534</v>
-      </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="117" t="s">
-        <v>523</v>
+      <c r="G20" s="118" t="s">
+        <v>522</v>
       </c>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
@@ -3503,20 +3503,20 @@
       <c r="B21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="118" t="s">
         <v>94</v>
       </c>
       <c r="D21" s="73" t="s">
+        <v>534</v>
+      </c>
+      <c r="E21" s="73" t="s">
         <v>535</v>
       </c>
-      <c r="E21" s="73" t="s">
-        <v>536</v>
-      </c>
-      <c r="F21" s="116">
+      <c r="F21" s="117">
         <v>18.0</v>
       </c>
-      <c r="G21" s="117" t="s">
-        <v>521</v>
+      <c r="G21" s="118" t="s">
+        <v>520</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -3536,7 +3536,7 @@
       <c r="A22" s="72">
         <v>15.0</v>
       </c>
-      <c r="B22" s="118" t="s">
+      <c r="B22" s="119" t="s">
         <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -3546,13 +3546,13 @@
         <v>363</v>
       </c>
       <c r="E22" s="73" t="s">
-        <v>537</v>
-      </c>
-      <c r="F22" s="116">
+        <v>536</v>
+      </c>
+      <c r="F22" s="117">
         <v>23.0</v>
       </c>
-      <c r="G22" s="117" t="s">
-        <v>523</v>
+      <c r="G22" s="118" t="s">
+        <v>522</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -3572,23 +3572,23 @@
       <c r="A23" s="74">
         <v>16.0</v>
       </c>
-      <c r="B23" s="118" t="s">
+      <c r="B23" s="119" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="117" t="s">
+      <c r="C23" s="118" t="s">
         <v>86</v>
       </c>
       <c r="D23" s="73" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E23" s="73" t="s">
-        <v>514</v>
-      </c>
-      <c r="F23" s="116">
+        <v>513</v>
+      </c>
+      <c r="F23" s="117">
         <v>22.0</v>
       </c>
-      <c r="G23" s="117" t="s">
-        <v>523</v>
+      <c r="G23" s="118" t="s">
+        <v>522</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -3605,26 +3605,26 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="119">
+      <c r="A24" s="120">
         <v>17.0</v>
       </c>
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="121" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="121" t="s">
+      <c r="C24" s="122" t="s">
         <v>94</v>
       </c>
       <c r="D24" s="82" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E24" s="82" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="116">
+      <c r="F24" s="117">
         <v>30.0</v>
       </c>
-      <c r="G24" s="117" t="s">
-        <v>515</v>
+      <c r="G24" s="118" t="s">
+        <v>514</v>
       </c>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
@@ -3647,20 +3647,20 @@
       <c r="B25" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="117" t="s">
+      <c r="C25" s="118" t="s">
         <v>94</v>
       </c>
       <c r="D25" s="73" t="s">
         <v>358</v>
       </c>
       <c r="E25" s="73" t="s">
-        <v>540</v>
-      </c>
-      <c r="F25" s="116">
+        <v>539</v>
+      </c>
+      <c r="F25" s="117">
         <v>19.0</v>
       </c>
-      <c r="G25" s="117" t="s">
-        <v>523</v>
+      <c r="G25" s="118" t="s">
+        <v>522</v>
       </c>
       <c r="H25" s="28"/>
       <c r="I25" s="29"/>
@@ -3683,18 +3683,18 @@
       <c r="B26" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="117" t="s">
+      <c r="C26" s="118" t="s">
         <v>94</v>
       </c>
       <c r="D26" s="73" t="s">
+        <v>540</v>
+      </c>
+      <c r="E26" s="73" t="s">
         <v>541</v>
-      </c>
-      <c r="E26" s="73" t="s">
-        <v>542</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="32"/>
@@ -3717,20 +3717,20 @@
       <c r="B27" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="117" t="s">
+      <c r="C27" s="118" t="s">
         <v>86</v>
       </c>
       <c r="D27" s="73" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E27" s="73" t="s">
         <v>185</v>
       </c>
-      <c r="F27" s="116">
+      <c r="F27" s="117">
         <v>22.0</v>
       </c>
-      <c r="G27" s="117" t="s">
-        <v>521</v>
+      <c r="G27" s="118" t="s">
+        <v>520</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -3747,26 +3747,26 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="119">
+      <c r="A28" s="120">
         <v>21.0</v>
       </c>
-      <c r="B28" s="120" t="s">
+      <c r="B28" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="121" t="s">
+      <c r="C28" s="122" t="s">
         <v>94</v>
       </c>
       <c r="D28" s="82" t="s">
+        <v>543</v>
+      </c>
+      <c r="E28" s="82" t="s">
         <v>544</v>
-      </c>
-      <c r="E28" s="82" t="s">
-        <v>545</v>
       </c>
       <c r="F28" s="102">
         <v>23.0</v>
       </c>
       <c r="G28" s="103" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H28" s="64"/>
       <c r="I28" s="65"/>
@@ -3793,16 +3793,16 @@
         <v>76</v>
       </c>
       <c r="D29" s="73" t="s">
+        <v>545</v>
+      </c>
+      <c r="E29" s="73" t="s">
         <v>546</v>
-      </c>
-      <c r="E29" s="73" t="s">
-        <v>547</v>
       </c>
       <c r="F29" s="40">
         <v>22.0</v>
       </c>
       <c r="G29" s="41" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -3825,20 +3825,20 @@
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="117" t="s">
+      <c r="C30" s="118" t="s">
         <v>86</v>
       </c>
       <c r="D30" s="73" t="s">
+        <v>547</v>
+      </c>
+      <c r="E30" s="73" t="s">
         <v>548</v>
       </c>
-      <c r="E30" s="73" t="s">
+      <c r="F30" s="117">
+        <v>21.0</v>
+      </c>
+      <c r="G30" s="118" t="s">
         <v>549</v>
-      </c>
-      <c r="F30" s="116">
-        <v>21.0</v>
-      </c>
-      <c r="G30" s="117" t="s">
-        <v>550</v>
       </c>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
@@ -3865,16 +3865,16 @@
         <v>76</v>
       </c>
       <c r="D31" s="73" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E31" s="73" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F31" s="40">
         <v>30.0</v>
       </c>
       <c r="G31" s="41" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
@@ -3897,20 +3897,20 @@
       <c r="B32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="117" t="s">
+      <c r="C32" s="118" t="s">
         <v>76</v>
       </c>
       <c r="D32" s="73" t="s">
+        <v>551</v>
+      </c>
+      <c r="E32" s="73" t="s">
         <v>552</v>
       </c>
-      <c r="E32" s="73" t="s">
+      <c r="F32" s="123">
+        <v>23.0</v>
+      </c>
+      <c r="G32" s="124" t="s">
         <v>553</v>
-      </c>
-      <c r="F32" s="122">
-        <v>23.0</v>
-      </c>
-      <c r="G32" s="123" t="s">
-        <v>554</v>
       </c>
       <c r="H32" s="64"/>
       <c r="I32" s="65"/>
@@ -3937,14 +3937,14 @@
         <v>94</v>
       </c>
       <c r="D33" s="73" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E33" s="73" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F33" s="3"/>
-      <c r="G33" s="117" t="s">
-        <v>521</v>
+      <c r="G33" s="118" t="s">
+        <v>520</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -12616,11 +12616,11 @@
       <c r="C33" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="112" t="s">
+      <c r="D33" s="116" t="s">
+        <v>181</v>
+      </c>
+      <c r="E33" s="116" t="s">
         <v>502</v>
-      </c>
-      <c r="E33" s="112" t="s">
-        <v>503</v>
       </c>
       <c r="F33" s="40"/>
       <c r="G33" s="41"/>

--- a/public/data/@Liste GROUPE B.xlsx
+++ b/public/data/@Liste GROUPE B.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="559">
   <si>
     <t xml:space="preserve">Équipe </t>
   </si>
@@ -314,10 +314,10 @@
     <t>MOSA</t>
   </si>
   <si>
-    <t>DAN MWIMBA</t>
-  </si>
-  <si>
-    <t>MULEDI</t>
+    <t>JEANCY</t>
+  </si>
+  <si>
+    <t>KAYOLO</t>
   </si>
   <si>
     <t>4-ATTAQUANT</t>
@@ -368,7 +368,10 @@
     <t>JUMAINE</t>
   </si>
   <si>
-    <t>REPOSE</t>
+    <t xml:space="preserve">THIERNO MAMADOU </t>
+  </si>
+  <si>
+    <t>BA</t>
   </si>
   <si>
     <t>VIGOR</t>
@@ -407,10 +410,10 @@
     <t>TITINGUERA</t>
   </si>
   <si>
-    <t>LÉO EMILIEN</t>
-  </si>
-  <si>
-    <t>NKOA</t>
+    <t>MIKE OSCAR</t>
+  </si>
+  <si>
+    <t>ILOUD</t>
   </si>
   <si>
     <t>ESPOIR</t>
@@ -710,7 +713,10 @@
     <t>Dosso</t>
   </si>
   <si>
-    <t>AHOGAN</t>
+    <t>FIACRE</t>
+  </si>
+  <si>
+    <t>KOFFI</t>
   </si>
   <si>
     <t>DANIEL KOMLAN</t>
@@ -1130,6 +1136,9 @@
     <t>MOUSSA</t>
   </si>
   <si>
+    <t>DJIGUI</t>
+  </si>
+  <si>
     <t>MOHAMED</t>
   </si>
   <si>
@@ -1493,57 +1502,57 @@
     <t>ZONGO</t>
   </si>
   <si>
-    <t>ELVIS</t>
+    <t>KECOUTA</t>
+  </si>
+  <si>
+    <t>ABDOUL</t>
+  </si>
+  <si>
+    <t>OUÉDRAOGO</t>
+  </si>
+  <si>
+    <t>MAX ILDEVER WENDPOUIRÉ</t>
+  </si>
+  <si>
+    <t>SOUILI</t>
+  </si>
+  <si>
+    <t>CHATELAIN</t>
+  </si>
+  <si>
+    <t>YADJUI</t>
+  </si>
+  <si>
+    <t>SOUHOUDOU</t>
+  </si>
+  <si>
+    <t>MICHEL DONALD</t>
+  </si>
+  <si>
+    <t>MAT-JUNIOR</t>
+  </si>
+  <si>
+    <t>SOBJANG NDJATOU</t>
+  </si>
+  <si>
+    <t>LASSINA</t>
+  </si>
+  <si>
+    <t>WILFREID</t>
+  </si>
+  <si>
+    <t>KINDO</t>
+  </si>
+  <si>
+    <t>ASSAGOU</t>
+  </si>
+  <si>
+    <t>VÉRON</t>
   </si>
   <si>
     <t>KABORÉ</t>
   </si>
   <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>NDJIEUNDE</t>
-  </si>
-  <si>
-    <t>MAX ILDEVER WENDPOUIRÉ</t>
-  </si>
-  <si>
-    <t>SOUILI</t>
-  </si>
-  <si>
-    <t>CHATELAIN</t>
-  </si>
-  <si>
-    <t>YADJUI</t>
-  </si>
-  <si>
-    <t>SOUHOUDOU</t>
-  </si>
-  <si>
-    <t>MICHEL DONALD</t>
-  </si>
-  <si>
-    <t>MAT-JUNIOR</t>
-  </si>
-  <si>
-    <t>SOBJANG NDJATOU</t>
-  </si>
-  <si>
-    <t>LASSINA</t>
-  </si>
-  <si>
-    <t>WILFREID</t>
-  </si>
-  <si>
-    <t>KINDO</t>
-  </si>
-  <si>
-    <t>ASSAGOU</t>
-  </si>
-  <si>
-    <t>VÉRON</t>
-  </si>
-  <si>
     <t>MANA</t>
   </si>
   <si>
@@ -1556,13 +1565,16 @@
     <t>TÉL D'URGENCE : 4182658413</t>
   </si>
   <si>
-    <t>NOM DU COACH : Frédérick</t>
+    <t>NOM DU COACH : BOUBACAR NABÉ</t>
   </si>
   <si>
     <t>NOM DU CAPITAINE : Moustapha Donzo</t>
   </si>
   <si>
-    <t>BAH</t>
+    <t>ANGA</t>
+  </si>
+  <si>
+    <t>JOSUÉ</t>
   </si>
   <si>
     <t>Guinéen</t>
@@ -1664,50 +1676,50 @@
     <t>DIANE</t>
   </si>
   <si>
+    <t>SAIDOU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEVE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DABIRÉ </t>
+  </si>
+  <si>
+    <t>AMADOU</t>
+  </si>
+  <si>
+    <t>CHERIF</t>
+  </si>
+  <si>
+    <t>DARSY</t>
+  </si>
+  <si>
+    <t>BIGNOUMBA</t>
+  </si>
+  <si>
+    <t>Gabonaise</t>
+  </si>
+  <si>
+    <t>ELHADJ</t>
+  </si>
+  <si>
+    <t>DICKO SIDI MOUCTAR</t>
+  </si>
+  <si>
+    <t>KEITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guinee </t>
+  </si>
+  <si>
     <t>MAMADOU KINDY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEVE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DABIRÉ </t>
-  </si>
-  <si>
-    <t>AMADOU</t>
-  </si>
-  <si>
-    <t>CHERIF</t>
-  </si>
-  <si>
-    <t>DARSY</t>
-  </si>
-  <si>
-    <t>BIGNOUMBA</t>
-  </si>
-  <si>
-    <t>Gabonaise</t>
-  </si>
-  <si>
-    <t>ELHADJ AMADOU</t>
-  </si>
-  <si>
-    <t>DICKO SIDI MOUCTAR</t>
-  </si>
-  <si>
-    <t>KEITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guinee </t>
-  </si>
-  <si>
-    <t>SAIDOU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="34">
+  <fonts count="37">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1791,7 +1803,7 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1832,6 +1844,11 @@
       <sz val="12.0"/>
       <color rgb="FF434343"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -1875,6 +1892,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="18.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="16.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1885,8 +1907,12 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1945,6 +1971,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF6F8F9"/>
         <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9900FF"/>
+        <bgColor rgb="FF9900FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -2027,7 +2059,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="131">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2106,10 +2138,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2140,6 +2172,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2200,11 +2235,11 @@
     <xf borderId="0" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="11" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
@@ -2233,16 +2268,16 @@
     <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="11" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="12" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2257,7 +2292,7 @@
     <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2269,37 +2304,40 @@
     <xf borderId="6" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="8" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="11" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2314,7 +2352,7 @@
     <xf borderId="1" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2331,7 +2369,7 @@
     <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="36" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2343,11 +2381,17 @@
     <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="36" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -2366,6 +2410,12 @@
     </xf>
     <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -2902,7 +2952,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2925,7 +2975,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2937,7 +2987,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2948,8 +2998,8 @@
       <c r="H3" s="13"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>506</v>
+      <c r="A4" s="119" t="s">
+        <v>509</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -2961,7 +3011,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3035,26 +3085,26 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="72">
+      <c r="A8" s="73">
         <v>1.0</v>
       </c>
-      <c r="B8" s="73" t="s">
+      <c r="B8" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>508</v>
+      <c r="D8" s="120" t="s">
+        <v>511</v>
+      </c>
+      <c r="E8" s="120" t="s">
+        <v>512</v>
       </c>
       <c r="F8" s="40">
         <v>26.0</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -3071,26 +3121,26 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="74">
+      <c r="A9" s="75">
         <v>2.0</v>
       </c>
-      <c r="B9" s="73" t="s">
+      <c r="B9" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="73" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" s="73" t="s">
-        <v>510</v>
-      </c>
-      <c r="F9" s="117">
+      <c r="D9" s="74" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="74" t="s">
+        <v>514</v>
+      </c>
+      <c r="F9" s="121">
         <v>22.0</v>
       </c>
-      <c r="G9" s="118" t="s">
-        <v>511</v>
+      <c r="G9" s="122" t="s">
+        <v>515</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -3107,7 +3157,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="72">
+      <c r="A10" s="73">
         <v>3.0</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -3116,17 +3166,17 @@
       <c r="C10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="73" t="s">
-        <v>512</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>513</v>
-      </c>
-      <c r="F10" s="117">
+      <c r="D10" s="74" t="s">
+        <v>516</v>
+      </c>
+      <c r="E10" s="74" t="s">
+        <v>517</v>
+      </c>
+      <c r="F10" s="121">
         <v>30.0</v>
       </c>
-      <c r="G10" s="118" t="s">
-        <v>514</v>
+      <c r="G10" s="122" t="s">
+        <v>518</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -3143,26 +3193,26 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="72">
+      <c r="A11" s="73">
         <v>4.0</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="118" t="s">
+      <c r="C11" s="122" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="73" t="s">
-        <v>515</v>
-      </c>
-      <c r="E11" s="73" t="s">
-        <v>516</v>
-      </c>
-      <c r="F11" s="117">
+      <c r="D11" s="74" t="s">
+        <v>519</v>
+      </c>
+      <c r="E11" s="74" t="s">
+        <v>520</v>
+      </c>
+      <c r="F11" s="121">
         <v>25.0</v>
       </c>
-      <c r="G11" s="118" t="s">
-        <v>517</v>
+      <c r="G11" s="122" t="s">
+        <v>521</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11" s="29"/>
@@ -3179,24 +3229,24 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="72">
+      <c r="A12" s="73">
         <v>5.0</v>
       </c>
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="118" t="s">
+      <c r="C12" s="122" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="73" t="s">
-        <v>518</v>
-      </c>
-      <c r="E12" s="73" t="s">
-        <v>519</v>
+      <c r="D12" s="74" t="s">
+        <v>522</v>
+      </c>
+      <c r="E12" s="74" t="s">
+        <v>523</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="41" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -3213,26 +3263,26 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="72">
+      <c r="A13" s="73">
         <v>6.0</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="118" t="s">
+      <c r="C13" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="73" t="s">
-        <v>394</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>521</v>
-      </c>
-      <c r="F13" s="117">
+      <c r="D13" s="74" t="s">
+        <v>397</v>
+      </c>
+      <c r="E13" s="74" t="s">
+        <v>525</v>
+      </c>
+      <c r="F13" s="121">
         <v>25.0</v>
       </c>
-      <c r="G13" s="118" t="s">
-        <v>522</v>
+      <c r="G13" s="122" t="s">
+        <v>526</v>
       </c>
       <c r="H13" s="28"/>
       <c r="I13" s="29"/>
@@ -3249,26 +3299,26 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="72">
+      <c r="A14" s="73">
         <v>7.0</v>
       </c>
-      <c r="B14" s="73" t="s">
+      <c r="B14" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="118" t="s">
+      <c r="C14" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="73" t="s">
-        <v>394</v>
-      </c>
-      <c r="E14" s="73" t="s">
-        <v>523</v>
-      </c>
-      <c r="F14" s="117">
+      <c r="D14" s="74" t="s">
+        <v>397</v>
+      </c>
+      <c r="E14" s="74" t="s">
+        <v>527</v>
+      </c>
+      <c r="F14" s="121">
         <v>30.0</v>
       </c>
-      <c r="G14" s="118" t="s">
-        <v>522</v>
+      <c r="G14" s="122" t="s">
+        <v>526</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
@@ -3285,7 +3335,7 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="72">
+      <c r="A15" s="73">
         <v>8.0</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3294,17 +3344,17 @@
       <c r="C15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="73" t="s">
-        <v>524</v>
-      </c>
-      <c r="E15" s="73" t="s">
-        <v>521</v>
-      </c>
-      <c r="F15" s="117">
+      <c r="D15" s="74" t="s">
+        <v>528</v>
+      </c>
+      <c r="E15" s="74" t="s">
+        <v>525</v>
+      </c>
+      <c r="F15" s="121">
         <v>22.0</v>
       </c>
-      <c r="G15" s="118" t="s">
-        <v>522</v>
+      <c r="G15" s="122" t="s">
+        <v>526</v>
       </c>
       <c r="H15" s="28"/>
       <c r="I15" s="29"/>
@@ -3321,24 +3371,24 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="72">
+      <c r="A16" s="73">
         <v>9.0</v>
       </c>
-      <c r="B16" s="73" t="s">
+      <c r="B16" s="74" t="s">
         <v>102</v>
       </c>
       <c r="C16" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="73" t="s">
-        <v>363</v>
-      </c>
-      <c r="E16" s="73" t="s">
-        <v>525</v>
+      <c r="D16" s="74" t="s">
+        <v>365</v>
+      </c>
+      <c r="E16" s="74" t="s">
+        <v>529</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -3355,26 +3405,26 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="74">
+      <c r="A17" s="75">
         <v>10.0</v>
       </c>
-      <c r="B17" s="73" t="s">
+      <c r="B17" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="118" t="s">
+      <c r="C17" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="73" t="s">
-        <v>527</v>
-      </c>
-      <c r="E17" s="73" t="s">
-        <v>528</v>
-      </c>
-      <c r="F17" s="117">
+      <c r="D17" s="74" t="s">
+        <v>531</v>
+      </c>
+      <c r="E17" s="74" t="s">
+        <v>532</v>
+      </c>
+      <c r="F17" s="121">
         <v>27.0</v>
       </c>
-      <c r="G17" s="118" t="s">
-        <v>514</v>
+      <c r="G17" s="122" t="s">
+        <v>518</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
@@ -3391,26 +3441,26 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="72">
+      <c r="A18" s="73">
         <v>11.0</v>
       </c>
-      <c r="B18" s="73" t="s">
+      <c r="B18" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="118" t="s">
+      <c r="C18" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="73" t="s">
-        <v>529</v>
-      </c>
-      <c r="E18" s="73" t="s">
-        <v>530</v>
-      </c>
-      <c r="F18" s="117">
+      <c r="D18" s="74" t="s">
+        <v>533</v>
+      </c>
+      <c r="E18" s="74" t="s">
+        <v>534</v>
+      </c>
+      <c r="F18" s="121">
         <v>23.0</v>
       </c>
-      <c r="G18" s="118" t="s">
-        <v>522</v>
+      <c r="G18" s="122" t="s">
+        <v>526</v>
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
@@ -3427,26 +3477,26 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="74">
+      <c r="A19" s="75">
         <v>12.0</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="118" t="s">
+      <c r="C19" s="122" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="73" t="s">
-        <v>179</v>
-      </c>
-      <c r="E19" s="73" t="s">
-        <v>531</v>
-      </c>
-      <c r="F19" s="117">
+      <c r="D19" s="74" t="s">
+        <v>180</v>
+      </c>
+      <c r="E19" s="74" t="s">
+        <v>535</v>
+      </c>
+      <c r="F19" s="121">
         <v>30.0</v>
       </c>
-      <c r="G19" s="118" t="s">
-        <v>514</v>
+      <c r="G19" s="122" t="s">
+        <v>518</v>
       </c>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
@@ -3463,24 +3513,24 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="74">
+      <c r="A20" s="75">
         <v>13.0</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="118" t="s">
+      <c r="C20" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="73" t="s">
-        <v>532</v>
-      </c>
-      <c r="E20" s="73" t="s">
-        <v>533</v>
+      <c r="D20" s="74" t="s">
+        <v>536</v>
+      </c>
+      <c r="E20" s="74" t="s">
+        <v>537</v>
       </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="118" t="s">
-        <v>522</v>
+      <c r="G20" s="122" t="s">
+        <v>526</v>
       </c>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
@@ -3497,26 +3547,26 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="74">
+      <c r="A21" s="75">
         <v>14.0</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="118" t="s">
+      <c r="C21" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="73" t="s">
-        <v>534</v>
-      </c>
-      <c r="E21" s="73" t="s">
-        <v>535</v>
-      </c>
-      <c r="F21" s="117">
+      <c r="D21" s="74" t="s">
+        <v>538</v>
+      </c>
+      <c r="E21" s="74" t="s">
+        <v>539</v>
+      </c>
+      <c r="F21" s="121">
         <v>18.0</v>
       </c>
-      <c r="G21" s="118" t="s">
-        <v>520</v>
+      <c r="G21" s="122" t="s">
+        <v>524</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -3533,26 +3583,26 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="72">
+      <c r="A22" s="73">
         <v>15.0</v>
       </c>
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="123" t="s">
         <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="73" t="s">
-        <v>363</v>
-      </c>
-      <c r="E22" s="73" t="s">
-        <v>536</v>
-      </c>
-      <c r="F22" s="117">
+      <c r="D22" s="74" t="s">
+        <v>365</v>
+      </c>
+      <c r="E22" s="74" t="s">
+        <v>540</v>
+      </c>
+      <c r="F22" s="121">
         <v>23.0</v>
       </c>
-      <c r="G22" s="118" t="s">
-        <v>522</v>
+      <c r="G22" s="122" t="s">
+        <v>526</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -3569,26 +3619,26 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="74">
+      <c r="A23" s="75">
         <v>16.0</v>
       </c>
-      <c r="B23" s="119" t="s">
+      <c r="B23" s="123" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="118" t="s">
+      <c r="C23" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="73" t="s">
-        <v>537</v>
-      </c>
-      <c r="E23" s="73" t="s">
-        <v>513</v>
-      </c>
-      <c r="F23" s="117">
+      <c r="D23" s="74" t="s">
+        <v>541</v>
+      </c>
+      <c r="E23" s="74" t="s">
+        <v>517</v>
+      </c>
+      <c r="F23" s="121">
         <v>22.0</v>
       </c>
-      <c r="G23" s="118" t="s">
-        <v>522</v>
+      <c r="G23" s="122" t="s">
+        <v>526</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -3605,26 +3655,26 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="120">
+      <c r="A24" s="124">
         <v>17.0</v>
       </c>
-      <c r="B24" s="121" t="s">
+      <c r="B24" s="125" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="122" t="s">
+      <c r="C24" s="126" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="82" t="s">
-        <v>538</v>
-      </c>
-      <c r="E24" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="F24" s="117">
+      <c r="D24" s="83" t="s">
+        <v>542</v>
+      </c>
+      <c r="E24" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="F24" s="121">
         <v>30.0</v>
       </c>
-      <c r="G24" s="118" t="s">
-        <v>514</v>
+      <c r="G24" s="122" t="s">
+        <v>518</v>
       </c>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
@@ -3641,26 +3691,26 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="72">
+      <c r="A25" s="73">
         <v>18.0</v>
       </c>
-      <c r="B25" s="73" t="s">
+      <c r="B25" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="118" t="s">
+      <c r="C25" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="73" t="s">
-        <v>358</v>
-      </c>
-      <c r="E25" s="73" t="s">
-        <v>539</v>
-      </c>
-      <c r="F25" s="117">
+      <c r="D25" s="74" t="s">
+        <v>360</v>
+      </c>
+      <c r="E25" s="74" t="s">
+        <v>543</v>
+      </c>
+      <c r="F25" s="121">
         <v>19.0</v>
       </c>
-      <c r="G25" s="118" t="s">
-        <v>522</v>
+      <c r="G25" s="122" t="s">
+        <v>526</v>
       </c>
       <c r="H25" s="28"/>
       <c r="I25" s="29"/>
@@ -3677,24 +3727,24 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="74">
+      <c r="A26" s="75">
         <v>19.0</v>
       </c>
-      <c r="B26" s="73" t="s">
+      <c r="B26" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="118" t="s">
+      <c r="C26" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="73" t="s">
-        <v>540</v>
-      </c>
-      <c r="E26" s="73" t="s">
-        <v>541</v>
+      <c r="D26" s="74" t="s">
+        <v>544</v>
+      </c>
+      <c r="E26" s="74" t="s">
+        <v>545</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="32"/>
@@ -3711,26 +3761,24 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="74">
+      <c r="A27" s="127">
         <v>20.0</v>
       </c>
-      <c r="B27" s="73" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="118" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="73" t="s">
-        <v>542</v>
-      </c>
-      <c r="E27" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="F27" s="117">
-        <v>22.0</v>
-      </c>
-      <c r="G27" s="118" t="s">
-        <v>520</v>
+      <c r="B27" s="74" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="74" t="s">
+        <v>546</v>
+      </c>
+      <c r="E27" s="74" t="s">
+        <v>534</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="122" t="s">
+        <v>524</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -3747,62 +3795,62 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="120">
+      <c r="A28" s="124">
         <v>21.0</v>
       </c>
-      <c r="B28" s="121" t="s">
+      <c r="B28" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="122" t="s">
+      <c r="C28" s="126" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="82" t="s">
-        <v>543</v>
-      </c>
-      <c r="E28" s="82" t="s">
-        <v>544</v>
-      </c>
-      <c r="F28" s="102">
+      <c r="D28" s="83" t="s">
+        <v>547</v>
+      </c>
+      <c r="E28" s="83" t="s">
+        <v>548</v>
+      </c>
+      <c r="F28" s="104">
         <v>23.0</v>
       </c>
-      <c r="G28" s="103" t="s">
-        <v>520</v>
-      </c>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="65"/>
-      <c r="P28" s="65"/>
-      <c r="Q28" s="64">
+      <c r="G28" s="105" t="s">
+        <v>524</v>
+      </c>
+      <c r="H28" s="65"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
+      <c r="L28" s="66"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="66"/>
+      <c r="P28" s="66"/>
+      <c r="Q28" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="74">
+      <c r="A29" s="75">
         <v>22.0</v>
       </c>
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="74" t="s">
         <v>102</v>
       </c>
       <c r="C29" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="73" t="s">
-        <v>545</v>
-      </c>
-      <c r="E29" s="73" t="s">
-        <v>546</v>
+      <c r="D29" s="74" t="s">
+        <v>549</v>
+      </c>
+      <c r="E29" s="74" t="s">
+        <v>550</v>
       </c>
       <c r="F29" s="40">
         <v>22.0</v>
       </c>
       <c r="G29" s="41" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -3819,26 +3867,26 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="74">
+      <c r="A30" s="75">
         <v>23.0</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="118" t="s">
+      <c r="C30" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="73" t="s">
-        <v>547</v>
-      </c>
-      <c r="E30" s="73" t="s">
-        <v>548</v>
-      </c>
-      <c r="F30" s="117">
+      <c r="D30" s="74" t="s">
+        <v>551</v>
+      </c>
+      <c r="E30" s="74" t="s">
+        <v>552</v>
+      </c>
+      <c r="F30" s="121">
         <v>21.0</v>
       </c>
-      <c r="G30" s="118" t="s">
-        <v>549</v>
+      <c r="G30" s="122" t="s">
+        <v>553</v>
       </c>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
@@ -3855,26 +3903,26 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="74">
+      <c r="A31" s="75">
         <v>24.0</v>
       </c>
-      <c r="B31" s="73" t="s">
+      <c r="B31" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="73" t="s">
-        <v>550</v>
-      </c>
-      <c r="E31" s="73" t="s">
-        <v>513</v>
+      <c r="D31" s="128" t="s">
+        <v>554</v>
+      </c>
+      <c r="E31" s="74" t="s">
+        <v>517</v>
       </c>
       <c r="F31" s="40">
         <v>30.0</v>
       </c>
       <c r="G31" s="41" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
@@ -3891,60 +3939,62 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="74">
+      <c r="A32" s="75">
         <v>25.0</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="118" t="s">
+      <c r="C32" s="122" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="73" t="s">
-        <v>551</v>
-      </c>
-      <c r="E32" s="73" t="s">
-        <v>552</v>
-      </c>
-      <c r="F32" s="123">
+      <c r="D32" s="74" t="s">
+        <v>555</v>
+      </c>
+      <c r="E32" s="74" t="s">
+        <v>556</v>
+      </c>
+      <c r="F32" s="129">
         <v>23.0</v>
       </c>
-      <c r="G32" s="124" t="s">
-        <v>553</v>
-      </c>
-      <c r="H32" s="64"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65"/>
-      <c r="L32" s="65"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="65"/>
-      <c r="O32" s="65"/>
-      <c r="P32" s="65"/>
-      <c r="Q32" s="64">
+      <c r="G32" s="130" t="s">
+        <v>557</v>
+      </c>
+      <c r="H32" s="65"/>
+      <c r="I32" s="66"/>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="66"/>
+      <c r="M32" s="66"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="66"/>
+      <c r="P32" s="66"/>
+      <c r="Q32" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="74">
+      <c r="A33" s="127">
         <v>26.0</v>
       </c>
-      <c r="B33" s="73" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="73" t="s">
-        <v>554</v>
-      </c>
-      <c r="E33" s="73" t="s">
-        <v>530</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="118" t="s">
-        <v>520</v>
+      <c r="B33" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="122" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="74" t="s">
+        <v>558</v>
+      </c>
+      <c r="E33" s="74" t="s">
+        <v>186</v>
+      </c>
+      <c r="F33" s="121">
+        <v>22.0</v>
+      </c>
+      <c r="G33" s="122" t="s">
+        <v>524</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -4462,7 +4512,7 @@
       <c r="C15" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="35" t="s">
         <v>92</v>
       </c>
       <c r="E15" s="35" t="s">
@@ -4721,11 +4771,11 @@
       <c r="C22" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="26" t="s">
+      <c r="D22" s="34" t="s">
         <v>110</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>111</v>
       </c>
       <c r="F22" s="26"/>
       <c r="G22" s="26" t="s">
@@ -4759,10 +4809,10 @@
         <v>94</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F23" s="26"/>
       <c r="G23" s="26" t="s">
@@ -4796,14 +4846,14 @@
         <v>94</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F24" s="26"/>
       <c r="G24" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H24" s="33"/>
       <c r="I24" s="33"/>
@@ -4836,7 +4886,7 @@
         <v>95</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F25" s="26"/>
       <c r="G25" s="26" t="s">
@@ -4870,14 +4920,14 @@
         <v>94</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F26" s="26"/>
       <c r="G26" s="26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
@@ -4901,16 +4951,16 @@
         <v>20.0</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C27" s="26" t="s">
         <v>76</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F27" s="26"/>
       <c r="G27" s="26" t="s">
@@ -4943,11 +4993,11 @@
       <c r="C28" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="E28" s="26" t="s">
+      <c r="D28" s="34" t="s">
         <v>124</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>125</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="26" t="s">
@@ -4981,10 +5031,10 @@
         <v>86</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="26" t="s">
@@ -5018,10 +5068,10 @@
         <v>76</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F30" s="26"/>
       <c r="G30" s="26" t="s">
@@ -5055,10 +5105,10 @@
         <v>76</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F31" s="26"/>
       <c r="G31" s="26" t="s">
@@ -5092,10 +5142,10 @@
         <v>94</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F32" s="26"/>
       <c r="G32" s="26" t="s">
@@ -5129,10 +5179,10 @@
         <v>76</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F33" s="26"/>
       <c r="G33" s="26" t="s">
@@ -5213,7 +5263,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5236,7 +5286,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5248,7 +5298,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -5260,7 +5310,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -5272,7 +5322,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -5297,7 +5347,7 @@
         <v>50</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>52</v>
@@ -5356,10 +5406,10 @@
         <v>68</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F8" s="40"/>
       <c r="G8" s="41"/>
@@ -5388,10 +5438,10 @@
         <v>76</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F9" s="40"/>
       <c r="G9" s="41"/>
@@ -5420,10 +5470,10 @@
         <v>76</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F10" s="40"/>
       <c r="G10" s="41"/>
@@ -5452,10 +5502,10 @@
         <v>76</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="41"/>
@@ -5484,10 +5534,10 @@
         <v>86</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="41"/>
@@ -5516,10 +5566,10 @@
         <v>86</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="41"/>
@@ -5548,10 +5598,10 @@
         <v>86</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="41"/>
@@ -5580,10 +5630,10 @@
         <v>86</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F15" s="40"/>
       <c r="G15" s="41"/>
@@ -5612,10 +5662,10 @@
         <v>86</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E16" s="43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41"/>
@@ -5644,10 +5694,10 @@
         <v>86</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F17" s="40"/>
       <c r="G17" s="41"/>
@@ -5676,10 +5726,10 @@
         <v>94</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F18" s="40"/>
       <c r="G18" s="41"/>
@@ -5708,10 +5758,10 @@
         <v>76</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F19" s="40"/>
       <c r="G19" s="41"/>
@@ -5740,10 +5790,10 @@
         <v>94</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F20" s="40"/>
       <c r="G20" s="41"/>
@@ -5772,10 +5822,10 @@
         <v>86</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F21" s="40"/>
       <c r="G21" s="41"/>
@@ -5804,10 +5854,10 @@
         <v>86</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="41"/>
@@ -5835,11 +5885,11 @@
       <c r="C23" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23" s="34" t="s">
+      <c r="D23" s="46" t="s">
         <v>168</v>
+      </c>
+      <c r="E23" s="46" t="s">
+        <v>169</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="41"/>
@@ -5868,10 +5918,10 @@
         <v>76</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F24" s="40"/>
       <c r="G24" s="41"/>
@@ -5900,10 +5950,10 @@
         <v>94</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F25" s="40"/>
       <c r="G25" s="41"/>
@@ -5932,10 +5982,10 @@
         <v>94</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41"/>
@@ -5954,7 +6004,7 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="46">
+      <c r="A27" s="47">
         <v>20.0</v>
       </c>
       <c r="B27" s="23" t="s">
@@ -5964,10 +6014,10 @@
         <v>94</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="41"/>
@@ -5996,10 +6046,10 @@
         <v>86</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="41"/>
@@ -6028,10 +6078,10 @@
         <v>94</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="41"/>
@@ -6060,10 +6110,10 @@
         <v>76</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F30" s="40"/>
       <c r="G30" s="41"/>
@@ -6092,10 +6142,10 @@
         <v>76</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E31" s="43" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F31" s="40"/>
       <c r="G31" s="41"/>
@@ -6124,10 +6174,10 @@
         <v>86</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F32" s="40"/>
       <c r="G32" s="41"/>
@@ -6155,11 +6205,11 @@
       <c r="C33" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="E33" s="34" t="s">
+      <c r="D33" s="46" t="s">
         <v>185</v>
+      </c>
+      <c r="E33" s="46" t="s">
+        <v>186</v>
       </c>
       <c r="F33" s="40"/>
       <c r="G33" s="41"/>
@@ -6241,7 +6291,7 @@
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="6"/>
@@ -6266,7 +6316,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
@@ -6280,7 +6330,7 @@
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
       <c r="E3" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -6294,7 +6344,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -6308,7 +6358,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -6331,7 +6381,7 @@
       <c r="B7" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="20" t="s">
@@ -6378,24 +6428,24 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="48">
+      <c r="A8" s="49">
         <v>1.0</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="E8" s="51" t="s">
+      <c r="D8" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="53" t="s">
+      <c r="E8" s="52" t="s">
         <v>193</v>
+      </c>
+      <c r="F8" s="53"/>
+      <c r="G8" s="54" t="s">
+        <v>194</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -6412,24 +6462,24 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="54">
+      <c r="A9" s="55">
         <v>2.0</v>
       </c>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="55" t="s">
-        <v>194</v>
-      </c>
-      <c r="E9" s="55" t="s">
+      <c r="D9" s="56" t="s">
         <v>195</v>
       </c>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56" t="s">
-        <v>186</v>
+      <c r="E9" s="56" t="s">
+        <v>196</v>
+      </c>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57" t="s">
+        <v>187</v>
       </c>
       <c r="H9" s="28"/>
       <c r="I9" s="29"/>
@@ -6446,24 +6496,24 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="54">
+      <c r="A10" s="55">
         <v>3.0</v>
       </c>
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" s="55" t="s">
+      <c r="D10" s="56" t="s">
         <v>197</v>
       </c>
-      <c r="F10" s="52"/>
-      <c r="G10" s="53" t="s">
-        <v>186</v>
+      <c r="E10" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="53"/>
+      <c r="G10" s="54" t="s">
+        <v>187</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -6480,24 +6530,24 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="48">
+      <c r="A11" s="49">
         <v>4.0</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="E11" s="51" t="s">
+      <c r="D11" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="F11" s="57"/>
-      <c r="G11" s="56" t="s">
-        <v>186</v>
+      <c r="E11" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="F11" s="58"/>
+      <c r="G11" s="57" t="s">
+        <v>187</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
@@ -6514,24 +6564,24 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="48">
+      <c r="A12" s="49">
         <v>5.0</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E12" s="51" t="s">
+      <c r="D12" s="52" t="s">
         <v>201</v>
       </c>
-      <c r="F12" s="52"/>
-      <c r="G12" s="53" t="s">
-        <v>186</v>
+      <c r="E12" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="F12" s="53"/>
+      <c r="G12" s="54" t="s">
+        <v>187</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -6548,24 +6598,24 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="48">
+      <c r="A13" s="49">
         <v>6.0</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="51" t="s">
-        <v>202</v>
-      </c>
-      <c r="E13" s="51" t="s">
+      <c r="D13" s="52" t="s">
         <v>203</v>
       </c>
-      <c r="F13" s="57"/>
-      <c r="G13" s="56" t="s">
-        <v>119</v>
+      <c r="E13" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="F13" s="58"/>
+      <c r="G13" s="57" t="s">
+        <v>120</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
@@ -6582,24 +6632,24 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="54">
+      <c r="A14" s="55">
         <v>7.0</v>
       </c>
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="55" t="s">
-        <v>204</v>
-      </c>
-      <c r="E14" s="55" t="s">
+      <c r="D14" s="56" t="s">
         <v>205</v>
       </c>
-      <c r="F14" s="57"/>
-      <c r="G14" s="56" t="s">
-        <v>186</v>
+      <c r="E14" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="F14" s="58"/>
+      <c r="G14" s="57" t="s">
+        <v>187</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="32"/>
@@ -6616,24 +6666,24 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="48">
+      <c r="A15" s="49">
         <v>8.0</v>
       </c>
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="E15" s="51" t="s">
+      <c r="D15" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="F15" s="57"/>
-      <c r="G15" s="56" t="s">
-        <v>186</v>
+      <c r="E15" s="52" t="s">
+        <v>208</v>
+      </c>
+      <c r="F15" s="58"/>
+      <c r="G15" s="57" t="s">
+        <v>187</v>
       </c>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
@@ -6650,24 +6700,24 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="48">
+      <c r="A16" s="49">
         <v>9.0</v>
       </c>
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="51" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="51" t="s">
+      <c r="D16" s="52" t="s">
         <v>209</v>
       </c>
-      <c r="F16" s="58"/>
-      <c r="G16" s="59" t="s">
-        <v>186</v>
+      <c r="E16" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16" s="59"/>
+      <c r="G16" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="H16" s="31"/>
       <c r="I16" s="32"/>
@@ -6684,24 +6734,24 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="48">
+      <c r="A17" s="49">
         <v>10.0</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="E17" s="51" t="s">
+      <c r="D17" s="52" t="s">
         <v>211</v>
       </c>
-      <c r="F17" s="52"/>
-      <c r="G17" s="53" t="s">
-        <v>186</v>
+      <c r="E17" s="52" t="s">
+        <v>212</v>
+      </c>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54" t="s">
+        <v>187</v>
       </c>
       <c r="H17" s="28"/>
       <c r="I17" s="29"/>
@@ -6718,24 +6768,24 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="60">
+      <c r="A18" s="61">
         <v>11.0</v>
       </c>
-      <c r="B18" s="49" t="s">
+      <c r="B18" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="55" t="s">
-        <v>212</v>
-      </c>
-      <c r="E18" s="55" t="s">
+      <c r="D18" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="F18" s="52"/>
-      <c r="G18" s="53" t="s">
-        <v>186</v>
+      <c r="E18" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="F18" s="53"/>
+      <c r="G18" s="54" t="s">
+        <v>187</v>
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
@@ -6752,24 +6802,24 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="48">
+      <c r="A19" s="49">
         <v>12.0</v>
       </c>
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="51" t="s">
-        <v>214</v>
-      </c>
-      <c r="E19" s="51" t="s">
+      <c r="D19" s="52" t="s">
         <v>215</v>
       </c>
-      <c r="F19" s="52"/>
-      <c r="G19" s="53" t="s">
-        <v>186</v>
+      <c r="E19" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54" t="s">
+        <v>187</v>
       </c>
       <c r="H19" s="28"/>
       <c r="I19" s="29"/>
@@ -6786,24 +6836,24 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="61">
+      <c r="A20" s="62">
         <v>13.0</v>
       </c>
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="51" t="s">
-        <v>216</v>
-      </c>
-      <c r="E20" s="51" t="s">
+      <c r="D20" s="52" t="s">
         <v>217</v>
       </c>
-      <c r="F20" s="52"/>
-      <c r="G20" s="53" t="s">
-        <v>186</v>
+      <c r="E20" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54" t="s">
+        <v>187</v>
       </c>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
@@ -6820,58 +6870,58 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="60">
+      <c r="A21" s="61">
         <v>14.0</v>
       </c>
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="55" t="s">
-        <v>218</v>
-      </c>
-      <c r="E21" s="55" t="s">
+      <c r="D21" s="56" t="s">
         <v>219</v>
       </c>
-      <c r="F21" s="62"/>
-      <c r="G21" s="63" t="s">
-        <v>186</v>
-      </c>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="64">
+      <c r="E21" s="56" t="s">
+        <v>220</v>
+      </c>
+      <c r="F21" s="63"/>
+      <c r="G21" s="64" t="s">
+        <v>187</v>
+      </c>
+      <c r="H21" s="65"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="66"/>
+      <c r="L21" s="66"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="66"/>
+      <c r="P21" s="66"/>
+      <c r="Q21" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="54">
+      <c r="A22" s="55">
         <v>15.0</v>
       </c>
-      <c r="B22" s="49" t="s">
+      <c r="B22" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="55" t="s">
-        <v>220</v>
-      </c>
-      <c r="E22" s="55" t="s">
+      <c r="D22" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="F22" s="57"/>
-      <c r="G22" s="56" t="s">
-        <v>186</v>
+      <c r="E22" s="56" t="s">
+        <v>222</v>
+      </c>
+      <c r="F22" s="58"/>
+      <c r="G22" s="57" t="s">
+        <v>187</v>
       </c>
       <c r="H22" s="31"/>
       <c r="I22" s="32"/>
@@ -6888,24 +6938,24 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="48">
+      <c r="A23" s="49">
         <v>16.0</v>
       </c>
-      <c r="B23" s="49" t="s">
+      <c r="B23" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="E23" s="51" t="s">
+      <c r="D23" s="52" t="s">
         <v>223</v>
       </c>
-      <c r="F23" s="57"/>
-      <c r="G23" s="56" t="s">
-        <v>186</v>
+      <c r="E23" s="52" t="s">
+        <v>224</v>
+      </c>
+      <c r="F23" s="58"/>
+      <c r="G23" s="57" t="s">
+        <v>187</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -6922,24 +6972,24 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="60">
+      <c r="A24" s="61">
         <v>17.0</v>
       </c>
-      <c r="B24" s="49" t="s">
+      <c r="B24" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="F24" s="52"/>
-      <c r="G24" s="53" t="s">
-        <v>186</v>
+      <c r="D24" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="E24" s="67" t="s">
+        <v>226</v>
+      </c>
+      <c r="F24" s="53"/>
+      <c r="G24" s="54" t="s">
+        <v>187</v>
       </c>
       <c r="H24" s="31"/>
       <c r="I24" s="32"/>
@@ -6956,24 +7006,24 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="61">
+      <c r="A25" s="62">
         <v>18.0</v>
       </c>
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="51" t="s">
-        <v>225</v>
-      </c>
-      <c r="E25" s="51" t="s">
-        <v>226</v>
-      </c>
-      <c r="F25" s="57"/>
-      <c r="G25" s="56" t="s">
-        <v>186</v>
+      <c r="D25" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="E25" s="52" t="s">
+        <v>228</v>
+      </c>
+      <c r="F25" s="58"/>
+      <c r="G25" s="57" t="s">
+        <v>187</v>
       </c>
       <c r="H25" s="28"/>
       <c r="I25" s="29"/>
@@ -6990,24 +7040,24 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="61">
+      <c r="A26" s="62">
         <v>19.0</v>
       </c>
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C26" s="68" t="s">
         <v>94</v>
       </c>
       <c r="D26" s="67" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E26" s="67" t="s">
-        <v>228</v>
-      </c>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53" t="s">
-        <v>229</v>
+        <v>230</v>
+      </c>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54" t="s">
+        <v>231</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="32"/>
@@ -7024,24 +7074,24 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="48">
+      <c r="A27" s="49">
         <v>20.0</v>
       </c>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>231</v>
-      </c>
-      <c r="F27" s="52"/>
-      <c r="G27" s="53" t="s">
-        <v>186</v>
+      <c r="D27" s="52" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>233</v>
+      </c>
+      <c r="F27" s="53"/>
+      <c r="G27" s="54" t="s">
+        <v>187</v>
       </c>
       <c r="H27" s="28"/>
       <c r="I27" s="29"/>
@@ -7058,23 +7108,23 @@
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
-      <c r="A28" s="54">
+      <c r="A28" s="55">
         <v>21.0</v>
       </c>
-      <c r="B28" s="49" t="s">
+      <c r="B28" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="50" t="s">
+      <c r="C28" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="55" t="s">
-        <v>232</v>
-      </c>
-      <c r="E28" s="55" t="s">
-        <v>233</v>
-      </c>
-      <c r="F28" s="68"/>
-      <c r="G28" s="59"/>
+      <c r="D28" s="56" t="s">
+        <v>234</v>
+      </c>
+      <c r="E28" s="56" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" s="69"/>
+      <c r="G28" s="60"/>
       <c r="H28" s="31"/>
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
@@ -7087,24 +7137,24 @@
       <c r="Q28" s="31"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="61">
+      <c r="A29" s="62">
         <v>22.0</v>
       </c>
-      <c r="B29" s="49" t="s">
+      <c r="B29" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="51" t="s">
-        <v>234</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>235</v>
-      </c>
-      <c r="F29" s="68"/>
-      <c r="G29" s="59" t="s">
+      <c r="D29" s="52" t="s">
         <v>236</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="F29" s="69"/>
+      <c r="G29" s="60" t="s">
+        <v>238</v>
       </c>
       <c r="H29" s="28"/>
       <c r="I29" s="29"/>
@@ -7121,23 +7171,23 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="60">
+      <c r="A30" s="61">
         <v>23.0</v>
       </c>
-      <c r="B30" s="49" t="s">
+      <c r="B30" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="50" t="s">
+      <c r="C30" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="55" t="s">
-        <v>237</v>
-      </c>
-      <c r="E30" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="F30" s="68"/>
-      <c r="G30" s="59"/>
+      <c r="D30" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="E30" s="56" t="s">
+        <v>240</v>
+      </c>
+      <c r="F30" s="69"/>
+      <c r="G30" s="60"/>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
@@ -7153,23 +7203,23 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="61">
+      <c r="A31" s="62">
         <v>24.0</v>
       </c>
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C31" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="51" t="s">
-        <v>239</v>
-      </c>
-      <c r="E31" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="F31" s="68"/>
-      <c r="G31" s="59"/>
+      <c r="D31" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>242</v>
+      </c>
+      <c r="F31" s="69"/>
+      <c r="G31" s="60"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
       <c r="J31" s="29"/>
@@ -7185,23 +7235,23 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="61">
+      <c r="A32" s="62">
         <v>25.0</v>
       </c>
-      <c r="B32" s="49" t="s">
+      <c r="B32" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E32" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="F32" s="68"/>
-      <c r="G32" s="59"/>
+      <c r="D32" s="52" t="s">
+        <v>243</v>
+      </c>
+      <c r="E32" s="52" t="s">
+        <v>244</v>
+      </c>
+      <c r="F32" s="69"/>
+      <c r="G32" s="60"/>
       <c r="H32" s="31"/>
       <c r="I32" s="32"/>
       <c r="J32" s="32"/>
@@ -7217,24 +7267,24 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="48">
+      <c r="A33" s="49">
         <v>26.0</v>
       </c>
-      <c r="B33" s="49" t="s">
+      <c r="B33" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="69" t="s">
-        <v>243</v>
-      </c>
-      <c r="E33" s="51" t="s">
-        <v>244</v>
-      </c>
-      <c r="F33" s="57"/>
-      <c r="G33" s="56" t="s">
-        <v>186</v>
+      <c r="D33" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="E33" s="52" t="s">
+        <v>246</v>
+      </c>
+      <c r="F33" s="58"/>
+      <c r="G33" s="57" t="s">
+        <v>187</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -7251,13 +7301,13 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="61"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="71"/>
+      <c r="A34" s="62"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="72"/>
       <c r="H34" s="31"/>
       <c r="I34" s="32"/>
       <c r="J34" s="32"/>
@@ -7460,20 +7510,20 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="72">
+      <c r="A8" s="73">
         <v>1.0</v>
       </c>
-      <c r="B8" s="73" t="s">
+      <c r="B8" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="73" t="s">
-        <v>245</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>246</v>
+      <c r="D8" s="74" t="s">
+        <v>247</v>
+      </c>
+      <c r="E8" s="74" t="s">
+        <v>248</v>
       </c>
       <c r="F8" s="40"/>
       <c r="G8" s="41"/>
@@ -7492,18 +7542,18 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="74">
+      <c r="A9" s="75">
         <v>2.0</v>
       </c>
-      <c r="B9" s="73" t="s">
+      <c r="B9" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C9" s="41"/>
-      <c r="D9" s="73" t="s">
-        <v>247</v>
-      </c>
-      <c r="E9" s="73" t="s">
-        <v>248</v>
+      <c r="D9" s="74" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" s="74" t="s">
+        <v>250</v>
       </c>
       <c r="F9" s="40"/>
       <c r="G9" s="41"/>
@@ -7522,18 +7572,18 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="72">
+      <c r="A10" s="73">
         <v>3.0</v>
       </c>
-      <c r="B10" s="73" t="s">
+      <c r="B10" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C10" s="41"/>
-      <c r="D10" s="73" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>250</v>
+      <c r="D10" s="74" t="s">
+        <v>251</v>
+      </c>
+      <c r="E10" s="74" t="s">
+        <v>252</v>
       </c>
       <c r="F10" s="40"/>
       <c r="G10" s="41"/>
@@ -7552,18 +7602,18 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="74">
+      <c r="A11" s="75">
         <v>4.0</v>
       </c>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C11" s="41"/>
-      <c r="D11" s="73" t="s">
-        <v>251</v>
-      </c>
-      <c r="E11" s="73" t="s">
-        <v>252</v>
+      <c r="D11" s="74" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" s="74" t="s">
+        <v>254</v>
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="41"/>
@@ -7582,18 +7632,18 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="72">
+      <c r="A12" s="73">
         <v>5.0</v>
       </c>
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C12" s="41"/>
-      <c r="D12" s="73" t="s">
-        <v>253</v>
-      </c>
-      <c r="E12" s="73" t="s">
-        <v>254</v>
+      <c r="D12" s="74" t="s">
+        <v>255</v>
+      </c>
+      <c r="E12" s="74" t="s">
+        <v>256</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="41"/>
@@ -7612,18 +7662,18 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="74">
+      <c r="A13" s="75">
         <v>6.0</v>
       </c>
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C13" s="41"/>
-      <c r="D13" s="73" t="s">
-        <v>255</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>256</v>
+      <c r="D13" s="74" t="s">
+        <v>257</v>
+      </c>
+      <c r="E13" s="74" t="s">
+        <v>258</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="41"/>
@@ -7642,18 +7692,18 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="72">
+      <c r="A14" s="73">
         <v>7.0</v>
       </c>
-      <c r="B14" s="73" t="s">
+      <c r="B14" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="41"/>
-      <c r="D14" s="73" t="s">
-        <v>257</v>
-      </c>
-      <c r="E14" s="73" t="s">
-        <v>258</v>
+      <c r="D14" s="74" t="s">
+        <v>259</v>
+      </c>
+      <c r="E14" s="74" t="s">
+        <v>260</v>
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="41"/>
@@ -7672,18 +7722,18 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="74">
+      <c r="A15" s="75">
         <v>8.0</v>
       </c>
-      <c r="B15" s="73" t="s">
+      <c r="B15" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C15" s="41"/>
-      <c r="D15" s="73" t="s">
-        <v>259</v>
-      </c>
-      <c r="E15" s="73" t="s">
-        <v>260</v>
+      <c r="D15" s="74" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" s="74" t="s">
+        <v>262</v>
       </c>
       <c r="F15" s="40"/>
       <c r="G15" s="41"/>
@@ -7702,18 +7752,18 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="72">
+      <c r="A16" s="73">
         <v>9.0</v>
       </c>
-      <c r="B16" s="73" t="s">
+      <c r="B16" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C16" s="41"/>
-      <c r="D16" s="73" t="s">
-        <v>261</v>
-      </c>
-      <c r="E16" s="73" t="s">
-        <v>254</v>
+      <c r="D16" s="74" t="s">
+        <v>263</v>
+      </c>
+      <c r="E16" s="74" t="s">
+        <v>256</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41"/>
@@ -7732,18 +7782,18 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="74">
+      <c r="A17" s="75">
         <v>10.0</v>
       </c>
-      <c r="B17" s="73" t="s">
+      <c r="B17" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="41"/>
-      <c r="D17" s="73" t="s">
-        <v>262</v>
-      </c>
-      <c r="E17" s="73" t="s">
-        <v>263</v>
+      <c r="D17" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="E17" s="74" t="s">
+        <v>265</v>
       </c>
       <c r="F17" s="40"/>
       <c r="G17" s="41"/>
@@ -7762,18 +7812,18 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="72">
+      <c r="A18" s="73">
         <v>11.0</v>
       </c>
-      <c r="B18" s="73" t="s">
+      <c r="B18" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="41"/>
-      <c r="D18" s="73" t="s">
-        <v>264</v>
-      </c>
-      <c r="E18" s="73" t="s">
-        <v>256</v>
+      <c r="D18" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="E18" s="74" t="s">
+        <v>258</v>
       </c>
       <c r="F18" s="40"/>
       <c r="G18" s="41"/>
@@ -7792,18 +7842,18 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="74">
+      <c r="A19" s="75">
         <v>12.0</v>
       </c>
-      <c r="B19" s="73" t="s">
+      <c r="B19" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="73" t="s">
-        <v>265</v>
-      </c>
-      <c r="E19" s="73" t="s">
-        <v>266</v>
+      <c r="D19" s="74" t="s">
+        <v>267</v>
+      </c>
+      <c r="E19" s="74" t="s">
+        <v>268</v>
       </c>
       <c r="F19" s="40"/>
       <c r="G19" s="41"/>
@@ -7822,18 +7872,18 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="72">
+      <c r="A20" s="73">
         <v>13.0</v>
       </c>
-      <c r="B20" s="73" t="s">
+      <c r="B20" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C20" s="41"/>
-      <c r="D20" s="73" t="s">
-        <v>267</v>
-      </c>
-      <c r="E20" s="75" t="s">
-        <v>268</v>
+      <c r="D20" s="74" t="s">
+        <v>269</v>
+      </c>
+      <c r="E20" s="76" t="s">
+        <v>270</v>
       </c>
       <c r="F20" s="40"/>
       <c r="G20" s="41"/>
@@ -7852,18 +7902,18 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="74">
+      <c r="A21" s="75">
         <v>14.0</v>
       </c>
-      <c r="B21" s="73" t="s">
+      <c r="B21" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C21" s="41"/>
-      <c r="D21" s="73" t="s">
-        <v>269</v>
-      </c>
-      <c r="E21" s="73" t="s">
-        <v>270</v>
+      <c r="D21" s="74" t="s">
+        <v>271</v>
+      </c>
+      <c r="E21" s="74" t="s">
+        <v>272</v>
       </c>
       <c r="F21" s="40"/>
       <c r="G21" s="41"/>
@@ -7882,18 +7932,18 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="72">
+      <c r="A22" s="73">
         <v>15.0</v>
       </c>
-      <c r="B22" s="73" t="s">
+      <c r="B22" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C22" s="41"/>
-      <c r="D22" s="73" t="s">
-        <v>271</v>
-      </c>
-      <c r="E22" s="73" t="s">
-        <v>272</v>
+      <c r="D22" s="74" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="74" t="s">
+        <v>274</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="41"/>
@@ -7912,18 +7962,18 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="74">
+      <c r="A23" s="75">
         <v>16.0</v>
       </c>
-      <c r="B23" s="73" t="s">
+      <c r="B23" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C23" s="41"/>
-      <c r="D23" s="73" t="s">
-        <v>273</v>
-      </c>
-      <c r="E23" s="75" t="s">
-        <v>274</v>
+      <c r="D23" s="74" t="s">
+        <v>275</v>
+      </c>
+      <c r="E23" s="76" t="s">
+        <v>276</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="41"/>
@@ -7942,18 +7992,18 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="72">
+      <c r="A24" s="73">
         <v>17.0</v>
       </c>
-      <c r="B24" s="73" t="s">
+      <c r="B24" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C24" s="41"/>
-      <c r="D24" s="76" t="s">
-        <v>275</v>
-      </c>
-      <c r="E24" s="76" t="s">
-        <v>276</v>
+      <c r="D24" s="77" t="s">
+        <v>277</v>
+      </c>
+      <c r="E24" s="77" t="s">
+        <v>278</v>
       </c>
       <c r="F24" s="40"/>
       <c r="G24" s="41"/>
@@ -7972,18 +8022,18 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="74">
+      <c r="A25" s="75">
         <v>18.0</v>
       </c>
-      <c r="B25" s="73" t="s">
+      <c r="B25" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C25" s="41"/>
-      <c r="D25" s="73" t="s">
-        <v>277</v>
-      </c>
-      <c r="E25" s="73" t="s">
-        <v>278</v>
+      <c r="D25" s="74" t="s">
+        <v>279</v>
+      </c>
+      <c r="E25" s="74" t="s">
+        <v>280</v>
       </c>
       <c r="F25" s="40"/>
       <c r="G25" s="41"/>
@@ -8002,18 +8052,18 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="72">
+      <c r="A26" s="73">
         <v>19.0</v>
       </c>
-      <c r="B26" s="73" t="s">
+      <c r="B26" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C26" s="41"/>
-      <c r="D26" s="77" t="s">
-        <v>279</v>
-      </c>
-      <c r="E26" s="77" t="s">
-        <v>280</v>
+      <c r="D26" s="78" t="s">
+        <v>281</v>
+      </c>
+      <c r="E26" s="78" t="s">
+        <v>282</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41"/>
@@ -8032,18 +8082,18 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="74">
+      <c r="A27" s="75">
         <v>20.0</v>
       </c>
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="41"/>
-      <c r="D27" s="73" t="s">
-        <v>281</v>
-      </c>
-      <c r="E27" s="73" t="s">
-        <v>282</v>
+      <c r="D27" s="74" t="s">
+        <v>283</v>
+      </c>
+      <c r="E27" s="74" t="s">
+        <v>284</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="41"/>
@@ -8062,18 +8112,18 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="72">
+      <c r="A28" s="73">
         <v>21.0</v>
       </c>
-      <c r="B28" s="73" t="s">
+      <c r="B28" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C28" s="41"/>
-      <c r="D28" s="73" t="s">
-        <v>283</v>
-      </c>
-      <c r="E28" s="73" t="s">
-        <v>284</v>
+      <c r="D28" s="74" t="s">
+        <v>285</v>
+      </c>
+      <c r="E28" s="74" t="s">
+        <v>286</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="41"/>
@@ -8092,18 +8142,18 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="74">
+      <c r="A29" s="75">
         <v>22.0</v>
       </c>
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C29" s="41"/>
-      <c r="D29" s="73" t="s">
-        <v>285</v>
-      </c>
-      <c r="E29" s="73" t="s">
-        <v>286</v>
+      <c r="D29" s="74" t="s">
+        <v>287</v>
+      </c>
+      <c r="E29" s="74" t="s">
+        <v>288</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="41"/>
@@ -8122,18 +8172,18 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="72">
+      <c r="A30" s="73">
         <v>23.0</v>
       </c>
-      <c r="B30" s="73" t="s">
+      <c r="B30" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C30" s="41"/>
-      <c r="D30" s="73" t="s">
-        <v>271</v>
-      </c>
-      <c r="E30" s="73" t="s">
-        <v>287</v>
+      <c r="D30" s="74" t="s">
+        <v>273</v>
+      </c>
+      <c r="E30" s="74" t="s">
+        <v>289</v>
       </c>
       <c r="F30" s="40"/>
       <c r="G30" s="41"/>
@@ -8152,18 +8202,18 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="74">
+      <c r="A31" s="75">
         <v>24.0</v>
       </c>
-      <c r="B31" s="73" t="s">
+      <c r="B31" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="41"/>
-      <c r="D31" s="73" t="s">
-        <v>288</v>
-      </c>
-      <c r="E31" s="75" t="s">
-        <v>289</v>
+      <c r="D31" s="74" t="s">
+        <v>290</v>
+      </c>
+      <c r="E31" s="76" t="s">
+        <v>291</v>
       </c>
       <c r="F31" s="40"/>
       <c r="G31" s="41"/>
@@ -8182,18 +8232,18 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="72">
+      <c r="A32" s="73">
         <v>25.0</v>
       </c>
-      <c r="B32" s="73" t="s">
+      <c r="B32" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C32" s="41"/>
-      <c r="D32" s="73" t="s">
-        <v>290</v>
-      </c>
-      <c r="E32" s="73" t="s">
-        <v>291</v>
+      <c r="D32" s="74" t="s">
+        <v>292</v>
+      </c>
+      <c r="E32" s="74" t="s">
+        <v>293</v>
       </c>
       <c r="F32" s="40"/>
       <c r="G32" s="41"/>
@@ -8212,18 +8262,18 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="74">
+      <c r="A33" s="75">
         <v>26.0</v>
       </c>
-      <c r="B33" s="73" t="s">
+      <c r="B33" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="41"/>
-      <c r="D33" s="73" t="s">
-        <v>261</v>
-      </c>
-      <c r="E33" s="73" t="s">
-        <v>292</v>
+      <c r="D33" s="74" t="s">
+        <v>263</v>
+      </c>
+      <c r="E33" s="74" t="s">
+        <v>294</v>
       </c>
       <c r="F33" s="40"/>
       <c r="G33" s="41"/>
@@ -8305,7 +8355,7 @@
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="6"/>
@@ -8330,7 +8380,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
@@ -8343,8 +8393,8 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="78" t="s">
-        <v>295</v>
+      <c r="E3" s="79" t="s">
+        <v>297</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -8358,7 +8408,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -8372,7 +8422,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -8442,26 +8492,26 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="72">
+      <c r="A8" s="73">
         <v>1.0</v>
       </c>
-      <c r="B8" s="73" t="s">
+      <c r="B8" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>299</v>
+      <c r="D8" s="74" t="s">
+        <v>300</v>
+      </c>
+      <c r="E8" s="74" t="s">
+        <v>301</v>
       </c>
       <c r="F8" s="40">
         <v>37.0</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -8478,26 +8528,26 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="74">
+      <c r="A9" s="75">
         <v>2.0</v>
       </c>
-      <c r="B9" s="73" t="s">
+      <c r="B9" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="79" t="s">
-        <v>300</v>
-      </c>
-      <c r="E9" s="80" t="s">
-        <v>301</v>
+      <c r="D9" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="81" t="s">
+        <v>303</v>
       </c>
       <c r="F9" s="40">
         <v>32.0</v>
       </c>
       <c r="G9" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -8514,26 +8564,26 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="72">
+      <c r="A10" s="73">
         <v>3.0</v>
       </c>
-      <c r="B10" s="73" t="s">
+      <c r="B10" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C10" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="73" t="s">
-        <v>302</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>303</v>
+      <c r="D10" s="74" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10" s="74" t="s">
+        <v>305</v>
       </c>
       <c r="F10" s="40">
         <v>25.0</v>
       </c>
       <c r="G10" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -8550,26 +8600,26 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="72">
+      <c r="A11" s="73">
         <v>4.0</v>
       </c>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C11" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="73" t="s">
-        <v>304</v>
-      </c>
-      <c r="E11" s="73" t="s">
-        <v>305</v>
+      <c r="D11" s="74" t="s">
+        <v>306</v>
+      </c>
+      <c r="E11" s="74" t="s">
+        <v>307</v>
       </c>
       <c r="F11" s="40">
         <v>29.0</v>
       </c>
       <c r="G11" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11" s="29"/>
@@ -8586,26 +8636,26 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="74">
+      <c r="A12" s="75">
         <v>5.0</v>
       </c>
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C12" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="73" t="s">
-        <v>306</v>
-      </c>
-      <c r="E12" s="73" t="s">
-        <v>307</v>
+      <c r="D12" s="74" t="s">
+        <v>308</v>
+      </c>
+      <c r="E12" s="74" t="s">
+        <v>309</v>
       </c>
       <c r="F12" s="40">
         <v>27.0</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="32"/>
@@ -8622,24 +8672,24 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="74">
+      <c r="A13" s="75">
         <v>6.0</v>
       </c>
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C13" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="81" t="s">
-        <v>309</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>310</v>
+      <c r="D13" s="82" t="s">
+        <v>311</v>
+      </c>
+      <c r="E13" s="74" t="s">
+        <v>312</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
@@ -8656,26 +8706,26 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="72">
+      <c r="A14" s="73">
         <v>7.0</v>
       </c>
-      <c r="B14" s="73" t="s">
+      <c r="B14" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="82" t="s">
-        <v>311</v>
-      </c>
-      <c r="E14" s="82" t="s">
-        <v>312</v>
+      <c r="D14" s="83" t="s">
+        <v>313</v>
+      </c>
+      <c r="E14" s="83" t="s">
+        <v>314</v>
       </c>
       <c r="F14" s="40">
         <v>23.0</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
@@ -8692,26 +8742,26 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="74">
+      <c r="A15" s="75">
         <v>8.0</v>
       </c>
-      <c r="B15" s="73" t="s">
+      <c r="B15" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C15" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="73" t="s">
-        <v>313</v>
-      </c>
-      <c r="E15" s="73" t="s">
-        <v>314</v>
+      <c r="D15" s="74" t="s">
+        <v>315</v>
+      </c>
+      <c r="E15" s="74" t="s">
+        <v>316</v>
       </c>
       <c r="F15" s="40">
         <v>28.0</v>
       </c>
       <c r="G15" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
@@ -8728,26 +8778,26 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="72">
+      <c r="A16" s="73">
         <v>9.0</v>
       </c>
-      <c r="B16" s="73" t="s">
+      <c r="B16" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C16" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="73" t="s">
-        <v>315</v>
-      </c>
-      <c r="E16" s="73" t="s">
-        <v>316</v>
+      <c r="D16" s="74" t="s">
+        <v>317</v>
+      </c>
+      <c r="E16" s="74" t="s">
+        <v>318</v>
       </c>
       <c r="F16" s="40">
         <v>40.0</v>
       </c>
       <c r="G16" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -8764,26 +8814,26 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="72">
+      <c r="A17" s="73">
         <v>10.0</v>
       </c>
-      <c r="B17" s="73" t="s">
+      <c r="B17" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C17" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="73" t="s">
-        <v>317</v>
-      </c>
-      <c r="E17" s="73" t="s">
-        <v>318</v>
+      <c r="D17" s="74" t="s">
+        <v>319</v>
+      </c>
+      <c r="E17" s="74" t="s">
+        <v>320</v>
       </c>
       <c r="F17" s="40">
         <v>37.0</v>
       </c>
       <c r="G17" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H17" s="28"/>
       <c r="I17" s="29"/>
@@ -8800,26 +8850,26 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="74">
+      <c r="A18" s="75">
         <v>11.0</v>
       </c>
-      <c r="B18" s="73" t="s">
+      <c r="B18" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="73" t="s">
-        <v>319</v>
-      </c>
-      <c r="E18" s="73" t="s">
-        <v>320</v>
+      <c r="D18" s="74" t="s">
+        <v>321</v>
+      </c>
+      <c r="E18" s="74" t="s">
+        <v>322</v>
       </c>
       <c r="F18" s="40">
         <v>32.0</v>
       </c>
       <c r="G18" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H18" s="31"/>
       <c r="I18" s="32"/>
@@ -8836,26 +8886,26 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="74">
+      <c r="A19" s="75">
         <v>12.0</v>
       </c>
-      <c r="B19" s="73" t="s">
-        <v>120</v>
+      <c r="B19" s="74" t="s">
+        <v>121</v>
       </c>
       <c r="C19" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="81" t="s">
-        <v>321</v>
-      </c>
-      <c r="E19" s="73" t="s">
-        <v>322</v>
+      <c r="D19" s="82" t="s">
+        <v>323</v>
+      </c>
+      <c r="E19" s="74" t="s">
+        <v>324</v>
       </c>
       <c r="F19" s="40">
         <v>20.0</v>
       </c>
       <c r="G19" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
@@ -8872,24 +8922,24 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="72">
+      <c r="A20" s="73">
         <v>13.0</v>
       </c>
-      <c r="B20" s="73" t="s">
+      <c r="B20" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C20" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="82" t="s">
-        <v>323</v>
-      </c>
-      <c r="E20" s="82" t="s">
-        <v>324</v>
+      <c r="D20" s="83" t="s">
+        <v>325</v>
+      </c>
+      <c r="E20" s="83" t="s">
+        <v>326</v>
       </c>
       <c r="F20" s="40"/>
       <c r="G20" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
@@ -8906,26 +8956,26 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="74">
+      <c r="A21" s="75">
         <v>14.0</v>
       </c>
-      <c r="B21" s="73" t="s">
+      <c r="B21" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C21" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="73" t="s">
-        <v>325</v>
-      </c>
-      <c r="E21" s="73" t="s">
-        <v>326</v>
+      <c r="D21" s="74" t="s">
+        <v>327</v>
+      </c>
+      <c r="E21" s="74" t="s">
+        <v>328</v>
       </c>
       <c r="F21" s="40">
         <v>33.0</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -8942,26 +8992,26 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="72">
+      <c r="A22" s="73">
         <v>15.0</v>
       </c>
-      <c r="B22" s="73" t="s">
+      <c r="B22" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C22" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="73" t="s">
-        <v>327</v>
-      </c>
-      <c r="E22" s="73" t="s">
-        <v>328</v>
+      <c r="D22" s="74" t="s">
+        <v>329</v>
+      </c>
+      <c r="E22" s="74" t="s">
+        <v>330</v>
       </c>
       <c r="F22" s="40">
         <v>33.0</v>
       </c>
       <c r="G22" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -8978,26 +9028,26 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="74">
+      <c r="A23" s="75">
         <v>16.0</v>
       </c>
-      <c r="B23" s="73" t="s">
+      <c r="B23" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="83" t="s">
+      <c r="C23" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="84" t="s">
-        <v>329</v>
-      </c>
-      <c r="E23" s="84" t="s">
-        <v>330</v>
+      <c r="D23" s="85" t="s">
+        <v>331</v>
+      </c>
+      <c r="E23" s="85" t="s">
+        <v>332</v>
       </c>
       <c r="F23" s="40">
         <v>41.0</v>
       </c>
       <c r="G23" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -9014,26 +9064,26 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="72">
+      <c r="A24" s="73">
         <v>17.0</v>
       </c>
-      <c r="B24" s="73" t="s">
+      <c r="B24" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C24" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="81" t="s">
-        <v>331</v>
-      </c>
-      <c r="E24" s="73" t="s">
-        <v>332</v>
+      <c r="D24" s="82" t="s">
+        <v>333</v>
+      </c>
+      <c r="E24" s="74" t="s">
+        <v>334</v>
       </c>
       <c r="F24" s="40">
         <v>20.0</v>
       </c>
       <c r="G24" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
@@ -9050,26 +9100,26 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="74">
+      <c r="A25" s="75">
         <v>18.0</v>
       </c>
-      <c r="B25" s="73" t="s">
+      <c r="B25" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C25" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="81" t="s">
-        <v>333</v>
-      </c>
-      <c r="E25" s="73" t="s">
-        <v>334</v>
+      <c r="D25" s="82" t="s">
+        <v>335</v>
+      </c>
+      <c r="E25" s="74" t="s">
+        <v>336</v>
       </c>
       <c r="F25" s="40">
         <v>34.0</v>
       </c>
       <c r="G25" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
@@ -9086,24 +9136,24 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="72">
+      <c r="A26" s="73">
         <v>19.0</v>
       </c>
-      <c r="B26" s="73" t="s">
+      <c r="B26" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C26" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="81" t="s">
-        <v>335</v>
-      </c>
-      <c r="E26" s="73" t="s">
-        <v>336</v>
+      <c r="D26" s="82" t="s">
+        <v>337</v>
+      </c>
+      <c r="E26" s="74" t="s">
+        <v>338</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
@@ -9120,26 +9170,26 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="74">
+      <c r="A27" s="75">
         <v>20.0</v>
       </c>
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="81" t="s">
-        <v>337</v>
-      </c>
-      <c r="E27" s="73" t="s">
+      <c r="D27" s="82" t="s">
+        <v>339</v>
+      </c>
+      <c r="E27" s="74" t="s">
         <v>87</v>
       </c>
       <c r="F27" s="40">
         <v>27.0</v>
       </c>
       <c r="G27" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -9156,26 +9206,26 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="74">
+      <c r="A28" s="75">
         <v>21.0</v>
       </c>
-      <c r="B28" s="73" t="s">
+      <c r="B28" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="73" t="s">
-        <v>338</v>
-      </c>
-      <c r="E28" s="73" t="s">
-        <v>339</v>
+      <c r="D28" s="74" t="s">
+        <v>340</v>
+      </c>
+      <c r="E28" s="74" t="s">
+        <v>341</v>
       </c>
       <c r="F28" s="40">
         <v>32.0</v>
       </c>
       <c r="G28" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H28" s="31"/>
       <c r="I28" s="32"/>
@@ -9192,26 +9242,26 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="74">
+      <c r="A29" s="75">
         <v>22.0</v>
       </c>
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C29" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="84" t="s">
-        <v>340</v>
-      </c>
-      <c r="E29" s="84" t="s">
-        <v>341</v>
+      <c r="D29" s="85" t="s">
+        <v>342</v>
+      </c>
+      <c r="E29" s="85" t="s">
+        <v>343</v>
       </c>
       <c r="F29" s="40">
         <v>28.0</v>
       </c>
       <c r="G29" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -9228,26 +9278,26 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="72">
+      <c r="A30" s="73">
         <v>23.0</v>
       </c>
-      <c r="B30" s="73" t="s">
+      <c r="B30" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="84" t="s">
-        <v>342</v>
-      </c>
-      <c r="E30" s="84" t="s">
-        <v>343</v>
+      <c r="D30" s="85" t="s">
+        <v>344</v>
+      </c>
+      <c r="E30" s="85" t="s">
+        <v>345</v>
       </c>
       <c r="F30" s="40">
         <v>41.0</v>
       </c>
       <c r="G30" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
@@ -9264,22 +9314,22 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="72">
+      <c r="A31" s="73">
         <v>24.0</v>
       </c>
-      <c r="B31" s="73" t="s">
+      <c r="B31" s="74" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="81"/>
-      <c r="E31" s="73"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="74"/>
       <c r="F31" s="40">
         <v>36.0</v>
       </c>
       <c r="G31" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
@@ -9296,20 +9346,20 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="72">
+      <c r="A32" s="73">
         <v>25.0</v>
       </c>
-      <c r="B32" s="73" t="s">
+      <c r="B32" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="73" t="s">
-        <v>344</v>
-      </c>
-      <c r="E32" s="73" t="s">
-        <v>345</v>
+      <c r="D32" s="74" t="s">
+        <v>346</v>
+      </c>
+      <c r="E32" s="74" t="s">
+        <v>347</v>
       </c>
       <c r="F32" s="40">
         <v>19.0</v>
@@ -9330,20 +9380,20 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="74">
+      <c r="A33" s="75">
         <v>26.0</v>
       </c>
-      <c r="B33" s="73" t="s">
-        <v>120</v>
+      <c r="B33" s="74" t="s">
+        <v>121</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="73" t="s">
-        <v>346</v>
-      </c>
-      <c r="E33" s="73" t="s">
-        <v>347</v>
+      <c r="D33" s="74" t="s">
+        <v>348</v>
+      </c>
+      <c r="E33" s="74" t="s">
+        <v>349</v>
       </c>
       <c r="F33" s="40">
         <v>19.0</v>
@@ -9428,12 +9478,12 @@
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="85" t="s">
+      <c r="F1" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="86"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88" t="s">
+      <c r="G1" s="87"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="89" t="s">
         <v>42</v>
       </c>
       <c r="J1" s="10"/>
@@ -9455,7 +9505,7 @@
       <c r="D2" s="5"/>
       <c r="E2" s="6"/>
       <c r="F2" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="6"/>
@@ -9469,7 +9519,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="6"/>
       <c r="F3" s="11" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="6"/>
@@ -9483,27 +9533,27 @@
       <c r="D4" s="5"/>
       <c r="E4" s="6"/>
       <c r="F4" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="6"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="90" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="90" t="s">
-        <v>351</v>
-      </c>
-      <c r="G5" s="91"/>
-      <c r="H5" s="92"/>
+      <c r="F5" s="91" t="s">
+        <v>353</v>
+      </c>
+      <c r="G5" s="92"/>
+      <c r="H5" s="93"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="93"/>
+      <c r="A6" s="94"/>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -9514,13 +9564,13 @@
     </row>
     <row r="7" ht="21.0" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>52</v>
@@ -9569,26 +9619,26 @@
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1">
-      <c r="A8" s="94">
+      <c r="A8" s="95">
         <v>1.0</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="95" t="s">
+      <c r="D8" s="96" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="96" t="s">
-        <v>355</v>
-      </c>
-      <c r="F8" s="96" t="s">
-        <v>356</v>
+      <c r="E8" s="97" t="s">
+        <v>357</v>
+      </c>
+      <c r="F8" s="97" t="s">
+        <v>358</v>
       </c>
       <c r="G8" s="40"/>
-      <c r="H8" s="97" t="s">
+      <c r="H8" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I8" s="28"/>
@@ -9606,26 +9656,26 @@
       </c>
     </row>
     <row r="9" ht="21.0" customHeight="1">
-      <c r="A9" s="94">
+      <c r="A9" s="95">
         <v>2.0</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="94" t="s">
+      <c r="C9" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="95" t="s">
+      <c r="D9" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="96" t="s">
-        <v>357</v>
-      </c>
-      <c r="F9" s="96" t="s">
-        <v>358</v>
+      <c r="E9" s="97" t="s">
+        <v>359</v>
+      </c>
+      <c r="F9" s="97" t="s">
+        <v>360</v>
       </c>
       <c r="G9" s="40"/>
-      <c r="H9" s="97" t="s">
+      <c r="H9" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I9" s="31"/>
@@ -9643,26 +9693,26 @@
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1">
-      <c r="A10" s="94">
+      <c r="A10" s="95">
         <v>3.0</v>
       </c>
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="94" t="s">
+      <c r="C10" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="95" t="s">
+      <c r="D10" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="98" t="s">
-        <v>359</v>
-      </c>
-      <c r="F10" s="98" t="s">
-        <v>360</v>
+      <c r="E10" s="99" t="s">
+        <v>361</v>
+      </c>
+      <c r="F10" s="99" t="s">
+        <v>362</v>
       </c>
       <c r="G10" s="40"/>
-      <c r="H10" s="97" t="s">
+      <c r="H10" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I10" s="31"/>
@@ -9680,26 +9730,26 @@
       </c>
     </row>
     <row r="11" ht="21.0" customHeight="1">
-      <c r="A11" s="94">
+      <c r="A11" s="95">
         <v>4.0</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="94" t="s">
+      <c r="C11" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="95" t="s">
+      <c r="D11" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="96" t="s">
-        <v>361</v>
-      </c>
-      <c r="F11" s="96" t="s">
-        <v>362</v>
+      <c r="E11" s="97" t="s">
+        <v>363</v>
+      </c>
+      <c r="F11" s="97" t="s">
+        <v>364</v>
       </c>
       <c r="G11" s="40"/>
-      <c r="H11" s="97" t="s">
+      <c r="H11" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I11" s="31"/>
@@ -9717,26 +9767,26 @@
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="94">
+      <c r="A12" s="95">
         <v>5.0</v>
       </c>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="95" t="s">
+      <c r="D12" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="96" t="s">
-        <v>363</v>
-      </c>
-      <c r="F12" s="96" t="s">
-        <v>356</v>
+      <c r="E12" s="97" t="s">
+        <v>365</v>
+      </c>
+      <c r="F12" s="97" t="s">
+        <v>358</v>
       </c>
       <c r="G12" s="40"/>
-      <c r="H12" s="97" t="s">
+      <c r="H12" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I12" s="28"/>
@@ -9754,26 +9804,26 @@
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1">
-      <c r="A13" s="94">
+      <c r="A13" s="95">
         <v>6.0</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="94" t="s">
+      <c r="C13" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="95" t="s">
+      <c r="D13" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="F13" s="96" t="s">
-        <v>181</v>
+      <c r="E13" s="100" t="s">
+        <v>366</v>
+      </c>
+      <c r="F13" s="100" t="s">
+        <v>186</v>
       </c>
       <c r="G13" s="40"/>
-      <c r="H13" s="97" t="s">
+      <c r="H13" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I13" s="31"/>
@@ -9791,26 +9841,26 @@
       </c>
     </row>
     <row r="14" ht="24.75" customHeight="1">
-      <c r="A14" s="94">
+      <c r="A14" s="95">
         <v>7.0</v>
       </c>
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="94" t="s">
+      <c r="C14" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="95" t="s">
+      <c r="D14" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="96" t="s">
-        <v>364</v>
-      </c>
-      <c r="F14" s="96" t="s">
-        <v>181</v>
+      <c r="E14" s="97" t="s">
+        <v>367</v>
+      </c>
+      <c r="F14" s="97" t="s">
+        <v>182</v>
       </c>
       <c r="G14" s="40"/>
-      <c r="H14" s="97" t="s">
+      <c r="H14" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I14" s="28"/>
@@ -9828,26 +9878,26 @@
       </c>
     </row>
     <row r="15" ht="21.0" customHeight="1">
-      <c r="A15" s="94">
+      <c r="A15" s="95">
         <v>8.0</v>
       </c>
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="95" t="s">
+      <c r="D15" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="96" t="s">
-        <v>365</v>
-      </c>
-      <c r="F15" s="96" t="s">
-        <v>181</v>
+      <c r="E15" s="97" t="s">
+        <v>368</v>
+      </c>
+      <c r="F15" s="97" t="s">
+        <v>182</v>
       </c>
       <c r="G15" s="40"/>
-      <c r="H15" s="97" t="s">
+      <c r="H15" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I15" s="31"/>
@@ -9865,26 +9915,26 @@
       </c>
     </row>
     <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="94">
+      <c r="A16" s="95">
         <v>9.0</v>
       </c>
-      <c r="B16" s="94" t="s">
+      <c r="B16" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="94" t="s">
+      <c r="C16" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="95" t="s">
+      <c r="D16" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="96" t="s">
-        <v>366</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>367</v>
+      <c r="E16" s="97" t="s">
+        <v>369</v>
+      </c>
+      <c r="F16" s="97" t="s">
+        <v>370</v>
       </c>
       <c r="G16" s="40"/>
-      <c r="H16" s="97" t="s">
+      <c r="H16" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I16" s="28"/>
@@ -9902,26 +9952,26 @@
       </c>
     </row>
     <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="94">
+      <c r="A17" s="95">
         <v>10.0</v>
       </c>
-      <c r="B17" s="94" t="s">
+      <c r="B17" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="95" t="s">
+      <c r="D17" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="96" t="s">
-        <v>368</v>
-      </c>
-      <c r="F17" s="96" t="s">
-        <v>369</v>
+      <c r="E17" s="97" t="s">
+        <v>371</v>
+      </c>
+      <c r="F17" s="97" t="s">
+        <v>372</v>
       </c>
       <c r="G17" s="40"/>
-      <c r="H17" s="97" t="s">
+      <c r="H17" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I17" s="31"/>
@@ -9939,26 +9989,26 @@
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="94">
+      <c r="A18" s="95">
         <v>11.0</v>
       </c>
-      <c r="B18" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="94" t="s">
+      <c r="B18" s="95" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="95" t="s">
+      <c r="D18" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="96" t="s">
-        <v>370</v>
-      </c>
-      <c r="F18" s="96" t="s">
-        <v>371</v>
+      <c r="E18" s="97" t="s">
+        <v>373</v>
+      </c>
+      <c r="F18" s="97" t="s">
+        <v>374</v>
       </c>
       <c r="G18" s="40"/>
-      <c r="H18" s="97" t="s">
+      <c r="H18" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I18" s="28"/>
@@ -9976,26 +10026,26 @@
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1">
-      <c r="A19" s="94">
+      <c r="A19" s="95">
         <v>12.0</v>
       </c>
-      <c r="B19" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="94" t="s">
+      <c r="B19" s="95" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="95" t="s">
+      <c r="D19" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="96" t="s">
-        <v>372</v>
-      </c>
-      <c r="F19" s="96" t="s">
-        <v>373</v>
+      <c r="E19" s="97" t="s">
+        <v>375</v>
+      </c>
+      <c r="F19" s="97" t="s">
+        <v>376</v>
       </c>
       <c r="G19" s="40"/>
-      <c r="H19" s="97" t="s">
+      <c r="H19" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I19" s="31"/>
@@ -10013,26 +10063,26 @@
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1">
-      <c r="A20" s="94">
+      <c r="A20" s="95">
         <v>13.0</v>
       </c>
-      <c r="B20" s="94" t="s">
+      <c r="B20" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="94" t="s">
+      <c r="C20" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="95" t="s">
+      <c r="D20" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="96" t="s">
-        <v>374</v>
-      </c>
-      <c r="F20" s="96" t="s">
-        <v>375</v>
+      <c r="E20" s="97" t="s">
+        <v>377</v>
+      </c>
+      <c r="F20" s="97" t="s">
+        <v>378</v>
       </c>
       <c r="G20" s="40"/>
-      <c r="H20" s="97" t="s">
+      <c r="H20" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I20" s="28"/>
@@ -10050,26 +10100,26 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="94">
+      <c r="A21" s="95">
         <v>14.0</v>
       </c>
-      <c r="B21" s="94" t="s">
+      <c r="B21" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="94" t="s">
+      <c r="C21" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="95" t="s">
+      <c r="D21" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="96" t="s">
-        <v>376</v>
-      </c>
-      <c r="F21" s="96" t="s">
-        <v>146</v>
+      <c r="E21" s="97" t="s">
+        <v>379</v>
+      </c>
+      <c r="F21" s="97" t="s">
+        <v>147</v>
       </c>
       <c r="G21" s="40"/>
-      <c r="H21" s="97" t="s">
+      <c r="H21" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I21" s="31"/>
@@ -10087,26 +10137,26 @@
       </c>
     </row>
     <row r="22" ht="23.25" customHeight="1">
-      <c r="A22" s="94">
+      <c r="A22" s="95">
         <v>15.0</v>
       </c>
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="94" t="s">
+      <c r="C22" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="96" t="s">
-        <v>377</v>
-      </c>
-      <c r="F22" s="96" t="s">
-        <v>378</v>
+      <c r="E22" s="97" t="s">
+        <v>380</v>
+      </c>
+      <c r="F22" s="97" t="s">
+        <v>381</v>
       </c>
       <c r="G22" s="40"/>
-      <c r="H22" s="97" t="s">
+      <c r="H22" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I22" s="28"/>
@@ -10124,26 +10174,26 @@
       </c>
     </row>
     <row r="23" ht="21.75" customHeight="1">
-      <c r="A23" s="94">
+      <c r="A23" s="95">
         <v>16.0</v>
       </c>
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="94" t="s">
+      <c r="C23" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="95" t="s">
+      <c r="D23" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="96" t="s">
-        <v>379</v>
-      </c>
-      <c r="F23" s="96" t="s">
-        <v>380</v>
+      <c r="E23" s="97" t="s">
+        <v>382</v>
+      </c>
+      <c r="F23" s="97" t="s">
+        <v>383</v>
       </c>
       <c r="G23" s="40"/>
-      <c r="H23" s="99" t="s">
+      <c r="H23" s="101" t="s">
         <v>71</v>
       </c>
       <c r="I23" s="31"/>
@@ -10161,26 +10211,26 @@
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1">
-      <c r="A24" s="94">
+      <c r="A24" s="95">
         <v>17.0</v>
       </c>
-      <c r="B24" s="94" t="s">
+      <c r="B24" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="94" t="s">
+      <c r="C24" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="95" t="s">
+      <c r="D24" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="96" t="s">
-        <v>381</v>
-      </c>
-      <c r="F24" s="96" t="s">
-        <v>382</v>
+      <c r="E24" s="97" t="s">
+        <v>384</v>
+      </c>
+      <c r="F24" s="97" t="s">
+        <v>385</v>
       </c>
       <c r="G24" s="40"/>
-      <c r="H24" s="97" t="s">
+      <c r="H24" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I24" s="31"/>
@@ -10198,26 +10248,26 @@
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="94">
+      <c r="A25" s="95">
         <v>18.0</v>
       </c>
-      <c r="B25" s="94" t="s">
+      <c r="B25" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="94" t="s">
+      <c r="C25" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="95" t="s">
+      <c r="D25" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="96" t="s">
-        <v>383</v>
-      </c>
-      <c r="F25" s="96" t="s">
-        <v>384</v>
+      <c r="E25" s="97" t="s">
+        <v>386</v>
+      </c>
+      <c r="F25" s="97" t="s">
+        <v>387</v>
       </c>
       <c r="G25" s="40"/>
-      <c r="H25" s="97" t="s">
+      <c r="H25" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I25" s="28"/>
@@ -10235,26 +10285,26 @@
       </c>
     </row>
     <row r="26" ht="24.0" customHeight="1">
-      <c r="A26" s="94">
+      <c r="A26" s="95">
         <v>19.0</v>
       </c>
-      <c r="B26" s="94" t="s">
+      <c r="B26" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="94" t="s">
+      <c r="C26" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="95" t="s">
+      <c r="D26" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="96" t="s">
-        <v>385</v>
-      </c>
-      <c r="F26" s="96" t="s">
-        <v>386</v>
+      <c r="E26" s="97" t="s">
+        <v>388</v>
+      </c>
+      <c r="F26" s="97" t="s">
+        <v>389</v>
       </c>
       <c r="G26" s="40"/>
-      <c r="H26" s="97" t="s">
+      <c r="H26" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I26" s="28"/>
@@ -10272,26 +10322,26 @@
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1">
-      <c r="A27" s="94">
+      <c r="A27" s="95">
         <v>20.0</v>
       </c>
-      <c r="B27" s="94" t="s">
+      <c r="B27" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="94" t="s">
+      <c r="C27" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="95" t="s">
+      <c r="D27" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="96" t="s">
-        <v>387</v>
-      </c>
-      <c r="F27" s="96" t="s">
-        <v>362</v>
+      <c r="E27" s="97" t="s">
+        <v>390</v>
+      </c>
+      <c r="F27" s="97" t="s">
+        <v>364</v>
       </c>
       <c r="G27" s="40"/>
-      <c r="H27" s="97" t="s">
+      <c r="H27" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I27" s="28"/>
@@ -10309,26 +10359,26 @@
       </c>
     </row>
     <row r="28" ht="20.25" customHeight="1">
-      <c r="A28" s="94">
+      <c r="A28" s="95">
         <v>21.0</v>
       </c>
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="94" t="s">
+      <c r="C28" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="95" t="s">
+      <c r="D28" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="96" t="s">
-        <v>388</v>
-      </c>
-      <c r="F28" s="96" t="s">
-        <v>389</v>
+      <c r="E28" s="97" t="s">
+        <v>391</v>
+      </c>
+      <c r="F28" s="97" t="s">
+        <v>392</v>
       </c>
       <c r="G28" s="40"/>
-      <c r="H28" s="97" t="s">
+      <c r="H28" s="98" t="s">
         <v>99</v>
       </c>
       <c r="I28" s="31"/>
@@ -10346,26 +10396,26 @@
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="94">
+      <c r="A29" s="95">
         <v>22.0</v>
       </c>
-      <c r="B29" s="94" t="s">
+      <c r="B29" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="94" t="s">
+      <c r="C29" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="95" t="s">
+      <c r="D29" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="96" t="s">
-        <v>390</v>
-      </c>
-      <c r="F29" s="96" t="s">
-        <v>391</v>
+      <c r="E29" s="97" t="s">
+        <v>393</v>
+      </c>
+      <c r="F29" s="97" t="s">
+        <v>394</v>
       </c>
       <c r="G29" s="40"/>
-      <c r="H29" s="97" t="s">
+      <c r="H29" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I29" s="28"/>
@@ -10383,26 +10433,26 @@
       </c>
     </row>
     <row r="30" ht="20.25" customHeight="1">
-      <c r="A30" s="94">
+      <c r="A30" s="95">
         <v>23.0</v>
       </c>
-      <c r="B30" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="C30" s="94" t="s">
+      <c r="B30" s="95" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="95" t="s">
+      <c r="D30" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="96" t="s">
-        <v>392</v>
-      </c>
-      <c r="F30" s="96" t="s">
-        <v>393</v>
+      <c r="E30" s="97" t="s">
+        <v>395</v>
+      </c>
+      <c r="F30" s="97" t="s">
+        <v>396</v>
       </c>
       <c r="G30" s="40"/>
-      <c r="H30" s="97" t="s">
+      <c r="H30" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I30" s="31"/>
@@ -10420,26 +10470,26 @@
       </c>
     </row>
     <row r="31" ht="21.0" customHeight="1">
-      <c r="A31" s="94">
+      <c r="A31" s="95">
         <v>24.0</v>
       </c>
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="94" t="s">
+      <c r="C31" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="95" t="s">
+      <c r="D31" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="96" t="s">
-        <v>394</v>
-      </c>
-      <c r="F31" s="96" t="s">
-        <v>395</v>
+      <c r="E31" s="97" t="s">
+        <v>397</v>
+      </c>
+      <c r="F31" s="97" t="s">
+        <v>398</v>
       </c>
       <c r="G31" s="40"/>
-      <c r="H31" s="97" t="s">
+      <c r="H31" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I31" s="28"/>
@@ -10457,26 +10507,26 @@
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="94">
+      <c r="A32" s="95">
         <v>25.0</v>
       </c>
-      <c r="B32" s="94" t="s">
+      <c r="B32" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="94" t="s">
+      <c r="C32" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="95" t="s">
+      <c r="D32" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="96" t="s">
-        <v>396</v>
-      </c>
-      <c r="F32" s="96" t="s">
-        <v>397</v>
+      <c r="E32" s="97" t="s">
+        <v>399</v>
+      </c>
+      <c r="F32" s="97" t="s">
+        <v>400</v>
       </c>
       <c r="G32" s="40"/>
-      <c r="H32" s="97" t="s">
+      <c r="H32" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I32" s="31"/>
@@ -10494,27 +10544,27 @@
       </c>
     </row>
     <row r="33" ht="21.0" customHeight="1">
-      <c r="A33" s="94">
+      <c r="A33" s="95">
         <v>26.0</v>
       </c>
-      <c r="B33" s="94" t="s">
+      <c r="B33" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="94" t="s">
+      <c r="C33" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="95" t="s">
+      <c r="D33" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="96" t="s">
+      <c r="E33" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="96" t="s">
-        <v>398</v>
+      <c r="F33" s="97" t="s">
+        <v>401</v>
       </c>
       <c r="G33" s="40"/>
-      <c r="H33" s="97" t="s">
-        <v>399</v>
+      <c r="H33" s="98" t="s">
+        <v>402</v>
       </c>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
@@ -10592,7 +10642,7 @@
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="7" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="6"/>
@@ -10617,7 +10667,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="11" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
@@ -10631,7 +10681,7 @@
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
       <c r="E3" s="11" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -10645,7 +10695,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -10659,7 +10709,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="11" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -10729,20 +10779,20 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="46">
+      <c r="A8" s="47">
         <v>3.0</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="101" t="s">
-        <v>305</v>
-      </c>
-      <c r="E8" s="101" t="s">
-        <v>405</v>
+      <c r="D8" s="103" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="103" t="s">
+        <v>408</v>
       </c>
       <c r="F8" s="40"/>
       <c r="G8" s="41" t="s">
@@ -10773,14 +10823,14 @@
         <v>76</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F9" s="40"/>
       <c r="G9" s="41" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -10797,7 +10847,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="46">
+      <c r="A10" s="47">
         <v>1.0</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -10807,14 +10857,14 @@
         <v>68</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F10" s="40"/>
       <c r="G10" s="41" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -10841,14 +10891,14 @@
         <v>76</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="41" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
@@ -10875,14 +10925,14 @@
         <v>86</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="41" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -10909,14 +10959,14 @@
         <v>86</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="41" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
@@ -10943,10 +10993,10 @@
         <v>94</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="41" t="s">
@@ -10977,10 +11027,10 @@
         <v>86</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F15" s="40"/>
       <c r="G15" s="41" t="s">
@@ -11011,14 +11061,14 @@
         <v>94</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -11045,14 +11095,14 @@
         <v>94</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F17" s="40"/>
       <c r="G17" s="41" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
@@ -11079,25 +11129,25 @@
         <v>94</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>426</v>
-      </c>
-      <c r="F18" s="102"/>
-      <c r="G18" s="103" t="s">
-        <v>427</v>
-      </c>
-      <c r="H18" s="64"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="104"/>
-      <c r="N18" s="104"/>
-      <c r="O18" s="104"/>
-      <c r="P18" s="104"/>
-      <c r="Q18" s="64">
+        <v>429</v>
+      </c>
+      <c r="F18" s="104"/>
+      <c r="G18" s="105" t="s">
+        <v>430</v>
+      </c>
+      <c r="H18" s="65"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
+      <c r="L18" s="106"/>
+      <c r="M18" s="106"/>
+      <c r="N18" s="106"/>
+      <c r="O18" s="106"/>
+      <c r="P18" s="106"/>
+      <c r="Q18" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11113,25 +11163,25 @@
         <v>76</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>429</v>
-      </c>
-      <c r="F19" s="102"/>
-      <c r="G19" s="103" t="s">
-        <v>400</v>
-      </c>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="65"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="65"/>
-      <c r="P19" s="65"/>
-      <c r="Q19" s="64">
+        <v>432</v>
+      </c>
+      <c r="F19" s="104"/>
+      <c r="G19" s="105" t="s">
+        <v>403</v>
+      </c>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="66"/>
+      <c r="M19" s="66"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="66"/>
+      <c r="P19" s="66"/>
+      <c r="Q19" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11147,25 +11197,25 @@
         <v>76</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="F20" s="102"/>
-      <c r="G20" s="103" t="s">
-        <v>400</v>
-      </c>
-      <c r="H20" s="64"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="104"/>
-      <c r="O20" s="104"/>
-      <c r="P20" s="104"/>
-      <c r="Q20" s="64">
+        <v>434</v>
+      </c>
+      <c r="F20" s="104"/>
+      <c r="G20" s="105" t="s">
+        <v>403</v>
+      </c>
+      <c r="H20" s="65"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="106"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="106"/>
+      <c r="O20" s="106"/>
+      <c r="P20" s="106"/>
+      <c r="Q20" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11181,16 +11231,16 @@
         <v>76</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F21" s="40">
         <v>20.0</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -11217,14 +11267,14 @@
         <v>86</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -11251,23 +11301,23 @@
         <v>86</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="F23" s="102"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="104"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="104"/>
-      <c r="Q23" s="64">
+        <v>441</v>
+      </c>
+      <c r="F23" s="104"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="106"/>
+      <c r="K23" s="106"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="106"/>
+      <c r="N23" s="106"/>
+      <c r="O23" s="106"/>
+      <c r="P23" s="106"/>
+      <c r="Q23" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11283,10 +11333,10 @@
         <v>86</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F24" s="40"/>
       <c r="G24" s="41" t="s">
@@ -11317,25 +11367,25 @@
         <v>86</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>405</v>
-      </c>
-      <c r="F25" s="102"/>
-      <c r="G25" s="103" t="s">
+        <v>408</v>
+      </c>
+      <c r="F25" s="104"/>
+      <c r="G25" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="H25" s="64"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="104"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="104"/>
-      <c r="Q25" s="64">
+      <c r="H25" s="65"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="106"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="106"/>
+      <c r="O25" s="106"/>
+      <c r="P25" s="106"/>
+      <c r="Q25" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11351,10 +11401,10 @@
         <v>94</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41" t="s">
@@ -11385,14 +11435,14 @@
         <v>76</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="41" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -11419,10 +11469,10 @@
         <v>86</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="41"/>
@@ -11451,14 +11501,14 @@
         <v>94</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="41" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -11485,14 +11535,14 @@
         <v>76</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F30" s="40"/>
       <c r="G30" s="41" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
@@ -11519,57 +11569,57 @@
         <v>94</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>429</v>
-      </c>
-      <c r="F31" s="102"/>
-      <c r="G31" s="103" t="s">
-        <v>400</v>
-      </c>
-      <c r="H31" s="64"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="104"/>
-      <c r="N31" s="104"/>
-      <c r="O31" s="104"/>
-      <c r="P31" s="104"/>
-      <c r="Q31" s="64">
+        <v>432</v>
+      </c>
+      <c r="F31" s="104"/>
+      <c r="G31" s="105" t="s">
+        <v>403</v>
+      </c>
+      <c r="H31" s="65"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="106"/>
+      <c r="L31" s="106"/>
+      <c r="M31" s="106"/>
+      <c r="N31" s="106"/>
+      <c r="O31" s="106"/>
+      <c r="P31" s="106"/>
+      <c r="Q31" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="105">
+      <c r="A32" s="107">
         <v>25.0</v>
       </c>
-      <c r="B32" s="106" t="s">
+      <c r="B32" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="107" t="s">
+      <c r="C32" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="106" t="s">
-        <v>453</v>
-      </c>
-      <c r="E32" s="106" t="s">
-        <v>454</v>
-      </c>
-      <c r="F32" s="102"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="104"/>
-      <c r="N32" s="104"/>
-      <c r="O32" s="104"/>
-      <c r="P32" s="104"/>
-      <c r="Q32" s="64">
+      <c r="D32" s="108" t="s">
+        <v>456</v>
+      </c>
+      <c r="E32" s="108" t="s">
+        <v>457</v>
+      </c>
+      <c r="F32" s="104"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="106"/>
+      <c r="J32" s="106"/>
+      <c r="K32" s="106"/>
+      <c r="L32" s="106"/>
+      <c r="M32" s="106"/>
+      <c r="N32" s="106"/>
+      <c r="O32" s="106"/>
+      <c r="P32" s="106"/>
+      <c r="Q32" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11585,14 +11635,14 @@
         <v>76</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F33" s="40"/>
       <c r="G33" s="41" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -11671,7 +11721,7 @@
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="110" t="s">
         <v>37</v>
       </c>
       <c r="F1" s="5"/>
@@ -11696,7 +11746,7 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="108"/>
+      <c r="E2" s="110"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="13"/>
@@ -11708,8 +11758,8 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="108" t="s">
-        <v>458</v>
+      <c r="E3" s="110" t="s">
+        <v>461</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -11722,8 +11772,8 @@
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
-      <c r="E4" s="109" t="s">
-        <v>459</v>
+      <c r="E4" s="111" t="s">
+        <v>462</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -11736,8 +11786,8 @@
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="108" t="s">
-        <v>460</v>
+      <c r="E5" s="110" t="s">
+        <v>463</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -11807,20 +11857,20 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="72">
+      <c r="A8" s="73">
         <v>1.0</v>
       </c>
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="111" t="s">
+      <c r="C8" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="112" t="s">
-        <v>461</v>
-      </c>
-      <c r="E8" s="112" t="s">
-        <v>239</v>
+      <c r="D8" s="114" t="s">
+        <v>464</v>
+      </c>
+      <c r="E8" s="114" t="s">
+        <v>241</v>
       </c>
       <c r="F8" s="40"/>
       <c r="G8" s="41"/>
@@ -11839,20 +11889,20 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="74">
+      <c r="A9" s="75">
         <v>2.0</v>
       </c>
-      <c r="B9" s="110" t="s">
+      <c r="B9" s="112" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="111" t="s">
+      <c r="C9" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="112" t="s">
-        <v>462</v>
-      </c>
-      <c r="E9" s="112" t="s">
-        <v>463</v>
+      <c r="D9" s="114" t="s">
+        <v>465</v>
+      </c>
+      <c r="E9" s="114" t="s">
+        <v>466</v>
       </c>
       <c r="F9" s="40"/>
       <c r="G9" s="41"/>
@@ -11871,20 +11921,20 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="72">
+      <c r="A10" s="73">
         <v>3.0</v>
       </c>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="111" t="s">
+      <c r="C10" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="113" t="s">
-        <v>464</v>
-      </c>
-      <c r="E10" s="113" t="s">
-        <v>465</v>
+      <c r="D10" s="115" t="s">
+        <v>467</v>
+      </c>
+      <c r="E10" s="115" t="s">
+        <v>468</v>
       </c>
       <c r="F10" s="40"/>
       <c r="G10" s="41"/>
@@ -11903,20 +11953,20 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="74">
+      <c r="A11" s="75">
         <v>4.0</v>
       </c>
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="111" t="s">
+      <c r="C11" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="113" t="s">
-        <v>466</v>
-      </c>
-      <c r="E11" s="113" t="s">
-        <v>467</v>
+      <c r="D11" s="115" t="s">
+        <v>469</v>
+      </c>
+      <c r="E11" s="115" t="s">
+        <v>470</v>
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="41"/>
@@ -11935,20 +11985,20 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="72">
+      <c r="A12" s="73">
         <v>5.0</v>
       </c>
-      <c r="B12" s="110" t="s">
+      <c r="B12" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="111" t="s">
+      <c r="C12" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="114" t="s">
-        <v>468</v>
-      </c>
-      <c r="E12" s="112" t="s">
-        <v>469</v>
+      <c r="D12" s="116" t="s">
+        <v>471</v>
+      </c>
+      <c r="E12" s="114" t="s">
+        <v>472</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="41"/>
@@ -11967,20 +12017,20 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="74">
+      <c r="A13" s="75">
         <v>6.0</v>
       </c>
-      <c r="B13" s="110" t="s">
+      <c r="B13" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="115" t="s">
+      <c r="C13" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="114" t="s">
-        <v>470</v>
-      </c>
-      <c r="E13" s="114" t="s">
-        <v>471</v>
+      <c r="D13" s="116" t="s">
+        <v>473</v>
+      </c>
+      <c r="E13" s="116" t="s">
+        <v>474</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="41"/>
@@ -11999,20 +12049,20 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="72">
+      <c r="A14" s="73">
         <v>7.0</v>
       </c>
-      <c r="B14" s="110" t="s">
+      <c r="B14" s="112" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="115" t="s">
+      <c r="C14" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="114" t="s">
-        <v>472</v>
-      </c>
-      <c r="E14" s="114" t="s">
-        <v>473</v>
+      <c r="D14" s="116" t="s">
+        <v>475</v>
+      </c>
+      <c r="E14" s="116" t="s">
+        <v>476</v>
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="41"/>
@@ -12031,20 +12081,20 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="74">
+      <c r="A15" s="75">
         <v>8.0</v>
       </c>
-      <c r="B15" s="110" t="s">
+      <c r="B15" s="112" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="115" t="s">
+      <c r="C15" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="114" t="s">
-        <v>474</v>
-      </c>
-      <c r="E15" s="114" t="s">
-        <v>475</v>
+      <c r="D15" s="116" t="s">
+        <v>477</v>
+      </c>
+      <c r="E15" s="116" t="s">
+        <v>478</v>
       </c>
       <c r="F15" s="40"/>
       <c r="G15" s="41"/>
@@ -12063,20 +12113,20 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="72">
+      <c r="A16" s="73">
         <v>9.0</v>
       </c>
-      <c r="B16" s="110" t="s">
+      <c r="B16" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="114" t="s">
-        <v>476</v>
-      </c>
-      <c r="E16" s="114" t="s">
-        <v>477</v>
+      <c r="D16" s="116" t="s">
+        <v>479</v>
+      </c>
+      <c r="E16" s="116" t="s">
+        <v>480</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41"/>
@@ -12095,20 +12145,20 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="74">
+      <c r="A17" s="75">
         <v>10.0</v>
       </c>
-      <c r="B17" s="110" t="s">
+      <c r="B17" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="115" t="s">
+      <c r="C17" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="114" t="s">
-        <v>478</v>
-      </c>
-      <c r="E17" s="114" t="s">
-        <v>469</v>
+      <c r="D17" s="116" t="s">
+        <v>481</v>
+      </c>
+      <c r="E17" s="116" t="s">
+        <v>472</v>
       </c>
       <c r="F17" s="40"/>
       <c r="G17" s="41"/>
@@ -12127,20 +12177,20 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="72">
+      <c r="A18" s="73">
         <v>12.0</v>
       </c>
-      <c r="B18" s="110" t="s">
+      <c r="B18" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="115" t="s">
+      <c r="C18" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="114" t="s">
-        <v>479</v>
-      </c>
-      <c r="E18" s="114" t="s">
-        <v>480</v>
+      <c r="D18" s="116" t="s">
+        <v>482</v>
+      </c>
+      <c r="E18" s="116" t="s">
+        <v>483</v>
       </c>
       <c r="F18" s="40"/>
       <c r="G18" s="41"/>
@@ -12159,20 +12209,20 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="74">
+      <c r="A19" s="75">
         <v>11.0</v>
       </c>
-      <c r="B19" s="110" t="s">
+      <c r="B19" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="115" t="s">
+      <c r="C19" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="114" t="s">
-        <v>481</v>
-      </c>
-      <c r="E19" s="114" t="s">
-        <v>482</v>
+      <c r="D19" s="116" t="s">
+        <v>484</v>
+      </c>
+      <c r="E19" s="116" t="s">
+        <v>485</v>
       </c>
       <c r="F19" s="40"/>
       <c r="G19" s="41"/>
@@ -12191,20 +12241,20 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="72">
+      <c r="A20" s="73">
         <v>13.0</v>
       </c>
-      <c r="B20" s="110" t="s">
+      <c r="B20" s="112" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="115" t="s">
+      <c r="C20" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="114" t="s">
+      <c r="D20" s="116" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="114" t="s">
-        <v>483</v>
+      <c r="E20" s="116" t="s">
+        <v>486</v>
       </c>
       <c r="F20" s="40"/>
       <c r="G20" s="41"/>
@@ -12223,20 +12273,20 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="74">
+      <c r="A21" s="75">
         <v>14.0</v>
       </c>
-      <c r="B21" s="110" t="s">
+      <c r="B21" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="115" t="s">
+      <c r="C21" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="114" t="s">
-        <v>472</v>
-      </c>
-      <c r="E21" s="114" t="s">
-        <v>484</v>
+      <c r="D21" s="116" t="s">
+        <v>475</v>
+      </c>
+      <c r="E21" s="116" t="s">
+        <v>487</v>
       </c>
       <c r="F21" s="40"/>
       <c r="G21" s="41"/>
@@ -12255,20 +12305,20 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="72">
+      <c r="A22" s="73">
         <v>15.0</v>
       </c>
-      <c r="B22" s="110" t="s">
+      <c r="B22" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="111" t="s">
+      <c r="C22" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="112" t="s">
-        <v>485</v>
-      </c>
-      <c r="E22" s="112" t="s">
-        <v>486</v>
+      <c r="D22" s="118" t="s">
+        <v>488</v>
+      </c>
+      <c r="E22" s="118" t="s">
+        <v>376</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="41"/>
@@ -12287,20 +12337,20 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="74">
+      <c r="A23" s="75">
         <v>16.0</v>
       </c>
-      <c r="B23" s="110" t="s">
+      <c r="B23" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="111" t="s">
+      <c r="C23" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="112" t="s">
-        <v>487</v>
-      </c>
-      <c r="E23" s="112" t="s">
-        <v>488</v>
+      <c r="D23" s="118" t="s">
+        <v>489</v>
+      </c>
+      <c r="E23" s="118" t="s">
+        <v>490</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="41"/>
@@ -12319,20 +12369,20 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="72">
+      <c r="A24" s="73">
         <v>17.0</v>
       </c>
-      <c r="B24" s="110" t="s">
+      <c r="B24" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="111" t="s">
+      <c r="C24" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="112" t="s">
-        <v>489</v>
-      </c>
-      <c r="E24" s="112" t="s">
-        <v>490</v>
+      <c r="D24" s="114" t="s">
+        <v>491</v>
+      </c>
+      <c r="E24" s="114" t="s">
+        <v>492</v>
       </c>
       <c r="F24" s="40"/>
       <c r="G24" s="41"/>
@@ -12351,20 +12401,20 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="72">
+      <c r="A25" s="73">
         <v>18.0</v>
       </c>
-      <c r="B25" s="110" t="s">
+      <c r="B25" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="111" t="s">
+      <c r="C25" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="112" t="s">
-        <v>491</v>
-      </c>
-      <c r="E25" s="112" t="s">
-        <v>492</v>
+      <c r="D25" s="114" t="s">
+        <v>493</v>
+      </c>
+      <c r="E25" s="114" t="s">
+        <v>494</v>
       </c>
       <c r="F25" s="40"/>
       <c r="G25" s="41"/>
@@ -12383,20 +12433,20 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="72">
+      <c r="A26" s="73">
         <v>19.0</v>
       </c>
-      <c r="B26" s="110" t="s">
+      <c r="B26" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="111" t="s">
+      <c r="C26" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="112" t="s">
-        <v>493</v>
-      </c>
-      <c r="E26" s="112" t="s">
-        <v>469</v>
+      <c r="D26" s="114" t="s">
+        <v>495</v>
+      </c>
+      <c r="E26" s="114" t="s">
+        <v>472</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41"/>
@@ -12415,20 +12465,20 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="72">
+      <c r="A27" s="73">
         <v>20.0</v>
       </c>
-      <c r="B27" s="110" t="s">
+      <c r="B27" s="112" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="111" t="s">
+      <c r="C27" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="112" t="s">
-        <v>494</v>
-      </c>
-      <c r="E27" s="112" t="s">
-        <v>484</v>
+      <c r="D27" s="114" t="s">
+        <v>496</v>
+      </c>
+      <c r="E27" s="114" t="s">
+        <v>487</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="41"/>
@@ -12447,20 +12497,20 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="72">
+      <c r="A28" s="73">
         <v>21.0</v>
       </c>
-      <c r="B28" s="110" t="s">
+      <c r="B28" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="111" t="s">
+      <c r="C28" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="112" t="s">
-        <v>495</v>
-      </c>
-      <c r="E28" s="112" t="s">
-        <v>496</v>
+      <c r="D28" s="114" t="s">
+        <v>497</v>
+      </c>
+      <c r="E28" s="114" t="s">
+        <v>498</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="41"/>
@@ -12479,20 +12529,20 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="72">
+      <c r="A29" s="73">
         <v>22.0</v>
       </c>
-      <c r="B29" s="110" t="s">
+      <c r="B29" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="111" t="s">
+      <c r="C29" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="112" t="s">
-        <v>497</v>
-      </c>
-      <c r="E29" s="112" t="s">
-        <v>181</v>
+      <c r="D29" s="114" t="s">
+        <v>499</v>
+      </c>
+      <c r="E29" s="114" t="s">
+        <v>182</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="41"/>
@@ -12511,20 +12561,20 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="72">
+      <c r="A30" s="73">
         <v>23.0</v>
       </c>
-      <c r="B30" s="110" t="s">
+      <c r="B30" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="111" t="s">
+      <c r="C30" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="112" t="s">
-        <v>498</v>
-      </c>
-      <c r="E30" s="112" t="s">
-        <v>499</v>
+      <c r="D30" s="114" t="s">
+        <v>500</v>
+      </c>
+      <c r="E30" s="114" t="s">
+        <v>501</v>
       </c>
       <c r="F30" s="40"/>
       <c r="G30" s="41"/>
@@ -12543,20 +12593,20 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="74">
+      <c r="A31" s="75">
         <v>24.0</v>
       </c>
-      <c r="B31" s="110" t="s">
+      <c r="B31" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="111" t="s">
+      <c r="C31" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="112" t="s">
-        <v>281</v>
-      </c>
-      <c r="E31" s="112" t="s">
-        <v>500</v>
+      <c r="D31" s="114" t="s">
+        <v>283</v>
+      </c>
+      <c r="E31" s="114" t="s">
+        <v>502</v>
       </c>
       <c r="F31" s="40"/>
       <c r="G31" s="41"/>
@@ -12575,20 +12625,20 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="72">
+      <c r="A32" s="73">
         <v>25.0</v>
       </c>
-      <c r="B32" s="110" t="s">
+      <c r="B32" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="111" t="s">
+      <c r="C32" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="112" t="s">
-        <v>501</v>
-      </c>
-      <c r="E32" s="112" t="s">
-        <v>486</v>
+      <c r="D32" s="114" t="s">
+        <v>503</v>
+      </c>
+      <c r="E32" s="114" t="s">
+        <v>504</v>
       </c>
       <c r="F32" s="40"/>
       <c r="G32" s="41"/>
@@ -12607,20 +12657,20 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="74">
+      <c r="A33" s="75">
         <v>26.0</v>
       </c>
-      <c r="B33" s="110" t="s">
+      <c r="B33" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="111" t="s">
+      <c r="C33" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="116" t="s">
-        <v>181</v>
-      </c>
-      <c r="E33" s="116" t="s">
-        <v>502</v>
+      <c r="D33" s="118" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="118" t="s">
+        <v>505</v>
       </c>
       <c r="F33" s="40"/>
       <c r="G33" s="41"/>

--- a/public/data/@Liste GROUPE B.xlsx
+++ b/public/data/@Liste GROUPE B.xlsx
@@ -368,10 +368,10 @@
     <t>JUMAINE</t>
   </si>
   <si>
-    <t xml:space="preserve">THIERNO MAMADOU </t>
-  </si>
-  <si>
-    <t>BA</t>
+    <t xml:space="preserve">DAN MWIMBA </t>
+  </si>
+  <si>
+    <t>MULEDI</t>
   </si>
   <si>
     <t>VIGOR</t>

--- a/public/data/@Liste GROUPE B.xlsx
+++ b/public/data/@Liste GROUPE B.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="558">
   <si>
     <t xml:space="preserve">Équipe </t>
   </si>
@@ -536,954 +536,951 @@
     <t>SÉBASTIEN LIONEL</t>
   </si>
   <si>
-    <t>ABOUBACAR EL HADJI</t>
+    <t>MASSEYE</t>
+  </si>
+  <si>
+    <t>DIOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOUSTAPHA </t>
+  </si>
+  <si>
+    <t>PAPE IBRAHIMA</t>
+  </si>
+  <si>
+    <t>MANGANE</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>SÉNE</t>
+  </si>
+  <si>
+    <t>SERIGNE</t>
+  </si>
+  <si>
+    <t>FALL</t>
+  </si>
+  <si>
+    <t>BABA MAMADOU</t>
+  </si>
+  <si>
+    <t>CAMARA</t>
+  </si>
+  <si>
+    <t>PAPA BABACAR</t>
+  </si>
+  <si>
+    <t>SECK</t>
+  </si>
+  <si>
+    <t>MOUSTAPHA</t>
+  </si>
+  <si>
+    <t>PAPA GARBA</t>
+  </si>
+  <si>
+    <t>COULIBALY</t>
+  </si>
+  <si>
+    <t>GORA</t>
+  </si>
+  <si>
+    <t>MBODJ</t>
+  </si>
+  <si>
+    <t>SOULEYMANE</t>
+  </si>
+  <si>
+    <t>DIALLO</t>
+  </si>
+  <si>
+    <t>Togo</t>
+  </si>
+  <si>
+    <t>Alatevi.k@gmail.com</t>
+  </si>
+  <si>
+    <t>438-827-6129</t>
+  </si>
+  <si>
+    <t>Fabrice</t>
+  </si>
+  <si>
+    <t>Komi Alatevi</t>
+  </si>
+  <si>
+    <t>CARL ISAAC PENCHEV</t>
+  </si>
+  <si>
+    <t>RENEVIL</t>
+  </si>
+  <si>
+    <t>Haïti</t>
+  </si>
+  <si>
+    <t>KOMI</t>
+  </si>
+  <si>
+    <t>ALATEVI</t>
+  </si>
+  <si>
+    <t>AMIDOU</t>
+  </si>
+  <si>
+    <t>AKOH</t>
+  </si>
+  <si>
+    <t>KOSSI ANTHONY</t>
+  </si>
+  <si>
+    <t>ADJAMA</t>
+  </si>
+  <si>
+    <t>KOSSI SAMSON</t>
+  </si>
+  <si>
+    <t>KLOUSSE</t>
+  </si>
+  <si>
+    <t>BOTCHA</t>
+  </si>
+  <si>
+    <t>HENOC</t>
+  </si>
+  <si>
+    <t>OTNIEL</t>
+  </si>
+  <si>
+    <t>AKOEGNON</t>
+  </si>
+  <si>
+    <t>KOFFI MOÏSE</t>
+  </si>
+  <si>
+    <t>AMEVO</t>
+  </si>
+  <si>
+    <t>MANI</t>
+  </si>
+  <si>
+    <t>BABALIM</t>
+  </si>
+  <si>
+    <t>BASSITOU</t>
+  </si>
+  <si>
+    <t>ASSANI</t>
+  </si>
+  <si>
+    <t>FOUMI MAJID</t>
+  </si>
+  <si>
+    <t>OLA</t>
+  </si>
+  <si>
+    <t>FRANCIS</t>
+  </si>
+  <si>
+    <t>AGBOGBO</t>
+  </si>
+  <si>
+    <t>Tia Cixte</t>
+  </si>
+  <si>
+    <t>Marti Dji</t>
+  </si>
+  <si>
+    <t>Essofa Oubote</t>
+  </si>
+  <si>
+    <t>ABODJI</t>
+  </si>
+  <si>
+    <t>Allassane</t>
+  </si>
+  <si>
+    <t>Kone</t>
+  </si>
+  <si>
+    <t>Mouh amed</t>
+  </si>
+  <si>
+    <t>Dosso</t>
+  </si>
+  <si>
+    <t>FIACRE</t>
+  </si>
+  <si>
+    <t>KOFFI</t>
+  </si>
+  <si>
+    <t>DANIEL KOMLAN</t>
+  </si>
+  <si>
+    <t>DEKASSI</t>
+  </si>
+  <si>
+    <t>EMMANUEL BORIS</t>
+  </si>
+  <si>
+    <t>OLÉ OBALÉ</t>
+  </si>
+  <si>
+    <t>guinée</t>
+  </si>
+  <si>
+    <t>KOUTAO RAKOU</t>
+  </si>
+  <si>
+    <t>TALMANTA</t>
+  </si>
+  <si>
+    <t>ALOGNISSO</t>
+  </si>
+  <si>
+    <t>RONALD</t>
+  </si>
+  <si>
+    <t>PETERSON</t>
+  </si>
+  <si>
+    <t>AUGUSTE</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>LOCHINA</t>
+  </si>
+  <si>
+    <t>DJAFAROU</t>
+  </si>
+  <si>
+    <t>KONATÉ</t>
+  </si>
+  <si>
+    <t>MANSOUR</t>
+  </si>
+  <si>
+    <t>KOMLAN AMEN</t>
+  </si>
+  <si>
+    <t>AKAMA</t>
+  </si>
+  <si>
+    <t>ESSODONA</t>
+  </si>
+  <si>
+    <t>HALAOUI</t>
+  </si>
+  <si>
+    <t>ADONIS</t>
+  </si>
+  <si>
+    <t>KALENGA</t>
+  </si>
+  <si>
+    <t>MKOLE</t>
+  </si>
+  <si>
+    <t>RAMADHANI</t>
+  </si>
+  <si>
+    <t>DESIRE</t>
+  </si>
+  <si>
+    <t>BICUKA</t>
+  </si>
+  <si>
+    <t>ABEDI</t>
+  </si>
+  <si>
+    <t>SAIDI</t>
+  </si>
+  <si>
+    <t>ATAMBA</t>
+  </si>
+  <si>
+    <t>SHAURI</t>
+  </si>
+  <si>
+    <t>JONAS</t>
+  </si>
+  <si>
+    <t>KISUBI</t>
+  </si>
+  <si>
+    <t>PATIENT</t>
+  </si>
+  <si>
+    <t>ECA MBOKO</t>
+  </si>
+  <si>
+    <t>SALEH</t>
+  </si>
+  <si>
+    <t>ECA</t>
+  </si>
+  <si>
+    <t>UWEZO</t>
+  </si>
+  <si>
+    <t>JUMAPILI</t>
+  </si>
+  <si>
+    <t>NDIKUMANA</t>
+  </si>
+  <si>
+    <t>JANVIER</t>
+  </si>
+  <si>
+    <t>REUBEN</t>
+  </si>
+  <si>
+    <t>MLONGEKA</t>
+  </si>
+  <si>
+    <t>AMURI</t>
+  </si>
+  <si>
+    <t>NDUME</t>
+  </si>
+  <si>
+    <t>OMARI</t>
+  </si>
+  <si>
+    <t>KASHINDI</t>
+  </si>
+  <si>
+    <t>WILONDJA</t>
+  </si>
+  <si>
+    <t>LWAMAGENA</t>
+  </si>
+  <si>
+    <t>GILEO</t>
+  </si>
+  <si>
+    <t>MTABI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGAZINI </t>
+  </si>
+  <si>
+    <t>LWABOSHI MAJEGEZA</t>
+  </si>
+  <si>
+    <t>ERICK</t>
+  </si>
+  <si>
+    <t>NISHIMWE</t>
+  </si>
+  <si>
+    <t>ASENDE</t>
+  </si>
+  <si>
+    <t>ABANGWA</t>
+  </si>
+  <si>
+    <t>OLIVIER</t>
+  </si>
+  <si>
+    <t>RIPHIN</t>
+  </si>
+  <si>
+    <t>HONNEUR</t>
+  </si>
+  <si>
+    <t>JEAN MARIE</t>
+  </si>
+  <si>
+    <t>ELIAZERI</t>
+  </si>
+  <si>
+    <t>NIYOGUSENGA</t>
+  </si>
+  <si>
+    <t>BYAOMBE</t>
+  </si>
+  <si>
+    <t>BAHOME</t>
+  </si>
+  <si>
+    <t>YAMUNGU MLENBA</t>
+  </si>
+  <si>
+    <t>ZAKARIA</t>
+  </si>
+  <si>
+    <t>RÉMY</t>
+  </si>
+  <si>
+    <t>MILAMBO</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>soccerangranmoun@gmail.com; flounes37@gmail.com</t>
+  </si>
+  <si>
+    <t>4189563785 / 4388384936</t>
+  </si>
+  <si>
+    <t>Lounès Félicin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hans Raldy Saint-Preux </t>
+  </si>
+  <si>
+    <t>MAQUINGSON</t>
+  </si>
+  <si>
+    <t>MAIGNAN</t>
+  </si>
+  <si>
+    <t>AMILICA</t>
+  </si>
+  <si>
+    <t>BOUKARI BOURDJA</t>
+  </si>
+  <si>
+    <t>MICHAEL PERSHINGSON</t>
+  </si>
+  <si>
+    <t>PIERRE</t>
+  </si>
+  <si>
+    <t>JEFFERSON</t>
+  </si>
+  <si>
+    <t>ANTOINE</t>
+  </si>
+  <si>
+    <t>GREGORY</t>
+  </si>
+  <si>
+    <t>ANNAY</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>JERRY</t>
+  </si>
+  <si>
+    <t>PAULIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXEL </t>
+  </si>
+  <si>
+    <t>ALIMASI</t>
+  </si>
+  <si>
+    <t>MARC-ARTHUR</t>
+  </si>
+  <si>
+    <t>REGISTRE</t>
+  </si>
+  <si>
+    <t>MARC-DONALD</t>
+  </si>
+  <si>
+    <t>SIMEUS</t>
+  </si>
+  <si>
+    <t>EVEDERSON</t>
+  </si>
+  <si>
+    <t>PREVILON</t>
+  </si>
+  <si>
+    <t>WOODSON</t>
+  </si>
+  <si>
+    <t>SAINT-LOUIS</t>
+  </si>
+  <si>
+    <t>ROMAIN</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>RYSDAEL C.</t>
+  </si>
+  <si>
+    <t>DUVELSAINT</t>
+  </si>
+  <si>
+    <t>TEVINSON</t>
+  </si>
+  <si>
+    <t>GARCON</t>
+  </si>
+  <si>
+    <t>ISMAEL GAMA</t>
+  </si>
+  <si>
+    <t>GABRIEL</t>
+  </si>
+  <si>
+    <t>SCHADRAC</t>
+  </si>
+  <si>
+    <t>DARLENS</t>
+  </si>
+  <si>
+    <t>CEPOUDY</t>
+  </si>
+  <si>
+    <t>ELICLES</t>
+  </si>
+  <si>
+    <t>OMRA VALDJY WOODLEY</t>
+  </si>
+  <si>
+    <t>BARTHELUS</t>
+  </si>
+  <si>
+    <t>KENLEY</t>
+  </si>
+  <si>
+    <t>MAXI</t>
+  </si>
+  <si>
+    <t>CLIFORD</t>
+  </si>
+  <si>
+    <t>CHARLES</t>
+  </si>
+  <si>
+    <t>MARKENLOVE</t>
+  </si>
+  <si>
+    <t>SYLVESTRE STALONNE</t>
+  </si>
+  <si>
+    <t>SECHOUAM</t>
+  </si>
+  <si>
+    <t>CEBATIEN</t>
+  </si>
+  <si>
+    <t>PIERRE-LOUIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JERRY BENNEDICT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOEL </t>
+  </si>
+  <si>
+    <t>oudoucis@yahoo.com</t>
+  </si>
+  <si>
+    <t>418 953 6873</t>
+  </si>
+  <si>
+    <t>ABDRAHAMANE TRAORE</t>
+  </si>
+  <si>
+    <t>Mohamed Coulibaly</t>
+  </si>
+  <si>
+    <t>NUMBER</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>SHORT</t>
+  </si>
+  <si>
+    <t>JACOB</t>
+  </si>
+  <si>
+    <t>DEMBÉLÉ</t>
+  </si>
+  <si>
+    <t>HAMED</t>
+  </si>
+  <si>
+    <t>OUSMANE</t>
+  </si>
+  <si>
+    <t>ABDOULAYE</t>
+  </si>
+  <si>
+    <t>DAO</t>
+  </si>
+  <si>
+    <t>NAMAKÉ FALAYE</t>
+  </si>
+  <si>
+    <t>SISSOKO</t>
+  </si>
+  <si>
+    <t>MOUSSA</t>
+  </si>
+  <si>
+    <t>DJIGUI</t>
+  </si>
+  <si>
+    <t>MOHAMED</t>
+  </si>
+  <si>
+    <t>ALESSANDRO DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>SALIM</t>
+  </si>
+  <si>
+    <t>NIMAGA</t>
+  </si>
+  <si>
+    <t>SIDY MAHAMANE</t>
+  </si>
+  <si>
+    <t>TOURÉ</t>
+  </si>
+  <si>
+    <t>MAHAMOUDOU</t>
+  </si>
+  <si>
+    <t>KONÉ</t>
+  </si>
+  <si>
+    <t>IDRISSA DADYS</t>
+  </si>
+  <si>
+    <t>SIDIBÉ</t>
+  </si>
+  <si>
+    <t>ABOUBAKRINE</t>
+  </si>
+  <si>
+    <t>INTALLA</t>
+  </si>
+  <si>
+    <t>SEKOU SOULEYMANE</t>
+  </si>
+  <si>
+    <t>MAMADOU BAZAN</t>
+  </si>
+  <si>
+    <t>TOGOLA</t>
+  </si>
+  <si>
+    <t>DJIMÉ</t>
+  </si>
+  <si>
+    <t>KÉBÉ</t>
+  </si>
+  <si>
+    <t>MOULAYE MOHAMED</t>
+  </si>
+  <si>
+    <t>DICKO</t>
+  </si>
+  <si>
+    <t>HAROUNA</t>
+  </si>
+  <si>
+    <t>BACHIR</t>
+  </si>
+  <si>
+    <t>BASSIROU</t>
+  </si>
+  <si>
+    <t>HAIDARA</t>
+  </si>
+  <si>
+    <t>GUESSOUMA</t>
+  </si>
+  <si>
+    <t>PATRICK STÉPHANE</t>
+  </si>
+  <si>
+    <t>KAMDEM WAKAM</t>
+  </si>
+  <si>
+    <t>MALIK</t>
+  </si>
+  <si>
+    <t>DIARRA</t>
+  </si>
+  <si>
+    <t>IBRAHIM</t>
+  </si>
+  <si>
+    <t>ISSAKA</t>
+  </si>
+  <si>
+    <t>OUMAR</t>
+  </si>
+  <si>
+    <t>CISSÉ</t>
+  </si>
+  <si>
+    <t>ALMAMY</t>
+  </si>
+  <si>
+    <t>GUINDO</t>
+  </si>
+  <si>
+    <t>KOULBÉ</t>
+  </si>
+  <si>
+    <t>Tchad</t>
+  </si>
+  <si>
+    <t>Gabon</t>
+  </si>
+  <si>
+    <t>georgesarmel1@hotmail.fr</t>
+  </si>
+  <si>
+    <t>(581)849-3674</t>
+  </si>
+  <si>
+    <t>Georges armel Nguimbi</t>
+  </si>
+  <si>
+    <t>Cedrick essockamba</t>
+  </si>
+  <si>
+    <t>DROLET</t>
+  </si>
+  <si>
+    <t>DIEUDONNÉ</t>
+  </si>
+  <si>
+    <t>CIZA</t>
+  </si>
+  <si>
+    <t>Rwanda</t>
+  </si>
+  <si>
+    <t>STEPHANE</t>
+  </si>
+  <si>
+    <t>PREDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada </t>
+  </si>
+  <si>
+    <t>CEDRIC</t>
+  </si>
+  <si>
+    <t>ESSOCKAMBA</t>
+  </si>
+  <si>
+    <t>JEAN-THERRY</t>
+  </si>
+  <si>
+    <t>YAMA</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>BAMBA</t>
+  </si>
+  <si>
+    <t>FARAJA</t>
+  </si>
+  <si>
+    <t>DIEU BENIT</t>
+  </si>
+  <si>
+    <t>SOUMAI</t>
+  </si>
+  <si>
+    <t>FEDSON</t>
+  </si>
+  <si>
+    <t>ROSIER</t>
+  </si>
+  <si>
+    <t>YANNICK</t>
+  </si>
+  <si>
+    <t>KAYILOU</t>
+  </si>
+  <si>
+    <t>ESTEBAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cote d'ivoire </t>
+  </si>
+  <si>
+    <t>JEAN DANIEL</t>
+  </si>
+  <si>
+    <t>POTTEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE </t>
+  </si>
+  <si>
+    <t>KOKORA</t>
+  </si>
+  <si>
+    <t>ABDELAZIZ</t>
+  </si>
+  <si>
+    <t>KAPATA</t>
+  </si>
+  <si>
+    <t>Centre-afrique</t>
+  </si>
+  <si>
+    <t>VINCENT</t>
+  </si>
+  <si>
+    <t>CORNEAU</t>
+  </si>
+  <si>
+    <t>DEMOYER</t>
+  </si>
+  <si>
+    <t>KOUASSI</t>
+  </si>
+  <si>
+    <t>BENONI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÉMILE </t>
+  </si>
+  <si>
+    <t>FRANCK NELSON</t>
+  </si>
+  <si>
+    <t>VOUFO</t>
+  </si>
+  <si>
+    <t>SAMUEL</t>
+  </si>
+  <si>
+    <t>POATY</t>
+  </si>
+  <si>
+    <t>DYLAN</t>
+  </si>
+  <si>
+    <t>POTE</t>
+  </si>
+  <si>
+    <t>ARGI</t>
+  </si>
+  <si>
+    <t>PASCAL</t>
+  </si>
+  <si>
+    <t>BIENVENUE</t>
+  </si>
+  <si>
+    <t>STANY</t>
+  </si>
+  <si>
+    <t>Burundi</t>
+  </si>
+  <si>
+    <t>MARC</t>
+  </si>
+  <si>
+    <t>ÉRISA</t>
+  </si>
+  <si>
+    <t>NSHIMIYIMANA</t>
+  </si>
+  <si>
+    <t>JUNIOR</t>
+  </si>
+  <si>
+    <t>POKOU</t>
+  </si>
+  <si>
+    <t>Cote d'ivoire</t>
+  </si>
+  <si>
+    <t>418-554-0364</t>
+  </si>
+  <si>
+    <t>ABDOUL-AZIZ</t>
+  </si>
+  <si>
+    <t>Hamidou Ouédraogo</t>
+  </si>
+  <si>
+    <t>FAAROOQ</t>
+  </si>
+  <si>
+    <t>CHEIK OMAR</t>
+  </si>
+  <si>
+    <t>BOUSSIM FADEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORESTE </t>
+  </si>
+  <si>
+    <t>TOMPOUDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAPI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KANE </t>
+  </si>
+  <si>
+    <t>HAMED-TIDJANI</t>
+  </si>
+  <si>
+    <t>OUEDRAOGO</t>
+  </si>
+  <si>
+    <t>ABDOUL-FATAHOU</t>
+  </si>
+  <si>
+    <t>COMPAORÉ</t>
+  </si>
+  <si>
+    <t>YACOUBA</t>
+  </si>
+  <si>
+    <t>DARGA</t>
+  </si>
+  <si>
+    <t>RAOUF</t>
+  </si>
+  <si>
+    <t>KRIGAH</t>
+  </si>
+  <si>
+    <t>HANS</t>
+  </si>
+  <si>
+    <t>KOUAKOU</t>
+  </si>
+  <si>
+    <t>ALASSANE</t>
   </si>
   <si>
     <t>FAYE</t>
   </si>
   <si>
-    <t xml:space="preserve">MOUSTAPHA </t>
-  </si>
-  <si>
-    <t>DIOP</t>
-  </si>
-  <si>
-    <t>PAPE IBRAHIMA</t>
-  </si>
-  <si>
-    <t>MANGANE</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>SÉNE</t>
-  </si>
-  <si>
-    <t>SERIGNE</t>
-  </si>
-  <si>
-    <t>FALL</t>
-  </si>
-  <si>
-    <t>BABA MAMADOU</t>
-  </si>
-  <si>
-    <t>CAMARA</t>
-  </si>
-  <si>
-    <t>PAPA BABACAR</t>
-  </si>
-  <si>
-    <t>SECK</t>
-  </si>
-  <si>
-    <t>MOUSTAPHA</t>
-  </si>
-  <si>
-    <t>PAPA GARBA</t>
-  </si>
-  <si>
-    <t>COULIBALY</t>
-  </si>
-  <si>
-    <t>GORA</t>
-  </si>
-  <si>
-    <t>MBODJ</t>
-  </si>
-  <si>
-    <t>SOULEYMANE</t>
-  </si>
-  <si>
-    <t>DIALLO</t>
-  </si>
-  <si>
-    <t>Togo</t>
-  </si>
-  <si>
-    <t>Alatevi.k@gmail.com</t>
-  </si>
-  <si>
-    <t>438-827-6129</t>
-  </si>
-  <si>
-    <t>Fabrice</t>
-  </si>
-  <si>
-    <t>Komi Alatevi</t>
-  </si>
-  <si>
-    <t>CARL ISAAC PENCHEV</t>
-  </si>
-  <si>
-    <t>RENEVIL</t>
-  </si>
-  <si>
-    <t>Haïti</t>
-  </si>
-  <si>
-    <t>KOMI</t>
-  </si>
-  <si>
-    <t>ALATEVI</t>
-  </si>
-  <si>
-    <t>AMIDOU</t>
-  </si>
-  <si>
-    <t>AKOH</t>
-  </si>
-  <si>
-    <t>KOSSI ANTHONY</t>
-  </si>
-  <si>
-    <t>ADJAMA</t>
-  </si>
-  <si>
-    <t>KOSSI SAMSON</t>
-  </si>
-  <si>
-    <t>KLOUSSE</t>
-  </si>
-  <si>
-    <t>BOTCHA</t>
-  </si>
-  <si>
-    <t>HENOC</t>
-  </si>
-  <si>
-    <t>OTNIEL</t>
-  </si>
-  <si>
-    <t>AKOEGNON</t>
-  </si>
-  <si>
-    <t>KOFFI MOÏSE</t>
-  </si>
-  <si>
-    <t>AMEVO</t>
-  </si>
-  <si>
-    <t>MANI</t>
-  </si>
-  <si>
-    <t>BABALIM</t>
-  </si>
-  <si>
-    <t>BASSITOU</t>
-  </si>
-  <si>
-    <t>ASSANI</t>
-  </si>
-  <si>
-    <t>FOUMI MAJID</t>
-  </si>
-  <si>
-    <t>OLA</t>
-  </si>
-  <si>
-    <t>FRANCIS</t>
-  </si>
-  <si>
-    <t>AGBOGBO</t>
-  </si>
-  <si>
-    <t>Tia Cixte</t>
-  </si>
-  <si>
-    <t>Marti Dji</t>
-  </si>
-  <si>
-    <t>Essofa Oubote</t>
-  </si>
-  <si>
-    <t>ABODJI</t>
-  </si>
-  <si>
-    <t>Allassane</t>
-  </si>
-  <si>
-    <t>Kone</t>
-  </si>
-  <si>
-    <t>Mouh amed</t>
-  </si>
-  <si>
-    <t>Dosso</t>
-  </si>
-  <si>
-    <t>FIACRE</t>
-  </si>
-  <si>
-    <t>KOFFI</t>
-  </si>
-  <si>
-    <t>DANIEL KOMLAN</t>
-  </si>
-  <si>
-    <t>DEKASSI</t>
-  </si>
-  <si>
-    <t>EMMANUEL BORIS</t>
-  </si>
-  <si>
-    <t>OLÉ OBALÉ</t>
-  </si>
-  <si>
-    <t>guinée</t>
-  </si>
-  <si>
-    <t>KOUTAO RAKOU</t>
-  </si>
-  <si>
-    <t>TALMANTA</t>
-  </si>
-  <si>
-    <t>ALOGNISSO</t>
-  </si>
-  <si>
-    <t>RONALD</t>
-  </si>
-  <si>
-    <t>PETERSON</t>
-  </si>
-  <si>
-    <t>AUGUSTE</t>
-  </si>
-  <si>
-    <t>CI</t>
-  </si>
-  <si>
-    <t>LOCHINA</t>
-  </si>
-  <si>
-    <t>DJAFAROU</t>
-  </si>
-  <si>
-    <t>KONATÉ</t>
-  </si>
-  <si>
-    <t>MANSOUR</t>
-  </si>
-  <si>
-    <t>KOMLAN AMEN</t>
-  </si>
-  <si>
-    <t>AKAMA</t>
-  </si>
-  <si>
-    <t>ESSODONA</t>
-  </si>
-  <si>
-    <t>HALAOUI</t>
-  </si>
-  <si>
-    <t>ADONIS</t>
-  </si>
-  <si>
-    <t>KALENGA</t>
-  </si>
-  <si>
-    <t>MKOLE</t>
-  </si>
-  <si>
-    <t>RAMADHANI</t>
-  </si>
-  <si>
-    <t>DESIRE</t>
-  </si>
-  <si>
-    <t>BICUKA</t>
-  </si>
-  <si>
-    <t>ABEDI</t>
-  </si>
-  <si>
-    <t>SAIDI</t>
-  </si>
-  <si>
-    <t>ATAMBA</t>
-  </si>
-  <si>
-    <t>SHAURI</t>
-  </si>
-  <si>
-    <t>JONAS</t>
-  </si>
-  <si>
-    <t>KISUBI</t>
-  </si>
-  <si>
-    <t>PATIENT</t>
-  </si>
-  <si>
-    <t>ECA MBOKO</t>
-  </si>
-  <si>
-    <t>SALEH</t>
-  </si>
-  <si>
-    <t>ECA</t>
-  </si>
-  <si>
-    <t>UWEZO</t>
-  </si>
-  <si>
-    <t>JUMAPILI</t>
-  </si>
-  <si>
-    <t>NDIKUMANA</t>
-  </si>
-  <si>
-    <t>JANVIER</t>
-  </si>
-  <si>
-    <t>REUBEN</t>
-  </si>
-  <si>
-    <t>MLONGEKA</t>
-  </si>
-  <si>
-    <t>AMURI</t>
-  </si>
-  <si>
-    <t>NDUME</t>
-  </si>
-  <si>
-    <t>OMARI</t>
-  </si>
-  <si>
-    <t>KASHINDI</t>
-  </si>
-  <si>
-    <t>WILONDJA</t>
-  </si>
-  <si>
-    <t>LWAMAGENA</t>
-  </si>
-  <si>
-    <t>SADIKI</t>
-  </si>
-  <si>
-    <t>SHOKU MAJEGEZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGAZINI </t>
-  </si>
-  <si>
-    <t>LWABOSHI MAJEGEZA</t>
-  </si>
-  <si>
-    <t>ERICK</t>
-  </si>
-  <si>
-    <t>NISHIMWE</t>
-  </si>
-  <si>
-    <t>ASENDE</t>
-  </si>
-  <si>
-    <t>ABANGWA</t>
-  </si>
-  <si>
-    <t>OLIVIER</t>
-  </si>
-  <si>
-    <t>RIPHIN</t>
-  </si>
-  <si>
-    <t>HONNEUR</t>
-  </si>
-  <si>
-    <t>JEAN MARIE</t>
-  </si>
-  <si>
-    <t>ELIAZERI</t>
-  </si>
-  <si>
-    <t>NIYOGUSENGA</t>
-  </si>
-  <si>
-    <t>BYAOMBE</t>
-  </si>
-  <si>
-    <t>BAHOME</t>
-  </si>
-  <si>
-    <t>YAMUNGU MLENBA</t>
-  </si>
-  <si>
-    <t>ZAKARIA</t>
-  </si>
-  <si>
-    <t>RÉMY</t>
-  </si>
-  <si>
-    <t>MILAMBO</t>
-  </si>
-  <si>
-    <t>Haiti</t>
-  </si>
-  <si>
-    <t>soccerangranmoun@gmail.com; flounes37@gmail.com</t>
-  </si>
-  <si>
-    <t>4189563785 / 4388384936</t>
-  </si>
-  <si>
-    <t>Lounès Félicin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hans Raldy Saint-Preux </t>
-  </si>
-  <si>
-    <t>MAQUINGSON</t>
-  </si>
-  <si>
-    <t>MAIGNAN</t>
-  </si>
-  <si>
-    <t>AMILICA</t>
-  </si>
-  <si>
-    <t>BOUKARI BOURDJA</t>
-  </si>
-  <si>
-    <t>MICHAEL PERSHINGSON</t>
-  </si>
-  <si>
-    <t>PIERRE</t>
-  </si>
-  <si>
-    <t>JEFFERSON</t>
-  </si>
-  <si>
-    <t>ANTOINE</t>
-  </si>
-  <si>
-    <t>GREGORY</t>
-  </si>
-  <si>
-    <t>ANNAY</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>JERRY</t>
-  </si>
-  <si>
-    <t>PAULIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AXEL </t>
-  </si>
-  <si>
-    <t>ALIMASI</t>
-  </si>
-  <si>
-    <t>MARC-ARTHUR</t>
-  </si>
-  <si>
-    <t>REGISTRE</t>
-  </si>
-  <si>
-    <t>MARC-DONALD</t>
-  </si>
-  <si>
-    <t>SIMEUS</t>
-  </si>
-  <si>
-    <t>EVEDERSON</t>
-  </si>
-  <si>
-    <t>PREVILON</t>
-  </si>
-  <si>
-    <t>WOODSON</t>
-  </si>
-  <si>
-    <t>SAINT-LOUIS</t>
-  </si>
-  <si>
-    <t>ROMAIN</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>RYSDAEL C.</t>
-  </si>
-  <si>
-    <t>DUVELSAINT</t>
-  </si>
-  <si>
-    <t>TEVINSON</t>
-  </si>
-  <si>
-    <t>GARCON</t>
-  </si>
-  <si>
-    <t>HANS RALDY</t>
-  </si>
-  <si>
-    <t>SAINT-PREUX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RÉGINALD </t>
-  </si>
-  <si>
-    <t>CADET</t>
-  </si>
-  <si>
-    <t>DARLENS</t>
-  </si>
-  <si>
-    <t>CEPOUDY</t>
-  </si>
-  <si>
-    <t>HUGGUENS</t>
-  </si>
-  <si>
-    <t>VEILLARD</t>
-  </si>
-  <si>
-    <t>OMRA VALDJY WOODLEY</t>
-  </si>
-  <si>
-    <t>BARTHELUS</t>
-  </si>
-  <si>
-    <t>KENLEY</t>
-  </si>
-  <si>
-    <t>MAXI</t>
-  </si>
-  <si>
-    <t>CLIFORD</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>TEIKEU</t>
-  </si>
-  <si>
-    <t>SYLVESTRE STALONNE</t>
-  </si>
-  <si>
-    <t>SECHOUAM</t>
-  </si>
-  <si>
-    <t>CEBATIEN</t>
-  </si>
-  <si>
-    <t>PIERRE-LOUIS</t>
-  </si>
-  <si>
-    <t>YVES-MARY</t>
-  </si>
-  <si>
-    <t>BEAUBRUN</t>
-  </si>
-  <si>
-    <t>oudoucis@yahoo.com</t>
-  </si>
-  <si>
-    <t>418 953 6873</t>
-  </si>
-  <si>
-    <t>ABDRAHAMANE TRAORE</t>
-  </si>
-  <si>
-    <t>Mohamed Coulibaly</t>
-  </si>
-  <si>
-    <t>NUMBER</t>
-  </si>
-  <si>
-    <t>TOP</t>
-  </si>
-  <si>
-    <t>SHORT</t>
-  </si>
-  <si>
-    <t>JACOB</t>
-  </si>
-  <si>
-    <t>DEMBÉLÉ</t>
-  </si>
-  <si>
-    <t>HAMED</t>
-  </si>
-  <si>
-    <t>OUSMANE</t>
-  </si>
-  <si>
-    <t>ABDOULAYE</t>
-  </si>
-  <si>
-    <t>DAO</t>
-  </si>
-  <si>
-    <t>NAMAKÉ FALAYE</t>
-  </si>
-  <si>
-    <t>SISSOKO</t>
-  </si>
-  <si>
-    <t>MOUSSA</t>
-  </si>
-  <si>
-    <t>DJIGUI</t>
-  </si>
-  <si>
-    <t>MOHAMED</t>
-  </si>
-  <si>
-    <t>KALILOU</t>
-  </si>
-  <si>
-    <t>SALIM</t>
-  </si>
-  <si>
-    <t>NIMAGA</t>
-  </si>
-  <si>
-    <t>SIDY MAHAMANE</t>
-  </si>
-  <si>
-    <t>TOURÉ</t>
-  </si>
-  <si>
-    <t>MAHAMOUDOU</t>
-  </si>
-  <si>
-    <t>KONÉ</t>
-  </si>
-  <si>
-    <t>IDRISSA DADYS</t>
-  </si>
-  <si>
-    <t>SIDIBÉ</t>
-  </si>
-  <si>
-    <t>ABOUBAKRINE</t>
-  </si>
-  <si>
-    <t>INTALLA</t>
-  </si>
-  <si>
-    <t>SEKOU SOULEYMANE</t>
-  </si>
-  <si>
-    <t>MAMADOU BAZAN</t>
-  </si>
-  <si>
-    <t>TOGOLA</t>
-  </si>
-  <si>
-    <t>DJIMÉ</t>
-  </si>
-  <si>
-    <t>KÉBÉ</t>
-  </si>
-  <si>
-    <t>MOULAYE MOHAMED</t>
-  </si>
-  <si>
-    <t>DICKO</t>
-  </si>
-  <si>
-    <t>HAROUNA</t>
-  </si>
-  <si>
-    <t>BACHIR</t>
-  </si>
-  <si>
-    <t>BASSIROU</t>
-  </si>
-  <si>
-    <t>HAIDARA</t>
-  </si>
-  <si>
-    <t>GUESSOUMA</t>
-  </si>
-  <si>
-    <t>PATRICK STÉPHANE</t>
-  </si>
-  <si>
-    <t>KAMDEM WAKAM</t>
-  </si>
-  <si>
-    <t>MALIK</t>
-  </si>
-  <si>
-    <t>DIARRA</t>
-  </si>
-  <si>
-    <t>IBRAHIM</t>
-  </si>
-  <si>
-    <t>ISSAKA</t>
-  </si>
-  <si>
-    <t>OUMAR</t>
-  </si>
-  <si>
-    <t>CISSÉ</t>
-  </si>
-  <si>
-    <t>ALMAMY</t>
-  </si>
-  <si>
-    <t>GUINDO</t>
-  </si>
-  <si>
-    <t>KOULBÉ</t>
-  </si>
-  <si>
-    <t>Tchad</t>
-  </si>
-  <si>
-    <t>Gabon</t>
-  </si>
-  <si>
-    <t>georgesarmel1@hotmail.fr</t>
-  </si>
-  <si>
-    <t>(581)849-3674</t>
-  </si>
-  <si>
-    <t>Georges armel Nguimbi</t>
-  </si>
-  <si>
-    <t>Cedrick essockamba</t>
-  </si>
-  <si>
-    <t>DROLET</t>
-  </si>
-  <si>
-    <t>DIEUDONNÉ</t>
-  </si>
-  <si>
-    <t>CIZA</t>
-  </si>
-  <si>
-    <t>Rwanda</t>
-  </si>
-  <si>
-    <t>STEPHANE</t>
-  </si>
-  <si>
-    <t>PREDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada </t>
-  </si>
-  <si>
-    <t>CEDRIC</t>
-  </si>
-  <si>
-    <t>ESSOCKAMBA</t>
-  </si>
-  <si>
-    <t>JEAN-THERRY</t>
-  </si>
-  <si>
-    <t>YAMA</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>BAMBA</t>
-  </si>
-  <si>
-    <t>FARAJA</t>
-  </si>
-  <si>
-    <t>DIEU BENIT</t>
-  </si>
-  <si>
-    <t>SOUMAI</t>
-  </si>
-  <si>
-    <t>FEDSON</t>
-  </si>
-  <si>
-    <t>ROSIER</t>
-  </si>
-  <si>
-    <t>YANNICK</t>
-  </si>
-  <si>
-    <t>KAYILOU</t>
-  </si>
-  <si>
-    <t>ESTEBAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cote d'ivoire </t>
-  </si>
-  <si>
-    <t>JEAN DANIEL</t>
-  </si>
-  <si>
-    <t>POTTEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALEXANDRE </t>
-  </si>
-  <si>
-    <t>KOKORA</t>
-  </si>
-  <si>
-    <t>ABDELAZIZ</t>
-  </si>
-  <si>
-    <t>KAPATA</t>
-  </si>
-  <si>
-    <t>Centre-afrique</t>
-  </si>
-  <si>
-    <t>VINCENT</t>
-  </si>
-  <si>
-    <t>CORNEAU</t>
-  </si>
-  <si>
-    <t>DEMOYER</t>
-  </si>
-  <si>
-    <t>KOUASSI</t>
-  </si>
-  <si>
-    <t>BENONI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ÉMILE </t>
-  </si>
-  <si>
-    <t>FRANCK NELSON</t>
-  </si>
-  <si>
-    <t>VOUFO</t>
-  </si>
-  <si>
-    <t>SAMUEL</t>
-  </si>
-  <si>
-    <t>POATY</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>POTE</t>
-  </si>
-  <si>
-    <t>ARGI</t>
-  </si>
-  <si>
-    <t>PASCAL</t>
-  </si>
-  <si>
-    <t>BIENVENUE</t>
-  </si>
-  <si>
-    <t>STANY</t>
-  </si>
-  <si>
-    <t>Burundi</t>
-  </si>
-  <si>
-    <t>MARC</t>
-  </si>
-  <si>
-    <t>ÉRISA</t>
-  </si>
-  <si>
-    <t>NSHIMIYIMANA</t>
-  </si>
-  <si>
-    <t>JUNIOR</t>
-  </si>
-  <si>
-    <t>POKOU</t>
-  </si>
-  <si>
-    <t>Cote d'ivoire</t>
-  </si>
-  <si>
-    <t>418-554-0364</t>
-  </si>
-  <si>
-    <t>ABDOUL-AZIZ</t>
-  </si>
-  <si>
-    <t>Hamidou Ouédraogo</t>
-  </si>
-  <si>
-    <t>FAAROOQ</t>
-  </si>
-  <si>
-    <t>CHEIK OMAR</t>
-  </si>
-  <si>
-    <t>BOUSSIM FADEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORESTE </t>
-  </si>
-  <si>
-    <t>TOMPOUDI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KANE </t>
-  </si>
-  <si>
-    <t>HAMED-TIDJANI</t>
-  </si>
-  <si>
-    <t>OUEDRAOGO</t>
-  </si>
-  <si>
-    <t>ABDOUL-FATAHOU</t>
-  </si>
-  <si>
-    <t>COMPAORÉ</t>
-  </si>
-  <si>
-    <t>YACOUBA</t>
-  </si>
-  <si>
-    <t>DARGA</t>
-  </si>
-  <si>
-    <t>RAOUF</t>
-  </si>
-  <si>
-    <t>KRIGAH</t>
-  </si>
-  <si>
-    <t>HANS</t>
-  </si>
-  <si>
-    <t>KOUAKOU</t>
-  </si>
-  <si>
-    <t>HAMIDOU</t>
-  </si>
-  <si>
     <t>KEVIN ESPÉRAT</t>
   </si>
   <si>
@@ -1571,10 +1568,10 @@
     <t>NOM DU CAPITAINE : Moustapha Donzo</t>
   </si>
   <si>
-    <t>ANGA</t>
-  </si>
-  <si>
-    <t>JOSUÉ</t>
+    <t>KOUROUMA NEMA</t>
+  </si>
+  <si>
+    <t>SOUA</t>
   </si>
   <si>
     <t>Guinéen</t>
@@ -2059,7 +2056,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="129">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2171,6 +2168,9 @@
     <xf borderId="1" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -2265,9 +2265,6 @@
     <xf borderId="1" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="1" fillId="8" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
@@ -2285,9 +2282,6 @@
     </xf>
     <xf borderId="1" fillId="9" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
@@ -2342,9 +2336,6 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
@@ -2952,7 +2943,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2975,7 +2966,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2987,7 +2978,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2998,8 +2989,8 @@
       <c r="H3" s="13"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="119" t="s">
-        <v>509</v>
+      <c r="A4" s="117" t="s">
+        <v>508</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -3011,7 +3002,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3085,26 +3076,26 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="73">
+      <c r="A8" s="74">
         <v>1.0</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="120" t="s">
+      <c r="D8" s="118" t="s">
+        <v>510</v>
+      </c>
+      <c r="E8" s="118" t="s">
         <v>511</v>
-      </c>
-      <c r="E8" s="120" t="s">
-        <v>512</v>
       </c>
       <c r="F8" s="40">
         <v>26.0</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -3121,26 +3112,26 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="75">
+      <c r="A9" s="76">
         <v>2.0</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="74" t="s">
+      <c r="D9" s="75" t="s">
         <v>142</v>
       </c>
-      <c r="E9" s="74" t="s">
+      <c r="E9" s="75" t="s">
+        <v>513</v>
+      </c>
+      <c r="F9" s="119">
+        <v>22.0</v>
+      </c>
+      <c r="G9" s="120" t="s">
         <v>514</v>
-      </c>
-      <c r="F9" s="121">
-        <v>22.0</v>
-      </c>
-      <c r="G9" s="122" t="s">
-        <v>515</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -3157,7 +3148,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="73">
+      <c r="A10" s="74">
         <v>3.0</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -3166,17 +3157,17 @@
       <c r="C10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="75" t="s">
+        <v>515</v>
+      </c>
+      <c r="E10" s="75" t="s">
         <v>516</v>
       </c>
-      <c r="E10" s="74" t="s">
+      <c r="F10" s="119">
+        <v>30.0</v>
+      </c>
+      <c r="G10" s="120" t="s">
         <v>517</v>
-      </c>
-      <c r="F10" s="121">
-        <v>30.0</v>
-      </c>
-      <c r="G10" s="122" t="s">
-        <v>518</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -3193,26 +3184,26 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="73">
+      <c r="A11" s="74">
         <v>4.0</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="122" t="s">
+      <c r="C11" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="75" t="s">
+        <v>518</v>
+      </c>
+      <c r="E11" s="75" t="s">
         <v>519</v>
       </c>
-      <c r="E11" s="74" t="s">
+      <c r="F11" s="119">
+        <v>25.0</v>
+      </c>
+      <c r="G11" s="120" t="s">
         <v>520</v>
-      </c>
-      <c r="F11" s="121">
-        <v>25.0</v>
-      </c>
-      <c r="G11" s="122" t="s">
-        <v>521</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11" s="29"/>
@@ -3229,24 +3220,24 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="73">
+      <c r="A12" s="74">
         <v>5.0</v>
       </c>
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="122" t="s">
+      <c r="C12" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="74" t="s">
+      <c r="D12" s="75" t="s">
+        <v>521</v>
+      </c>
+      <c r="E12" s="75" t="s">
         <v>522</v>
-      </c>
-      <c r="E12" s="74" t="s">
-        <v>523</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="41" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -3263,26 +3254,26 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="73">
+      <c r="A13" s="74">
         <v>6.0</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="122" t="s">
+      <c r="C13" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="74" t="s">
-        <v>397</v>
-      </c>
-      <c r="E13" s="74" t="s">
+      <c r="D13" s="75" t="s">
+        <v>395</v>
+      </c>
+      <c r="E13" s="75" t="s">
+        <v>524</v>
+      </c>
+      <c r="F13" s="119">
+        <v>25.0</v>
+      </c>
+      <c r="G13" s="120" t="s">
         <v>525</v>
-      </c>
-      <c r="F13" s="121">
-        <v>25.0</v>
-      </c>
-      <c r="G13" s="122" t="s">
-        <v>526</v>
       </c>
       <c r="H13" s="28"/>
       <c r="I13" s="29"/>
@@ -3299,26 +3290,26 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="73">
+      <c r="A14" s="74">
         <v>7.0</v>
       </c>
-      <c r="B14" s="74" t="s">
+      <c r="B14" s="75" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="122" t="s">
+      <c r="C14" s="120" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="74" t="s">
-        <v>397</v>
-      </c>
-      <c r="E14" s="74" t="s">
-        <v>527</v>
-      </c>
-      <c r="F14" s="121">
+      <c r="D14" s="75" t="s">
+        <v>395</v>
+      </c>
+      <c r="E14" s="75" t="s">
+        <v>526</v>
+      </c>
+      <c r="F14" s="119">
         <v>30.0</v>
       </c>
-      <c r="G14" s="122" t="s">
-        <v>526</v>
+      <c r="G14" s="120" t="s">
+        <v>525</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
@@ -3335,7 +3326,7 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="73">
+      <c r="A15" s="74">
         <v>8.0</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3344,17 +3335,17 @@
       <c r="C15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="74" t="s">
-        <v>528</v>
-      </c>
-      <c r="E15" s="74" t="s">
+      <c r="D15" s="75" t="s">
+        <v>527</v>
+      </c>
+      <c r="E15" s="75" t="s">
+        <v>524</v>
+      </c>
+      <c r="F15" s="119">
+        <v>22.0</v>
+      </c>
+      <c r="G15" s="120" t="s">
         <v>525</v>
-      </c>
-      <c r="F15" s="121">
-        <v>22.0</v>
-      </c>
-      <c r="G15" s="122" t="s">
-        <v>526</v>
       </c>
       <c r="H15" s="28"/>
       <c r="I15" s="29"/>
@@ -3371,24 +3362,24 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="73">
+      <c r="A16" s="74">
         <v>9.0</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="75" t="s">
         <v>102</v>
       </c>
       <c r="C16" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="74" t="s">
-        <v>365</v>
-      </c>
-      <c r="E16" s="74" t="s">
-        <v>529</v>
+      <c r="D16" s="75" t="s">
+        <v>362</v>
+      </c>
+      <c r="E16" s="75" t="s">
+        <v>528</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -3405,26 +3396,26 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="75">
+      <c r="A17" s="76">
         <v>10.0</v>
       </c>
-      <c r="B17" s="74" t="s">
+      <c r="B17" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="122" t="s">
+      <c r="C17" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="75" t="s">
+        <v>530</v>
+      </c>
+      <c r="E17" s="75" t="s">
         <v>531</v>
       </c>
-      <c r="E17" s="74" t="s">
-        <v>532</v>
-      </c>
-      <c r="F17" s="121">
+      <c r="F17" s="119">
         <v>27.0</v>
       </c>
-      <c r="G17" s="122" t="s">
-        <v>518</v>
+      <c r="G17" s="120" t="s">
+        <v>517</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
@@ -3441,26 +3432,26 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="73">
+      <c r="A18" s="74">
         <v>11.0</v>
       </c>
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="122" t="s">
+      <c r="C18" s="120" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="74" t="s">
+      <c r="D18" s="75" t="s">
+        <v>532</v>
+      </c>
+      <c r="E18" s="75" t="s">
         <v>533</v>
       </c>
-      <c r="E18" s="74" t="s">
-        <v>534</v>
-      </c>
-      <c r="F18" s="121">
+      <c r="F18" s="119">
         <v>23.0</v>
       </c>
-      <c r="G18" s="122" t="s">
-        <v>526</v>
+      <c r="G18" s="120" t="s">
+        <v>525</v>
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
@@ -3477,26 +3468,26 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="75">
+      <c r="A19" s="76">
         <v>12.0</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="122" t="s">
+      <c r="C19" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="74" t="s">
-        <v>180</v>
-      </c>
-      <c r="E19" s="74" t="s">
-        <v>535</v>
-      </c>
-      <c r="F19" s="121">
+      <c r="D19" s="75" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" s="75" t="s">
+        <v>534</v>
+      </c>
+      <c r="F19" s="119">
         <v>30.0</v>
       </c>
-      <c r="G19" s="122" t="s">
-        <v>518</v>
+      <c r="G19" s="120" t="s">
+        <v>517</v>
       </c>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
@@ -3513,24 +3504,24 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="75">
+      <c r="A20" s="76">
         <v>13.0</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="122" t="s">
+      <c r="C20" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="74" t="s">
+      <c r="D20" s="75" t="s">
+        <v>535</v>
+      </c>
+      <c r="E20" s="75" t="s">
         <v>536</v>
       </c>
-      <c r="E20" s="74" t="s">
-        <v>537</v>
-      </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="122" t="s">
-        <v>526</v>
+      <c r="G20" s="120" t="s">
+        <v>525</v>
       </c>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
@@ -3547,26 +3538,26 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="75">
+      <c r="A21" s="76">
         <v>14.0</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="122" t="s">
+      <c r="C21" s="120" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="74" t="s">
+      <c r="D21" s="75" t="s">
+        <v>537</v>
+      </c>
+      <c r="E21" s="75" t="s">
         <v>538</v>
       </c>
-      <c r="E21" s="74" t="s">
-        <v>539</v>
-      </c>
-      <c r="F21" s="121">
+      <c r="F21" s="119">
         <v>18.0</v>
       </c>
-      <c r="G21" s="122" t="s">
-        <v>524</v>
+      <c r="G21" s="120" t="s">
+        <v>523</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -3583,26 +3574,26 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="73">
+      <c r="A22" s="74">
         <v>15.0</v>
       </c>
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="121" t="s">
         <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="74" t="s">
-        <v>365</v>
-      </c>
-      <c r="E22" s="74" t="s">
-        <v>540</v>
-      </c>
-      <c r="F22" s="121">
+      <c r="D22" s="75" t="s">
+        <v>362</v>
+      </c>
+      <c r="E22" s="75" t="s">
+        <v>539</v>
+      </c>
+      <c r="F22" s="119">
         <v>23.0</v>
       </c>
-      <c r="G22" s="122" t="s">
-        <v>526</v>
+      <c r="G22" s="120" t="s">
+        <v>525</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -3619,26 +3610,26 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="75">
+      <c r="A23" s="76">
         <v>16.0</v>
       </c>
-      <c r="B23" s="123" t="s">
+      <c r="B23" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="122" t="s">
+      <c r="C23" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="74" t="s">
-        <v>541</v>
-      </c>
-      <c r="E23" s="74" t="s">
-        <v>517</v>
-      </c>
-      <c r="F23" s="121">
+      <c r="D23" s="75" t="s">
+        <v>540</v>
+      </c>
+      <c r="E23" s="75" t="s">
+        <v>516</v>
+      </c>
+      <c r="F23" s="119">
         <v>22.0</v>
       </c>
-      <c r="G23" s="122" t="s">
-        <v>526</v>
+      <c r="G23" s="120" t="s">
+        <v>525</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -3655,26 +3646,26 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="124">
+      <c r="A24" s="122">
         <v>17.0</v>
       </c>
-      <c r="B24" s="125" t="s">
+      <c r="B24" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="126" t="s">
+      <c r="C24" s="124" t="s">
         <v>94</v>
       </c>
       <c r="D24" s="83" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E24" s="83" t="s">
-        <v>186</v>
-      </c>
-      <c r="F24" s="121">
+        <v>185</v>
+      </c>
+      <c r="F24" s="119">
         <v>30.0</v>
       </c>
-      <c r="G24" s="122" t="s">
-        <v>518</v>
+      <c r="G24" s="120" t="s">
+        <v>517</v>
       </c>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
@@ -3691,26 +3682,26 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="73">
+      <c r="A25" s="74">
         <v>18.0</v>
       </c>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="122" t="s">
+      <c r="C25" s="120" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="74" t="s">
-        <v>360</v>
-      </c>
-      <c r="E25" s="74" t="s">
-        <v>543</v>
-      </c>
-      <c r="F25" s="121">
+      <c r="D25" s="75" t="s">
+        <v>357</v>
+      </c>
+      <c r="E25" s="75" t="s">
+        <v>542</v>
+      </c>
+      <c r="F25" s="119">
         <v>19.0</v>
       </c>
-      <c r="G25" s="122" t="s">
-        <v>526</v>
+      <c r="G25" s="120" t="s">
+        <v>525</v>
       </c>
       <c r="H25" s="28"/>
       <c r="I25" s="29"/>
@@ -3727,24 +3718,24 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="75">
+      <c r="A26" s="76">
         <v>19.0</v>
       </c>
-      <c r="B26" s="74" t="s">
+      <c r="B26" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="122" t="s">
+      <c r="C26" s="120" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="74" t="s">
+      <c r="D26" s="75" t="s">
+        <v>543</v>
+      </c>
+      <c r="E26" s="75" t="s">
         <v>544</v>
-      </c>
-      <c r="E26" s="74" t="s">
-        <v>545</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="32"/>
@@ -3761,24 +3752,24 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="127">
+      <c r="A27" s="125">
         <v>20.0</v>
       </c>
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="75" t="s">
         <v>102</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="74" t="s">
-        <v>546</v>
-      </c>
-      <c r="E27" s="74" t="s">
-        <v>534</v>
+      <c r="D27" s="75" t="s">
+        <v>545</v>
+      </c>
+      <c r="E27" s="75" t="s">
+        <v>533</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="122" t="s">
-        <v>524</v>
+      <c r="G27" s="120" t="s">
+        <v>523</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -3795,62 +3786,62 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="124">
+      <c r="A28" s="122">
         <v>21.0</v>
       </c>
-      <c r="B28" s="125" t="s">
+      <c r="B28" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="126" t="s">
+      <c r="C28" s="124" t="s">
         <v>94</v>
       </c>
       <c r="D28" s="83" t="s">
+        <v>546</v>
+      </c>
+      <c r="E28" s="83" t="s">
         <v>547</v>
       </c>
-      <c r="E28" s="83" t="s">
-        <v>548</v>
-      </c>
-      <c r="F28" s="104">
+      <c r="F28" s="102">
         <v>23.0</v>
       </c>
-      <c r="G28" s="105" t="s">
-        <v>524</v>
-      </c>
-      <c r="H28" s="65"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="65">
+      <c r="G28" s="103" t="s">
+        <v>523</v>
+      </c>
+      <c r="H28" s="66"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="67"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="75">
+      <c r="A29" s="76">
         <v>22.0</v>
       </c>
-      <c r="B29" s="74" t="s">
+      <c r="B29" s="75" t="s">
         <v>102</v>
       </c>
       <c r="C29" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="74" t="s">
+      <c r="D29" s="75" t="s">
+        <v>548</v>
+      </c>
+      <c r="E29" s="75" t="s">
         <v>549</v>
-      </c>
-      <c r="E29" s="74" t="s">
-        <v>550</v>
       </c>
       <c r="F29" s="40">
         <v>22.0</v>
       </c>
       <c r="G29" s="41" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -3867,26 +3858,26 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="75">
+      <c r="A30" s="76">
         <v>23.0</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="122" t="s">
+      <c r="C30" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="74" t="s">
+      <c r="D30" s="75" t="s">
+        <v>550</v>
+      </c>
+      <c r="E30" s="75" t="s">
         <v>551</v>
       </c>
-      <c r="E30" s="74" t="s">
+      <c r="F30" s="119">
+        <v>21.0</v>
+      </c>
+      <c r="G30" s="120" t="s">
         <v>552</v>
-      </c>
-      <c r="F30" s="121">
-        <v>21.0</v>
-      </c>
-      <c r="G30" s="122" t="s">
-        <v>553</v>
       </c>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
@@ -3903,26 +3894,26 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="75">
+      <c r="A31" s="76">
         <v>24.0</v>
       </c>
-      <c r="B31" s="74" t="s">
+      <c r="B31" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="128" t="s">
-        <v>554</v>
-      </c>
-      <c r="E31" s="74" t="s">
-        <v>517</v>
+      <c r="D31" s="126" t="s">
+        <v>553</v>
+      </c>
+      <c r="E31" s="75" t="s">
+        <v>516</v>
       </c>
       <c r="F31" s="40">
         <v>30.0</v>
       </c>
       <c r="G31" s="41" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
@@ -3939,62 +3930,62 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="75">
+      <c r="A32" s="76">
         <v>25.0</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="122" t="s">
+      <c r="C32" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="74" t="s">
+      <c r="D32" s="75" t="s">
+        <v>554</v>
+      </c>
+      <c r="E32" s="75" t="s">
         <v>555</v>
       </c>
-      <c r="E32" s="74" t="s">
+      <c r="F32" s="127">
+        <v>23.0</v>
+      </c>
+      <c r="G32" s="128" t="s">
         <v>556</v>
       </c>
-      <c r="F32" s="129">
-        <v>23.0</v>
-      </c>
-      <c r="G32" s="130" t="s">
+      <c r="H32" s="66"/>
+      <c r="I32" s="67"/>
+      <c r="J32" s="67"/>
+      <c r="K32" s="67"/>
+      <c r="L32" s="67"/>
+      <c r="M32" s="67"/>
+      <c r="N32" s="67"/>
+      <c r="O32" s="67"/>
+      <c r="P32" s="67"/>
+      <c r="Q32" s="66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="125">
+        <v>26.0</v>
+      </c>
+      <c r="B33" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="120" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="75" t="s">
         <v>557</v>
       </c>
-      <c r="H32" s="65"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="66"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="66"/>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="65">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="127">
-        <v>26.0</v>
-      </c>
-      <c r="B33" s="74" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="122" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="74" t="s">
-        <v>558</v>
-      </c>
-      <c r="E33" s="74" t="s">
-        <v>186</v>
-      </c>
-      <c r="F33" s="121">
+      <c r="E33" s="75" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="119">
         <v>22.0</v>
       </c>
-      <c r="G33" s="122" t="s">
-        <v>524</v>
+      <c r="G33" s="120" t="s">
+        <v>523</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -5853,10 +5844,10 @@
       <c r="C22" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="45" t="s">
         <v>167</v>
       </c>
       <c r="F22" s="40"/>
@@ -5882,14 +5873,14 @@
       <c r="B23" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="46" t="s">
-        <v>169</v>
+      <c r="E23" s="47" t="s">
+        <v>167</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="41"/>
@@ -5918,10 +5909,10 @@
         <v>76</v>
       </c>
       <c r="D24" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="23" t="s">
         <v>170</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>171</v>
       </c>
       <c r="F24" s="40"/>
       <c r="G24" s="41"/>
@@ -5950,10 +5941,10 @@
         <v>94</v>
       </c>
       <c r="D25" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>172</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>173</v>
       </c>
       <c r="F25" s="40"/>
       <c r="G25" s="41"/>
@@ -5982,10 +5973,10 @@
         <v>94</v>
       </c>
       <c r="D26" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="23" t="s">
         <v>174</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>175</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41"/>
@@ -6004,7 +5995,7 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="47">
+      <c r="A27" s="48">
         <v>20.0</v>
       </c>
       <c r="B27" s="23" t="s">
@@ -6014,10 +6005,10 @@
         <v>94</v>
       </c>
       <c r="D27" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="23" t="s">
         <v>176</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>177</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="41"/>
@@ -6046,7 +6037,7 @@
         <v>86</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E28" s="23" t="s">
         <v>155</v>
@@ -6078,10 +6069,10 @@
         <v>94</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="41"/>
@@ -6110,7 +6101,7 @@
         <v>76</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E30" s="23" t="s">
         <v>153</v>
@@ -6142,10 +6133,10 @@
         <v>76</v>
       </c>
       <c r="D31" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="43" t="s">
         <v>181</v>
-      </c>
-      <c r="E31" s="43" t="s">
-        <v>182</v>
       </c>
       <c r="F31" s="40"/>
       <c r="G31" s="41"/>
@@ -6174,10 +6165,10 @@
         <v>86</v>
       </c>
       <c r="D32" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="23" t="s">
         <v>183</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>184</v>
       </c>
       <c r="F32" s="40"/>
       <c r="G32" s="41"/>
@@ -6202,14 +6193,14 @@
       <c r="B33" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="45" t="s">
+      <c r="C33" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="46" t="s">
+      <c r="D33" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" s="47" t="s">
         <v>185</v>
-      </c>
-      <c r="E33" s="46" t="s">
-        <v>186</v>
       </c>
       <c r="F33" s="40"/>
       <c r="G33" s="41"/>
@@ -6291,7 +6282,7 @@
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="6"/>
@@ -6316,7 +6307,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
@@ -6330,7 +6321,7 @@
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
       <c r="E3" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -6344,7 +6335,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -6358,7 +6349,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -6381,7 +6372,7 @@
       <c r="B7" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="49" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="20" t="s">
@@ -6428,24 +6419,24 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="49">
+      <c r="A8" s="50">
         <v>1.0</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="53" t="s">
         <v>192</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="F8" s="54"/>
+      <c r="G8" s="55" t="s">
         <v>193</v>
-      </c>
-      <c r="F8" s="53"/>
-      <c r="G8" s="54" t="s">
-        <v>194</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -6462,24 +6453,24 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="55">
+      <c r="A9" s="56">
         <v>2.0</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="D9" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="E9" s="56" t="s">
-        <v>196</v>
-      </c>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57" t="s">
-        <v>187</v>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58" t="s">
+        <v>186</v>
       </c>
       <c r="H9" s="28"/>
       <c r="I9" s="29"/>
@@ -6496,24 +6487,24 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="55">
+      <c r="A10" s="56">
         <v>3.0</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10" s="57" t="s">
         <v>197</v>
       </c>
-      <c r="E10" s="56" t="s">
-        <v>198</v>
-      </c>
-      <c r="F10" s="53"/>
-      <c r="G10" s="54" t="s">
-        <v>187</v>
+      <c r="F10" s="54"/>
+      <c r="G10" s="55" t="s">
+        <v>186</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -6530,24 +6521,24 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="49">
+      <c r="A11" s="50">
         <v>4.0</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="E11" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="F11" s="58"/>
-      <c r="G11" s="57" t="s">
-        <v>187</v>
+      <c r="F11" s="59"/>
+      <c r="G11" s="58" t="s">
+        <v>186</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
@@ -6564,24 +6555,24 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="49">
+      <c r="A12" s="50">
         <v>5.0</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="E12" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="52" t="s">
-        <v>202</v>
-      </c>
-      <c r="F12" s="53"/>
-      <c r="G12" s="54" t="s">
-        <v>187</v>
+      <c r="F12" s="54"/>
+      <c r="G12" s="55" t="s">
+        <v>186</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -6598,23 +6589,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="49">
+      <c r="A13" s="50">
         <v>6.0</v>
       </c>
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="53" t="s">
         <v>203</v>
       </c>
-      <c r="E13" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="F13" s="58"/>
-      <c r="G13" s="57" t="s">
+      <c r="F13" s="59"/>
+      <c r="G13" s="58" t="s">
         <v>120</v>
       </c>
       <c r="H13" s="31"/>
@@ -6632,24 +6623,24 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="55">
+      <c r="A14" s="56">
         <v>7.0</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="56" t="s">
+      <c r="D14" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="E14" s="56" t="s">
-        <v>206</v>
-      </c>
-      <c r="F14" s="58"/>
-      <c r="G14" s="57" t="s">
-        <v>187</v>
+      <c r="F14" s="59"/>
+      <c r="G14" s="58" t="s">
+        <v>186</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="32"/>
@@ -6666,24 +6657,24 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="49">
+      <c r="A15" s="50">
         <v>8.0</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="E15" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="F15" s="58"/>
-      <c r="G15" s="57" t="s">
-        <v>187</v>
+      <c r="F15" s="59"/>
+      <c r="G15" s="58" t="s">
+        <v>186</v>
       </c>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
@@ -6700,24 +6691,24 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="49">
+      <c r="A16" s="50">
         <v>9.0</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="52" t="s">
+      <c r="D16" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="E16" s="52" t="s">
-        <v>210</v>
-      </c>
-      <c r="F16" s="59"/>
-      <c r="G16" s="60" t="s">
-        <v>187</v>
+      <c r="F16" s="60"/>
+      <c r="G16" s="61" t="s">
+        <v>186</v>
       </c>
       <c r="H16" s="31"/>
       <c r="I16" s="32"/>
@@ -6734,24 +6725,24 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="49">
+      <c r="A17" s="50">
         <v>10.0</v>
       </c>
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="52" t="s">
+      <c r="D17" s="53" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="E17" s="52" t="s">
-        <v>212</v>
-      </c>
-      <c r="F17" s="53"/>
-      <c r="G17" s="54" t="s">
-        <v>187</v>
+      <c r="F17" s="54"/>
+      <c r="G17" s="55" t="s">
+        <v>186</v>
       </c>
       <c r="H17" s="28"/>
       <c r="I17" s="29"/>
@@ -6768,24 +6759,24 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="61">
+      <c r="A18" s="62">
         <v>11.0</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="51" t="s">
+      <c r="C18" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="56" t="s">
+      <c r="D18" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="E18" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="E18" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="F18" s="53"/>
-      <c r="G18" s="54" t="s">
-        <v>187</v>
+      <c r="F18" s="54"/>
+      <c r="G18" s="55" t="s">
+        <v>186</v>
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
@@ -6802,24 +6793,24 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="49">
+      <c r="A19" s="50">
         <v>12.0</v>
       </c>
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="51" t="s">
+      <c r="C19" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="52" t="s">
+      <c r="D19" s="53" t="s">
+        <v>214</v>
+      </c>
+      <c r="E19" s="53" t="s">
         <v>215</v>
       </c>
-      <c r="E19" s="52" t="s">
-        <v>216</v>
-      </c>
-      <c r="F19" s="53"/>
-      <c r="G19" s="54" t="s">
-        <v>187</v>
+      <c r="F19" s="54"/>
+      <c r="G19" s="55" t="s">
+        <v>186</v>
       </c>
       <c r="H19" s="28"/>
       <c r="I19" s="29"/>
@@ -6836,24 +6827,24 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="62">
+      <c r="A20" s="63">
         <v>13.0</v>
       </c>
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="51" t="s">
+      <c r="C20" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="D20" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" s="53" t="s">
         <v>217</v>
       </c>
-      <c r="E20" s="52" t="s">
-        <v>218</v>
-      </c>
-      <c r="F20" s="53"/>
-      <c r="G20" s="54" t="s">
-        <v>187</v>
+      <c r="F20" s="54"/>
+      <c r="G20" s="55" t="s">
+        <v>186</v>
       </c>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
@@ -6870,58 +6861,58 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="61">
+      <c r="A21" s="62">
         <v>14.0</v>
       </c>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="51" t="s">
+      <c r="C21" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="56" t="s">
+      <c r="D21" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="E21" s="57" t="s">
         <v>219</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="F21" s="64"/>
+      <c r="G21" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="H21" s="66"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="67"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="67"/>
+      <c r="Q21" s="66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="56">
+        <v>15.0</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="F21" s="63"/>
-      <c r="G21" s="64" t="s">
-        <v>187</v>
-      </c>
-      <c r="H21" s="65"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="65">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="55">
-        <v>15.0</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="56" t="s">
+      <c r="E22" s="57" t="s">
         <v>221</v>
       </c>
-      <c r="E22" s="56" t="s">
-        <v>222</v>
-      </c>
-      <c r="F22" s="58"/>
-      <c r="G22" s="57" t="s">
-        <v>187</v>
+      <c r="F22" s="59"/>
+      <c r="G22" s="58" t="s">
+        <v>186</v>
       </c>
       <c r="H22" s="31"/>
       <c r="I22" s="32"/>
@@ -6938,24 +6929,24 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="49">
+      <c r="A23" s="50">
         <v>16.0</v>
       </c>
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="E23" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="E23" s="52" t="s">
-        <v>224</v>
-      </c>
-      <c r="F23" s="58"/>
-      <c r="G23" s="57" t="s">
-        <v>187</v>
+      <c r="F23" s="59"/>
+      <c r="G23" s="58" t="s">
+        <v>186</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -6972,24 +6963,24 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="61">
+      <c r="A24" s="62">
         <v>17.0</v>
       </c>
-      <c r="B24" s="50" t="s">
+      <c r="B24" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="67" t="s">
+      <c r="D24" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="E24" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="E24" s="67" t="s">
-        <v>226</v>
-      </c>
-      <c r="F24" s="53"/>
-      <c r="G24" s="54" t="s">
-        <v>187</v>
+      <c r="F24" s="54"/>
+      <c r="G24" s="55" t="s">
+        <v>186</v>
       </c>
       <c r="H24" s="31"/>
       <c r="I24" s="32"/>
@@ -7006,24 +6997,24 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="62">
+      <c r="A25" s="63">
         <v>18.0</v>
       </c>
-      <c r="B25" s="50" t="s">
+      <c r="B25" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="52" t="s">
+      <c r="D25" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="E25" s="53" t="s">
         <v>227</v>
       </c>
-      <c r="E25" s="52" t="s">
-        <v>228</v>
-      </c>
-      <c r="F25" s="58"/>
-      <c r="G25" s="57" t="s">
-        <v>187</v>
+      <c r="F25" s="59"/>
+      <c r="G25" s="58" t="s">
+        <v>186</v>
       </c>
       <c r="H25" s="28"/>
       <c r="I25" s="29"/>
@@ -7040,24 +7031,24 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="62">
+      <c r="A26" s="63">
         <v>19.0</v>
       </c>
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="67" t="s">
+      <c r="D26" s="68" t="s">
+        <v>228</v>
+      </c>
+      <c r="E26" s="68" t="s">
         <v>229</v>
       </c>
-      <c r="E26" s="67" t="s">
+      <c r="F26" s="55"/>
+      <c r="G26" s="55" t="s">
         <v>230</v>
-      </c>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54" t="s">
-        <v>231</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="32"/>
@@ -7074,24 +7065,24 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="49">
+      <c r="A27" s="50">
         <v>20.0</v>
       </c>
-      <c r="B27" s="50" t="s">
+      <c r="B27" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="52" t="s">
+      <c r="D27" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="E27" s="53" t="s">
         <v>232</v>
       </c>
-      <c r="E27" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="54" t="s">
-        <v>187</v>
+      <c r="F27" s="54"/>
+      <c r="G27" s="55" t="s">
+        <v>186</v>
       </c>
       <c r="H27" s="28"/>
       <c r="I27" s="29"/>
@@ -7108,23 +7099,23 @@
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
-      <c r="A28" s="55">
+      <c r="A28" s="56">
         <v>21.0</v>
       </c>
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="56" t="s">
+      <c r="D28" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="E28" s="57" t="s">
         <v>234</v>
       </c>
-      <c r="E28" s="56" t="s">
-        <v>235</v>
-      </c>
-      <c r="F28" s="69"/>
-      <c r="G28" s="60"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="61"/>
       <c r="H28" s="31"/>
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
@@ -7137,24 +7128,24 @@
       <c r="Q28" s="31"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="62">
+      <c r="A29" s="63">
         <v>22.0</v>
       </c>
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D29" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="E29" s="53" t="s">
         <v>236</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="F29" s="70"/>
+      <c r="G29" s="61" t="s">
         <v>237</v>
-      </c>
-      <c r="F29" s="69"/>
-      <c r="G29" s="60" t="s">
-        <v>238</v>
       </c>
       <c r="H29" s="28"/>
       <c r="I29" s="29"/>
@@ -7171,23 +7162,23 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="61">
+      <c r="A30" s="62">
         <v>23.0</v>
       </c>
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="56" t="s">
+      <c r="D30" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="E30" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E30" s="56" t="s">
-        <v>240</v>
-      </c>
-      <c r="F30" s="69"/>
-      <c r="G30" s="60"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="61"/>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
@@ -7203,23 +7194,23 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="62">
+      <c r="A31" s="63">
         <v>24.0</v>
       </c>
-      <c r="B31" s="50" t="s">
+      <c r="B31" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="51" t="s">
+      <c r="C31" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="D31" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="E31" s="53" t="s">
         <v>241</v>
       </c>
-      <c r="E31" s="52" t="s">
-        <v>242</v>
-      </c>
-      <c r="F31" s="69"/>
-      <c r="G31" s="60"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="61"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
       <c r="J31" s="29"/>
@@ -7235,23 +7226,23 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="62">
+      <c r="A32" s="63">
         <v>25.0</v>
       </c>
-      <c r="B32" s="50" t="s">
+      <c r="B32" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="52" t="s">
+      <c r="D32" s="53" t="s">
+        <v>242</v>
+      </c>
+      <c r="E32" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="E32" s="52" t="s">
-        <v>244</v>
-      </c>
-      <c r="F32" s="69"/>
-      <c r="G32" s="60"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="61"/>
       <c r="H32" s="31"/>
       <c r="I32" s="32"/>
       <c r="J32" s="32"/>
@@ -7267,24 +7258,24 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="49">
+      <c r="A33" s="50">
         <v>26.0</v>
       </c>
-      <c r="B33" s="50" t="s">
+      <c r="B33" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="70" t="s">
+      <c r="D33" s="71" t="s">
+        <v>244</v>
+      </c>
+      <c r="E33" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="E33" s="52" t="s">
-        <v>246</v>
-      </c>
-      <c r="F33" s="58"/>
-      <c r="G33" s="57" t="s">
-        <v>187</v>
+      <c r="F33" s="59"/>
+      <c r="G33" s="58" t="s">
+        <v>186</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -7301,13 +7292,13 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="62"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="72"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="73"/>
       <c r="H34" s="31"/>
       <c r="I34" s="32"/>
       <c r="J34" s="32"/>
@@ -7510,20 +7501,20 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="73">
+      <c r="A8" s="74">
         <v>1.0</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="75" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="75" t="s">
         <v>247</v>
-      </c>
-      <c r="E8" s="74" t="s">
-        <v>248</v>
       </c>
       <c r="F8" s="40"/>
       <c r="G8" s="41"/>
@@ -7542,18 +7533,18 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="75">
+      <c r="A9" s="76">
         <v>2.0</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C9" s="41"/>
-      <c r="D9" s="74" t="s">
+      <c r="D9" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E9" s="75" t="s">
         <v>249</v>
-      </c>
-      <c r="E9" s="74" t="s">
-        <v>250</v>
       </c>
       <c r="F9" s="40"/>
       <c r="G9" s="41"/>
@@ -7572,18 +7563,18 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="73">
+      <c r="A10" s="74">
         <v>3.0</v>
       </c>
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C10" s="41"/>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="75" t="s">
+        <v>250</v>
+      </c>
+      <c r="E10" s="75" t="s">
         <v>251</v>
-      </c>
-      <c r="E10" s="74" t="s">
-        <v>252</v>
       </c>
       <c r="F10" s="40"/>
       <c r="G10" s="41"/>
@@ -7602,18 +7593,18 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="75">
+      <c r="A11" s="76">
         <v>4.0</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C11" s="41"/>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="75" t="s">
+        <v>252</v>
+      </c>
+      <c r="E11" s="75" t="s">
         <v>253</v>
-      </c>
-      <c r="E11" s="74" t="s">
-        <v>254</v>
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="41"/>
@@ -7632,18 +7623,18 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="73">
+      <c r="A12" s="74">
         <v>5.0</v>
       </c>
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C12" s="41"/>
-      <c r="D12" s="74" t="s">
+      <c r="D12" s="75" t="s">
+        <v>254</v>
+      </c>
+      <c r="E12" s="75" t="s">
         <v>255</v>
-      </c>
-      <c r="E12" s="74" t="s">
-        <v>256</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="41"/>
@@ -7662,18 +7653,18 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="75">
+      <c r="A13" s="76">
         <v>6.0</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C13" s="41"/>
-      <c r="D13" s="74" t="s">
+      <c r="D13" s="75" t="s">
+        <v>256</v>
+      </c>
+      <c r="E13" s="75" t="s">
         <v>257</v>
-      </c>
-      <c r="E13" s="74" t="s">
-        <v>258</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="41"/>
@@ -7692,18 +7683,18 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="73">
+      <c r="A14" s="74">
         <v>7.0</v>
       </c>
-      <c r="B14" s="74" t="s">
+      <c r="B14" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="41"/>
-      <c r="D14" s="74" t="s">
+      <c r="D14" s="75" t="s">
+        <v>258</v>
+      </c>
+      <c r="E14" s="75" t="s">
         <v>259</v>
-      </c>
-      <c r="E14" s="74" t="s">
-        <v>260</v>
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="41"/>
@@ -7722,18 +7713,18 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="75">
+      <c r="A15" s="76">
         <v>8.0</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="B15" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C15" s="41"/>
-      <c r="D15" s="74" t="s">
+      <c r="D15" s="75" t="s">
+        <v>260</v>
+      </c>
+      <c r="E15" s="75" t="s">
         <v>261</v>
-      </c>
-      <c r="E15" s="74" t="s">
-        <v>262</v>
       </c>
       <c r="F15" s="40"/>
       <c r="G15" s="41"/>
@@ -7752,18 +7743,18 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="73">
+      <c r="A16" s="74">
         <v>9.0</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C16" s="41"/>
-      <c r="D16" s="74" t="s">
-        <v>263</v>
-      </c>
-      <c r="E16" s="74" t="s">
-        <v>256</v>
+      <c r="D16" s="75" t="s">
+        <v>262</v>
+      </c>
+      <c r="E16" s="75" t="s">
+        <v>255</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41"/>
@@ -7782,18 +7773,18 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="75">
+      <c r="A17" s="76">
         <v>10.0</v>
       </c>
-      <c r="B17" s="74" t="s">
+      <c r="B17" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="41"/>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="75" t="s">
+        <v>263</v>
+      </c>
+      <c r="E17" s="75" t="s">
         <v>264</v>
-      </c>
-      <c r="E17" s="74" t="s">
-        <v>265</v>
       </c>
       <c r="F17" s="40"/>
       <c r="G17" s="41"/>
@@ -7812,18 +7803,18 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="73">
+      <c r="A18" s="74">
         <v>11.0</v>
       </c>
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="41"/>
-      <c r="D18" s="74" t="s">
-        <v>266</v>
-      </c>
-      <c r="E18" s="74" t="s">
-        <v>258</v>
+      <c r="D18" s="75" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" s="75" t="s">
+        <v>257</v>
       </c>
       <c r="F18" s="40"/>
       <c r="G18" s="41"/>
@@ -7842,18 +7833,18 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="75">
+      <c r="A19" s="76">
         <v>12.0</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="74" t="s">
+      <c r="D19" s="75" t="s">
+        <v>266</v>
+      </c>
+      <c r="E19" s="75" t="s">
         <v>267</v>
-      </c>
-      <c r="E19" s="74" t="s">
-        <v>268</v>
       </c>
       <c r="F19" s="40"/>
       <c r="G19" s="41"/>
@@ -7872,18 +7863,18 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="73">
+      <c r="A20" s="74">
         <v>13.0</v>
       </c>
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C20" s="41"/>
-      <c r="D20" s="74" t="s">
+      <c r="D20" s="75" t="s">
+        <v>268</v>
+      </c>
+      <c r="E20" s="77" t="s">
         <v>269</v>
-      </c>
-      <c r="E20" s="76" t="s">
-        <v>270</v>
       </c>
       <c r="F20" s="40"/>
       <c r="G20" s="41"/>
@@ -7902,18 +7893,18 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="75">
+      <c r="A21" s="76">
         <v>14.0</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C21" s="41"/>
-      <c r="D21" s="74" t="s">
+      <c r="D21" s="75" t="s">
+        <v>270</v>
+      </c>
+      <c r="E21" s="75" t="s">
         <v>271</v>
-      </c>
-      <c r="E21" s="74" t="s">
-        <v>272</v>
       </c>
       <c r="F21" s="40"/>
       <c r="G21" s="41"/>
@@ -7932,18 +7923,18 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="73">
+      <c r="A22" s="74">
         <v>15.0</v>
       </c>
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C22" s="41"/>
-      <c r="D22" s="74" t="s">
+      <c r="D22" s="75" t="s">
+        <v>272</v>
+      </c>
+      <c r="E22" s="75" t="s">
         <v>273</v>
-      </c>
-      <c r="E22" s="74" t="s">
-        <v>274</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="41"/>
@@ -7962,18 +7953,18 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="75">
+      <c r="A23" s="76">
         <v>16.0</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C23" s="41"/>
-      <c r="D23" s="74" t="s">
+      <c r="D23" s="78" t="s">
+        <v>274</v>
+      </c>
+      <c r="E23" s="78" t="s">
         <v>275</v>
-      </c>
-      <c r="E23" s="76" t="s">
-        <v>276</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="41"/>
@@ -7992,18 +7983,18 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="73">
+      <c r="A24" s="74">
         <v>17.0</v>
       </c>
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C24" s="41"/>
-      <c r="D24" s="77" t="s">
+      <c r="D24" s="78" t="s">
+        <v>276</v>
+      </c>
+      <c r="E24" s="78" t="s">
         <v>277</v>
-      </c>
-      <c r="E24" s="77" t="s">
-        <v>278</v>
       </c>
       <c r="F24" s="40"/>
       <c r="G24" s="41"/>
@@ -8022,18 +8013,18 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="75">
+      <c r="A25" s="76">
         <v>18.0</v>
       </c>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C25" s="41"/>
-      <c r="D25" s="74" t="s">
+      <c r="D25" s="75" t="s">
+        <v>278</v>
+      </c>
+      <c r="E25" s="75" t="s">
         <v>279</v>
-      </c>
-      <c r="E25" s="74" t="s">
-        <v>280</v>
       </c>
       <c r="F25" s="40"/>
       <c r="G25" s="41"/>
@@ -8052,18 +8043,18 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="73">
+      <c r="A26" s="74">
         <v>19.0</v>
       </c>
-      <c r="B26" s="74" t="s">
+      <c r="B26" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C26" s="41"/>
       <c r="D26" s="78" t="s">
+        <v>280</v>
+      </c>
+      <c r="E26" s="78" t="s">
         <v>281</v>
-      </c>
-      <c r="E26" s="78" t="s">
-        <v>282</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41"/>
@@ -8082,18 +8073,18 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="75">
+      <c r="A27" s="76">
         <v>20.0</v>
       </c>
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="41"/>
-      <c r="D27" s="74" t="s">
+      <c r="D27" s="75" t="s">
+        <v>282</v>
+      </c>
+      <c r="E27" s="75" t="s">
         <v>283</v>
-      </c>
-      <c r="E27" s="74" t="s">
-        <v>284</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="41"/>
@@ -8112,18 +8103,18 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="73">
+      <c r="A28" s="74">
         <v>21.0</v>
       </c>
-      <c r="B28" s="74" t="s">
+      <c r="B28" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C28" s="41"/>
-      <c r="D28" s="74" t="s">
+      <c r="D28" s="75" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="75" t="s">
         <v>285</v>
-      </c>
-      <c r="E28" s="74" t="s">
-        <v>286</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="41"/>
@@ -8142,18 +8133,18 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="75">
+      <c r="A29" s="76">
         <v>22.0</v>
       </c>
-      <c r="B29" s="74" t="s">
+      <c r="B29" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C29" s="41"/>
-      <c r="D29" s="74" t="s">
+      <c r="D29" s="75" t="s">
+        <v>286</v>
+      </c>
+      <c r="E29" s="75" t="s">
         <v>287</v>
-      </c>
-      <c r="E29" s="74" t="s">
-        <v>288</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="41"/>
@@ -8172,18 +8163,18 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="73">
+      <c r="A30" s="74">
         <v>23.0</v>
       </c>
-      <c r="B30" s="74" t="s">
+      <c r="B30" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C30" s="41"/>
-      <c r="D30" s="74" t="s">
-        <v>273</v>
-      </c>
-      <c r="E30" s="74" t="s">
-        <v>289</v>
+      <c r="D30" s="75" t="s">
+        <v>272</v>
+      </c>
+      <c r="E30" s="75" t="s">
+        <v>288</v>
       </c>
       <c r="F30" s="40"/>
       <c r="G30" s="41"/>
@@ -8202,18 +8193,18 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="75">
+      <c r="A31" s="76">
         <v>24.0</v>
       </c>
-      <c r="B31" s="74" t="s">
+      <c r="B31" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="41"/>
-      <c r="D31" s="74" t="s">
+      <c r="D31" s="75" t="s">
+        <v>289</v>
+      </c>
+      <c r="E31" s="77" t="s">
         <v>290</v>
-      </c>
-      <c r="E31" s="76" t="s">
-        <v>291</v>
       </c>
       <c r="F31" s="40"/>
       <c r="G31" s="41"/>
@@ -8232,18 +8223,18 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="73">
+      <c r="A32" s="74">
         <v>25.0</v>
       </c>
-      <c r="B32" s="74" t="s">
+      <c r="B32" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C32" s="41"/>
-      <c r="D32" s="74" t="s">
+      <c r="D32" s="75" t="s">
+        <v>291</v>
+      </c>
+      <c r="E32" s="75" t="s">
         <v>292</v>
-      </c>
-      <c r="E32" s="74" t="s">
-        <v>293</v>
       </c>
       <c r="F32" s="40"/>
       <c r="G32" s="41"/>
@@ -8262,18 +8253,18 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="75">
+      <c r="A33" s="76">
         <v>26.0</v>
       </c>
-      <c r="B33" s="74" t="s">
+      <c r="B33" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="41"/>
-      <c r="D33" s="74" t="s">
-        <v>263</v>
-      </c>
-      <c r="E33" s="74" t="s">
-        <v>294</v>
+      <c r="D33" s="75" t="s">
+        <v>262</v>
+      </c>
+      <c r="E33" s="75" t="s">
+        <v>293</v>
       </c>
       <c r="F33" s="40"/>
       <c r="G33" s="41"/>
@@ -8355,7 +8346,7 @@
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="6"/>
@@ -8380,7 +8371,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
@@ -8394,7 +8385,7 @@
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
       <c r="E3" s="79" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -8408,7 +8399,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -8422,7 +8413,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -8492,26 +8483,26 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="73">
+      <c r="A8" s="74">
         <v>1.0</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="75" t="s">
+        <v>299</v>
+      </c>
+      <c r="E8" s="75" t="s">
         <v>300</v>
-      </c>
-      <c r="E8" s="74" t="s">
-        <v>301</v>
       </c>
       <c r="F8" s="40">
         <v>37.0</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -8528,26 +8519,26 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="75">
+      <c r="A9" s="76">
         <v>2.0</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>86</v>
       </c>
       <c r="D9" s="80" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" s="81" t="s">
         <v>302</v>
-      </c>
-      <c r="E9" s="81" t="s">
-        <v>303</v>
       </c>
       <c r="F9" s="40">
         <v>32.0</v>
       </c>
       <c r="G9" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -8564,26 +8555,26 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="73">
+      <c r="A10" s="74">
         <v>3.0</v>
       </c>
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C10" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="E10" s="75" t="s">
         <v>304</v>
-      </c>
-      <c r="E10" s="74" t="s">
-        <v>305</v>
       </c>
       <c r="F10" s="40">
         <v>25.0</v>
       </c>
       <c r="G10" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -8600,26 +8591,26 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="73">
+      <c r="A11" s="74">
         <v>4.0</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C11" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="75" t="s">
+        <v>305</v>
+      </c>
+      <c r="E11" s="75" t="s">
         <v>306</v>
-      </c>
-      <c r="E11" s="74" t="s">
-        <v>307</v>
       </c>
       <c r="F11" s="40">
         <v>29.0</v>
       </c>
       <c r="G11" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11" s="29"/>
@@ -8636,26 +8627,26 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="75">
+      <c r="A12" s="76">
         <v>5.0</v>
       </c>
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C12" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="74" t="s">
+      <c r="D12" s="75" t="s">
+        <v>307</v>
+      </c>
+      <c r="E12" s="75" t="s">
         <v>308</v>
-      </c>
-      <c r="E12" s="74" t="s">
-        <v>309</v>
       </c>
       <c r="F12" s="40">
         <v>27.0</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="32"/>
@@ -8672,24 +8663,24 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="75">
+      <c r="A13" s="76">
         <v>6.0</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C13" s="41" t="s">
         <v>86</v>
       </c>
       <c r="D13" s="82" t="s">
+        <v>310</v>
+      </c>
+      <c r="E13" s="75" t="s">
         <v>311</v>
-      </c>
-      <c r="E13" s="74" t="s">
-        <v>312</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
@@ -8706,26 +8697,26 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="73">
+      <c r="A14" s="74">
         <v>7.0</v>
       </c>
-      <c r="B14" s="74" t="s">
+      <c r="B14" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="41" t="s">
         <v>86</v>
       </c>
       <c r="D14" s="83" t="s">
+        <v>312</v>
+      </c>
+      <c r="E14" s="83" t="s">
         <v>313</v>
-      </c>
-      <c r="E14" s="83" t="s">
-        <v>314</v>
       </c>
       <c r="F14" s="40">
         <v>23.0</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
@@ -8742,26 +8733,26 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="75">
+      <c r="A15" s="76">
         <v>8.0</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="B15" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C15" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="74" t="s">
+      <c r="D15" s="75" t="s">
+        <v>314</v>
+      </c>
+      <c r="E15" s="75" t="s">
         <v>315</v>
-      </c>
-      <c r="E15" s="74" t="s">
-        <v>316</v>
       </c>
       <c r="F15" s="40">
         <v>28.0</v>
       </c>
       <c r="G15" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
@@ -8778,26 +8769,26 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="73">
+      <c r="A16" s="74">
         <v>9.0</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C16" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="74" t="s">
+      <c r="D16" s="75" t="s">
+        <v>316</v>
+      </c>
+      <c r="E16" s="75" t="s">
         <v>317</v>
-      </c>
-      <c r="E16" s="74" t="s">
-        <v>318</v>
       </c>
       <c r="F16" s="40">
         <v>40.0</v>
       </c>
       <c r="G16" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -8814,26 +8805,26 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="73">
+      <c r="A17" s="74">
         <v>10.0</v>
       </c>
-      <c r="B17" s="74" t="s">
+      <c r="B17" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C17" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="75" t="s">
+        <v>318</v>
+      </c>
+      <c r="E17" s="75" t="s">
         <v>319</v>
-      </c>
-      <c r="E17" s="74" t="s">
-        <v>320</v>
       </c>
       <c r="F17" s="40">
         <v>37.0</v>
       </c>
       <c r="G17" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H17" s="28"/>
       <c r="I17" s="29"/>
@@ -8850,26 +8841,26 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="75">
+      <c r="A18" s="76">
         <v>11.0</v>
       </c>
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="74" t="s">
+      <c r="D18" s="75" t="s">
+        <v>320</v>
+      </c>
+      <c r="E18" s="75" t="s">
         <v>321</v>
-      </c>
-      <c r="E18" s="74" t="s">
-        <v>322</v>
       </c>
       <c r="F18" s="40">
         <v>32.0</v>
       </c>
       <c r="G18" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H18" s="31"/>
       <c r="I18" s="32"/>
@@ -8886,26 +8877,26 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="75">
+      <c r="A19" s="76">
         <v>12.0</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="75" t="s">
         <v>121</v>
       </c>
       <c r="C19" s="41" t="s">
         <v>94</v>
       </c>
       <c r="D19" s="82" t="s">
+        <v>322</v>
+      </c>
+      <c r="E19" s="75" t="s">
         <v>323</v>
-      </c>
-      <c r="E19" s="74" t="s">
-        <v>324</v>
       </c>
       <c r="F19" s="40">
         <v>20.0</v>
       </c>
       <c r="G19" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
@@ -8922,24 +8913,24 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="73">
+      <c r="A20" s="74">
         <v>13.0</v>
       </c>
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C20" s="41" t="s">
         <v>76</v>
       </c>
       <c r="D20" s="83" t="s">
+        <v>324</v>
+      </c>
+      <c r="E20" s="83" t="s">
         <v>325</v>
-      </c>
-      <c r="E20" s="83" t="s">
-        <v>326</v>
       </c>
       <c r="F20" s="40"/>
       <c r="G20" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
@@ -8956,26 +8947,26 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="75">
+      <c r="A21" s="76">
         <v>14.0</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C21" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="74" t="s">
+      <c r="D21" s="75" t="s">
+        <v>326</v>
+      </c>
+      <c r="E21" s="75" t="s">
         <v>327</v>
-      </c>
-      <c r="E21" s="74" t="s">
-        <v>328</v>
       </c>
       <c r="F21" s="40">
         <v>33.0</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -8992,26 +8983,26 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="73">
+      <c r="A22" s="74">
         <v>15.0</v>
       </c>
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C22" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="74" t="s">
+      <c r="D22" s="78" t="s">
+        <v>328</v>
+      </c>
+      <c r="E22" s="78" t="s">
         <v>329</v>
-      </c>
-      <c r="E22" s="74" t="s">
-        <v>330</v>
       </c>
       <c r="F22" s="40">
         <v>33.0</v>
       </c>
       <c r="G22" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -9028,26 +9019,26 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="75">
+      <c r="A23" s="76">
         <v>16.0</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="84" t="s">
+      <c r="C23" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="85" t="s">
-        <v>331</v>
-      </c>
-      <c r="E23" s="85" t="s">
-        <v>332</v>
+      <c r="D23" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="E23" s="78" t="s">
+        <v>329</v>
       </c>
       <c r="F23" s="40">
         <v>41.0</v>
       </c>
       <c r="G23" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -9064,26 +9055,26 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="73">
+      <c r="A24" s="74">
         <v>17.0</v>
       </c>
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C24" s="41" t="s">
         <v>94</v>
       </c>
       <c r="D24" s="82" t="s">
-        <v>333</v>
-      </c>
-      <c r="E24" s="74" t="s">
-        <v>334</v>
+        <v>331</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>332</v>
       </c>
       <c r="F24" s="40">
         <v>20.0</v>
       </c>
       <c r="G24" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
@@ -9100,26 +9091,26 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="75">
+      <c r="A25" s="76">
         <v>18.0</v>
       </c>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C25" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="82" t="s">
-        <v>335</v>
-      </c>
-      <c r="E25" s="74" t="s">
-        <v>336</v>
+      <c r="D25" s="78" t="s">
+        <v>333</v>
+      </c>
+      <c r="E25" s="78" t="s">
+        <v>13</v>
       </c>
       <c r="F25" s="40">
         <v>34.0</v>
       </c>
       <c r="G25" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
@@ -9136,24 +9127,24 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="73">
+      <c r="A26" s="74">
         <v>19.0</v>
       </c>
-      <c r="B26" s="74" t="s">
+      <c r="B26" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C26" s="41" t="s">
         <v>94</v>
       </c>
       <c r="D26" s="82" t="s">
-        <v>337</v>
-      </c>
-      <c r="E26" s="74" t="s">
-        <v>338</v>
+        <v>334</v>
+      </c>
+      <c r="E26" s="75" t="s">
+        <v>335</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
@@ -9170,26 +9161,26 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="75">
+      <c r="A27" s="76">
         <v>20.0</v>
       </c>
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>86</v>
       </c>
       <c r="D27" s="82" t="s">
-        <v>339</v>
-      </c>
-      <c r="E27" s="74" t="s">
+        <v>336</v>
+      </c>
+      <c r="E27" s="75" t="s">
         <v>87</v>
       </c>
       <c r="F27" s="40">
         <v>27.0</v>
       </c>
       <c r="G27" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -9206,26 +9197,26 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="75">
+      <c r="A28" s="76">
         <v>21.0</v>
       </c>
-      <c r="B28" s="74" t="s">
+      <c r="B28" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="74" t="s">
-        <v>340</v>
-      </c>
-      <c r="E28" s="74" t="s">
-        <v>341</v>
+      <c r="D28" s="75" t="s">
+        <v>337</v>
+      </c>
+      <c r="E28" s="75" t="s">
+        <v>338</v>
       </c>
       <c r="F28" s="40">
         <v>32.0</v>
       </c>
       <c r="G28" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H28" s="31"/>
       <c r="I28" s="32"/>
@@ -9242,26 +9233,26 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="75">
+      <c r="A29" s="76">
         <v>22.0</v>
       </c>
-      <c r="B29" s="74" t="s">
+      <c r="B29" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C29" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="85" t="s">
-        <v>342</v>
-      </c>
-      <c r="E29" s="85" t="s">
-        <v>343</v>
+      <c r="D29" s="78" t="s">
+        <v>339</v>
+      </c>
+      <c r="E29" s="78" t="s">
+        <v>340</v>
       </c>
       <c r="F29" s="40">
         <v>28.0</v>
       </c>
       <c r="G29" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -9278,26 +9269,26 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="73">
+      <c r="A30" s="74">
         <v>23.0</v>
       </c>
-      <c r="B30" s="74" t="s">
+      <c r="B30" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="85" t="s">
-        <v>344</v>
-      </c>
-      <c r="E30" s="85" t="s">
-        <v>345</v>
+      <c r="D30" s="84" t="s">
+        <v>341</v>
+      </c>
+      <c r="E30" s="84" t="s">
+        <v>342</v>
       </c>
       <c r="F30" s="40">
         <v>41.0</v>
       </c>
       <c r="G30" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
@@ -9314,22 +9305,22 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="73">
+      <c r="A31" s="74">
         <v>24.0</v>
       </c>
-      <c r="B31" s="74" t="s">
+      <c r="B31" s="75" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>86</v>
       </c>
       <c r="D31" s="82"/>
-      <c r="E31" s="74"/>
+      <c r="E31" s="75"/>
       <c r="F31" s="40">
         <v>36.0</v>
       </c>
       <c r="G31" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
@@ -9346,20 +9337,20 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="73">
+      <c r="A32" s="74">
         <v>25.0</v>
       </c>
-      <c r="B32" s="74" t="s">
+      <c r="B32" s="75" t="s">
         <v>72</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="74" t="s">
-        <v>346</v>
-      </c>
-      <c r="E32" s="74" t="s">
-        <v>347</v>
+      <c r="D32" s="75" t="s">
+        <v>343</v>
+      </c>
+      <c r="E32" s="75" t="s">
+        <v>344</v>
       </c>
       <c r="F32" s="40">
         <v>19.0</v>
@@ -9380,20 +9371,20 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="75">
+      <c r="A33" s="76">
         <v>26.0</v>
       </c>
-      <c r="B33" s="74" t="s">
+      <c r="B33" s="75" t="s">
         <v>121</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="74" t="s">
-        <v>348</v>
-      </c>
-      <c r="E33" s="74" t="s">
-        <v>349</v>
+      <c r="D33" s="78" t="s">
+        <v>345</v>
+      </c>
+      <c r="E33" s="78" t="s">
+        <v>346</v>
       </c>
       <c r="F33" s="40">
         <v>19.0</v>
@@ -9478,12 +9469,12 @@
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="86" t="s">
+      <c r="F1" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="89" t="s">
+      <c r="G1" s="86"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="88" t="s">
         <v>42</v>
       </c>
       <c r="J1" s="10"/>
@@ -9505,7 +9496,7 @@
       <c r="D2" s="5"/>
       <c r="E2" s="6"/>
       <c r="F2" s="11" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="6"/>
@@ -9519,7 +9510,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="6"/>
       <c r="F3" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="6"/>
@@ -9533,27 +9524,27 @@
       <c r="D4" s="5"/>
       <c r="E4" s="6"/>
       <c r="F4" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="6"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="89" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="91" t="s">
-        <v>353</v>
-      </c>
-      <c r="G5" s="92"/>
-      <c r="H5" s="93"/>
+      <c r="F5" s="90" t="s">
+        <v>350</v>
+      </c>
+      <c r="G5" s="91"/>
+      <c r="H5" s="92"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="94"/>
+      <c r="A6" s="93"/>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -9564,13 +9555,13 @@
     </row>
     <row r="7" ht="21.0" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>52</v>
@@ -9619,26 +9610,26 @@
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1">
-      <c r="A8" s="95">
+      <c r="A8" s="94">
         <v>1.0</v>
       </c>
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="95" t="s">
+      <c r="C8" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="96" t="s">
+      <c r="D8" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="97" t="s">
-        <v>357</v>
-      </c>
-      <c r="F8" s="97" t="s">
-        <v>358</v>
+      <c r="E8" s="96" t="s">
+        <v>354</v>
+      </c>
+      <c r="F8" s="96" t="s">
+        <v>355</v>
       </c>
       <c r="G8" s="40"/>
-      <c r="H8" s="98" t="s">
+      <c r="H8" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I8" s="28"/>
@@ -9656,26 +9647,26 @@
       </c>
     </row>
     <row r="9" ht="21.0" customHeight="1">
-      <c r="A9" s="95">
+      <c r="A9" s="94">
         <v>2.0</v>
       </c>
-      <c r="B9" s="95" t="s">
+      <c r="B9" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="95" t="s">
+      <c r="C9" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="96" t="s">
+      <c r="D9" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="97" t="s">
-        <v>359</v>
-      </c>
-      <c r="F9" s="97" t="s">
-        <v>360</v>
+      <c r="E9" s="96" t="s">
+        <v>356</v>
+      </c>
+      <c r="F9" s="96" t="s">
+        <v>357</v>
       </c>
       <c r="G9" s="40"/>
-      <c r="H9" s="98" t="s">
+      <c r="H9" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I9" s="31"/>
@@ -9693,26 +9684,26 @@
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1">
-      <c r="A10" s="95">
+      <c r="A10" s="94">
         <v>3.0</v>
       </c>
-      <c r="B10" s="95" t="s">
+      <c r="B10" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="95" t="s">
+      <c r="C10" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="D10" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="99" t="s">
-        <v>361</v>
-      </c>
-      <c r="F10" s="99" t="s">
-        <v>362</v>
+      <c r="E10" s="98" t="s">
+        <v>358</v>
+      </c>
+      <c r="F10" s="98" t="s">
+        <v>359</v>
       </c>
       <c r="G10" s="40"/>
-      <c r="H10" s="98" t="s">
+      <c r="H10" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I10" s="31"/>
@@ -9730,26 +9721,26 @@
       </c>
     </row>
     <row r="11" ht="21.0" customHeight="1">
-      <c r="A11" s="95">
+      <c r="A11" s="94">
         <v>4.0</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="95" t="s">
+      <c r="C11" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="96" t="s">
+      <c r="D11" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="97" t="s">
-        <v>363</v>
-      </c>
-      <c r="F11" s="97" t="s">
-        <v>364</v>
+      <c r="E11" s="96" t="s">
+        <v>360</v>
+      </c>
+      <c r="F11" s="96" t="s">
+        <v>361</v>
       </c>
       <c r="G11" s="40"/>
-      <c r="H11" s="98" t="s">
+      <c r="H11" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I11" s="31"/>
@@ -9767,26 +9758,26 @@
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="95">
+      <c r="A12" s="94">
         <v>5.0</v>
       </c>
-      <c r="B12" s="95" t="s">
+      <c r="B12" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="95" t="s">
+      <c r="C12" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="96" t="s">
+      <c r="D12" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="97" t="s">
-        <v>365</v>
-      </c>
-      <c r="F12" s="97" t="s">
-        <v>358</v>
+      <c r="E12" s="96" t="s">
+        <v>362</v>
+      </c>
+      <c r="F12" s="96" t="s">
+        <v>355</v>
       </c>
       <c r="G12" s="40"/>
-      <c r="H12" s="98" t="s">
+      <c r="H12" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I12" s="28"/>
@@ -9804,26 +9795,26 @@
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1">
-      <c r="A13" s="95">
+      <c r="A13" s="94">
         <v>6.0</v>
       </c>
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="95" t="s">
+      <c r="C13" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="96" t="s">
+      <c r="D13" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="100" t="s">
-        <v>366</v>
-      </c>
-      <c r="F13" s="100" t="s">
-        <v>186</v>
+      <c r="E13" s="99" t="s">
+        <v>363</v>
+      </c>
+      <c r="F13" s="99" t="s">
+        <v>185</v>
       </c>
       <c r="G13" s="40"/>
-      <c r="H13" s="98" t="s">
+      <c r="H13" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I13" s="31"/>
@@ -9841,26 +9832,26 @@
       </c>
     </row>
     <row r="14" ht="24.75" customHeight="1">
-      <c r="A14" s="95">
+      <c r="A14" s="94">
         <v>7.0</v>
       </c>
-      <c r="B14" s="95" t="s">
+      <c r="B14" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="95" t="s">
+      <c r="C14" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="96" t="s">
+      <c r="D14" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="97" t="s">
-        <v>367</v>
-      </c>
-      <c r="F14" s="97" t="s">
-        <v>182</v>
+      <c r="E14" s="96" t="s">
+        <v>364</v>
+      </c>
+      <c r="F14" s="96" t="s">
+        <v>181</v>
       </c>
       <c r="G14" s="40"/>
-      <c r="H14" s="98" t="s">
+      <c r="H14" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I14" s="28"/>
@@ -9878,26 +9869,26 @@
       </c>
     </row>
     <row r="15" ht="21.0" customHeight="1">
-      <c r="A15" s="95">
+      <c r="A15" s="94">
         <v>8.0</v>
       </c>
-      <c r="B15" s="95" t="s">
+      <c r="B15" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="95" t="s">
+      <c r="C15" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="96" t="s">
+      <c r="D15" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="97" t="s">
-        <v>368</v>
-      </c>
-      <c r="F15" s="97" t="s">
-        <v>182</v>
+      <c r="E15" s="99" t="s">
+        <v>365</v>
+      </c>
+      <c r="F15" s="99" t="s">
+        <v>366</v>
       </c>
       <c r="G15" s="40"/>
-      <c r="H15" s="98" t="s">
+      <c r="H15" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I15" s="31"/>
@@ -9915,26 +9906,26 @@
       </c>
     </row>
     <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="95">
+      <c r="A16" s="94">
         <v>9.0</v>
       </c>
-      <c r="B16" s="95" t="s">
+      <c r="B16" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="95" t="s">
+      <c r="C16" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="96" t="s">
+      <c r="D16" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="97" t="s">
-        <v>369</v>
-      </c>
-      <c r="F16" s="97" t="s">
-        <v>370</v>
+      <c r="E16" s="96" t="s">
+        <v>367</v>
+      </c>
+      <c r="F16" s="96" t="s">
+        <v>368</v>
       </c>
       <c r="G16" s="40"/>
-      <c r="H16" s="98" t="s">
+      <c r="H16" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I16" s="28"/>
@@ -9952,26 +9943,26 @@
       </c>
     </row>
     <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="95">
+      <c r="A17" s="94">
         <v>10.0</v>
       </c>
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="95" t="s">
+      <c r="C17" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="96" t="s">
+      <c r="D17" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="97" t="s">
-        <v>371</v>
-      </c>
-      <c r="F17" s="97" t="s">
-        <v>372</v>
+      <c r="E17" s="96" t="s">
+        <v>369</v>
+      </c>
+      <c r="F17" s="96" t="s">
+        <v>370</v>
       </c>
       <c r="G17" s="40"/>
-      <c r="H17" s="98" t="s">
+      <c r="H17" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I17" s="31"/>
@@ -9989,26 +9980,26 @@
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="95">
+      <c r="A18" s="94">
         <v>11.0</v>
       </c>
-      <c r="B18" s="95" t="s">
+      <c r="B18" s="94" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="95" t="s">
+      <c r="C18" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="96" t="s">
+      <c r="D18" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="97" t="s">
-        <v>373</v>
-      </c>
-      <c r="F18" s="97" t="s">
-        <v>374</v>
+      <c r="E18" s="96" t="s">
+        <v>371</v>
+      </c>
+      <c r="F18" s="96" t="s">
+        <v>372</v>
       </c>
       <c r="G18" s="40"/>
-      <c r="H18" s="98" t="s">
+      <c r="H18" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I18" s="28"/>
@@ -10026,26 +10017,26 @@
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1">
-      <c r="A19" s="95">
+      <c r="A19" s="94">
         <v>12.0</v>
       </c>
-      <c r="B19" s="95" t="s">
+      <c r="B19" s="94" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="95" t="s">
+      <c r="C19" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="96" t="s">
+      <c r="D19" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="97" t="s">
-        <v>375</v>
-      </c>
-      <c r="F19" s="97" t="s">
-        <v>376</v>
+      <c r="E19" s="96" t="s">
+        <v>373</v>
+      </c>
+      <c r="F19" s="96" t="s">
+        <v>374</v>
       </c>
       <c r="G19" s="40"/>
-      <c r="H19" s="98" t="s">
+      <c r="H19" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I19" s="31"/>
@@ -10063,26 +10054,26 @@
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1">
-      <c r="A20" s="95">
+      <c r="A20" s="94">
         <v>13.0</v>
       </c>
-      <c r="B20" s="95" t="s">
+      <c r="B20" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="95" t="s">
+      <c r="C20" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="96" t="s">
+      <c r="D20" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="97" t="s">
-        <v>377</v>
-      </c>
-      <c r="F20" s="97" t="s">
-        <v>378</v>
+      <c r="E20" s="96" t="s">
+        <v>375</v>
+      </c>
+      <c r="F20" s="96" t="s">
+        <v>376</v>
       </c>
       <c r="G20" s="40"/>
-      <c r="H20" s="98" t="s">
+      <c r="H20" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I20" s="28"/>
@@ -10100,26 +10091,26 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="95">
+      <c r="A21" s="94">
         <v>14.0</v>
       </c>
-      <c r="B21" s="95" t="s">
+      <c r="B21" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="95" t="s">
+      <c r="C21" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="96" t="s">
+      <c r="D21" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="97" t="s">
-        <v>379</v>
-      </c>
-      <c r="F21" s="97" t="s">
+      <c r="E21" s="96" t="s">
+        <v>377</v>
+      </c>
+      <c r="F21" s="96" t="s">
         <v>147</v>
       </c>
       <c r="G21" s="40"/>
-      <c r="H21" s="98" t="s">
+      <c r="H21" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I21" s="31"/>
@@ -10137,26 +10128,26 @@
       </c>
     </row>
     <row r="22" ht="23.25" customHeight="1">
-      <c r="A22" s="95">
+      <c r="A22" s="94">
         <v>15.0</v>
       </c>
-      <c r="B22" s="95" t="s">
+      <c r="B22" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="95" t="s">
+      <c r="C22" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="96" t="s">
+      <c r="D22" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="97" t="s">
-        <v>380</v>
-      </c>
-      <c r="F22" s="97" t="s">
-        <v>381</v>
+      <c r="E22" s="96" t="s">
+        <v>378</v>
+      </c>
+      <c r="F22" s="96" t="s">
+        <v>379</v>
       </c>
       <c r="G22" s="40"/>
-      <c r="H22" s="98" t="s">
+      <c r="H22" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I22" s="28"/>
@@ -10174,26 +10165,26 @@
       </c>
     </row>
     <row r="23" ht="21.75" customHeight="1">
-      <c r="A23" s="95">
+      <c r="A23" s="94">
         <v>16.0</v>
       </c>
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="95" t="s">
+      <c r="C23" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="96" t="s">
+      <c r="D23" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="97" t="s">
-        <v>382</v>
-      </c>
-      <c r="F23" s="97" t="s">
-        <v>383</v>
+      <c r="E23" s="96" t="s">
+        <v>380</v>
+      </c>
+      <c r="F23" s="96" t="s">
+        <v>381</v>
       </c>
       <c r="G23" s="40"/>
-      <c r="H23" s="101" t="s">
+      <c r="H23" s="100" t="s">
         <v>71</v>
       </c>
       <c r="I23" s="31"/>
@@ -10211,26 +10202,26 @@
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1">
-      <c r="A24" s="95">
+      <c r="A24" s="94">
         <v>17.0</v>
       </c>
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="95" t="s">
+      <c r="C24" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="96" t="s">
+      <c r="D24" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="97" t="s">
-        <v>384</v>
-      </c>
-      <c r="F24" s="97" t="s">
-        <v>385</v>
+      <c r="E24" s="96" t="s">
+        <v>382</v>
+      </c>
+      <c r="F24" s="96" t="s">
+        <v>383</v>
       </c>
       <c r="G24" s="40"/>
-      <c r="H24" s="98" t="s">
+      <c r="H24" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I24" s="31"/>
@@ -10248,26 +10239,26 @@
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="95">
+      <c r="A25" s="94">
         <v>18.0</v>
       </c>
-      <c r="B25" s="95" t="s">
+      <c r="B25" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="95" t="s">
+      <c r="C25" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="96" t="s">
+      <c r="D25" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="97" t="s">
-        <v>386</v>
-      </c>
-      <c r="F25" s="97" t="s">
-        <v>387</v>
+      <c r="E25" s="96" t="s">
+        <v>384</v>
+      </c>
+      <c r="F25" s="96" t="s">
+        <v>385</v>
       </c>
       <c r="G25" s="40"/>
-      <c r="H25" s="98" t="s">
+      <c r="H25" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I25" s="28"/>
@@ -10285,26 +10276,26 @@
       </c>
     </row>
     <row r="26" ht="24.0" customHeight="1">
-      <c r="A26" s="95">
+      <c r="A26" s="94">
         <v>19.0</v>
       </c>
-      <c r="B26" s="95" t="s">
+      <c r="B26" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="95" t="s">
+      <c r="C26" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="96" t="s">
+      <c r="D26" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="97" t="s">
-        <v>388</v>
-      </c>
-      <c r="F26" s="97" t="s">
-        <v>389</v>
+      <c r="E26" s="96" t="s">
+        <v>386</v>
+      </c>
+      <c r="F26" s="96" t="s">
+        <v>387</v>
       </c>
       <c r="G26" s="40"/>
-      <c r="H26" s="98" t="s">
+      <c r="H26" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I26" s="28"/>
@@ -10322,26 +10313,26 @@
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1">
-      <c r="A27" s="95">
+      <c r="A27" s="94">
         <v>20.0</v>
       </c>
-      <c r="B27" s="95" t="s">
+      <c r="B27" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="95" t="s">
+      <c r="C27" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="96" t="s">
+      <c r="D27" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="97" t="s">
-        <v>390</v>
-      </c>
-      <c r="F27" s="97" t="s">
-        <v>364</v>
+      <c r="E27" s="96" t="s">
+        <v>388</v>
+      </c>
+      <c r="F27" s="96" t="s">
+        <v>361</v>
       </c>
       <c r="G27" s="40"/>
-      <c r="H27" s="98" t="s">
+      <c r="H27" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I27" s="28"/>
@@ -10359,26 +10350,26 @@
       </c>
     </row>
     <row r="28" ht="20.25" customHeight="1">
-      <c r="A28" s="95">
+      <c r="A28" s="94">
         <v>21.0</v>
       </c>
-      <c r="B28" s="95" t="s">
+      <c r="B28" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="95" t="s">
+      <c r="C28" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="96" t="s">
+      <c r="D28" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="97" t="s">
-        <v>391</v>
-      </c>
-      <c r="F28" s="97" t="s">
-        <v>392</v>
+      <c r="E28" s="96" t="s">
+        <v>389</v>
+      </c>
+      <c r="F28" s="96" t="s">
+        <v>390</v>
       </c>
       <c r="G28" s="40"/>
-      <c r="H28" s="98" t="s">
+      <c r="H28" s="97" t="s">
         <v>99</v>
       </c>
       <c r="I28" s="31"/>
@@ -10396,26 +10387,26 @@
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="95">
+      <c r="A29" s="94">
         <v>22.0</v>
       </c>
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="95" t="s">
+      <c r="C29" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="96" t="s">
+      <c r="D29" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="97" t="s">
-        <v>393</v>
-      </c>
-      <c r="F29" s="97" t="s">
-        <v>394</v>
+      <c r="E29" s="96" t="s">
+        <v>391</v>
+      </c>
+      <c r="F29" s="96" t="s">
+        <v>392</v>
       </c>
       <c r="G29" s="40"/>
-      <c r="H29" s="98" t="s">
+      <c r="H29" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I29" s="28"/>
@@ -10433,26 +10424,26 @@
       </c>
     </row>
     <row r="30" ht="20.25" customHeight="1">
-      <c r="A30" s="95">
+      <c r="A30" s="94">
         <v>23.0</v>
       </c>
-      <c r="B30" s="95" t="s">
+      <c r="B30" s="94" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="95" t="s">
+      <c r="C30" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="96" t="s">
+      <c r="D30" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="97" t="s">
-        <v>395</v>
-      </c>
-      <c r="F30" s="97" t="s">
-        <v>396</v>
+      <c r="E30" s="96" t="s">
+        <v>393</v>
+      </c>
+      <c r="F30" s="96" t="s">
+        <v>394</v>
       </c>
       <c r="G30" s="40"/>
-      <c r="H30" s="98" t="s">
+      <c r="H30" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I30" s="31"/>
@@ -10470,26 +10461,26 @@
       </c>
     </row>
     <row r="31" ht="21.0" customHeight="1">
-      <c r="A31" s="95">
+      <c r="A31" s="94">
         <v>24.0</v>
       </c>
-      <c r="B31" s="95" t="s">
+      <c r="B31" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="95" t="s">
+      <c r="C31" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="96" t="s">
+      <c r="D31" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="97" t="s">
-        <v>397</v>
-      </c>
-      <c r="F31" s="97" t="s">
-        <v>398</v>
+      <c r="E31" s="96" t="s">
+        <v>395</v>
+      </c>
+      <c r="F31" s="96" t="s">
+        <v>396</v>
       </c>
       <c r="G31" s="40"/>
-      <c r="H31" s="98" t="s">
+      <c r="H31" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I31" s="28"/>
@@ -10507,26 +10498,26 @@
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="95">
+      <c r="A32" s="94">
         <v>25.0</v>
       </c>
-      <c r="B32" s="95" t="s">
+      <c r="B32" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="95" t="s">
+      <c r="C32" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="96" t="s">
+      <c r="D32" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="97" t="s">
-        <v>399</v>
-      </c>
-      <c r="F32" s="97" t="s">
-        <v>400</v>
+      <c r="E32" s="96" t="s">
+        <v>397</v>
+      </c>
+      <c r="F32" s="96" t="s">
+        <v>398</v>
       </c>
       <c r="G32" s="40"/>
-      <c r="H32" s="98" t="s">
+      <c r="H32" s="97" t="s">
         <v>71</v>
       </c>
       <c r="I32" s="31"/>
@@ -10544,27 +10535,27 @@
       </c>
     </row>
     <row r="33" ht="21.0" customHeight="1">
-      <c r="A33" s="95">
+      <c r="A33" s="94">
         <v>26.0</v>
       </c>
-      <c r="B33" s="95" t="s">
+      <c r="B33" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="95" t="s">
+      <c r="C33" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="96" t="s">
+      <c r="D33" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="97" t="s">
+      <c r="E33" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="97" t="s">
-        <v>401</v>
+      <c r="F33" s="96" t="s">
+        <v>399</v>
       </c>
       <c r="G33" s="40"/>
-      <c r="H33" s="98" t="s">
-        <v>402</v>
+      <c r="H33" s="97" t="s">
+        <v>400</v>
       </c>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
@@ -10642,7 +10633,7 @@
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="6"/>
@@ -10667,7 +10658,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="11" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
@@ -10681,7 +10672,7 @@
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
       <c r="E3" s="11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -10695,7 +10686,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -10709,7 +10700,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="11" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -10779,20 +10770,20 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="47">
+      <c r="A8" s="48">
         <v>3.0</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="102" t="s">
+      <c r="C8" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="103" t="s">
-        <v>307</v>
-      </c>
-      <c r="E8" s="103" t="s">
-        <v>408</v>
+      <c r="D8" s="45" t="s">
+        <v>306</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>406</v>
       </c>
       <c r="F8" s="40"/>
       <c r="G8" s="41" t="s">
@@ -10823,14 +10814,14 @@
         <v>76</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F9" s="40"/>
       <c r="G9" s="41" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -10847,7 +10838,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="47">
+      <c r="A10" s="48">
         <v>1.0</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -10857,14 +10848,14 @@
         <v>68</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F10" s="40"/>
       <c r="G10" s="41" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -10891,14 +10882,14 @@
         <v>76</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="41" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
@@ -10925,14 +10916,14 @@
         <v>86</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="41" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -10959,14 +10950,14 @@
         <v>86</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="41" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
@@ -10993,10 +10984,10 @@
         <v>94</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="41" t="s">
@@ -11027,10 +11018,10 @@
         <v>86</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F15" s="40"/>
       <c r="G15" s="41" t="s">
@@ -11061,14 +11052,14 @@
         <v>94</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -11095,14 +11086,14 @@
         <v>94</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F17" s="40"/>
       <c r="G17" s="41" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
@@ -11129,25 +11120,25 @@
         <v>94</v>
       </c>
       <c r="D18" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="F18" s="102"/>
+      <c r="G18" s="103" t="s">
         <v>428</v>
       </c>
-      <c r="E18" s="23" t="s">
-        <v>429</v>
-      </c>
-      <c r="F18" s="104"/>
-      <c r="G18" s="105" t="s">
-        <v>430</v>
-      </c>
-      <c r="H18" s="65"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="106"/>
-      <c r="N18" s="106"/>
-      <c r="O18" s="106"/>
-      <c r="P18" s="106"/>
-      <c r="Q18" s="65">
+      <c r="H18" s="66"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="104"/>
+      <c r="N18" s="104"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="104"/>
+      <c r="Q18" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11163,25 +11154,25 @@
         <v>76</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="F19" s="104"/>
-      <c r="G19" s="105" t="s">
-        <v>403</v>
-      </c>
-      <c r="H19" s="65"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="65">
+        <v>430</v>
+      </c>
+      <c r="F19" s="102"/>
+      <c r="G19" s="103" t="s">
+        <v>401</v>
+      </c>
+      <c r="H19" s="66"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="67"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="67"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11197,25 +11188,25 @@
         <v>76</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="F20" s="104"/>
-      <c r="G20" s="105" t="s">
-        <v>403</v>
-      </c>
-      <c r="H20" s="65"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="106"/>
-      <c r="N20" s="106"/>
-      <c r="O20" s="106"/>
-      <c r="P20" s="106"/>
-      <c r="Q20" s="65">
+        <v>432</v>
+      </c>
+      <c r="F20" s="102"/>
+      <c r="G20" s="103" t="s">
+        <v>401</v>
+      </c>
+      <c r="H20" s="66"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="104"/>
+      <c r="O20" s="104"/>
+      <c r="P20" s="104"/>
+      <c r="Q20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11231,16 +11222,16 @@
         <v>76</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F21" s="40">
         <v>20.0</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -11267,14 +11258,14 @@
         <v>86</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -11301,23 +11292,23 @@
         <v>86</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>441</v>
-      </c>
-      <c r="F23" s="104"/>
-      <c r="G23" s="105"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="106"/>
-      <c r="N23" s="106"/>
-      <c r="O23" s="106"/>
-      <c r="P23" s="106"/>
-      <c r="Q23" s="65">
+        <v>439</v>
+      </c>
+      <c r="F23" s="102"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="104"/>
+      <c r="N23" s="104"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="104"/>
+      <c r="Q23" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11333,7 +11324,7 @@
         <v>86</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E24" s="23" t="s">
         <v>113</v>
@@ -11367,25 +11358,25 @@
         <v>86</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="F25" s="104"/>
-      <c r="G25" s="105" t="s">
+        <v>406</v>
+      </c>
+      <c r="F25" s="102"/>
+      <c r="G25" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="H25" s="65"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="106"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="106"/>
-      <c r="Q25" s="65">
+      <c r="H25" s="66"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="104"/>
+      <c r="N25" s="104"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="104"/>
+      <c r="Q25" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11401,10 +11392,10 @@
         <v>94</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41" t="s">
@@ -11435,14 +11426,14 @@
         <v>76</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="41" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -11469,10 +11460,10 @@
         <v>86</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="41"/>
@@ -11501,14 +11492,14 @@
         <v>94</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="41" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -11535,14 +11526,14 @@
         <v>76</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F30" s="40"/>
       <c r="G30" s="41" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
@@ -11569,57 +11560,57 @@
         <v>94</v>
       </c>
       <c r="D31" s="23" t="s">
+        <v>453</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="F31" s="102"/>
+      <c r="G31" s="103" t="s">
+        <v>401</v>
+      </c>
+      <c r="H31" s="66"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="104"/>
+      <c r="N31" s="104"/>
+      <c r="O31" s="104"/>
+      <c r="P31" s="104"/>
+      <c r="Q31" s="66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="105">
+        <v>25.0</v>
+      </c>
+      <c r="B32" s="106" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="107" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="106" t="s">
+        <v>454</v>
+      </c>
+      <c r="E32" s="106" t="s">
         <v>455</v>
       </c>
-      <c r="E31" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="F31" s="104"/>
-      <c r="G31" s="105" t="s">
-        <v>403</v>
-      </c>
-      <c r="H31" s="65"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="106"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="106"/>
-      <c r="M31" s="106"/>
-      <c r="N31" s="106"/>
-      <c r="O31" s="106"/>
-      <c r="P31" s="106"/>
-      <c r="Q31" s="65">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="107">
-        <v>25.0</v>
-      </c>
-      <c r="B32" s="108" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="109" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="108" t="s">
-        <v>456</v>
-      </c>
-      <c r="E32" s="108" t="s">
-        <v>457</v>
-      </c>
-      <c r="F32" s="104"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="106"/>
-      <c r="J32" s="106"/>
-      <c r="K32" s="106"/>
-      <c r="L32" s="106"/>
-      <c r="M32" s="106"/>
-      <c r="N32" s="106"/>
-      <c r="O32" s="106"/>
-      <c r="P32" s="106"/>
-      <c r="Q32" s="65">
+      <c r="F32" s="102"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="104"/>
+      <c r="N32" s="104"/>
+      <c r="O32" s="104"/>
+      <c r="P32" s="104"/>
+      <c r="Q32" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11635,14 +11626,14 @@
         <v>76</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F33" s="40"/>
       <c r="G33" s="41" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -11721,7 +11712,7 @@
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="110" t="s">
+      <c r="E1" s="108" t="s">
         <v>37</v>
       </c>
       <c r="F1" s="5"/>
@@ -11746,7 +11737,7 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="110"/>
+      <c r="E2" s="108"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="13"/>
@@ -11758,8 +11749,8 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="110" t="s">
-        <v>461</v>
+      <c r="E3" s="108" t="s">
+        <v>459</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -11772,8 +11763,8 @@
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
-      <c r="E4" s="111" t="s">
-        <v>462</v>
+      <c r="E4" s="109" t="s">
+        <v>460</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -11786,8 +11777,8 @@
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="110" t="s">
-        <v>463</v>
+      <c r="E5" s="108" t="s">
+        <v>461</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -11857,20 +11848,20 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="73">
+      <c r="A8" s="74">
         <v>1.0</v>
       </c>
-      <c r="B8" s="112" t="s">
+      <c r="B8" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="113" t="s">
+      <c r="C8" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="114" t="s">
-        <v>464</v>
-      </c>
-      <c r="E8" s="114" t="s">
-        <v>241</v>
+      <c r="D8" s="112" t="s">
+        <v>462</v>
+      </c>
+      <c r="E8" s="112" t="s">
+        <v>240</v>
       </c>
       <c r="F8" s="40"/>
       <c r="G8" s="41"/>
@@ -11889,20 +11880,20 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="75">
+      <c r="A9" s="76">
         <v>2.0</v>
       </c>
-      <c r="B9" s="112" t="s">
+      <c r="B9" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="113" t="s">
+      <c r="C9" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="114" t="s">
-        <v>465</v>
-      </c>
-      <c r="E9" s="114" t="s">
-        <v>466</v>
+      <c r="D9" s="112" t="s">
+        <v>463</v>
+      </c>
+      <c r="E9" s="112" t="s">
+        <v>464</v>
       </c>
       <c r="F9" s="40"/>
       <c r="G9" s="41"/>
@@ -11921,20 +11912,20 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="73">
+      <c r="A10" s="74">
         <v>3.0</v>
       </c>
-      <c r="B10" s="112" t="s">
+      <c r="B10" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="113" t="s">
+      <c r="C10" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="115" t="s">
-        <v>467</v>
-      </c>
-      <c r="E10" s="115" t="s">
-        <v>468</v>
+      <c r="D10" s="113" t="s">
+        <v>465</v>
+      </c>
+      <c r="E10" s="113" t="s">
+        <v>466</v>
       </c>
       <c r="F10" s="40"/>
       <c r="G10" s="41"/>
@@ -11953,20 +11944,20 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="75">
+      <c r="A11" s="76">
         <v>4.0</v>
       </c>
-      <c r="B11" s="112" t="s">
+      <c r="B11" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="113" t="s">
+      <c r="C11" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="115" t="s">
-        <v>469</v>
-      </c>
-      <c r="E11" s="115" t="s">
-        <v>470</v>
+      <c r="D11" s="113" t="s">
+        <v>467</v>
+      </c>
+      <c r="E11" s="113" t="s">
+        <v>468</v>
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="41"/>
@@ -11985,20 +11976,20 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="73">
+      <c r="A12" s="74">
         <v>5.0</v>
       </c>
-      <c r="B12" s="112" t="s">
+      <c r="B12" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="113" t="s">
+      <c r="C12" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="116" t="s">
-        <v>471</v>
-      </c>
-      <c r="E12" s="114" t="s">
-        <v>472</v>
+      <c r="D12" s="114" t="s">
+        <v>469</v>
+      </c>
+      <c r="E12" s="112" t="s">
+        <v>470</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="41"/>
@@ -12017,20 +12008,20 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="75">
+      <c r="A13" s="76">
         <v>6.0</v>
       </c>
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="116" t="s">
-        <v>473</v>
-      </c>
-      <c r="E13" s="116" t="s">
-        <v>474</v>
+      <c r="D13" s="114" t="s">
+        <v>471</v>
+      </c>
+      <c r="E13" s="114" t="s">
+        <v>472</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="41"/>
@@ -12049,20 +12040,20 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="73">
+      <c r="A14" s="74">
         <v>7.0</v>
       </c>
-      <c r="B14" s="112" t="s">
+      <c r="B14" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="116" t="s">
-        <v>475</v>
-      </c>
-      <c r="E14" s="116" t="s">
-        <v>476</v>
+      <c r="D14" s="114" t="s">
+        <v>473</v>
+      </c>
+      <c r="E14" s="114" t="s">
+        <v>474</v>
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="41"/>
@@ -12081,20 +12072,20 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="75">
+      <c r="A15" s="76">
         <v>8.0</v>
       </c>
-      <c r="B15" s="112" t="s">
+      <c r="B15" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="116" t="s">
-        <v>477</v>
-      </c>
-      <c r="E15" s="116" t="s">
-        <v>478</v>
+      <c r="D15" s="114" t="s">
+        <v>475</v>
+      </c>
+      <c r="E15" s="114" t="s">
+        <v>476</v>
       </c>
       <c r="F15" s="40"/>
       <c r="G15" s="41"/>
@@ -12113,20 +12104,20 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="73">
+      <c r="A16" s="74">
         <v>9.0</v>
       </c>
-      <c r="B16" s="112" t="s">
+      <c r="B16" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="116" t="s">
-        <v>479</v>
-      </c>
-      <c r="E16" s="116" t="s">
-        <v>480</v>
+      <c r="D16" s="114" t="s">
+        <v>477</v>
+      </c>
+      <c r="E16" s="114" t="s">
+        <v>478</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="41"/>
@@ -12145,20 +12136,20 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="75">
+      <c r="A17" s="76">
         <v>10.0</v>
       </c>
-      <c r="B17" s="112" t="s">
+      <c r="B17" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="115" t="s">
         <v>94</v>
       </c>
       <c r="D17" s="116" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E17" s="116" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F17" s="40"/>
       <c r="G17" s="41"/>
@@ -12177,20 +12168,20 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="73">
+      <c r="A18" s="74">
         <v>12.0</v>
       </c>
-      <c r="B18" s="112" t="s">
+      <c r="B18" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="116" t="s">
+      <c r="D18" s="114" t="s">
+        <v>481</v>
+      </c>
+      <c r="E18" s="114" t="s">
         <v>482</v>
-      </c>
-      <c r="E18" s="116" t="s">
-        <v>483</v>
       </c>
       <c r="F18" s="40"/>
       <c r="G18" s="41"/>
@@ -12209,20 +12200,20 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="75">
+      <c r="A19" s="76">
         <v>11.0</v>
       </c>
-      <c r="B19" s="112" t="s">
+      <c r="B19" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="116" t="s">
+      <c r="D19" s="114" t="s">
+        <v>483</v>
+      </c>
+      <c r="E19" s="114" t="s">
         <v>484</v>
-      </c>
-      <c r="E19" s="116" t="s">
-        <v>485</v>
       </c>
       <c r="F19" s="40"/>
       <c r="G19" s="41"/>
@@ -12241,20 +12232,20 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="73">
+      <c r="A20" s="74">
         <v>13.0</v>
       </c>
-      <c r="B20" s="112" t="s">
+      <c r="B20" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="117" t="s">
+      <c r="C20" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="116" t="s">
+      <c r="D20" s="114" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="116" t="s">
-        <v>486</v>
+      <c r="E20" s="114" t="s">
+        <v>485</v>
       </c>
       <c r="F20" s="40"/>
       <c r="G20" s="41"/>
@@ -12273,20 +12264,20 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="75">
+      <c r="A21" s="76">
         <v>14.0</v>
       </c>
-      <c r="B21" s="112" t="s">
+      <c r="B21" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="116" t="s">
-        <v>475</v>
-      </c>
-      <c r="E21" s="116" t="s">
-        <v>487</v>
+      <c r="D21" s="114" t="s">
+        <v>473</v>
+      </c>
+      <c r="E21" s="114" t="s">
+        <v>486</v>
       </c>
       <c r="F21" s="40"/>
       <c r="G21" s="41"/>
@@ -12305,20 +12296,20 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="73">
+      <c r="A22" s="74">
         <v>15.0</v>
       </c>
-      <c r="B22" s="112" t="s">
+      <c r="B22" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="113" t="s">
+      <c r="C22" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="118" t="s">
-        <v>488</v>
-      </c>
-      <c r="E22" s="118" t="s">
-        <v>376</v>
+      <c r="D22" s="116" t="s">
+        <v>487</v>
+      </c>
+      <c r="E22" s="116" t="s">
+        <v>374</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="41"/>
@@ -12337,20 +12328,20 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="75">
+      <c r="A23" s="76">
         <v>16.0</v>
       </c>
-      <c r="B23" s="112" t="s">
+      <c r="B23" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="113" t="s">
+      <c r="C23" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="118" t="s">
+      <c r="D23" s="116" t="s">
+        <v>488</v>
+      </c>
+      <c r="E23" s="116" t="s">
         <v>489</v>
-      </c>
-      <c r="E23" s="118" t="s">
-        <v>490</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="41"/>
@@ -12369,20 +12360,20 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="73">
+      <c r="A24" s="74">
         <v>17.0</v>
       </c>
-      <c r="B24" s="112" t="s">
+      <c r="B24" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="113" t="s">
+      <c r="C24" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="114" t="s">
+      <c r="D24" s="112" t="s">
+        <v>490</v>
+      </c>
+      <c r="E24" s="112" t="s">
         <v>491</v>
-      </c>
-      <c r="E24" s="114" t="s">
-        <v>492</v>
       </c>
       <c r="F24" s="40"/>
       <c r="G24" s="41"/>
@@ -12401,20 +12392,20 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="73">
+      <c r="A25" s="74">
         <v>18.0</v>
       </c>
-      <c r="B25" s="112" t="s">
+      <c r="B25" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="113" t="s">
+      <c r="C25" s="111" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="114" t="s">
+      <c r="D25" s="112" t="s">
+        <v>492</v>
+      </c>
+      <c r="E25" s="112" t="s">
         <v>493</v>
-      </c>
-      <c r="E25" s="114" t="s">
-        <v>494</v>
       </c>
       <c r="F25" s="40"/>
       <c r="G25" s="41"/>
@@ -12433,20 +12424,20 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="73">
+      <c r="A26" s="74">
         <v>19.0</v>
       </c>
-      <c r="B26" s="112" t="s">
+      <c r="B26" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="113" t="s">
+      <c r="C26" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="114" t="s">
-        <v>495</v>
-      </c>
-      <c r="E26" s="114" t="s">
-        <v>472</v>
+      <c r="D26" s="112" t="s">
+        <v>494</v>
+      </c>
+      <c r="E26" s="112" t="s">
+        <v>470</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="41"/>
@@ -12465,20 +12456,20 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="73">
+      <c r="A27" s="74">
         <v>20.0</v>
       </c>
-      <c r="B27" s="112" t="s">
+      <c r="B27" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="113" t="s">
+      <c r="C27" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="114" t="s">
-        <v>496</v>
-      </c>
-      <c r="E27" s="114" t="s">
-        <v>487</v>
+      <c r="D27" s="112" t="s">
+        <v>495</v>
+      </c>
+      <c r="E27" s="112" t="s">
+        <v>486</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="41"/>
@@ -12497,20 +12488,20 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="73">
+      <c r="A28" s="74">
         <v>21.0</v>
       </c>
-      <c r="B28" s="112" t="s">
+      <c r="B28" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="113" t="s">
+      <c r="C28" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="114" t="s">
+      <c r="D28" s="112" t="s">
+        <v>496</v>
+      </c>
+      <c r="E28" s="112" t="s">
         <v>497</v>
-      </c>
-      <c r="E28" s="114" t="s">
-        <v>498</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="41"/>
@@ -12529,20 +12520,20 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="73">
+      <c r="A29" s="74">
         <v>22.0</v>
       </c>
-      <c r="B29" s="112" t="s">
+      <c r="B29" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="113" t="s">
+      <c r="C29" s="111" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="114" t="s">
-        <v>499</v>
-      </c>
-      <c r="E29" s="114" t="s">
-        <v>182</v>
+      <c r="D29" s="112" t="s">
+        <v>498</v>
+      </c>
+      <c r="E29" s="112" t="s">
+        <v>181</v>
       </c>
       <c r="F29" s="40"/>
       <c r="G29" s="41"/>
@@ -12561,20 +12552,20 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="73">
+      <c r="A30" s="74">
         <v>23.0</v>
       </c>
-      <c r="B30" s="112" t="s">
+      <c r="B30" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="113" t="s">
+      <c r="C30" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="114" t="s">
+      <c r="D30" s="112" t="s">
+        <v>499</v>
+      </c>
+      <c r="E30" s="112" t="s">
         <v>500</v>
-      </c>
-      <c r="E30" s="114" t="s">
-        <v>501</v>
       </c>
       <c r="F30" s="40"/>
       <c r="G30" s="41"/>
@@ -12593,20 +12584,20 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="75">
+      <c r="A31" s="76">
         <v>24.0</v>
       </c>
-      <c r="B31" s="112" t="s">
+      <c r="B31" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="113" t="s">
+      <c r="C31" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="114" t="s">
-        <v>283</v>
-      </c>
-      <c r="E31" s="114" t="s">
-        <v>502</v>
+      <c r="D31" s="112" t="s">
+        <v>282</v>
+      </c>
+      <c r="E31" s="112" t="s">
+        <v>501</v>
       </c>
       <c r="F31" s="40"/>
       <c r="G31" s="41"/>
@@ -12625,20 +12616,20 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="73">
+      <c r="A32" s="74">
         <v>25.0</v>
       </c>
-      <c r="B32" s="112" t="s">
+      <c r="B32" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="113" t="s">
+      <c r="C32" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="114" t="s">
+      <c r="D32" s="112" t="s">
+        <v>502</v>
+      </c>
+      <c r="E32" s="112" t="s">
         <v>503</v>
-      </c>
-      <c r="E32" s="114" t="s">
-        <v>504</v>
       </c>
       <c r="F32" s="40"/>
       <c r="G32" s="41"/>
@@ -12657,20 +12648,20 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="75">
+      <c r="A33" s="76">
         <v>26.0</v>
       </c>
-      <c r="B33" s="112" t="s">
+      <c r="B33" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="113" t="s">
+      <c r="C33" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="118" t="s">
-        <v>182</v>
-      </c>
-      <c r="E33" s="118" t="s">
-        <v>505</v>
+      <c r="D33" s="116" t="s">
+        <v>181</v>
+      </c>
+      <c r="E33" s="116" t="s">
+        <v>504</v>
       </c>
       <c r="F33" s="40"/>
       <c r="G33" s="41"/>

--- a/public/data/@Liste GROUPE B.xlsx
+++ b/public/data/@Liste GROUPE B.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="564">
   <si>
     <t xml:space="preserve">Équipe </t>
   </si>
@@ -347,10 +347,10 @@
     <t>M</t>
   </si>
   <si>
-    <t>GLODI</t>
-  </si>
-  <si>
-    <t>EBAMBA LOMPIEKA</t>
+    <t>KENZO</t>
+  </si>
+  <si>
+    <t>GANAMÉ</t>
   </si>
   <si>
     <t>congo</t>
@@ -374,1209 +374,1221 @@
     <t>MULEDI</t>
   </si>
   <si>
-    <t>VIGOR</t>
+    <t>FELIX</t>
+  </si>
+  <si>
+    <t>BADALI</t>
+  </si>
+  <si>
+    <t>SAM FAROUQ</t>
+  </si>
+  <si>
+    <t>IMAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Côte d'Ivoire </t>
+  </si>
+  <si>
+    <t>BRICE WATUE</t>
+  </si>
+  <si>
+    <t>TOGUEM</t>
+  </si>
+  <si>
+    <t>ABDULRAZAQ</t>
+  </si>
+  <si>
+    <t>SODEEQ OBALOWU</t>
+  </si>
+  <si>
+    <t>Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>2XL</t>
+  </si>
+  <si>
+    <t>YOHAN</t>
+  </si>
+  <si>
+    <t>TREMBLAY</t>
+  </si>
+  <si>
+    <t>LÉO EMILIEN</t>
+  </si>
+  <si>
+    <t>NKOA</t>
+  </si>
+  <si>
+    <t>ESPOIR</t>
+  </si>
+  <si>
+    <t>ASDJIM</t>
+  </si>
+  <si>
+    <t>AFONSO ALMEIDA</t>
+  </si>
+  <si>
+    <t>NGOMBO</t>
+  </si>
+  <si>
+    <t>DIEUDONNE DAN</t>
+  </si>
+  <si>
+    <t>MUTOBA MALU</t>
+  </si>
+  <si>
+    <t>JONATHAN LENGOLO</t>
+  </si>
+  <si>
+    <t>KANZA</t>
+  </si>
+  <si>
+    <t>ALEXANDRE</t>
+  </si>
+  <si>
+    <t>MIGUELA</t>
+  </si>
+  <si>
+    <t>NOM DE L'ÉQUIPE : SÉNÉGAL</t>
+  </si>
+  <si>
+    <t>ADRESSE  COURRIEL : doudousarrdieng25@gmail.com</t>
+  </si>
+  <si>
+    <t>TÉL D'URGENCE : 5819220240</t>
+  </si>
+  <si>
+    <t>NOM DU COACH : Babacar Niang</t>
+  </si>
+  <si>
+    <t>NOM DU CAPITAINE : Doudou Dieng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shirt 👕 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOUSTAPHA </t>
+  </si>
+  <si>
+    <t>DIOP</t>
+  </si>
+  <si>
+    <t>MAMADOU SARR</t>
+  </si>
+  <si>
+    <t>DIENG</t>
+  </si>
+  <si>
+    <t>MAMADOU MATHIAS BASSAMA</t>
+  </si>
+  <si>
+    <t>DIOUF</t>
+  </si>
+  <si>
+    <t>ALAIN GUY OMAR</t>
+  </si>
+  <si>
+    <t>DIAGNE</t>
+  </si>
+  <si>
+    <t>MOUHAMADOU MOUSTAPHA</t>
+  </si>
+  <si>
+    <t>HANE</t>
+  </si>
+  <si>
+    <t>NDIAGA</t>
+  </si>
+  <si>
+    <t>SARR</t>
+  </si>
+  <si>
+    <t>BABACAR</t>
+  </si>
+  <si>
+    <t>GUEYE</t>
+  </si>
+  <si>
+    <t>FALLOU</t>
+  </si>
+  <si>
+    <t>THIAM</t>
+  </si>
+  <si>
+    <t>KHALIFA</t>
+  </si>
+  <si>
+    <t>NIANG</t>
+  </si>
+  <si>
+    <t>MAMADOU ALPHA</t>
+  </si>
+  <si>
+    <t>BARRY</t>
+  </si>
+  <si>
+    <t>IDRISSA</t>
+  </si>
+  <si>
+    <t>JOHNSON</t>
+  </si>
+  <si>
+    <t>SÉBASTIEN LIONEL</t>
+  </si>
+  <si>
+    <t>MASSEYE</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>GBOHOU</t>
+  </si>
+  <si>
+    <t>PAPE IBRAHIMA</t>
+  </si>
+  <si>
+    <t>MANGANE</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>SÉNE</t>
+  </si>
+  <si>
+    <t>SERIGNE</t>
+  </si>
+  <si>
+    <t>FALL</t>
+  </si>
+  <si>
+    <t>BABA MAMADOU</t>
+  </si>
+  <si>
+    <t>CAMARA</t>
+  </si>
+  <si>
+    <t>PAPA BABACAR</t>
+  </si>
+  <si>
+    <t>OMAR KHASSIMOU</t>
+  </si>
+  <si>
+    <t>DIA</t>
+  </si>
+  <si>
+    <t>MOUSTAPHA</t>
+  </si>
+  <si>
+    <t>PAPA GARBA</t>
+  </si>
+  <si>
+    <t>COULIBALY</t>
+  </si>
+  <si>
+    <t>PAPA OUSMANE MALICK RACHID</t>
+  </si>
+  <si>
+    <t>SOULEYMANE</t>
+  </si>
+  <si>
+    <t>DIALLO</t>
+  </si>
+  <si>
+    <t>Togo</t>
+  </si>
+  <si>
+    <t>Alatevi.k@gmail.com</t>
+  </si>
+  <si>
+    <t>438-827-6129</t>
+  </si>
+  <si>
+    <t>Fabrice</t>
+  </si>
+  <si>
+    <t>Komi Alatevi</t>
+  </si>
+  <si>
+    <t>CARL ISAAC PENCHEV</t>
+  </si>
+  <si>
+    <t>RENEVIL</t>
+  </si>
+  <si>
+    <t>Haïti</t>
+  </si>
+  <si>
+    <t>KOMI</t>
+  </si>
+  <si>
+    <t>ALATEVI</t>
+  </si>
+  <si>
+    <t>AMIDOU</t>
+  </si>
+  <si>
+    <t>AKOH</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>GOUNEHON</t>
+  </si>
+  <si>
+    <t>KOSSI SAMSON</t>
+  </si>
+  <si>
+    <t>KLOUSSE</t>
+  </si>
+  <si>
+    <t>BOTCHA</t>
+  </si>
+  <si>
+    <t>HENOC</t>
+  </si>
+  <si>
+    <t>OTNIEL</t>
+  </si>
+  <si>
+    <t>AKOEGNON</t>
+  </si>
+  <si>
+    <t>KOFFI MOÏSE</t>
+  </si>
+  <si>
+    <t>AMEVO</t>
+  </si>
+  <si>
+    <t>TAI MONDAKAN</t>
+  </si>
+  <si>
+    <t>HENRI-JOEL</t>
+  </si>
+  <si>
+    <t>BASSITOU</t>
+  </si>
+  <si>
+    <t>ASSANI</t>
+  </si>
+  <si>
+    <t>FOUMI MAJID</t>
+  </si>
+  <si>
+    <t>OLA</t>
+  </si>
+  <si>
+    <t>FRANCIS</t>
+  </si>
+  <si>
+    <t>AGBOGBO</t>
+  </si>
+  <si>
+    <t>Tia Cixte</t>
+  </si>
+  <si>
+    <t>Marti Dji</t>
+  </si>
+  <si>
+    <t>Essofa Oubote</t>
+  </si>
+  <si>
+    <t>ABODJI</t>
+  </si>
+  <si>
+    <t>Allassane</t>
+  </si>
+  <si>
+    <t>Kone</t>
+  </si>
+  <si>
+    <t>Mouh amed</t>
+  </si>
+  <si>
+    <t>Dosso</t>
+  </si>
+  <si>
+    <t>FIACRE</t>
+  </si>
+  <si>
+    <t>KOFFI</t>
+  </si>
+  <si>
+    <t>NOMEL</t>
+  </si>
+  <si>
+    <t>HERMAN</t>
+  </si>
+  <si>
+    <t>GBANGBISSE</t>
+  </si>
+  <si>
+    <t>CHRIST</t>
+  </si>
+  <si>
+    <t>guinée</t>
+  </si>
+  <si>
+    <t>PASCAL KOSSI</t>
+  </si>
+  <si>
+    <t>VIKPE</t>
+  </si>
+  <si>
+    <t>ALOGNISSO</t>
+  </si>
+  <si>
+    <t>RONALD</t>
+  </si>
+  <si>
+    <t>PETERSON</t>
+  </si>
+  <si>
+    <t>AUGUSTE</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>LOCHINA</t>
+  </si>
+  <si>
+    <t>DJAFAROU</t>
+  </si>
+  <si>
+    <t>DEGBE KOKOUVI</t>
+  </si>
+  <si>
+    <t>SAMUEL</t>
+  </si>
+  <si>
+    <t>KOMLAN AMEN</t>
+  </si>
+  <si>
+    <t>AKAMA</t>
+  </si>
+  <si>
+    <t>ESSODONA</t>
+  </si>
+  <si>
+    <t>HALAOUI</t>
+  </si>
+  <si>
+    <t>ADONIS</t>
+  </si>
+  <si>
+    <t>KALENGA</t>
+  </si>
+  <si>
+    <t>MKOLE</t>
+  </si>
+  <si>
+    <t>RAMADHANI</t>
+  </si>
+  <si>
+    <t>DESIRE</t>
+  </si>
+  <si>
+    <t>BICUKA</t>
+  </si>
+  <si>
+    <t>ABEDI</t>
+  </si>
+  <si>
+    <t>SAIDI</t>
+  </si>
+  <si>
+    <t>ATAMBA</t>
+  </si>
+  <si>
+    <t>SHAURI</t>
+  </si>
+  <si>
+    <t>JONAS</t>
+  </si>
+  <si>
+    <t>KISUBI</t>
+  </si>
+  <si>
+    <t>PATIENT</t>
+  </si>
+  <si>
+    <t>ECA MBOKO</t>
+  </si>
+  <si>
+    <t>SALEH</t>
+  </si>
+  <si>
+    <t>ECA</t>
+  </si>
+  <si>
+    <t>UWEZO</t>
+  </si>
+  <si>
+    <t>JUMAPILI</t>
+  </si>
+  <si>
+    <t>NDIKUMANA</t>
+  </si>
+  <si>
+    <t>JANVIER</t>
+  </si>
+  <si>
+    <t>REUBEN</t>
+  </si>
+  <si>
+    <t>MLONGEKA</t>
+  </si>
+  <si>
+    <t>AMURI</t>
+  </si>
+  <si>
+    <t>NDUME</t>
+  </si>
+  <si>
+    <t>OMARI</t>
+  </si>
+  <si>
+    <t>KASHINDI</t>
+  </si>
+  <si>
+    <t>WILONDJA</t>
+  </si>
+  <si>
+    <t>LWAMAGENA</t>
+  </si>
+  <si>
+    <t>GILEO</t>
+  </si>
+  <si>
+    <t>MTABI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGAZINI </t>
+  </si>
+  <si>
+    <t>LWABOSHI MAJEGEZA</t>
+  </si>
+  <si>
+    <t>ERICK</t>
+  </si>
+  <si>
+    <t>NISHIMWE</t>
+  </si>
+  <si>
+    <t>ASENDE</t>
+  </si>
+  <si>
+    <t>ABANGWA</t>
+  </si>
+  <si>
+    <t>OLIVIER</t>
+  </si>
+  <si>
+    <t>RIPHIN</t>
+  </si>
+  <si>
+    <t>HONNEUR</t>
+  </si>
+  <si>
+    <t>JEAN MARIE</t>
+  </si>
+  <si>
+    <t>ELIAZERI</t>
+  </si>
+  <si>
+    <t>NIYOGUSENGA</t>
+  </si>
+  <si>
+    <t>BYAOMBE</t>
+  </si>
+  <si>
+    <t>BAHOME</t>
+  </si>
+  <si>
+    <t>YAMUNGU MLENBA</t>
+  </si>
+  <si>
+    <t>ZAKARIA</t>
+  </si>
+  <si>
+    <t>RÉMY</t>
+  </si>
+  <si>
+    <t>MILAMBO</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>soccerangranmoun@gmail.com; flounes37@gmail.com</t>
+  </si>
+  <si>
+    <t>4189563785 / 4388384936</t>
+  </si>
+  <si>
+    <t>Lounès Félicin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hans Raldy Saint-Preux </t>
+  </si>
+  <si>
+    <t>MAQUINGSON</t>
+  </si>
+  <si>
+    <t>MAIGNAN</t>
+  </si>
+  <si>
+    <t>AMILICA</t>
+  </si>
+  <si>
+    <t>BOUKARI BOURDJA</t>
+  </si>
+  <si>
+    <t>MICHAEL PERSHINGSON</t>
+  </si>
+  <si>
+    <t>PIERRE</t>
+  </si>
+  <si>
+    <t>JEFFERSON</t>
+  </si>
+  <si>
+    <t>ANTOINE</t>
+  </si>
+  <si>
+    <t>GREGORY</t>
+  </si>
+  <si>
+    <t>ANNAY</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>HANS RALDY</t>
+  </si>
+  <si>
+    <t>SAINT-PREUX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXEL </t>
+  </si>
+  <si>
+    <t>ALIMASI</t>
+  </si>
+  <si>
+    <t>JEAN WILSON</t>
+  </si>
+  <si>
+    <t>CASIMIR</t>
+  </si>
+  <si>
+    <t>MARC-DONALD</t>
+  </si>
+  <si>
+    <t>SIMEUS</t>
+  </si>
+  <si>
+    <t>EVEDERSON</t>
+  </si>
+  <si>
+    <t>PREVILON</t>
+  </si>
+  <si>
+    <t>WOODSON</t>
+  </si>
+  <si>
+    <t>SAINT-LOUIS</t>
+  </si>
+  <si>
+    <t>ROMAIN</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>RYSDAEL C.</t>
+  </si>
+  <si>
+    <t>DUVELSAINT</t>
+  </si>
+  <si>
+    <t>TEVINSON</t>
+  </si>
+  <si>
+    <t>GARCON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISMAEL </t>
+  </si>
+  <si>
+    <t>GABRIEL</t>
+  </si>
+  <si>
+    <t>SCHADRAC</t>
+  </si>
+  <si>
+    <t>DIONALD</t>
+  </si>
+  <si>
+    <t>DESILUS</t>
+  </si>
+  <si>
+    <t>ELICLES</t>
+  </si>
+  <si>
+    <t>OMRA VALDJY WOODLEY</t>
+  </si>
+  <si>
+    <t>BARTHELUS</t>
+  </si>
+  <si>
+    <t>OLSEN</t>
+  </si>
+  <si>
+    <t>BERNARD</t>
+  </si>
+  <si>
+    <t>MAXI</t>
+  </si>
+  <si>
+    <t>CLIFORD</t>
+  </si>
+  <si>
+    <t>CHARLES</t>
+  </si>
+  <si>
+    <t>MARKENLOVE</t>
+  </si>
+  <si>
+    <t>RUTH TEIKEU</t>
+  </si>
+  <si>
+    <t>BLONDELE</t>
+  </si>
+  <si>
+    <t>FRANCIS TEGUIAKOU</t>
+  </si>
+  <si>
+    <t>MEZATIO</t>
+  </si>
+  <si>
+    <t>CEBATIEN</t>
+  </si>
+  <si>
+    <t>PIERRE-LOUIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JERRY BENNEDICT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOEL </t>
+  </si>
+  <si>
+    <t>oudoucis@yahoo.com</t>
+  </si>
+  <si>
+    <t>418 953 6873</t>
+  </si>
+  <si>
+    <t>ABDRAHAMANE TRAORE</t>
+  </si>
+  <si>
+    <t>Mohamed Coulibaly</t>
+  </si>
+  <si>
+    <t>NUMBER</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>SHORT</t>
+  </si>
+  <si>
+    <t>JACOB</t>
+  </si>
+  <si>
+    <t>DEMBÉLÉ</t>
+  </si>
+  <si>
+    <t>HAMED</t>
+  </si>
+  <si>
+    <t>OUSMANE</t>
+  </si>
+  <si>
+    <t>ABDOULAYE</t>
+  </si>
+  <si>
+    <t>DAO</t>
+  </si>
+  <si>
+    <t>NAMAKÉ FALAYE</t>
+  </si>
+  <si>
+    <t>SISSOKO</t>
+  </si>
+  <si>
+    <t>MOUSSA</t>
+  </si>
+  <si>
+    <t>HASSANE</t>
+  </si>
+  <si>
+    <t>KONÉ</t>
+  </si>
+  <si>
+    <t>MOHAMED</t>
+  </si>
+  <si>
+    <t>ALESSANDRO DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>SALIM</t>
+  </si>
+  <si>
+    <t>NIMAGA</t>
+  </si>
+  <si>
+    <t>SIDY MAHAMANE</t>
+  </si>
+  <si>
+    <t>TOURÉ</t>
+  </si>
+  <si>
+    <t>MAHAMOUDOU</t>
+  </si>
+  <si>
+    <t>IDRISSA DADYS</t>
+  </si>
+  <si>
+    <t>SIDIBÉ</t>
+  </si>
+  <si>
+    <t>ABOUBAKRINE</t>
+  </si>
+  <si>
+    <t>INTALLA</t>
+  </si>
+  <si>
+    <t>SEKOU SOULEYMANE</t>
+  </si>
+  <si>
+    <t>DOUMBIA</t>
+  </si>
+  <si>
+    <t>MAMADOU BAZAN</t>
+  </si>
+  <si>
+    <t>TOGOLA</t>
+  </si>
+  <si>
+    <t>DJIMÉ</t>
+  </si>
+  <si>
+    <t>KÉBÉ</t>
+  </si>
+  <si>
+    <t>MOULAYE MOHAMED</t>
+  </si>
+  <si>
+    <t>DICKO</t>
+  </si>
+  <si>
+    <t>HAROUNA</t>
+  </si>
+  <si>
+    <t>BACHIR</t>
+  </si>
+  <si>
+    <t>ZACHARIA</t>
+  </si>
+  <si>
+    <t>DJIRÉ</t>
+  </si>
+  <si>
+    <t>GUESSOUMA</t>
+  </si>
+  <si>
+    <t>PATRICK STÉPHANE</t>
+  </si>
+  <si>
+    <t>KAMDEM WAKAM</t>
+  </si>
+  <si>
+    <t>MALIK</t>
+  </si>
+  <si>
+    <t>DIARRA</t>
+  </si>
+  <si>
+    <t>IBRAHIM</t>
+  </si>
+  <si>
+    <t>ISSAKA</t>
+  </si>
+  <si>
+    <t>OUMAR</t>
+  </si>
+  <si>
+    <t>CISSÉ</t>
+  </si>
+  <si>
+    <t>ALMAMY</t>
+  </si>
+  <si>
+    <t>GUINDO</t>
+  </si>
+  <si>
+    <t>KOULBÉ</t>
+  </si>
+  <si>
+    <t>Tchad</t>
+  </si>
+  <si>
+    <t>Gabon</t>
+  </si>
+  <si>
+    <t>georgesarmel1@hotmail.fr</t>
+  </si>
+  <si>
+    <t>(581)849-3674</t>
+  </si>
+  <si>
+    <t>Georges armel Nguimbi</t>
+  </si>
+  <si>
+    <t>Cedrick essockamba</t>
+  </si>
+  <si>
+    <t>DROLET</t>
+  </si>
+  <si>
+    <t>DIEUDONNÉ</t>
+  </si>
+  <si>
+    <t>CIZA</t>
+  </si>
+  <si>
+    <t>Rwanda</t>
+  </si>
+  <si>
+    <t>STEPHANE</t>
+  </si>
+  <si>
+    <t>PREDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada </t>
+  </si>
+  <si>
+    <t>CEDRIC</t>
+  </si>
+  <si>
+    <t>ESSOCKAMBA</t>
+  </si>
+  <si>
+    <t>JEAN-THERRY</t>
+  </si>
+  <si>
+    <t>YAMA</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>BAMBA</t>
+  </si>
+  <si>
+    <t>FARAJA</t>
+  </si>
+  <si>
+    <t>DIEU BENIT</t>
+  </si>
+  <si>
+    <t>SOUMAI</t>
+  </si>
+  <si>
+    <t>FEDSON</t>
+  </si>
+  <si>
+    <t>ROSIER</t>
+  </si>
+  <si>
+    <t>EDOUARD</t>
+  </si>
+  <si>
+    <t>GAGNON</t>
+  </si>
+  <si>
+    <t>ESTEBAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cote d'ivoire </t>
+  </si>
+  <si>
+    <t>JEAN DANIEL</t>
+  </si>
+  <si>
+    <t>POTTEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE </t>
+  </si>
+  <si>
+    <t>KOKORA</t>
+  </si>
+  <si>
+    <t>ABDELAZIZ</t>
+  </si>
+  <si>
+    <t>KAPATA</t>
+  </si>
+  <si>
+    <t>Centre-afrique</t>
+  </si>
+  <si>
+    <t>VINCENT</t>
+  </si>
+  <si>
+    <t>CORNEAU</t>
+  </si>
+  <si>
+    <t>DEMOYER</t>
+  </si>
+  <si>
+    <t>KOUASSI</t>
+  </si>
+  <si>
+    <t>BENONI</t>
   </si>
   <si>
     <t>LUKUSA</t>
   </si>
   <si>
-    <t>EDIMO</t>
-  </si>
-  <si>
-    <t>HUGUES NGOUBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Côte d'Ivoire </t>
-  </si>
-  <si>
-    <t>KULABUNA MAKOLA</t>
-  </si>
-  <si>
-    <t>ABDULRAZAQ</t>
-  </si>
-  <si>
-    <t>SODEEQ OBALOWU</t>
-  </si>
-  <si>
-    <t>Côte d'Ivoire</t>
-  </si>
-  <si>
-    <t>2XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULLER </t>
-  </si>
-  <si>
-    <t>TITINGUERA</t>
-  </si>
-  <si>
-    <t>MIKE OSCAR</t>
-  </si>
-  <si>
-    <t>ILOUD</t>
-  </si>
-  <si>
-    <t>ESPOIR</t>
-  </si>
-  <si>
-    <t>ASDJIM</t>
-  </si>
-  <si>
-    <t>AFONSO ALMEIDA</t>
-  </si>
-  <si>
-    <t>NGOMBO</t>
-  </si>
-  <si>
-    <t>DIEUDONNE DAN</t>
-  </si>
-  <si>
-    <t>MUTOBA MALU</t>
-  </si>
-  <si>
-    <t>JONATHAN LENGOLO</t>
-  </si>
-  <si>
-    <t>KANZA</t>
-  </si>
-  <si>
-    <t>ALEXANDRE</t>
-  </si>
-  <si>
-    <t>MIGUELA</t>
-  </si>
-  <si>
-    <t>NOM DE L'ÉQUIPE : SÉNÉGAL</t>
-  </si>
-  <si>
-    <t>ADRESSE  COURRIEL : doudousarrdieng25@gmail.com</t>
-  </si>
-  <si>
-    <t>TÉL D'URGENCE : 5819220240</t>
-  </si>
-  <si>
-    <t>NOM DU COACH : Babacar Niang</t>
-  </si>
-  <si>
-    <t>NOM DU CAPITAINE : Doudou Dieng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shirt 👕 </t>
+    <t xml:space="preserve">ÉMILE </t>
+  </si>
+  <si>
+    <t>FRANCK NELSON</t>
+  </si>
+  <si>
+    <t>VOUFO</t>
+  </si>
+  <si>
+    <t>TONY</t>
+  </si>
+  <si>
+    <t>PENAMBO</t>
+  </si>
+  <si>
+    <t>DYLAN</t>
+  </si>
+  <si>
+    <t>POTE</t>
+  </si>
+  <si>
+    <t>ARGI</t>
+  </si>
+  <si>
+    <t>PASCAL</t>
+  </si>
+  <si>
+    <t>BIENVENUE</t>
+  </si>
+  <si>
+    <t>STANY</t>
+  </si>
+  <si>
+    <t>Burundi</t>
+  </si>
+  <si>
+    <t>CANELO</t>
+  </si>
+  <si>
+    <t>ÉRISA</t>
+  </si>
+  <si>
+    <t>NSHIMIYIMANA</t>
+  </si>
+  <si>
+    <t>JUNIOR</t>
+  </si>
+  <si>
+    <t>POKOU</t>
+  </si>
+  <si>
+    <t>Cote d'ivoire</t>
+  </si>
+  <si>
+    <t>418-554-0364</t>
+  </si>
+  <si>
+    <t>ABDOUL-AZIZ</t>
+  </si>
+  <si>
+    <t>Hamidou Ouédraogo</t>
+  </si>
+  <si>
+    <t>FAAROOQ</t>
+  </si>
+  <si>
+    <t>KONATÉ</t>
+  </si>
+  <si>
+    <t>CHEIK OMAR</t>
+  </si>
+  <si>
+    <t>BOUSSIM FADEL</t>
+  </si>
+  <si>
+    <t>HABIB</t>
+  </si>
+  <si>
+    <t>ISSA</t>
+  </si>
+  <si>
+    <t>GUEDJ</t>
+  </si>
+  <si>
+    <t>NDIAYE</t>
+  </si>
+  <si>
+    <t>HAMED-TIDJANI</t>
+  </si>
+  <si>
+    <t>OUEDRAOGO</t>
+  </si>
+  <si>
+    <t>ABDOUL-FATAHOU</t>
+  </si>
+  <si>
+    <t>COMPAORÉ</t>
+  </si>
+  <si>
+    <t>YACOUBA</t>
+  </si>
+  <si>
+    <t>DARGA</t>
+  </si>
+  <si>
+    <t>RAOUF</t>
+  </si>
+  <si>
+    <t>KRIGAH</t>
+  </si>
+  <si>
+    <t>HANS</t>
+  </si>
+  <si>
+    <t>KOUAKOU</t>
+  </si>
+  <si>
+    <t>HAMIDOU</t>
+  </si>
+  <si>
+    <t>KEVIN ESPÉRAT</t>
+  </si>
+  <si>
+    <t>SAWADOGO</t>
+  </si>
+  <si>
+    <t>ABDOUL-HAKIM</t>
+  </si>
+  <si>
+    <t>BANCÉ</t>
+  </si>
+  <si>
+    <t>SIMPORE</t>
+  </si>
+  <si>
+    <t>ZONGO</t>
+  </si>
+  <si>
+    <t>KEITA</t>
+  </si>
+  <si>
+    <t>ABDOUL</t>
+  </si>
+  <si>
+    <t>OUÉDRAOGO</t>
+  </si>
+  <si>
+    <t>MAX ILDEVER WENDPOUIRÉ</t>
+  </si>
+  <si>
+    <t>SOUILI</t>
+  </si>
+  <si>
+    <t>MARIUS</t>
+  </si>
+  <si>
+    <t>SOUHOUDOU</t>
+  </si>
+  <si>
+    <t>MICHEL DONALD</t>
+  </si>
+  <si>
+    <t>AHMEDOU MALICK</t>
+  </si>
+  <si>
+    <t>LASSINA</t>
+  </si>
+  <si>
+    <t>WILFREID</t>
+  </si>
+  <si>
+    <t>KINDO</t>
+  </si>
+  <si>
+    <t>ASSAGOU</t>
+  </si>
+  <si>
+    <t>VÉRON</t>
+  </si>
+  <si>
+    <t>KABORÉ</t>
+  </si>
+  <si>
+    <t>MANA</t>
+  </si>
+  <si>
+    <t>NOM DE L'ÉQUIPE :GUINÉE 🇬🇳</t>
+  </si>
+  <si>
+    <t>ADRESSE  COURRIEL :aboubabacarpapikeita@gmail.com</t>
+  </si>
+  <si>
+    <t>TÉL D'URGENCE : 4182658413</t>
+  </si>
+  <si>
+    <t>NOM DU COACH : BOUBACAR NABÉ</t>
+  </si>
+  <si>
+    <t>NOM DU CAPITAINE : Moustapha Donzo</t>
+  </si>
+  <si>
+    <t>KOUROUMA NEMA</t>
+  </si>
+  <si>
+    <t>SOUA</t>
+  </si>
+  <si>
+    <t>Guinéen</t>
   </si>
   <si>
     <t>IBRAHIMA</t>
   </si>
   <si>
-    <t>WONE</t>
-  </si>
-  <si>
-    <t>MAMADOU SARR</t>
-  </si>
-  <si>
-    <t>DIENG</t>
-  </si>
-  <si>
-    <t>MAME BALLA</t>
-  </si>
-  <si>
-    <t>DOUMBIA</t>
-  </si>
-  <si>
-    <t>ALAIN GUY OMAR</t>
-  </si>
-  <si>
-    <t>DIAGNE</t>
-  </si>
-  <si>
-    <t>MOUHAMADOU MOUSTAPHA</t>
-  </si>
-  <si>
-    <t>HANE</t>
-  </si>
-  <si>
-    <t>NDIAGA</t>
-  </si>
-  <si>
-    <t>SARR</t>
-  </si>
-  <si>
-    <t>BABACAR</t>
-  </si>
-  <si>
-    <t>GUEYE</t>
-  </si>
-  <si>
-    <t>FALLOU</t>
-  </si>
-  <si>
-    <t>THIAM</t>
-  </si>
-  <si>
-    <t>KHALIFA</t>
-  </si>
-  <si>
-    <t>NIANG</t>
-  </si>
-  <si>
-    <t>DAOUDA</t>
-  </si>
-  <si>
-    <t>NDIAYE</t>
-  </si>
-  <si>
-    <t>DIOUF</t>
-  </si>
-  <si>
-    <t>IDRISSA</t>
-  </si>
-  <si>
-    <t>JOHNSON</t>
-  </si>
-  <si>
-    <t>SÉBASTIEN LIONEL</t>
-  </si>
-  <si>
-    <t>MASSEYE</t>
-  </si>
-  <si>
-    <t>DIOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOUSTAPHA </t>
-  </si>
-  <si>
-    <t>PAPE IBRAHIMA</t>
-  </si>
-  <si>
-    <t>MANGANE</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>SÉNE</t>
-  </si>
-  <si>
-    <t>SERIGNE</t>
-  </si>
-  <si>
-    <t>FALL</t>
-  </si>
-  <si>
-    <t>BABA MAMADOU</t>
-  </si>
-  <si>
-    <t>CAMARA</t>
-  </si>
-  <si>
-    <t>PAPA BABACAR</t>
-  </si>
-  <si>
-    <t>SECK</t>
-  </si>
-  <si>
-    <t>MOUSTAPHA</t>
-  </si>
-  <si>
-    <t>PAPA GARBA</t>
-  </si>
-  <si>
-    <t>COULIBALY</t>
-  </si>
-  <si>
-    <t>GORA</t>
-  </si>
-  <si>
-    <t>MBODJ</t>
-  </si>
-  <si>
-    <t>SOULEYMANE</t>
-  </si>
-  <si>
-    <t>DIALLO</t>
-  </si>
-  <si>
-    <t>Togo</t>
-  </si>
-  <si>
-    <t>Alatevi.k@gmail.com</t>
-  </si>
-  <si>
-    <t>438-827-6129</t>
-  </si>
-  <si>
-    <t>Fabrice</t>
-  </si>
-  <si>
-    <t>Komi Alatevi</t>
-  </si>
-  <si>
-    <t>CARL ISAAC PENCHEV</t>
-  </si>
-  <si>
-    <t>RENEVIL</t>
-  </si>
-  <si>
-    <t>Haïti</t>
-  </si>
-  <si>
-    <t>KOMI</t>
-  </si>
-  <si>
-    <t>ALATEVI</t>
-  </si>
-  <si>
-    <t>AMIDOU</t>
-  </si>
-  <si>
-    <t>AKOH</t>
-  </si>
-  <si>
-    <t>KOSSI ANTHONY</t>
-  </si>
-  <si>
-    <t>ADJAMA</t>
-  </si>
-  <si>
-    <t>KOSSI SAMSON</t>
-  </si>
-  <si>
-    <t>KLOUSSE</t>
-  </si>
-  <si>
-    <t>BOTCHA</t>
-  </si>
-  <si>
-    <t>HENOC</t>
-  </si>
-  <si>
-    <t>OTNIEL</t>
-  </si>
-  <si>
-    <t>AKOEGNON</t>
-  </si>
-  <si>
-    <t>KOFFI MOÏSE</t>
-  </si>
-  <si>
-    <t>AMEVO</t>
-  </si>
-  <si>
-    <t>MANI</t>
-  </si>
-  <si>
-    <t>BABALIM</t>
-  </si>
-  <si>
-    <t>BASSITOU</t>
-  </si>
-  <si>
-    <t>ASSANI</t>
-  </si>
-  <si>
-    <t>FOUMI MAJID</t>
-  </si>
-  <si>
-    <t>OLA</t>
-  </si>
-  <si>
-    <t>FRANCIS</t>
-  </si>
-  <si>
-    <t>AGBOGBO</t>
-  </si>
-  <si>
-    <t>Tia Cixte</t>
-  </si>
-  <si>
-    <t>Marti Dji</t>
-  </si>
-  <si>
-    <t>Essofa Oubote</t>
-  </si>
-  <si>
-    <t>ABODJI</t>
-  </si>
-  <si>
-    <t>Allassane</t>
-  </si>
-  <si>
-    <t>Kone</t>
-  </si>
-  <si>
-    <t>Mouh amed</t>
-  </si>
-  <si>
-    <t>Dosso</t>
-  </si>
-  <si>
-    <t>FIACRE</t>
-  </si>
-  <si>
-    <t>KOFFI</t>
-  </si>
-  <si>
-    <t>DANIEL KOMLAN</t>
-  </si>
-  <si>
-    <t>DEKASSI</t>
-  </si>
-  <si>
-    <t>EMMANUEL BORIS</t>
-  </si>
-  <si>
-    <t>OLÉ OBALÉ</t>
-  </si>
-  <si>
-    <t>guinée</t>
-  </si>
-  <si>
-    <t>KOUTAO RAKOU</t>
-  </si>
-  <si>
-    <t>TALMANTA</t>
-  </si>
-  <si>
-    <t>ALOGNISSO</t>
-  </si>
-  <si>
-    <t>RONALD</t>
-  </si>
-  <si>
-    <t>PETERSON</t>
-  </si>
-  <si>
-    <t>AUGUSTE</t>
-  </si>
-  <si>
-    <t>CI</t>
-  </si>
-  <si>
-    <t>LOCHINA</t>
-  </si>
-  <si>
-    <t>DJAFAROU</t>
-  </si>
-  <si>
-    <t>KONATÉ</t>
-  </si>
-  <si>
-    <t>MANSOUR</t>
-  </si>
-  <si>
-    <t>KOMLAN AMEN</t>
-  </si>
-  <si>
-    <t>AKAMA</t>
-  </si>
-  <si>
-    <t>ESSODONA</t>
-  </si>
-  <si>
-    <t>HALAOUI</t>
-  </si>
-  <si>
-    <t>ADONIS</t>
-  </si>
-  <si>
-    <t>KALENGA</t>
-  </si>
-  <si>
-    <t>MKOLE</t>
-  </si>
-  <si>
-    <t>RAMADHANI</t>
-  </si>
-  <si>
-    <t>DESIRE</t>
-  </si>
-  <si>
-    <t>BICUKA</t>
-  </si>
-  <si>
-    <t>ABEDI</t>
-  </si>
-  <si>
-    <t>SAIDI</t>
-  </si>
-  <si>
-    <t>ATAMBA</t>
-  </si>
-  <si>
-    <t>SHAURI</t>
-  </si>
-  <si>
-    <t>JONAS</t>
-  </si>
-  <si>
-    <t>KISUBI</t>
-  </si>
-  <si>
-    <t>PATIENT</t>
-  </si>
-  <si>
-    <t>ECA MBOKO</t>
-  </si>
-  <si>
-    <t>SALEH</t>
-  </si>
-  <si>
-    <t>ECA</t>
-  </si>
-  <si>
-    <t>UWEZO</t>
-  </si>
-  <si>
-    <t>JUMAPILI</t>
-  </si>
-  <si>
-    <t>NDIKUMANA</t>
-  </si>
-  <si>
-    <t>JANVIER</t>
-  </si>
-  <si>
-    <t>REUBEN</t>
-  </si>
-  <si>
-    <t>MLONGEKA</t>
-  </si>
-  <si>
-    <t>AMURI</t>
-  </si>
-  <si>
-    <t>NDUME</t>
-  </si>
-  <si>
-    <t>OMARI</t>
-  </si>
-  <si>
-    <t>KASHINDI</t>
-  </si>
-  <si>
-    <t>WILONDJA</t>
-  </si>
-  <si>
-    <t>LWAMAGENA</t>
-  </si>
-  <si>
-    <t>GILEO</t>
-  </si>
-  <si>
-    <t>MTABI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGAZINI </t>
-  </si>
-  <si>
-    <t>LWABOSHI MAJEGEZA</t>
-  </si>
-  <si>
-    <t>ERICK</t>
-  </si>
-  <si>
-    <t>NISHIMWE</t>
-  </si>
-  <si>
-    <t>ASENDE</t>
-  </si>
-  <si>
-    <t>ABANGWA</t>
-  </si>
-  <si>
-    <t>OLIVIER</t>
-  </si>
-  <si>
-    <t>RIPHIN</t>
-  </si>
-  <si>
-    <t>HONNEUR</t>
-  </si>
-  <si>
-    <t>JEAN MARIE</t>
-  </si>
-  <si>
-    <t>ELIAZERI</t>
-  </si>
-  <si>
-    <t>NIYOGUSENGA</t>
-  </si>
-  <si>
-    <t>BYAOMBE</t>
-  </si>
-  <si>
-    <t>BAHOME</t>
-  </si>
-  <si>
-    <t>YAMUNGU MLENBA</t>
-  </si>
-  <si>
-    <t>ZAKARIA</t>
-  </si>
-  <si>
-    <t>RÉMY</t>
-  </si>
-  <si>
-    <t>MILAMBO</t>
-  </si>
-  <si>
-    <t>Haiti</t>
-  </si>
-  <si>
-    <t>soccerangranmoun@gmail.com; flounes37@gmail.com</t>
-  </si>
-  <si>
-    <t>4189563785 / 4388384936</t>
-  </si>
-  <si>
-    <t>Lounès Félicin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hans Raldy Saint-Preux </t>
-  </si>
-  <si>
-    <t>MAQUINGSON</t>
-  </si>
-  <si>
-    <t>MAIGNAN</t>
-  </si>
-  <si>
-    <t>AMILICA</t>
-  </si>
-  <si>
-    <t>BOUKARI BOURDJA</t>
-  </si>
-  <si>
-    <t>MICHAEL PERSHINGSON</t>
-  </si>
-  <si>
-    <t>PIERRE</t>
-  </si>
-  <si>
-    <t>JEFFERSON</t>
-  </si>
-  <si>
-    <t>ANTOINE</t>
-  </si>
-  <si>
-    <t>GREGORY</t>
-  </si>
-  <si>
-    <t>ANNAY</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>JERRY</t>
-  </si>
-  <si>
-    <t>PAULIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AXEL </t>
-  </si>
-  <si>
-    <t>ALIMASI</t>
-  </si>
-  <si>
-    <t>MARC-ARTHUR</t>
-  </si>
-  <si>
-    <t>REGISTRE</t>
-  </si>
-  <si>
-    <t>MARC-DONALD</t>
-  </si>
-  <si>
-    <t>SIMEUS</t>
-  </si>
-  <si>
-    <t>EVEDERSON</t>
-  </si>
-  <si>
-    <t>PREVILON</t>
-  </si>
-  <si>
-    <t>WOODSON</t>
-  </si>
-  <si>
-    <t>SAINT-LOUIS</t>
-  </si>
-  <si>
-    <t>ROMAIN</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>RYSDAEL C.</t>
-  </si>
-  <si>
-    <t>DUVELSAINT</t>
-  </si>
-  <si>
-    <t>TEVINSON</t>
-  </si>
-  <si>
-    <t>GARCON</t>
-  </si>
-  <si>
-    <t>ISMAEL GAMA</t>
-  </si>
-  <si>
-    <t>GABRIEL</t>
-  </si>
-  <si>
-    <t>SCHADRAC</t>
-  </si>
-  <si>
-    <t>DARLENS</t>
-  </si>
-  <si>
-    <t>CEPOUDY</t>
-  </si>
-  <si>
-    <t>ELICLES</t>
-  </si>
-  <si>
-    <t>OMRA VALDJY WOODLEY</t>
-  </si>
-  <si>
-    <t>BARTHELUS</t>
-  </si>
-  <si>
-    <t>KENLEY</t>
-  </si>
-  <si>
-    <t>MAXI</t>
-  </si>
-  <si>
-    <t>CLIFORD</t>
-  </si>
-  <si>
-    <t>CHARLES</t>
-  </si>
-  <si>
-    <t>MARKENLOVE</t>
-  </si>
-  <si>
-    <t>SYLVESTRE STALONNE</t>
-  </si>
-  <si>
-    <t>SECHOUAM</t>
-  </si>
-  <si>
-    <t>CEBATIEN</t>
-  </si>
-  <si>
-    <t>PIERRE-LOUIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JERRY BENNEDICT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOEL </t>
-  </si>
-  <si>
-    <t>oudoucis@yahoo.com</t>
-  </si>
-  <si>
-    <t>418 953 6873</t>
-  </si>
-  <si>
-    <t>ABDRAHAMANE TRAORE</t>
-  </si>
-  <si>
-    <t>Mohamed Coulibaly</t>
-  </si>
-  <si>
-    <t>NUMBER</t>
-  </si>
-  <si>
-    <t>TOP</t>
-  </si>
-  <si>
-    <t>SHORT</t>
-  </si>
-  <si>
-    <t>JACOB</t>
-  </si>
-  <si>
-    <t>DEMBÉLÉ</t>
-  </si>
-  <si>
-    <t>HAMED</t>
-  </si>
-  <si>
-    <t>OUSMANE</t>
-  </si>
-  <si>
-    <t>ABDOULAYE</t>
-  </si>
-  <si>
-    <t>DAO</t>
-  </si>
-  <si>
-    <t>NAMAKÉ FALAYE</t>
-  </si>
-  <si>
-    <t>SISSOKO</t>
-  </si>
-  <si>
-    <t>MOUSSA</t>
-  </si>
-  <si>
-    <t>DJIGUI</t>
-  </si>
-  <si>
-    <t>MOHAMED</t>
-  </si>
-  <si>
-    <t>ALESSANDRO DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SALIM</t>
-  </si>
-  <si>
-    <t>NIMAGA</t>
-  </si>
-  <si>
-    <t>SIDY MAHAMANE</t>
-  </si>
-  <si>
-    <t>TOURÉ</t>
-  </si>
-  <si>
-    <t>MAHAMOUDOU</t>
-  </si>
-  <si>
-    <t>KONÉ</t>
-  </si>
-  <si>
-    <t>IDRISSA DADYS</t>
-  </si>
-  <si>
-    <t>SIDIBÉ</t>
-  </si>
-  <si>
-    <t>ABOUBAKRINE</t>
-  </si>
-  <si>
-    <t>INTALLA</t>
-  </si>
-  <si>
-    <t>SEKOU SOULEYMANE</t>
-  </si>
-  <si>
-    <t>MAMADOU BAZAN</t>
-  </si>
-  <si>
-    <t>TOGOLA</t>
-  </si>
-  <si>
-    <t>DJIMÉ</t>
-  </si>
-  <si>
-    <t>KÉBÉ</t>
-  </si>
-  <si>
-    <t>MOULAYE MOHAMED</t>
-  </si>
-  <si>
-    <t>DICKO</t>
-  </si>
-  <si>
-    <t>HAROUNA</t>
-  </si>
-  <si>
-    <t>BACHIR</t>
-  </si>
-  <si>
-    <t>BASSIROU</t>
-  </si>
-  <si>
-    <t>HAIDARA</t>
-  </si>
-  <si>
-    <t>GUESSOUMA</t>
-  </si>
-  <si>
-    <t>PATRICK STÉPHANE</t>
-  </si>
-  <si>
-    <t>KAMDEM WAKAM</t>
-  </si>
-  <si>
-    <t>MALIK</t>
-  </si>
-  <si>
-    <t>DIARRA</t>
-  </si>
-  <si>
-    <t>IBRAHIM</t>
-  </si>
-  <si>
-    <t>ISSAKA</t>
-  </si>
-  <si>
-    <t>OUMAR</t>
-  </si>
-  <si>
-    <t>CISSÉ</t>
-  </si>
-  <si>
-    <t>ALMAMY</t>
-  </si>
-  <si>
-    <t>GUINDO</t>
-  </si>
-  <si>
-    <t>KOULBÉ</t>
-  </si>
-  <si>
-    <t>Tchad</t>
-  </si>
-  <si>
-    <t>Gabon</t>
-  </si>
-  <si>
-    <t>georgesarmel1@hotmail.fr</t>
-  </si>
-  <si>
-    <t>(581)849-3674</t>
-  </si>
-  <si>
-    <t>Georges armel Nguimbi</t>
-  </si>
-  <si>
-    <t>Cedrick essockamba</t>
-  </si>
-  <si>
-    <t>DROLET</t>
-  </si>
-  <si>
-    <t>DIEUDONNÉ</t>
-  </si>
-  <si>
-    <t>CIZA</t>
-  </si>
-  <si>
-    <t>Rwanda</t>
-  </si>
-  <si>
-    <t>STEPHANE</t>
-  </si>
-  <si>
-    <t>PREDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada </t>
-  </si>
-  <si>
-    <t>CEDRIC</t>
-  </si>
-  <si>
-    <t>ESSOCKAMBA</t>
-  </si>
-  <si>
-    <t>JEAN-THERRY</t>
-  </si>
-  <si>
-    <t>YAMA</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>BAMBA</t>
-  </si>
-  <si>
-    <t>FARAJA</t>
-  </si>
-  <si>
-    <t>DIEU BENIT</t>
-  </si>
-  <si>
-    <t>SOUMAI</t>
-  </si>
-  <si>
-    <t>FEDSON</t>
-  </si>
-  <si>
-    <t>ROSIER</t>
-  </si>
-  <si>
-    <t>YANNICK</t>
-  </si>
-  <si>
-    <t>KAYILOU</t>
-  </si>
-  <si>
-    <t>ESTEBAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cote d'ivoire </t>
-  </si>
-  <si>
-    <t>JEAN DANIEL</t>
-  </si>
-  <si>
-    <t>POTTEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALEXANDRE </t>
-  </si>
-  <si>
-    <t>KOKORA</t>
-  </si>
-  <si>
-    <t>ABDELAZIZ</t>
-  </si>
-  <si>
-    <t>KAPATA</t>
-  </si>
-  <si>
-    <t>Centre-afrique</t>
-  </si>
-  <si>
-    <t>VINCENT</t>
-  </si>
-  <si>
-    <t>CORNEAU</t>
-  </si>
-  <si>
-    <t>DEMOYER</t>
-  </si>
-  <si>
-    <t>KOUASSI</t>
-  </si>
-  <si>
-    <t>BENONI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ÉMILE </t>
-  </si>
-  <si>
-    <t>FRANCK NELSON</t>
-  </si>
-  <si>
-    <t>VOUFO</t>
-  </si>
-  <si>
-    <t>SAMUEL</t>
-  </si>
-  <si>
-    <t>POATY</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>POTE</t>
-  </si>
-  <si>
-    <t>ARGI</t>
-  </si>
-  <si>
-    <t>PASCAL</t>
-  </si>
-  <si>
-    <t>BIENVENUE</t>
-  </si>
-  <si>
-    <t>STANY</t>
-  </si>
-  <si>
-    <t>Burundi</t>
-  </si>
-  <si>
-    <t>MARC</t>
-  </si>
-  <si>
-    <t>ÉRISA</t>
-  </si>
-  <si>
-    <t>NSHIMIYIMANA</t>
-  </si>
-  <si>
-    <t>JUNIOR</t>
-  </si>
-  <si>
-    <t>POKOU</t>
-  </si>
-  <si>
-    <t>Cote d'ivoire</t>
-  </si>
-  <si>
-    <t>418-554-0364</t>
-  </si>
-  <si>
-    <t>ABDOUL-AZIZ</t>
-  </si>
-  <si>
-    <t>Hamidou Ouédraogo</t>
-  </si>
-  <si>
-    <t>FAAROOQ</t>
-  </si>
-  <si>
-    <t>CHEIK OMAR</t>
-  </si>
-  <si>
-    <t>BOUSSIM FADEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORESTE </t>
-  </si>
-  <si>
-    <t>TOMPOUDI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KANE </t>
-  </si>
-  <si>
-    <t>HAMED-TIDJANI</t>
-  </si>
-  <si>
-    <t>OUEDRAOGO</t>
-  </si>
-  <si>
-    <t>ABDOUL-FATAHOU</t>
-  </si>
-  <si>
-    <t>COMPAORÉ</t>
-  </si>
-  <si>
-    <t>YACOUBA</t>
-  </si>
-  <si>
-    <t>DARGA</t>
-  </si>
-  <si>
-    <t>RAOUF</t>
-  </si>
-  <si>
-    <t>KRIGAH</t>
-  </si>
-  <si>
-    <t>HANS</t>
-  </si>
-  <si>
-    <t>KOUAKOU</t>
-  </si>
-  <si>
-    <t>ALASSANE</t>
-  </si>
-  <si>
-    <t>FAYE</t>
-  </si>
-  <si>
-    <t>KEVIN ESPÉRAT</t>
-  </si>
-  <si>
-    <t>SAWADOGO</t>
-  </si>
-  <si>
-    <t>ABDOUL-HAKIM</t>
-  </si>
-  <si>
-    <t>BANCÉ</t>
-  </si>
-  <si>
-    <t>SIMPORE</t>
-  </si>
-  <si>
-    <t>ZONGO</t>
-  </si>
-  <si>
-    <t>KECOUTA</t>
-  </si>
-  <si>
-    <t>ABDOUL</t>
-  </si>
-  <si>
-    <t>OUÉDRAOGO</t>
-  </si>
-  <si>
-    <t>MAX ILDEVER WENDPOUIRÉ</t>
-  </si>
-  <si>
-    <t>SOUILI</t>
-  </si>
-  <si>
-    <t>CHATELAIN</t>
-  </si>
-  <si>
-    <t>YADJUI</t>
-  </si>
-  <si>
-    <t>SOUHOUDOU</t>
-  </si>
-  <si>
-    <t>MICHEL DONALD</t>
-  </si>
-  <si>
-    <t>MAT-JUNIOR</t>
-  </si>
-  <si>
-    <t>SOBJANG NDJATOU</t>
-  </si>
-  <si>
-    <t>LASSINA</t>
-  </si>
-  <si>
-    <t>WILFREID</t>
-  </si>
-  <si>
-    <t>KINDO</t>
-  </si>
-  <si>
-    <t>ASSAGOU</t>
-  </si>
-  <si>
-    <t>VÉRON</t>
-  </si>
-  <si>
-    <t>KABORÉ</t>
-  </si>
-  <si>
-    <t>MANA</t>
-  </si>
-  <si>
-    <t>NOM DE L'ÉQUIPE :GUINÉE 🇬🇳</t>
-  </si>
-  <si>
-    <t>ADRESSE  COURRIEL :aboubabacarpapikeita@gmail.com</t>
-  </si>
-  <si>
-    <t>TÉL D'URGENCE : 4182658413</t>
-  </si>
-  <si>
-    <t>NOM DU COACH : BOUBACAR NABÉ</t>
-  </si>
-  <si>
-    <t>NOM DU CAPITAINE : Moustapha Donzo</t>
-  </si>
-  <si>
-    <t>KOUROUMA NEMA</t>
-  </si>
-  <si>
-    <t>SOUA</t>
-  </si>
-  <si>
-    <t>Guinéen</t>
-  </si>
-  <si>
     <t>SY SAVANÉ</t>
   </si>
   <si>
@@ -1604,9 +1616,6 @@
     <t>ISMAEL</t>
   </si>
   <si>
-    <t>BARRY</t>
-  </si>
-  <si>
     <t>Guinée</t>
   </si>
   <si>
@@ -1619,10 +1628,16 @@
     <t>DIANÉ</t>
   </si>
   <si>
-    <t>ABOUBACAR</t>
-  </si>
-  <si>
-    <t>AKHYAR</t>
+    <t>ALY</t>
+  </si>
+  <si>
+    <t>FOFANA</t>
+  </si>
+  <si>
+    <t>BANGALY</t>
+  </si>
+  <si>
+    <t>NABE</t>
   </si>
   <si>
     <t>Mauritanien</t>
@@ -1658,7 +1673,10 @@
     <t>HAROU</t>
   </si>
   <si>
-    <t>THIERNO NOUHOU</t>
+    <t>ABDOUL AZIZ</t>
+  </si>
+  <si>
+    <t>BAH</t>
   </si>
   <si>
     <t>ELHADJ OUSMANE</t>
@@ -1688,28 +1706,28 @@
     <t>CHERIF</t>
   </si>
   <si>
-    <t>DARSY</t>
-  </si>
-  <si>
-    <t>BIGNOUMBA</t>
+    <t>ESEAKA</t>
+  </si>
+  <si>
+    <t>KANNEH</t>
   </si>
   <si>
     <t>Gabonaise</t>
   </si>
   <si>
-    <t>ELHADJ</t>
-  </si>
-  <si>
-    <t>DICKO SIDI MOUCTAR</t>
-  </si>
-  <si>
-    <t>KEITA</t>
+    <t>ELHADJ ABDOULAYE</t>
+  </si>
+  <si>
+    <t>MAHAMADOU</t>
   </si>
   <si>
     <t xml:space="preserve">Guinee </t>
   </si>
   <si>
-    <t>MAMADOU KINDY</t>
+    <t>MAMOUDOU KINDY</t>
+  </si>
+  <si>
+    <t>MASASSOUBA</t>
   </si>
 </sst>
 </file>
@@ -2056,7 +2074,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="137">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2141,16 +2159,22 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2158,6 +2182,9 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -2171,14 +2198,14 @@
     <xf borderId="1" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2209,6 +2236,9 @@
     </xf>
     <xf borderId="1" fillId="10" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
@@ -2278,13 +2308,22 @@
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -2334,8 +2373,8 @@
     <xf borderId="1" fillId="0" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="1" fillId="0" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
@@ -2378,6 +2417,9 @@
     <xf borderId="1" fillId="8" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -2405,8 +2447,8 @@
     <xf borderId="1" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -2943,7 +2985,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2966,7 +3008,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2978,7 +3020,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2989,8 +3031,8 @@
       <c r="H3" s="13"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="117" t="s">
-        <v>508</v>
+      <c r="A4" s="125" t="s">
+        <v>511</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -3002,7 +3044,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3023,10 +3065,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="40" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -3076,26 +3118,26 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="74">
+      <c r="A8" s="78">
         <v>1.0</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="118" t="s">
-        <v>510</v>
-      </c>
-      <c r="E8" s="118" t="s">
-        <v>511</v>
-      </c>
-      <c r="F8" s="40">
+      <c r="D8" s="126" t="s">
+        <v>513</v>
+      </c>
+      <c r="E8" s="126" t="s">
+        <v>514</v>
+      </c>
+      <c r="F8" s="42">
         <v>26.0</v>
       </c>
-      <c r="G8" s="41" t="s">
-        <v>512</v>
+      <c r="G8" s="43" t="s">
+        <v>515</v>
       </c>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
@@ -3112,26 +3154,26 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="76">
+      <c r="A9" s="80">
         <v>2.0</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="75" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" s="75" t="s">
-        <v>513</v>
-      </c>
-      <c r="F9" s="119">
+      <c r="D9" s="79" t="s">
+        <v>516</v>
+      </c>
+      <c r="E9" s="79" t="s">
+        <v>517</v>
+      </c>
+      <c r="F9" s="127">
         <v>22.0</v>
       </c>
-      <c r="G9" s="120" t="s">
-        <v>514</v>
+      <c r="G9" s="128" t="s">
+        <v>518</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -3148,7 +3190,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="74">
+      <c r="A10" s="78">
         <v>3.0</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -3157,17 +3199,17 @@
       <c r="C10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="75" t="s">
-        <v>515</v>
-      </c>
-      <c r="E10" s="75" t="s">
-        <v>516</v>
-      </c>
-      <c r="F10" s="119">
+      <c r="D10" s="79" t="s">
+        <v>519</v>
+      </c>
+      <c r="E10" s="79" t="s">
+        <v>520</v>
+      </c>
+      <c r="F10" s="127">
         <v>30.0</v>
       </c>
-      <c r="G10" s="120" t="s">
-        <v>517</v>
+      <c r="G10" s="128" t="s">
+        <v>521</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -3184,26 +3226,26 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="74">
+      <c r="A11" s="78">
         <v>4.0</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="120" t="s">
+      <c r="C11" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="75" t="s">
-        <v>518</v>
-      </c>
-      <c r="E11" s="75" t="s">
-        <v>519</v>
-      </c>
-      <c r="F11" s="119">
+      <c r="D11" s="79" t="s">
+        <v>522</v>
+      </c>
+      <c r="E11" s="79" t="s">
+        <v>523</v>
+      </c>
+      <c r="F11" s="127">
         <v>25.0</v>
       </c>
-      <c r="G11" s="120" t="s">
-        <v>520</v>
+      <c r="G11" s="128" t="s">
+        <v>524</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11" s="29"/>
@@ -3220,24 +3262,24 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="74">
+      <c r="A12" s="78">
         <v>5.0</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="120" t="s">
+      <c r="C12" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="75" t="s">
-        <v>521</v>
-      </c>
-      <c r="E12" s="75" t="s">
-        <v>522</v>
-      </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41" t="s">
-        <v>523</v>
+      <c r="D12" s="79" t="s">
+        <v>525</v>
+      </c>
+      <c r="E12" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="G12" s="43" t="s">
+        <v>526</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -3254,26 +3296,26 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="74">
+      <c r="A13" s="78">
         <v>6.0</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="120" t="s">
+      <c r="C13" s="128" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="75" t="s">
-        <v>395</v>
-      </c>
-      <c r="E13" s="75" t="s">
-        <v>524</v>
-      </c>
-      <c r="F13" s="119">
+      <c r="D13" s="79" t="s">
+        <v>399</v>
+      </c>
+      <c r="E13" s="79" t="s">
+        <v>527</v>
+      </c>
+      <c r="F13" s="127">
         <v>25.0</v>
       </c>
-      <c r="G13" s="120" t="s">
-        <v>525</v>
+      <c r="G13" s="128" t="s">
+        <v>528</v>
       </c>
       <c r="H13" s="28"/>
       <c r="I13" s="29"/>
@@ -3290,26 +3332,26 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="74">
+      <c r="A14" s="78">
         <v>7.0</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="79" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="75" t="s">
-        <v>395</v>
-      </c>
-      <c r="E14" s="75" t="s">
-        <v>526</v>
-      </c>
-      <c r="F14" s="119">
+      <c r="D14" s="79" t="s">
+        <v>399</v>
+      </c>
+      <c r="E14" s="79" t="s">
+        <v>529</v>
+      </c>
+      <c r="F14" s="127">
         <v>30.0</v>
       </c>
-      <c r="G14" s="120" t="s">
-        <v>525</v>
+      <c r="G14" s="128" t="s">
+        <v>528</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
@@ -3326,7 +3368,7 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="74">
+      <c r="A15" s="78">
         <v>8.0</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3335,17 +3377,17 @@
       <c r="C15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="75" t="s">
-        <v>527</v>
-      </c>
-      <c r="E15" s="75" t="s">
-        <v>524</v>
-      </c>
-      <c r="F15" s="119">
+      <c r="D15" s="87" t="s">
+        <v>530</v>
+      </c>
+      <c r="E15" s="87" t="s">
+        <v>531</v>
+      </c>
+      <c r="F15" s="127">
         <v>22.0</v>
       </c>
-      <c r="G15" s="120" t="s">
-        <v>525</v>
+      <c r="G15" s="128" t="s">
+        <v>528</v>
       </c>
       <c r="H15" s="28"/>
       <c r="I15" s="29"/>
@@ -3362,24 +3404,24 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="74">
+      <c r="A16" s="78">
         <v>9.0</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="79" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="75" t="s">
-        <v>362</v>
-      </c>
-      <c r="E16" s="75" t="s">
-        <v>528</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41" t="s">
-        <v>529</v>
+      <c r="D16" s="87" t="s">
+        <v>532</v>
+      </c>
+      <c r="E16" s="87" t="s">
+        <v>533</v>
+      </c>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43" t="s">
+        <v>534</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
@@ -3396,26 +3438,26 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="76">
+      <c r="A17" s="80">
         <v>10.0</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="120" t="s">
+      <c r="C17" s="128" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="75" t="s">
-        <v>530</v>
-      </c>
-      <c r="E17" s="75" t="s">
-        <v>531</v>
-      </c>
-      <c r="F17" s="119">
+      <c r="D17" s="79" t="s">
+        <v>535</v>
+      </c>
+      <c r="E17" s="79" t="s">
+        <v>536</v>
+      </c>
+      <c r="F17" s="127">
         <v>27.0</v>
       </c>
-      <c r="G17" s="120" t="s">
-        <v>517</v>
+      <c r="G17" s="128" t="s">
+        <v>521</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
@@ -3432,26 +3474,26 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="74">
+      <c r="A18" s="78">
         <v>11.0</v>
       </c>
-      <c r="B18" s="75" t="s">
+      <c r="B18" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="120" t="s">
+      <c r="C18" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="75" t="s">
-        <v>532</v>
-      </c>
-      <c r="E18" s="75" t="s">
-        <v>533</v>
-      </c>
-      <c r="F18" s="119">
+      <c r="D18" s="79" t="s">
+        <v>537</v>
+      </c>
+      <c r="E18" s="79" t="s">
+        <v>538</v>
+      </c>
+      <c r="F18" s="127">
         <v>23.0</v>
       </c>
-      <c r="G18" s="120" t="s">
-        <v>525</v>
+      <c r="G18" s="128" t="s">
+        <v>528</v>
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
@@ -3468,26 +3510,26 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="76">
+      <c r="A19" s="80">
         <v>12.0</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="120" t="s">
+      <c r="C19" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="E19" s="75" t="s">
-        <v>534</v>
-      </c>
-      <c r="F19" s="119">
+      <c r="D19" s="79" t="s">
+        <v>180</v>
+      </c>
+      <c r="E19" s="79" t="s">
+        <v>539</v>
+      </c>
+      <c r="F19" s="127">
         <v>30.0</v>
       </c>
-      <c r="G19" s="120" t="s">
-        <v>517</v>
+      <c r="G19" s="128" t="s">
+        <v>521</v>
       </c>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
@@ -3504,24 +3546,24 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="76">
+      <c r="A20" s="80">
         <v>13.0</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="120" t="s">
+      <c r="C20" s="128" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="75" t="s">
-        <v>535</v>
-      </c>
-      <c r="E20" s="75" t="s">
-        <v>536</v>
+      <c r="D20" s="79" t="s">
+        <v>540</v>
+      </c>
+      <c r="E20" s="79" t="s">
+        <v>541</v>
       </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="120" t="s">
-        <v>525</v>
+      <c r="G20" s="128" t="s">
+        <v>528</v>
       </c>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
@@ -3538,26 +3580,26 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="76">
+      <c r="A21" s="80">
         <v>14.0</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="75" t="s">
-        <v>537</v>
-      </c>
-      <c r="E21" s="75" t="s">
-        <v>538</v>
-      </c>
-      <c r="F21" s="119">
+      <c r="D21" s="79" t="s">
+        <v>542</v>
+      </c>
+      <c r="E21" s="79" t="s">
+        <v>543</v>
+      </c>
+      <c r="F21" s="127">
         <v>18.0</v>
       </c>
-      <c r="G21" s="120" t="s">
-        <v>523</v>
+      <c r="G21" s="128" t="s">
+        <v>526</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -3574,26 +3616,26 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="74">
+      <c r="A22" s="78">
         <v>15.0</v>
       </c>
-      <c r="B22" s="121" t="s">
+      <c r="B22" s="129" t="s">
         <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="75" t="s">
-        <v>362</v>
-      </c>
-      <c r="E22" s="75" t="s">
-        <v>539</v>
-      </c>
-      <c r="F22" s="119">
+      <c r="D22" s="79" t="s">
+        <v>365</v>
+      </c>
+      <c r="E22" s="79" t="s">
+        <v>544</v>
+      </c>
+      <c r="F22" s="127">
         <v>23.0</v>
       </c>
-      <c r="G22" s="120" t="s">
-        <v>525</v>
+      <c r="G22" s="128" t="s">
+        <v>528</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
@@ -3610,26 +3652,26 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="76">
+      <c r="A23" s="80">
         <v>16.0</v>
       </c>
-      <c r="B23" s="121" t="s">
+      <c r="B23" s="129" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="120" t="s">
+      <c r="C23" s="128" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="75" t="s">
-        <v>540</v>
-      </c>
-      <c r="E23" s="75" t="s">
-        <v>516</v>
-      </c>
-      <c r="F23" s="119">
+      <c r="D23" s="87" t="s">
+        <v>545</v>
+      </c>
+      <c r="E23" s="87" t="s">
+        <v>546</v>
+      </c>
+      <c r="F23" s="127">
         <v>22.0</v>
       </c>
-      <c r="G23" s="120" t="s">
-        <v>525</v>
+      <c r="G23" s="128" t="s">
+        <v>528</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
@@ -3646,26 +3688,26 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="122">
+      <c r="A24" s="130">
         <v>17.0</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="131" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="124" t="s">
+      <c r="C24" s="132" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="83" t="s">
-        <v>541</v>
-      </c>
-      <c r="E24" s="83" t="s">
+      <c r="D24" s="88" t="s">
+        <v>547</v>
+      </c>
+      <c r="E24" s="88" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="119">
+      <c r="F24" s="127">
         <v>30.0</v>
       </c>
-      <c r="G24" s="120" t="s">
-        <v>517</v>
+      <c r="G24" s="128" t="s">
+        <v>521</v>
       </c>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
@@ -3682,26 +3724,26 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="74">
+      <c r="A25" s="78">
         <v>18.0</v>
       </c>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="120" t="s">
+      <c r="C25" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="75" t="s">
-        <v>357</v>
-      </c>
-      <c r="E25" s="75" t="s">
-        <v>542</v>
-      </c>
-      <c r="F25" s="119">
+      <c r="D25" s="79" t="s">
+        <v>360</v>
+      </c>
+      <c r="E25" s="79" t="s">
+        <v>548</v>
+      </c>
+      <c r="F25" s="127">
         <v>19.0</v>
       </c>
-      <c r="G25" s="120" t="s">
-        <v>525</v>
+      <c r="G25" s="128" t="s">
+        <v>528</v>
       </c>
       <c r="H25" s="28"/>
       <c r="I25" s="29"/>
@@ -3718,24 +3760,24 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="76">
+      <c r="A26" s="80">
         <v>19.0</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="120" t="s">
+      <c r="C26" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="75" t="s">
-        <v>543</v>
-      </c>
-      <c r="E26" s="75" t="s">
-        <v>544</v>
-      </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41" t="s">
-        <v>523</v>
+      <c r="D26" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="E26" s="79" t="s">
+        <v>550</v>
+      </c>
+      <c r="F26" s="42"/>
+      <c r="G26" s="43" t="s">
+        <v>526</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="32"/>
@@ -3752,24 +3794,24 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="125">
+      <c r="A27" s="133">
         <v>20.0</v>
       </c>
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="79" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="75" t="s">
-        <v>545</v>
-      </c>
-      <c r="E27" s="75" t="s">
-        <v>533</v>
+      <c r="D27" s="79" t="s">
+        <v>551</v>
+      </c>
+      <c r="E27" s="79" t="s">
+        <v>538</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="120" t="s">
-        <v>523</v>
+      <c r="G27" s="128" t="s">
+        <v>526</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -3786,62 +3828,62 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="122">
+      <c r="A28" s="130">
         <v>21.0</v>
       </c>
-      <c r="B28" s="123" t="s">
+      <c r="B28" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="124" t="s">
+      <c r="C28" s="132" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="83" t="s">
-        <v>546</v>
-      </c>
-      <c r="E28" s="83" t="s">
-        <v>547</v>
-      </c>
-      <c r="F28" s="102">
+      <c r="D28" s="88" t="s">
+        <v>552</v>
+      </c>
+      <c r="E28" s="88" t="s">
+        <v>553</v>
+      </c>
+      <c r="F28" s="109">
         <v>23.0</v>
       </c>
-      <c r="G28" s="103" t="s">
-        <v>523</v>
-      </c>
-      <c r="H28" s="66"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="67"/>
-      <c r="L28" s="67"/>
-      <c r="M28" s="67"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="67"/>
-      <c r="P28" s="67"/>
-      <c r="Q28" s="66">
+      <c r="G28" s="110" t="s">
+        <v>526</v>
+      </c>
+      <c r="H28" s="70"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="71"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="71"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="76">
+      <c r="A29" s="80">
         <v>22.0</v>
       </c>
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="79" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="75" t="s">
-        <v>548</v>
-      </c>
-      <c r="E29" s="75" t="s">
-        <v>549</v>
-      </c>
-      <c r="F29" s="40">
+      <c r="D29" s="79" t="s">
+        <v>554</v>
+      </c>
+      <c r="E29" s="79" t="s">
+        <v>555</v>
+      </c>
+      <c r="F29" s="42">
         <v>22.0</v>
       </c>
-      <c r="G29" s="41" t="s">
-        <v>523</v>
+      <c r="G29" s="43" t="s">
+        <v>526</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -3858,26 +3900,26 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="76">
+      <c r="A30" s="80">
         <v>23.0</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="120" t="s">
+      <c r="C30" s="128" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="75" t="s">
-        <v>550</v>
-      </c>
-      <c r="E30" s="75" t="s">
-        <v>551</v>
-      </c>
-      <c r="F30" s="119">
+      <c r="D30" s="87" t="s">
+        <v>556</v>
+      </c>
+      <c r="E30" s="87" t="s">
+        <v>557</v>
+      </c>
+      <c r="F30" s="127">
         <v>21.0</v>
       </c>
-      <c r="G30" s="120" t="s">
-        <v>552</v>
+      <c r="G30" s="128" t="s">
+        <v>558</v>
       </c>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
@@ -3894,26 +3936,26 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="80">
         <v>24.0</v>
       </c>
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="126" t="s">
-        <v>553</v>
-      </c>
-      <c r="E31" s="75" t="s">
-        <v>516</v>
-      </c>
-      <c r="F31" s="40">
+      <c r="D31" s="87" t="s">
+        <v>559</v>
+      </c>
+      <c r="E31" s="79" t="s">
+        <v>520</v>
+      </c>
+      <c r="F31" s="42">
         <v>30.0</v>
       </c>
-      <c r="G31" s="41" t="s">
-        <v>512</v>
+      <c r="G31" s="43" t="s">
+        <v>515</v>
       </c>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
@@ -3930,62 +3972,62 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="76">
+      <c r="A32" s="80">
         <v>25.0</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="120" t="s">
-        <v>76</v>
-      </c>
-      <c r="D32" s="75" t="s">
-        <v>554</v>
-      </c>
-      <c r="E32" s="75" t="s">
-        <v>555</v>
-      </c>
-      <c r="F32" s="127">
+      <c r="C32" s="134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="87" t="s">
+        <v>372</v>
+      </c>
+      <c r="E32" s="87" t="s">
+        <v>560</v>
+      </c>
+      <c r="F32" s="135">
         <v>23.0</v>
       </c>
-      <c r="G32" s="128" t="s">
-        <v>556</v>
-      </c>
-      <c r="H32" s="66"/>
-      <c r="I32" s="67"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="67"/>
-      <c r="L32" s="67"/>
-      <c r="M32" s="67"/>
-      <c r="N32" s="67"/>
-      <c r="O32" s="67"/>
-      <c r="P32" s="67"/>
-      <c r="Q32" s="66">
+      <c r="G32" s="136" t="s">
+        <v>561</v>
+      </c>
+      <c r="H32" s="70"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="125">
+      <c r="A33" s="133">
         <v>26.0</v>
       </c>
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="120" t="s">
+      <c r="C33" s="128" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="75" t="s">
-        <v>557</v>
-      </c>
-      <c r="E33" s="75" t="s">
-        <v>185</v>
-      </c>
-      <c r="F33" s="119">
+      <c r="D33" s="87" t="s">
+        <v>562</v>
+      </c>
+      <c r="E33" s="87" t="s">
+        <v>563</v>
+      </c>
+      <c r="F33" s="127">
         <v>22.0</v>
       </c>
-      <c r="G33" s="120" t="s">
-        <v>523</v>
+      <c r="G33" s="128" t="s">
+        <v>526</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -4651,10 +4693,10 @@
       <c r="C19" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="36" t="s">
         <v>104</v>
       </c>
       <c r="F19" s="26"/>
@@ -4725,10 +4767,10 @@
       <c r="C21" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="E21" s="38" t="s">
         <v>109</v>
       </c>
       <c r="F21" s="26"/>
@@ -4799,10 +4841,10 @@
       <c r="C23" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="36" t="s">
         <v>113</v>
       </c>
       <c r="F23" s="26"/>
@@ -4836,10 +4878,10 @@
       <c r="C24" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="36" t="s">
         <v>115</v>
       </c>
       <c r="F24" s="26"/>
@@ -4873,11 +4915,11 @@
       <c r="C25" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E25" s="26" t="s">
+      <c r="D25" s="36" t="s">
         <v>117</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>118</v>
       </c>
       <c r="F25" s="26"/>
       <c r="G25" s="26" t="s">
@@ -4911,14 +4953,14 @@
         <v>94</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F26" s="26"/>
       <c r="G26" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
@@ -4942,16 +4984,16 @@
         <v>20.0</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C27" s="26" t="s">
         <v>76</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F27" s="26"/>
       <c r="G27" s="26" t="s">
@@ -4984,11 +5026,11 @@
       <c r="C28" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="E28" s="34" t="s">
+      <c r="D28" s="39" t="s">
         <v>125</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>126</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="26" t="s">
@@ -5022,10 +5064,10 @@
         <v>86</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="26" t="s">
@@ -5059,10 +5101,10 @@
         <v>76</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F30" s="26"/>
       <c r="G30" s="26" t="s">
@@ -5096,10 +5138,10 @@
         <v>76</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F31" s="26"/>
       <c r="G31" s="26" t="s">
@@ -5133,10 +5175,10 @@
         <v>94</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F32" s="26"/>
       <c r="G32" s="26" t="s">
@@ -5170,10 +5212,10 @@
         <v>76</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F33" s="26"/>
       <c r="G33" s="26" t="s">
@@ -5254,7 +5296,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5277,7 +5319,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5289,7 +5331,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -5301,7 +5343,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -5313,7 +5355,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -5334,11 +5376,11 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
-        <v>141</v>
+      <c r="B7" s="40" t="s">
+        <v>142</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>52</v>
@@ -5387,33 +5429,33 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="22">
-        <v>1.0</v>
+      <c r="A8" s="30">
+        <v>16.0</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" s="23" t="s">
+      <c r="D8" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="28">
+      <c r="E8" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="31">
         <f t="shared" ref="Q8:Q33" si="1">SUM(H8:P8)</f>
         <v>0</v>
       </c>
@@ -5429,13 +5471,13 @@
         <v>76</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
+        <v>146</v>
+      </c>
+      <c r="F9" s="42"/>
+      <c r="G9" s="43"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -5460,14 +5502,14 @@
       <c r="C10" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="23" t="s">
+      <c r="D10" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
+      <c r="E10" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -5493,13 +5535,13 @@
         <v>76</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
+        <v>150</v>
+      </c>
+      <c r="F11" s="42"/>
+      <c r="G11" s="43"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -5525,13 +5567,13 @@
         <v>86</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
+        <v>152</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="G12" s="43"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -5557,13 +5599,13 @@
         <v>86</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41"/>
+        <v>154</v>
+      </c>
+      <c r="F13" s="42"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -5589,13 +5631,13 @@
         <v>86</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
+        <v>156</v>
+      </c>
+      <c r="F14" s="42"/>
+      <c r="G14" s="43"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -5621,13 +5663,13 @@
         <v>86</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
+        <v>158</v>
+      </c>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -5643,7 +5685,7 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="42">
+      <c r="A16" s="45">
         <v>9.0</v>
       </c>
       <c r="B16" s="23" t="s">
@@ -5652,14 +5694,14 @@
       <c r="C16" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="E16" s="43" t="s">
+      <c r="D16" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
+      <c r="E16" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
       <c r="H16" s="31"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
@@ -5684,14 +5726,14 @@
       <c r="C17" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="E17" s="23" t="s">
+      <c r="D17" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
+      <c r="E17" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -5717,13 +5759,13 @@
         <v>94</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
+        <v>148</v>
+      </c>
+      <c r="F18" s="42"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -5754,8 +5796,8 @@
       <c r="E19" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -5783,11 +5825,11 @@
       <c r="D20" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="E20" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41"/>
+      <c r="E20" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="F20" s="42"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -5813,13 +5855,13 @@
         <v>86</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41"/>
+        <v>158</v>
+      </c>
+      <c r="F21" s="42"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -5844,14 +5886,14 @@
       <c r="C22" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="48" t="s">
         <v>166</v>
       </c>
-      <c r="E22" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41"/>
+      <c r="E22" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -5867,33 +5909,33 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="30">
+      <c r="A23" s="49">
         <v>16.0</v>
       </c>
       <c r="B23" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-      <c r="P23" s="32"/>
-      <c r="Q23" s="31">
+      <c r="F23" s="42"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5914,8 +5956,8 @@
       <c r="E24" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -5946,8 +5988,8 @@
       <c r="E25" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -5978,8 +6020,8 @@
       <c r="E26" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="43"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -5995,7 +6037,7 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="48">
+      <c r="A27" s="49">
         <v>20.0</v>
       </c>
       <c r="B27" s="23" t="s">
@@ -6010,8 +6052,8 @@
       <c r="E27" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43"/>
       <c r="H27" s="28"/>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
@@ -6040,10 +6082,10 @@
         <v>177</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
+        <v>156</v>
+      </c>
+      <c r="F28" s="42"/>
+      <c r="G28" s="43"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -6068,14 +6110,14 @@
       <c r="C29" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="E29" s="23" t="s">
+      <c r="D29" s="44" t="s">
         <v>178</v>
       </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41"/>
+      <c r="E29" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -6101,13 +6143,13 @@
         <v>76</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41"/>
+        <v>154</v>
+      </c>
+      <c r="F30" s="42"/>
+      <c r="G30" s="43"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -6132,14 +6174,14 @@
       <c r="C31" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" s="43" t="s">
+      <c r="D31" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
+      <c r="E31" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" s="42"/>
+      <c r="G31" s="43"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -6164,14 +6206,14 @@
       <c r="C32" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="E32" s="23" t="s">
+      <c r="D32" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41"/>
+      <c r="E32" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32" s="42"/>
+      <c r="G32" s="43"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -6193,17 +6235,17 @@
       <c r="B33" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="47" t="s">
+      <c r="D33" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="E33" s="47" t="s">
+      <c r="E33" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="43"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -6366,13 +6408,13 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="52" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="20" t="s">
@@ -6419,23 +6461,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="50">
+      <c r="A8" s="53">
         <v>1.0</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="56" t="s">
         <v>191</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="56" t="s">
         <v>192</v>
       </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="55" t="s">
+      <c r="F8" s="57"/>
+      <c r="G8" s="58" t="s">
         <v>193</v>
       </c>
       <c r="H8" s="28"/>
@@ -6453,23 +6495,23 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="56">
+      <c r="A9" s="59">
         <v>2.0</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="60" t="s">
         <v>194</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="60" t="s">
         <v>195</v>
       </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58" t="s">
+      <c r="F9" s="61"/>
+      <c r="G9" s="61" t="s">
         <v>186</v>
       </c>
       <c r="H9" s="28"/>
@@ -6487,23 +6529,23 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="56">
+      <c r="A10" s="59">
         <v>3.0</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="57" t="s">
+      <c r="D10" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="60" t="s">
         <v>197</v>
       </c>
-      <c r="F10" s="54"/>
-      <c r="G10" s="55" t="s">
+      <c r="F10" s="57"/>
+      <c r="G10" s="58" t="s">
         <v>186</v>
       </c>
       <c r="H10" s="28"/>
@@ -6521,23 +6563,23 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="50">
+      <c r="A11" s="53">
         <v>4.0</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="62" t="s">
         <v>198</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="E11" s="62" t="s">
         <v>199</v>
       </c>
-      <c r="F11" s="59"/>
-      <c r="G11" s="58" t="s">
+      <c r="F11" s="63"/>
+      <c r="G11" s="61" t="s">
         <v>186</v>
       </c>
       <c r="H11" s="31"/>
@@ -6555,23 +6597,23 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="50">
+      <c r="A12" s="53">
         <v>5.0</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="53" t="s">
+      <c r="D12" s="56" t="s">
         <v>200</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="56" t="s">
         <v>201</v>
       </c>
-      <c r="F12" s="54"/>
-      <c r="G12" s="55" t="s">
+      <c r="F12" s="57"/>
+      <c r="G12" s="58" t="s">
         <v>186</v>
       </c>
       <c r="H12" s="28"/>
@@ -6589,24 +6631,24 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="50">
+      <c r="A13" s="53">
         <v>6.0</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="53" t="s">
+      <c r="D13" s="56" t="s">
         <v>202</v>
       </c>
-      <c r="E13" s="53" t="s">
+      <c r="E13" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="58" t="s">
-        <v>120</v>
+      <c r="F13" s="63"/>
+      <c r="G13" s="61" t="s">
+        <v>121</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
@@ -6623,23 +6665,23 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="56">
+      <c r="A14" s="59">
         <v>7.0</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="57" t="s">
+      <c r="D14" s="60" t="s">
         <v>204</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="E14" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="58" t="s">
+      <c r="F14" s="63"/>
+      <c r="G14" s="61" t="s">
         <v>186</v>
       </c>
       <c r="H14" s="31"/>
@@ -6657,23 +6699,23 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="50">
+      <c r="A15" s="53">
         <v>8.0</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="53" t="s">
+      <c r="D15" s="56" t="s">
         <v>206</v>
       </c>
-      <c r="E15" s="53" t="s">
+      <c r="E15" s="56" t="s">
         <v>207</v>
       </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="58" t="s">
+      <c r="F15" s="63"/>
+      <c r="G15" s="61" t="s">
         <v>186</v>
       </c>
       <c r="H15" s="31"/>
@@ -6691,23 +6733,23 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="50">
+      <c r="A16" s="53">
         <v>9.0</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="E16" s="53" t="s">
+      <c r="E16" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="F16" s="60"/>
-      <c r="G16" s="61" t="s">
+      <c r="F16" s="64"/>
+      <c r="G16" s="65" t="s">
         <v>186</v>
       </c>
       <c r="H16" s="31"/>
@@ -6725,23 +6767,23 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="50">
+      <c r="A17" s="53">
         <v>10.0</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="C17" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="D17" s="56" t="s">
         <v>210</v>
       </c>
-      <c r="E17" s="53" t="s">
+      <c r="E17" s="56" t="s">
         <v>211</v>
       </c>
-      <c r="F17" s="54"/>
-      <c r="G17" s="55" t="s">
+      <c r="F17" s="57"/>
+      <c r="G17" s="58" t="s">
         <v>186</v>
       </c>
       <c r="H17" s="28"/>
@@ -6759,23 +6801,23 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="62">
+      <c r="A18" s="66">
         <v>11.0</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="52" t="s">
+      <c r="C18" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="57" t="s">
+      <c r="D18" s="60" t="s">
         <v>212</v>
       </c>
-      <c r="E18" s="57" t="s">
+      <c r="E18" s="60" t="s">
         <v>213</v>
       </c>
-      <c r="F18" s="54"/>
-      <c r="G18" s="55" t="s">
+      <c r="F18" s="57"/>
+      <c r="G18" s="58" t="s">
         <v>186</v>
       </c>
       <c r="H18" s="28"/>
@@ -6793,23 +6835,23 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="50">
+      <c r="A19" s="53">
         <v>12.0</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="D19" s="56" t="s">
         <v>214</v>
       </c>
-      <c r="E19" s="53" t="s">
+      <c r="E19" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="F19" s="54"/>
-      <c r="G19" s="55" t="s">
+      <c r="F19" s="57"/>
+      <c r="G19" s="58" t="s">
         <v>186</v>
       </c>
       <c r="H19" s="28"/>
@@ -6827,23 +6869,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="63">
+      <c r="A20" s="67">
         <v>13.0</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C20" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="56" t="s">
         <v>216</v>
       </c>
-      <c r="E20" s="53" t="s">
+      <c r="E20" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="F20" s="54"/>
-      <c r="G20" s="55" t="s">
+      <c r="F20" s="57"/>
+      <c r="G20" s="58" t="s">
         <v>186</v>
       </c>
       <c r="H20" s="28"/>
@@ -6861,57 +6903,57 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="62">
+      <c r="A21" s="66">
         <v>14.0</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="57" t="s">
+      <c r="D21" s="60" t="s">
         <v>218</v>
       </c>
-      <c r="E21" s="57" t="s">
+      <c r="E21" s="60" t="s">
         <v>219</v>
       </c>
-      <c r="F21" s="64"/>
-      <c r="G21" s="65" t="s">
+      <c r="F21" s="68"/>
+      <c r="G21" s="69" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="66"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="67"/>
-      <c r="M21" s="67"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="67"/>
-      <c r="Q21" s="66">
+      <c r="H21" s="70"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="56">
+      <c r="A22" s="59">
         <v>15.0</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="57" t="s">
+      <c r="D22" s="60" t="s">
         <v>220</v>
       </c>
-      <c r="E22" s="57" t="s">
+      <c r="E22" s="60" t="s">
         <v>221</v>
       </c>
-      <c r="F22" s="59"/>
-      <c r="G22" s="58" t="s">
+      <c r="F22" s="63"/>
+      <c r="G22" s="61" t="s">
         <v>186</v>
       </c>
       <c r="H22" s="31"/>
@@ -6929,23 +6971,23 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="50">
+      <c r="A23" s="53">
         <v>16.0</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="56" t="s">
         <v>222</v>
       </c>
-      <c r="E23" s="53" t="s">
+      <c r="E23" s="56" t="s">
         <v>223</v>
       </c>
-      <c r="F23" s="59"/>
-      <c r="G23" s="58" t="s">
+      <c r="F23" s="63"/>
+      <c r="G23" s="61" t="s">
         <v>186</v>
       </c>
       <c r="H23" s="31"/>
@@ -6963,23 +7005,23 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="62">
+      <c r="A24" s="66">
         <v>17.0</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="52" t="s">
+      <c r="C24" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="68" t="s">
+      <c r="D24" s="72" t="s">
         <v>224</v>
       </c>
-      <c r="E24" s="68" t="s">
+      <c r="E24" s="72" t="s">
         <v>225</v>
       </c>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55" t="s">
+      <c r="F24" s="57"/>
+      <c r="G24" s="58" t="s">
         <v>186</v>
       </c>
       <c r="H24" s="31"/>
@@ -6997,23 +7039,23 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="63">
+      <c r="A25" s="67">
         <v>18.0</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="53" t="s">
+      <c r="D25" s="62" t="s">
         <v>226</v>
       </c>
-      <c r="E25" s="53" t="s">
+      <c r="E25" s="62" t="s">
         <v>227</v>
       </c>
-      <c r="F25" s="59"/>
-      <c r="G25" s="58" t="s">
+      <c r="F25" s="63"/>
+      <c r="G25" s="61" t="s">
         <v>186</v>
       </c>
       <c r="H25" s="28"/>
@@ -7031,23 +7073,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="63">
+      <c r="A26" s="67">
         <v>19.0</v>
       </c>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="69" t="s">
+      <c r="C26" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="68" t="s">
+      <c r="D26" s="72" t="s">
         <v>228</v>
       </c>
-      <c r="E26" s="68" t="s">
+      <c r="E26" s="72" t="s">
         <v>229</v>
       </c>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55" t="s">
+      <c r="F26" s="58"/>
+      <c r="G26" s="58" t="s">
         <v>230</v>
       </c>
       <c r="H26" s="31"/>
@@ -7065,23 +7107,23 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="50">
+      <c r="A27" s="53">
         <v>20.0</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="52" t="s">
+      <c r="C27" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="53" t="s">
+      <c r="D27" s="62" t="s">
         <v>231</v>
       </c>
-      <c r="E27" s="53" t="s">
+      <c r="E27" s="62" t="s">
         <v>232</v>
       </c>
-      <c r="F27" s="54"/>
-      <c r="G27" s="55" t="s">
+      <c r="F27" s="57"/>
+      <c r="G27" s="58" t="s">
         <v>186</v>
       </c>
       <c r="H27" s="28"/>
@@ -7099,23 +7141,23 @@
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
-      <c r="A28" s="56">
+      <c r="A28" s="59">
         <v>21.0</v>
       </c>
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="57" t="s">
+      <c r="D28" s="60" t="s">
         <v>233</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="60" t="s">
         <v>234</v>
       </c>
-      <c r="F28" s="70"/>
-      <c r="G28" s="61"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="65"/>
       <c r="H28" s="31"/>
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
@@ -7128,23 +7170,23 @@
       <c r="Q28" s="31"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="63">
+      <c r="A29" s="67">
         <v>22.0</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="53" t="s">
+      <c r="D29" s="56" t="s">
         <v>235</v>
       </c>
-      <c r="E29" s="53" t="s">
+      <c r="E29" s="56" t="s">
         <v>236</v>
       </c>
-      <c r="F29" s="70"/>
-      <c r="G29" s="61" t="s">
+      <c r="F29" s="74"/>
+      <c r="G29" s="65" t="s">
         <v>237</v>
       </c>
       <c r="H29" s="28"/>
@@ -7162,23 +7204,23 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="62">
+      <c r="A30" s="66">
         <v>23.0</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="52" t="s">
+      <c r="C30" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="60" t="s">
         <v>238</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="60" t="s">
         <v>239</v>
       </c>
-      <c r="F30" s="70"/>
-      <c r="G30" s="61"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="65"/>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
@@ -7194,23 +7236,23 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="63">
+      <c r="A31" s="67">
         <v>24.0</v>
       </c>
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="D31" s="62" t="s">
         <v>240</v>
       </c>
-      <c r="E31" s="53" t="s">
+      <c r="E31" s="62" t="s">
         <v>241</v>
       </c>
-      <c r="F31" s="70"/>
-      <c r="G31" s="61"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="65"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
       <c r="J31" s="29"/>
@@ -7226,23 +7268,23 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="63">
+      <c r="A32" s="67">
         <v>25.0</v>
       </c>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="D32" s="56" t="s">
         <v>242</v>
       </c>
-      <c r="E32" s="53" t="s">
+      <c r="E32" s="56" t="s">
         <v>243</v>
       </c>
-      <c r="F32" s="70"/>
-      <c r="G32" s="61"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="65"/>
       <c r="H32" s="31"/>
       <c r="I32" s="32"/>
       <c r="J32" s="32"/>
@@ -7258,23 +7300,23 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="50">
+      <c r="A33" s="53">
         <v>26.0</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="52" t="s">
+      <c r="C33" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="71" t="s">
+      <c r="D33" s="75" t="s">
         <v>244</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" s="56" t="s">
         <v>245</v>
       </c>
-      <c r="F33" s="59"/>
-      <c r="G33" s="58" t="s">
+      <c r="F33" s="63"/>
+      <c r="G33" s="61" t="s">
         <v>186</v>
       </c>
       <c r="H33" s="31"/>
@@ -7292,13 +7334,13 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="63"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="73"/>
+      <c r="A34" s="67"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="77"/>
       <c r="H34" s="31"/>
       <c r="I34" s="32"/>
       <c r="J34" s="32"/>
@@ -7448,10 +7490,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="40" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -7501,23 +7543,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="74">
+      <c r="A8" s="78">
         <v>1.0</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="79" t="s">
         <v>246</v>
       </c>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="79" t="s">
         <v>247</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -7533,21 +7575,21 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="76">
+      <c r="A9" s="80">
         <v>2.0</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="75" t="s">
+      <c r="C9" s="43"/>
+      <c r="D9" s="79" t="s">
         <v>248</v>
       </c>
-      <c r="E9" s="75" t="s">
+      <c r="E9" s="79" t="s">
         <v>249</v>
       </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="43"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -7563,21 +7605,21 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="74">
+      <c r="A10" s="78">
         <v>3.0</v>
       </c>
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="75" t="s">
+      <c r="C10" s="43"/>
+      <c r="D10" s="79" t="s">
         <v>250</v>
       </c>
-      <c r="E10" s="75" t="s">
+      <c r="E10" s="79" t="s">
         <v>251</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -7593,21 +7635,21 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="76">
+      <c r="A11" s="80">
         <v>4.0</v>
       </c>
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="75" t="s">
+      <c r="C11" s="43"/>
+      <c r="D11" s="79" t="s">
         <v>252</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="79" t="s">
         <v>253</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="43"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -7623,21 +7665,21 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="74">
+      <c r="A12" s="78">
         <v>5.0</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="75" t="s">
+      <c r="C12" s="43"/>
+      <c r="D12" s="79" t="s">
         <v>254</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="79" t="s">
         <v>255</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="43"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -7653,21 +7695,21 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="76">
+      <c r="A13" s="80">
         <v>6.0</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="75" t="s">
+      <c r="C13" s="43"/>
+      <c r="D13" s="79" t="s">
         <v>256</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="79" t="s">
         <v>257</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -7683,21 +7725,21 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="74">
+      <c r="A14" s="78">
         <v>7.0</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="75" t="s">
+      <c r="C14" s="43"/>
+      <c r="D14" s="79" t="s">
         <v>258</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="79" t="s">
         <v>259</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="43"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -7713,21 +7755,21 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="76">
+      <c r="A15" s="80">
         <v>8.0</v>
       </c>
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="75" t="s">
+      <c r="C15" s="43"/>
+      <c r="D15" s="79" t="s">
         <v>260</v>
       </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="79" t="s">
         <v>261</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -7743,21 +7785,21 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="74">
+      <c r="A16" s="78">
         <v>9.0</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="75" t="s">
+      <c r="C16" s="43"/>
+      <c r="D16" s="79" t="s">
         <v>262</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="79" t="s">
         <v>255</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
       <c r="J16" s="29"/>
@@ -7773,21 +7815,21 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="76">
+      <c r="A17" s="80">
         <v>10.0</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="75" t="s">
+      <c r="C17" s="43"/>
+      <c r="D17" s="79" t="s">
         <v>263</v>
       </c>
-      <c r="E17" s="75" t="s">
+      <c r="E17" s="79" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -7803,21 +7845,21 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="74">
+      <c r="A18" s="78">
         <v>11.0</v>
       </c>
-      <c r="B18" s="75" t="s">
+      <c r="B18" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="75" t="s">
+      <c r="C18" s="43"/>
+      <c r="D18" s="79" t="s">
         <v>265</v>
       </c>
-      <c r="E18" s="75" t="s">
+      <c r="E18" s="79" t="s">
         <v>257</v>
       </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -7833,21 +7875,21 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="76">
+      <c r="A19" s="80">
         <v>12.0</v>
       </c>
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="75" t="s">
+      <c r="C19" s="43"/>
+      <c r="D19" s="79" t="s">
         <v>266</v>
       </c>
-      <c r="E19" s="75" t="s">
+      <c r="E19" s="79" t="s">
         <v>267</v>
       </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -7863,21 +7905,21 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="74">
+      <c r="A20" s="78">
         <v>13.0</v>
       </c>
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="75" t="s">
+      <c r="C20" s="43"/>
+      <c r="D20" s="79" t="s">
         <v>268</v>
       </c>
-      <c r="E20" s="77" t="s">
+      <c r="E20" s="81" t="s">
         <v>269</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -7893,21 +7935,21 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="76">
+      <c r="A21" s="80">
         <v>14.0</v>
       </c>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="75" t="s">
+      <c r="C21" s="43"/>
+      <c r="D21" s="79" t="s">
         <v>270</v>
       </c>
-      <c r="E21" s="75" t="s">
+      <c r="E21" s="79" t="s">
         <v>271</v>
       </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -7923,21 +7965,21 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="74">
+      <c r="A22" s="78">
         <v>15.0</v>
       </c>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="75" t="s">
+      <c r="C22" s="43"/>
+      <c r="D22" s="79" t="s">
         <v>272</v>
       </c>
-      <c r="E22" s="75" t="s">
+      <c r="E22" s="79" t="s">
         <v>273</v>
       </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -7953,21 +7995,21 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="76">
+      <c r="A23" s="80">
         <v>16.0</v>
       </c>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="78" t="s">
+      <c r="C23" s="43"/>
+      <c r="D23" s="82" t="s">
         <v>274</v>
       </c>
-      <c r="E23" s="78" t="s">
+      <c r="E23" s="82" t="s">
         <v>275</v>
       </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="43"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -7983,21 +8025,21 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="74">
+      <c r="A24" s="78">
         <v>17.0</v>
       </c>
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="78" t="s">
+      <c r="C24" s="43"/>
+      <c r="D24" s="82" t="s">
         <v>276</v>
       </c>
-      <c r="E24" s="78" t="s">
+      <c r="E24" s="82" t="s">
         <v>277</v>
       </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -8013,21 +8055,21 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="76">
+      <c r="A25" s="80">
         <v>18.0</v>
       </c>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="75" t="s">
+      <c r="C25" s="43"/>
+      <c r="D25" s="79" t="s">
         <v>278</v>
       </c>
-      <c r="E25" s="75" t="s">
+      <c r="E25" s="79" t="s">
         <v>279</v>
       </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -8043,21 +8085,21 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="74">
+      <c r="A26" s="78">
         <v>19.0</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="78" t="s">
+      <c r="C26" s="43"/>
+      <c r="D26" s="82" t="s">
         <v>280</v>
       </c>
-      <c r="E26" s="78" t="s">
+      <c r="E26" s="82" t="s">
         <v>281</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="43"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -8073,21 +8115,21 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="76">
+      <c r="A27" s="80">
         <v>20.0</v>
       </c>
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="75" t="s">
+      <c r="C27" s="43"/>
+      <c r="D27" s="79" t="s">
         <v>282</v>
       </c>
-      <c r="E27" s="75" t="s">
+      <c r="E27" s="79" t="s">
         <v>283</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43"/>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
@@ -8103,21 +8145,21 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="74">
+      <c r="A28" s="78">
         <v>21.0</v>
       </c>
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="75" t="s">
+      <c r="C28" s="43"/>
+      <c r="D28" s="79" t="s">
         <v>284</v>
       </c>
-      <c r="E28" s="75" t="s">
+      <c r="E28" s="79" t="s">
         <v>285</v>
       </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="43"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -8133,21 +8175,21 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="76">
+      <c r="A29" s="80">
         <v>22.0</v>
       </c>
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="75" t="s">
+      <c r="C29" s="43"/>
+      <c r="D29" s="79" t="s">
         <v>286</v>
       </c>
-      <c r="E29" s="75" t="s">
+      <c r="E29" s="79" t="s">
         <v>287</v>
       </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -8163,21 +8205,21 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="74">
+      <c r="A30" s="78">
         <v>23.0</v>
       </c>
-      <c r="B30" s="75" t="s">
+      <c r="B30" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="41"/>
-      <c r="D30" s="75" t="s">
+      <c r="C30" s="43"/>
+      <c r="D30" s="79" t="s">
         <v>272</v>
       </c>
-      <c r="E30" s="75" t="s">
+      <c r="E30" s="79" t="s">
         <v>288</v>
       </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="43"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -8193,21 +8235,21 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="80">
         <v>24.0</v>
       </c>
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="75" t="s">
+      <c r="C31" s="43"/>
+      <c r="D31" s="79" t="s">
         <v>289</v>
       </c>
-      <c r="E31" s="77" t="s">
+      <c r="E31" s="81" t="s">
         <v>290</v>
       </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="43"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -8223,21 +8265,21 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="74">
+      <c r="A32" s="78">
         <v>25.0</v>
       </c>
-      <c r="B32" s="75" t="s">
+      <c r="B32" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="75" t="s">
+      <c r="C32" s="43"/>
+      <c r="D32" s="79" t="s">
         <v>291</v>
       </c>
-      <c r="E32" s="75" t="s">
+      <c r="E32" s="79" t="s">
         <v>292</v>
       </c>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="43"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -8253,21 +8295,21 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="80">
         <v>26.0</v>
       </c>
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="75" t="s">
+      <c r="C33" s="43"/>
+      <c r="D33" s="79" t="s">
         <v>262</v>
       </c>
-      <c r="E33" s="75" t="s">
+      <c r="E33" s="79" t="s">
         <v>293</v>
       </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="43"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -8384,7 +8426,7 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="83" t="s">
         <v>296</v>
       </c>
       <c r="F3" s="5"/>
@@ -8430,10 +8472,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="40" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -8483,25 +8525,25 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="74">
+      <c r="A8" s="78">
         <v>1.0</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="79" t="s">
         <v>299</v>
       </c>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="79" t="s">
         <v>300</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="42">
         <v>37.0</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H8" s="28"/>
@@ -8519,25 +8561,25 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="76">
+      <c r="A9" s="80">
         <v>2.0</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="80" t="s">
+      <c r="D9" s="84" t="s">
         <v>301</v>
       </c>
-      <c r="E9" s="81" t="s">
+      <c r="E9" s="85" t="s">
         <v>302</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="42">
         <v>32.0</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H9" s="31"/>
@@ -8555,25 +8597,25 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="74">
+      <c r="A10" s="78">
         <v>3.0</v>
       </c>
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="75" t="s">
+      <c r="D10" s="79" t="s">
         <v>303</v>
       </c>
-      <c r="E10" s="75" t="s">
+      <c r="E10" s="79" t="s">
         <v>304</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="42">
         <v>25.0</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H10" s="28"/>
@@ -8591,25 +8633,25 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="74">
+      <c r="A11" s="78">
         <v>4.0</v>
       </c>
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="75" t="s">
+      <c r="D11" s="79" t="s">
         <v>305</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="79" t="s">
         <v>306</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="42">
         <v>29.0</v>
       </c>
-      <c r="G11" s="41" t="s">
+      <c r="G11" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H11" s="28"/>
@@ -8627,25 +8669,25 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="76">
+      <c r="A12" s="80">
         <v>5.0</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="75" t="s">
+      <c r="D12" s="79" t="s">
         <v>307</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="79" t="s">
         <v>308</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="42">
         <v>27.0</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="43" t="s">
         <v>309</v>
       </c>
       <c r="H12" s="31"/>
@@ -8663,23 +8705,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="76">
+      <c r="A13" s="80">
         <v>6.0</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="82" t="s">
+      <c r="D13" s="86" t="s">
         <v>310</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="87" t="s">
         <v>311</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41" t="s">
+      <c r="F13" s="42"/>
+      <c r="G13" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H13" s="31"/>
@@ -8697,25 +8739,25 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="74">
+      <c r="A14" s="78">
         <v>7.0</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="83" t="s">
+      <c r="D14" s="88" t="s">
         <v>312</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="88" t="s">
         <v>313</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="42">
         <v>23.0</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="G14" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H14" s="28"/>
@@ -8733,25 +8775,25 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="76">
+      <c r="A15" s="80">
         <v>8.0</v>
       </c>
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="87" t="s">
         <v>314</v>
       </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="87" t="s">
         <v>315</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="42">
         <v>28.0</v>
       </c>
-      <c r="G15" s="41" t="s">
+      <c r="G15" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H15" s="31"/>
@@ -8769,25 +8811,25 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="74">
+      <c r="A16" s="78">
         <v>9.0</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="75" t="s">
+      <c r="D16" s="79" t="s">
         <v>316</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="79" t="s">
         <v>317</v>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="42">
         <v>40.0</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H16" s="28"/>
@@ -8805,25 +8847,25 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="74">
+      <c r="A17" s="78">
         <v>10.0</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="75" t="s">
+      <c r="D17" s="79" t="s">
         <v>318</v>
       </c>
-      <c r="E17" s="75" t="s">
+      <c r="E17" s="79" t="s">
         <v>319</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="42">
         <v>37.0</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H17" s="28"/>
@@ -8841,25 +8883,25 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="76">
+      <c r="A18" s="80">
         <v>11.0</v>
       </c>
-      <c r="B18" s="75" t="s">
+      <c r="B18" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="75" t="s">
+      <c r="D18" s="79" t="s">
         <v>320</v>
       </c>
-      <c r="E18" s="75" t="s">
+      <c r="E18" s="79" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="42">
         <v>32.0</v>
       </c>
-      <c r="G18" s="41" t="s">
+      <c r="G18" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H18" s="31"/>
@@ -8877,25 +8919,25 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="76">
+      <c r="A19" s="80">
         <v>12.0</v>
       </c>
-      <c r="B19" s="75" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="41" t="s">
+      <c r="B19" s="79" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="82" t="s">
+      <c r="D19" s="89" t="s">
         <v>322</v>
       </c>
-      <c r="E19" s="75" t="s">
+      <c r="E19" s="79" t="s">
         <v>323</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="42">
         <v>20.0</v>
       </c>
-      <c r="G19" s="41" t="s">
+      <c r="G19" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H19" s="31"/>
@@ -8913,23 +8955,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="74">
+      <c r="A20" s="78">
         <v>13.0</v>
       </c>
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="83" t="s">
+      <c r="D20" s="88" t="s">
         <v>324</v>
       </c>
-      <c r="E20" s="83" t="s">
+      <c r="E20" s="88" t="s">
         <v>325</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41" t="s">
+      <c r="F20" s="42"/>
+      <c r="G20" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H20" s="28"/>
@@ -8947,25 +8989,25 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="76">
+      <c r="A21" s="80">
         <v>14.0</v>
       </c>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="75" t="s">
+      <c r="D21" s="79" t="s">
         <v>326</v>
       </c>
-      <c r="E21" s="75" t="s">
+      <c r="E21" s="79" t="s">
         <v>327</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="42">
         <v>33.0</v>
       </c>
-      <c r="G21" s="41" t="s">
+      <c r="G21" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H21" s="31"/>
@@ -8983,25 +9025,25 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="74">
+      <c r="A22" s="78">
         <v>15.0</v>
       </c>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="78" t="s">
+      <c r="D22" s="82" t="s">
         <v>328</v>
       </c>
-      <c r="E22" s="78" t="s">
+      <c r="E22" s="82" t="s">
         <v>329</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="42">
         <v>33.0</v>
       </c>
-      <c r="G22" s="41" t="s">
+      <c r="G22" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H22" s="28"/>
@@ -9019,25 +9061,25 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="76">
+      <c r="A23" s="80">
         <v>16.0</v>
       </c>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="78" t="s">
+      <c r="D23" s="82" t="s">
         <v>330</v>
       </c>
-      <c r="E23" s="78" t="s">
+      <c r="E23" s="82" t="s">
         <v>329</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="42">
         <v>41.0</v>
       </c>
-      <c r="G23" s="41" t="s">
+      <c r="G23" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H23" s="31"/>
@@ -9055,25 +9097,25 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="74">
+      <c r="A24" s="78">
         <v>17.0</v>
       </c>
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="82" t="s">
+      <c r="D24" s="86" t="s">
         <v>331</v>
       </c>
-      <c r="E24" s="75" t="s">
+      <c r="E24" s="87" t="s">
         <v>332</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="42">
         <v>20.0</v>
       </c>
-      <c r="G24" s="41" t="s">
+      <c r="G24" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H24" s="28"/>
@@ -9091,25 +9133,25 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="76">
+      <c r="A25" s="80">
         <v>18.0</v>
       </c>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="78" t="s">
+      <c r="D25" s="82" t="s">
         <v>333</v>
       </c>
-      <c r="E25" s="78" t="s">
+      <c r="E25" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="42">
         <v>34.0</v>
       </c>
-      <c r="G25" s="41" t="s">
+      <c r="G25" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H25" s="31"/>
@@ -9127,23 +9169,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="74">
+      <c r="A26" s="78">
         <v>19.0</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="82" t="s">
+      <c r="D26" s="89" t="s">
         <v>334</v>
       </c>
-      <c r="E26" s="75" t="s">
+      <c r="E26" s="79" t="s">
         <v>335</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41" t="s">
+      <c r="F26" s="42"/>
+      <c r="G26" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H26" s="28"/>
@@ -9161,25 +9203,25 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="76">
+      <c r="A27" s="80">
         <v>20.0</v>
       </c>
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="82" t="s">
+      <c r="D27" s="86" t="s">
         <v>336</v>
       </c>
-      <c r="E27" s="75" t="s">
-        <v>87</v>
-      </c>
-      <c r="F27" s="40">
+      <c r="E27" s="87" t="s">
+        <v>337</v>
+      </c>
+      <c r="F27" s="42">
         <v>27.0</v>
       </c>
-      <c r="G27" s="41" t="s">
+      <c r="G27" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H27" s="31"/>
@@ -9197,25 +9239,25 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="76">
+      <c r="A28" s="80">
         <v>21.0</v>
       </c>
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="75" t="s">
-        <v>337</v>
-      </c>
-      <c r="E28" s="75" t="s">
+      <c r="D28" s="79" t="s">
         <v>338</v>
       </c>
-      <c r="F28" s="40">
+      <c r="E28" s="79" t="s">
+        <v>339</v>
+      </c>
+      <c r="F28" s="42">
         <v>32.0</v>
       </c>
-      <c r="G28" s="41" t="s">
+      <c r="G28" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H28" s="31"/>
@@ -9233,25 +9275,25 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="76">
+      <c r="A29" s="80">
         <v>22.0</v>
       </c>
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="78" t="s">
-        <v>339</v>
-      </c>
-      <c r="E29" s="78" t="s">
+      <c r="D29" s="82" t="s">
         <v>340</v>
       </c>
-      <c r="F29" s="40">
+      <c r="E29" s="82" t="s">
+        <v>341</v>
+      </c>
+      <c r="F29" s="42">
         <v>28.0</v>
       </c>
-      <c r="G29" s="41" t="s">
+      <c r="G29" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H29" s="31"/>
@@ -9269,25 +9311,25 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="74">
+      <c r="A30" s="78">
         <v>23.0</v>
       </c>
-      <c r="B30" s="75" t="s">
+      <c r="B30" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="84" t="s">
-        <v>341</v>
-      </c>
-      <c r="E30" s="84" t="s">
+      <c r="D30" s="90" t="s">
         <v>342</v>
       </c>
-      <c r="F30" s="40">
+      <c r="E30" s="90" t="s">
+        <v>343</v>
+      </c>
+      <c r="F30" s="42">
         <v>41.0</v>
       </c>
-      <c r="G30" s="41" t="s">
+      <c r="G30" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H30" s="28"/>
@@ -9305,21 +9347,25 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="74">
+      <c r="A31" s="78">
         <v>24.0</v>
       </c>
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="D31" s="82"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="40">
+      <c r="C31" s="91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="86" t="s">
+        <v>344</v>
+      </c>
+      <c r="E31" s="87" t="s">
+        <v>345</v>
+      </c>
+      <c r="F31" s="42">
         <v>36.0</v>
       </c>
-      <c r="G31" s="41" t="s">
+      <c r="G31" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H31" s="28"/>
@@ -9337,25 +9383,25 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="74">
+      <c r="A32" s="78">
         <v>25.0</v>
       </c>
-      <c r="B32" s="75" t="s">
+      <c r="B32" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="41" t="s">
+      <c r="C32" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="75" t="s">
-        <v>343</v>
-      </c>
-      <c r="E32" s="75" t="s">
-        <v>344</v>
-      </c>
-      <c r="F32" s="40">
+      <c r="D32" s="79" t="s">
+        <v>346</v>
+      </c>
+      <c r="E32" s="79" t="s">
+        <v>347</v>
+      </c>
+      <c r="F32" s="42">
         <v>19.0</v>
       </c>
-      <c r="G32" s="41"/>
+      <c r="G32" s="43"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -9371,25 +9417,25 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="80">
         <v>26.0</v>
       </c>
-      <c r="B33" s="75" t="s">
-        <v>121</v>
-      </c>
-      <c r="C33" s="41" t="s">
+      <c r="B33" s="79" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="78" t="s">
-        <v>345</v>
-      </c>
-      <c r="E33" s="78" t="s">
-        <v>346</v>
-      </c>
-      <c r="F33" s="40">
+      <c r="D33" s="82" t="s">
+        <v>348</v>
+      </c>
+      <c r="E33" s="82" t="s">
+        <v>349</v>
+      </c>
+      <c r="F33" s="42">
         <v>19.0</v>
       </c>
-      <c r="G33" s="41"/>
+      <c r="G33" s="43"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -9469,12 +9515,12 @@
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="85" t="s">
+      <c r="F1" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="86"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88" t="s">
+      <c r="G1" s="93"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="95" t="s">
         <v>42</v>
       </c>
       <c r="J1" s="10"/>
@@ -9496,7 +9542,7 @@
       <c r="D2" s="5"/>
       <c r="E2" s="6"/>
       <c r="F2" s="11" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="6"/>
@@ -9510,7 +9556,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="6"/>
       <c r="F3" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="6"/>
@@ -9524,27 +9570,27 @@
       <c r="D4" s="5"/>
       <c r="E4" s="6"/>
       <c r="F4" s="11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="6"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="96" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="90" t="s">
-        <v>350</v>
-      </c>
-      <c r="G5" s="91"/>
-      <c r="H5" s="92"/>
+      <c r="F5" s="97" t="s">
+        <v>353</v>
+      </c>
+      <c r="G5" s="98"/>
+      <c r="H5" s="99"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="93"/>
+      <c r="A6" s="100"/>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -9554,14 +9600,14 @@
       <c r="H6" s="16"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
-        <v>351</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>352</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>353</v>
+      <c r="A7" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>356</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>52</v>
@@ -9610,26 +9656,26 @@
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1">
-      <c r="A8" s="94">
+      <c r="A8" s="101">
         <v>1.0</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="95" t="s">
+      <c r="D8" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="96" t="s">
-        <v>354</v>
-      </c>
-      <c r="F8" s="96" t="s">
-        <v>355</v>
-      </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="97" t="s">
+      <c r="E8" s="103" t="s">
+        <v>357</v>
+      </c>
+      <c r="F8" s="103" t="s">
+        <v>358</v>
+      </c>
+      <c r="G8" s="42"/>
+      <c r="H8" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I8" s="28"/>
@@ -9647,26 +9693,26 @@
       </c>
     </row>
     <row r="9" ht="21.0" customHeight="1">
-      <c r="A9" s="94">
+      <c r="A9" s="101">
         <v>2.0</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="94" t="s">
+      <c r="C9" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="95" t="s">
+      <c r="D9" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="96" t="s">
-        <v>356</v>
-      </c>
-      <c r="F9" s="96" t="s">
-        <v>357</v>
-      </c>
-      <c r="G9" s="40"/>
-      <c r="H9" s="97" t="s">
+      <c r="E9" s="103" t="s">
+        <v>359</v>
+      </c>
+      <c r="F9" s="103" t="s">
+        <v>360</v>
+      </c>
+      <c r="G9" s="42"/>
+      <c r="H9" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I9" s="31"/>
@@ -9684,26 +9730,26 @@
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1">
-      <c r="A10" s="94">
+      <c r="A10" s="101">
         <v>3.0</v>
       </c>
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="94" t="s">
+      <c r="C10" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="95" t="s">
+      <c r="D10" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="98" t="s">
-        <v>358</v>
-      </c>
-      <c r="F10" s="98" t="s">
-        <v>359</v>
-      </c>
-      <c r="G10" s="40"/>
-      <c r="H10" s="97" t="s">
+      <c r="E10" s="105" t="s">
+        <v>361</v>
+      </c>
+      <c r="F10" s="105" t="s">
+        <v>362</v>
+      </c>
+      <c r="G10" s="42"/>
+      <c r="H10" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I10" s="31"/>
@@ -9721,26 +9767,26 @@
       </c>
     </row>
     <row r="11" ht="21.0" customHeight="1">
-      <c r="A11" s="94">
+      <c r="A11" s="101">
         <v>4.0</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="94" t="s">
+      <c r="C11" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="95" t="s">
+      <c r="D11" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="96" t="s">
-        <v>360</v>
-      </c>
-      <c r="F11" s="96" t="s">
-        <v>361</v>
-      </c>
-      <c r="G11" s="40"/>
-      <c r="H11" s="97" t="s">
+      <c r="E11" s="103" t="s">
+        <v>363</v>
+      </c>
+      <c r="F11" s="103" t="s">
+        <v>364</v>
+      </c>
+      <c r="G11" s="42"/>
+      <c r="H11" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I11" s="31"/>
@@ -9758,26 +9804,26 @@
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="94">
+      <c r="A12" s="101">
         <v>5.0</v>
       </c>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="95" t="s">
+      <c r="D12" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="96" t="s">
-        <v>362</v>
-      </c>
-      <c r="F12" s="96" t="s">
-        <v>355</v>
-      </c>
-      <c r="G12" s="40"/>
-      <c r="H12" s="97" t="s">
+      <c r="E12" s="103" t="s">
+        <v>365</v>
+      </c>
+      <c r="F12" s="103" t="s">
+        <v>358</v>
+      </c>
+      <c r="G12" s="42"/>
+      <c r="H12" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I12" s="28"/>
@@ -9795,26 +9841,26 @@
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1">
-      <c r="A13" s="94">
+      <c r="A13" s="101">
         <v>6.0</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="94" t="s">
+      <c r="C13" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="95" t="s">
+      <c r="D13" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="99" t="s">
-        <v>363</v>
-      </c>
-      <c r="F13" s="99" t="s">
-        <v>185</v>
-      </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="97" t="s">
+      <c r="E13" s="106" t="s">
+        <v>366</v>
+      </c>
+      <c r="F13" s="106" t="s">
+        <v>367</v>
+      </c>
+      <c r="G13" s="42"/>
+      <c r="H13" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I13" s="31"/>
@@ -9832,26 +9878,26 @@
       </c>
     </row>
     <row r="14" ht="24.75" customHeight="1">
-      <c r="A14" s="94">
+      <c r="A14" s="101">
         <v>7.0</v>
       </c>
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="94" t="s">
+      <c r="C14" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="95" t="s">
+      <c r="D14" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="96" t="s">
-        <v>364</v>
-      </c>
-      <c r="F14" s="96" t="s">
-        <v>181</v>
-      </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="97" t="s">
+      <c r="E14" s="103" t="s">
+        <v>368</v>
+      </c>
+      <c r="F14" s="103" t="s">
+        <v>182</v>
+      </c>
+      <c r="G14" s="42"/>
+      <c r="H14" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I14" s="28"/>
@@ -9869,26 +9915,26 @@
       </c>
     </row>
     <row r="15" ht="21.0" customHeight="1">
-      <c r="A15" s="94">
+      <c r="A15" s="101">
         <v>8.0</v>
       </c>
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="95" t="s">
+      <c r="D15" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="99" t="s">
-        <v>365</v>
-      </c>
-      <c r="F15" s="99" t="s">
-        <v>366</v>
-      </c>
-      <c r="G15" s="40"/>
-      <c r="H15" s="97" t="s">
+      <c r="E15" s="106" t="s">
+        <v>369</v>
+      </c>
+      <c r="F15" s="106" t="s">
+        <v>370</v>
+      </c>
+      <c r="G15" s="42"/>
+      <c r="H15" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I15" s="31"/>
@@ -9906,26 +9952,26 @@
       </c>
     </row>
     <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="94">
+      <c r="A16" s="101">
         <v>9.0</v>
       </c>
-      <c r="B16" s="94" t="s">
+      <c r="B16" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="94" t="s">
+      <c r="C16" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="95" t="s">
+      <c r="D16" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="96" t="s">
-        <v>367</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>368</v>
-      </c>
-      <c r="G16" s="40"/>
-      <c r="H16" s="97" t="s">
+      <c r="E16" s="103" t="s">
+        <v>371</v>
+      </c>
+      <c r="F16" s="103" t="s">
+        <v>372</v>
+      </c>
+      <c r="G16" s="42"/>
+      <c r="H16" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I16" s="28"/>
@@ -9943,26 +9989,26 @@
       </c>
     </row>
     <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="94">
+      <c r="A17" s="101">
         <v>10.0</v>
       </c>
-      <c r="B17" s="94" t="s">
+      <c r="B17" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="95" t="s">
+      <c r="D17" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="96" t="s">
-        <v>369</v>
-      </c>
-      <c r="F17" s="96" t="s">
-        <v>370</v>
-      </c>
-      <c r="G17" s="40"/>
-      <c r="H17" s="97" t="s">
+      <c r="E17" s="103" t="s">
+        <v>373</v>
+      </c>
+      <c r="F17" s="103" t="s">
+        <v>374</v>
+      </c>
+      <c r="G17" s="42"/>
+      <c r="H17" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I17" s="31"/>
@@ -9980,26 +10026,26 @@
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="94">
+      <c r="A18" s="101">
         <v>11.0</v>
       </c>
-      <c r="B18" s="94" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="94" t="s">
+      <c r="B18" s="101" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="95" t="s">
+      <c r="D18" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="96" t="s">
-        <v>371</v>
-      </c>
-      <c r="F18" s="96" t="s">
-        <v>372</v>
-      </c>
-      <c r="G18" s="40"/>
-      <c r="H18" s="97" t="s">
+      <c r="E18" s="103" t="s">
+        <v>375</v>
+      </c>
+      <c r="F18" s="103" t="s">
+        <v>367</v>
+      </c>
+      <c r="G18" s="42"/>
+      <c r="H18" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I18" s="28"/>
@@ -10017,26 +10063,26 @@
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1">
-      <c r="A19" s="94">
+      <c r="A19" s="101">
         <v>12.0</v>
       </c>
-      <c r="B19" s="94" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="94" t="s">
+      <c r="B19" s="101" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="95" t="s">
+      <c r="D19" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="96" t="s">
-        <v>373</v>
-      </c>
-      <c r="F19" s="96" t="s">
-        <v>374</v>
-      </c>
-      <c r="G19" s="40"/>
-      <c r="H19" s="97" t="s">
+      <c r="E19" s="103" t="s">
+        <v>376</v>
+      </c>
+      <c r="F19" s="103" t="s">
+        <v>377</v>
+      </c>
+      <c r="G19" s="42"/>
+      <c r="H19" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I19" s="31"/>
@@ -10054,26 +10100,26 @@
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1">
-      <c r="A20" s="94">
+      <c r="A20" s="101">
         <v>13.0</v>
       </c>
-      <c r="B20" s="94" t="s">
+      <c r="B20" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="94" t="s">
+      <c r="C20" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="95" t="s">
+      <c r="D20" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="96" t="s">
-        <v>375</v>
-      </c>
-      <c r="F20" s="96" t="s">
-        <v>376</v>
-      </c>
-      <c r="G20" s="40"/>
-      <c r="H20" s="97" t="s">
+      <c r="E20" s="103" t="s">
+        <v>378</v>
+      </c>
+      <c r="F20" s="103" t="s">
+        <v>379</v>
+      </c>
+      <c r="G20" s="42"/>
+      <c r="H20" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I20" s="28"/>
@@ -10091,26 +10137,26 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="94">
+      <c r="A21" s="101">
         <v>14.0</v>
       </c>
-      <c r="B21" s="94" t="s">
+      <c r="B21" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="94" t="s">
+      <c r="C21" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="95" t="s">
+      <c r="D21" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="96" t="s">
-        <v>377</v>
-      </c>
-      <c r="F21" s="96" t="s">
-        <v>147</v>
-      </c>
-      <c r="G21" s="40"/>
-      <c r="H21" s="97" t="s">
+      <c r="E21" s="103" t="s">
+        <v>380</v>
+      </c>
+      <c r="F21" s="103" t="s">
+        <v>381</v>
+      </c>
+      <c r="G21" s="42"/>
+      <c r="H21" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I21" s="31"/>
@@ -10128,26 +10174,26 @@
       </c>
     </row>
     <row r="22" ht="23.25" customHeight="1">
-      <c r="A22" s="94">
+      <c r="A22" s="101">
         <v>15.0</v>
       </c>
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="94" t="s">
+      <c r="C22" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="96" t="s">
-        <v>378</v>
-      </c>
-      <c r="F22" s="96" t="s">
-        <v>379</v>
-      </c>
-      <c r="G22" s="40"/>
-      <c r="H22" s="97" t="s">
+      <c r="E22" s="103" t="s">
+        <v>382</v>
+      </c>
+      <c r="F22" s="103" t="s">
+        <v>383</v>
+      </c>
+      <c r="G22" s="42"/>
+      <c r="H22" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I22" s="28"/>
@@ -10165,26 +10211,26 @@
       </c>
     </row>
     <row r="23" ht="21.75" customHeight="1">
-      <c r="A23" s="94">
+      <c r="A23" s="101">
         <v>16.0</v>
       </c>
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="94" t="s">
+      <c r="C23" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="95" t="s">
+      <c r="D23" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="96" t="s">
-        <v>380</v>
-      </c>
-      <c r="F23" s="96" t="s">
-        <v>381</v>
-      </c>
-      <c r="G23" s="40"/>
-      <c r="H23" s="100" t="s">
+      <c r="E23" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="F23" s="103" t="s">
+        <v>385</v>
+      </c>
+      <c r="G23" s="42"/>
+      <c r="H23" s="107" t="s">
         <v>71</v>
       </c>
       <c r="I23" s="31"/>
@@ -10202,26 +10248,26 @@
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1">
-      <c r="A24" s="94">
+      <c r="A24" s="101">
         <v>17.0</v>
       </c>
-      <c r="B24" s="94" t="s">
+      <c r="B24" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="94" t="s">
+      <c r="C24" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="95" t="s">
+      <c r="D24" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="96" t="s">
-        <v>382</v>
-      </c>
-      <c r="F24" s="96" t="s">
-        <v>383</v>
-      </c>
-      <c r="G24" s="40"/>
-      <c r="H24" s="97" t="s">
+      <c r="E24" s="103" t="s">
+        <v>386</v>
+      </c>
+      <c r="F24" s="103" t="s">
+        <v>387</v>
+      </c>
+      <c r="G24" s="42"/>
+      <c r="H24" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I24" s="31"/>
@@ -10239,26 +10285,26 @@
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="94">
+      <c r="A25" s="101">
         <v>18.0</v>
       </c>
-      <c r="B25" s="94" t="s">
+      <c r="B25" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="94" t="s">
+      <c r="C25" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="95" t="s">
+      <c r="D25" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="96" t="s">
-        <v>384</v>
-      </c>
-      <c r="F25" s="96" t="s">
-        <v>385</v>
-      </c>
-      <c r="G25" s="40"/>
-      <c r="H25" s="97" t="s">
+      <c r="E25" s="103" t="s">
+        <v>388</v>
+      </c>
+      <c r="F25" s="103" t="s">
+        <v>389</v>
+      </c>
+      <c r="G25" s="42"/>
+      <c r="H25" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I25" s="28"/>
@@ -10276,26 +10322,26 @@
       </c>
     </row>
     <row r="26" ht="24.0" customHeight="1">
-      <c r="A26" s="94">
+      <c r="A26" s="101">
         <v>19.0</v>
       </c>
-      <c r="B26" s="94" t="s">
+      <c r="B26" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="94" t="s">
+      <c r="C26" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="95" t="s">
+      <c r="D26" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="96" t="s">
-        <v>386</v>
-      </c>
-      <c r="F26" s="96" t="s">
-        <v>387</v>
-      </c>
-      <c r="G26" s="40"/>
-      <c r="H26" s="97" t="s">
+      <c r="E26" s="108" t="s">
+        <v>390</v>
+      </c>
+      <c r="F26" s="108" t="s">
+        <v>391</v>
+      </c>
+      <c r="G26" s="42"/>
+      <c r="H26" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I26" s="28"/>
@@ -10313,26 +10359,26 @@
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1">
-      <c r="A27" s="94">
+      <c r="A27" s="101">
         <v>20.0</v>
       </c>
-      <c r="B27" s="94" t="s">
+      <c r="B27" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="94" t="s">
+      <c r="C27" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="95" t="s">
+      <c r="D27" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="96" t="s">
-        <v>388</v>
-      </c>
-      <c r="F27" s="96" t="s">
-        <v>361</v>
-      </c>
-      <c r="G27" s="40"/>
-      <c r="H27" s="97" t="s">
+      <c r="E27" s="103" t="s">
+        <v>392</v>
+      </c>
+      <c r="F27" s="103" t="s">
+        <v>364</v>
+      </c>
+      <c r="G27" s="42"/>
+      <c r="H27" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I27" s="28"/>
@@ -10350,26 +10396,26 @@
       </c>
     </row>
     <row r="28" ht="20.25" customHeight="1">
-      <c r="A28" s="94">
+      <c r="A28" s="101">
         <v>21.0</v>
       </c>
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="94" t="s">
+      <c r="C28" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="95" t="s">
+      <c r="D28" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="96" t="s">
-        <v>389</v>
-      </c>
-      <c r="F28" s="96" t="s">
-        <v>390</v>
-      </c>
-      <c r="G28" s="40"/>
-      <c r="H28" s="97" t="s">
+      <c r="E28" s="103" t="s">
+        <v>393</v>
+      </c>
+      <c r="F28" s="103" t="s">
+        <v>394</v>
+      </c>
+      <c r="G28" s="42"/>
+      <c r="H28" s="104" t="s">
         <v>99</v>
       </c>
       <c r="I28" s="31"/>
@@ -10387,26 +10433,26 @@
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="94">
+      <c r="A29" s="101">
         <v>22.0</v>
       </c>
-      <c r="B29" s="94" t="s">
+      <c r="B29" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="94" t="s">
+      <c r="C29" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="95" t="s">
+      <c r="D29" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="96" t="s">
-        <v>391</v>
-      </c>
-      <c r="F29" s="96" t="s">
-        <v>392</v>
-      </c>
-      <c r="G29" s="40"/>
-      <c r="H29" s="97" t="s">
+      <c r="E29" s="103" t="s">
+        <v>395</v>
+      </c>
+      <c r="F29" s="103" t="s">
+        <v>396</v>
+      </c>
+      <c r="G29" s="42"/>
+      <c r="H29" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I29" s="28"/>
@@ -10424,26 +10470,26 @@
       </c>
     </row>
     <row r="30" ht="20.25" customHeight="1">
-      <c r="A30" s="94">
+      <c r="A30" s="101">
         <v>23.0</v>
       </c>
-      <c r="B30" s="94" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" s="94" t="s">
+      <c r="B30" s="101" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="95" t="s">
+      <c r="D30" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="96" t="s">
-        <v>393</v>
-      </c>
-      <c r="F30" s="96" t="s">
-        <v>394</v>
-      </c>
-      <c r="G30" s="40"/>
-      <c r="H30" s="97" t="s">
+      <c r="E30" s="103" t="s">
+        <v>397</v>
+      </c>
+      <c r="F30" s="103" t="s">
+        <v>398</v>
+      </c>
+      <c r="G30" s="42"/>
+      <c r="H30" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I30" s="31"/>
@@ -10461,26 +10507,26 @@
       </c>
     </row>
     <row r="31" ht="21.0" customHeight="1">
-      <c r="A31" s="94">
+      <c r="A31" s="101">
         <v>24.0</v>
       </c>
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="94" t="s">
+      <c r="C31" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="95" t="s">
+      <c r="D31" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="96" t="s">
-        <v>395</v>
-      </c>
-      <c r="F31" s="96" t="s">
-        <v>396</v>
-      </c>
-      <c r="G31" s="40"/>
-      <c r="H31" s="97" t="s">
+      <c r="E31" s="103" t="s">
+        <v>399</v>
+      </c>
+      <c r="F31" s="103" t="s">
+        <v>400</v>
+      </c>
+      <c r="G31" s="42"/>
+      <c r="H31" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I31" s="28"/>
@@ -10498,26 +10544,26 @@
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="94">
+      <c r="A32" s="101">
         <v>25.0</v>
       </c>
-      <c r="B32" s="94" t="s">
+      <c r="B32" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="94" t="s">
+      <c r="C32" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="95" t="s">
+      <c r="D32" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="96" t="s">
-        <v>397</v>
-      </c>
-      <c r="F32" s="96" t="s">
-        <v>398</v>
-      </c>
-      <c r="G32" s="40"/>
-      <c r="H32" s="97" t="s">
+      <c r="E32" s="103" t="s">
+        <v>401</v>
+      </c>
+      <c r="F32" s="103" t="s">
+        <v>402</v>
+      </c>
+      <c r="G32" s="42"/>
+      <c r="H32" s="104" t="s">
         <v>71</v>
       </c>
       <c r="I32" s="31"/>
@@ -10535,27 +10581,27 @@
       </c>
     </row>
     <row r="33" ht="21.0" customHeight="1">
-      <c r="A33" s="94">
+      <c r="A33" s="101">
         <v>26.0</v>
       </c>
-      <c r="B33" s="94" t="s">
+      <c r="B33" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="94" t="s">
+      <c r="C33" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="95" t="s">
+      <c r="D33" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="96" t="s">
+      <c r="E33" s="103" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="96" t="s">
-        <v>399</v>
-      </c>
-      <c r="G33" s="40"/>
-      <c r="H33" s="97" t="s">
-        <v>400</v>
+      <c r="F33" s="103" t="s">
+        <v>403</v>
+      </c>
+      <c r="G33" s="42"/>
+      <c r="H33" s="104" t="s">
+        <v>404</v>
       </c>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
@@ -10633,7 +10679,7 @@
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="7" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="6"/>
@@ -10658,7 +10704,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
@@ -10672,7 +10718,7 @@
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
       <c r="E3" s="11" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -10686,7 +10732,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -10700,7 +10746,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="11" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -10717,10 +10763,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="40" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -10770,23 +10816,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="48">
+      <c r="A8" s="49">
         <v>3.0</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="101" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="48" t="s">
         <v>306</v>
       </c>
-      <c r="E8" s="45" t="s">
-        <v>406</v>
-      </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41" t="s">
+      <c r="E8" s="48" t="s">
+        <v>410</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="43" t="s">
         <v>85</v>
       </c>
       <c r="H8" s="28"/>
@@ -10814,14 +10860,14 @@
         <v>76</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41" t="s">
-        <v>409</v>
+        <v>412</v>
+      </c>
+      <c r="F9" s="42"/>
+      <c r="G9" s="43" t="s">
+        <v>413</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
@@ -10838,7 +10884,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="48">
+      <c r="A10" s="49">
         <v>1.0</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -10848,14 +10894,14 @@
         <v>68</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>411</v>
-      </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41" t="s">
-        <v>412</v>
+        <v>415</v>
+      </c>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43" t="s">
+        <v>416</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
@@ -10882,14 +10928,14 @@
         <v>76</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>414</v>
-      </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41" t="s">
-        <v>401</v>
+        <v>418</v>
+      </c>
+      <c r="F11" s="42"/>
+      <c r="G11" s="43" t="s">
+        <v>405</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
@@ -10916,14 +10962,14 @@
         <v>86</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>416</v>
-      </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41" t="s">
-        <v>401</v>
+        <v>420</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="G12" s="43" t="s">
+        <v>405</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
@@ -10950,14 +10996,14 @@
         <v>86</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>418</v>
-      </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41" t="s">
-        <v>401</v>
+        <v>422</v>
+      </c>
+      <c r="F13" s="42"/>
+      <c r="G13" s="43" t="s">
+        <v>405</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
@@ -10984,13 +11030,13 @@
         <v>94</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41" t="s">
+      <c r="F14" s="42"/>
+      <c r="G14" s="43" t="s">
         <v>75</v>
       </c>
       <c r="H14" s="28"/>
@@ -11018,13 +11064,13 @@
         <v>86</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>421</v>
-      </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41" t="s">
+        <v>425</v>
+      </c>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43" t="s">
         <v>71</v>
       </c>
       <c r="H15" s="31"/>
@@ -11052,13 +11098,13 @@
         <v>94</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>423</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41" t="s">
+        <v>427</v>
+      </c>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43" t="s">
         <v>294</v>
       </c>
       <c r="H16" s="28"/>
@@ -11085,15 +11131,15 @@
       <c r="C17" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="23" t="s">
-        <v>424</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>425</v>
-      </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41" t="s">
-        <v>401</v>
+      <c r="D17" s="44" t="s">
+        <v>428</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>429</v>
+      </c>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43" t="s">
+        <v>405</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
@@ -11120,25 +11166,25 @@
         <v>94</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="F18" s="102"/>
-      <c r="G18" s="103" t="s">
-        <v>428</v>
-      </c>
-      <c r="H18" s="66"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="104"/>
-      <c r="N18" s="104"/>
-      <c r="O18" s="104"/>
-      <c r="P18" s="104"/>
-      <c r="Q18" s="66">
+        <v>431</v>
+      </c>
+      <c r="F18" s="109"/>
+      <c r="G18" s="110" t="s">
+        <v>432</v>
+      </c>
+      <c r="H18" s="70"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="111"/>
+      <c r="M18" s="111"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11154,25 +11200,25 @@
         <v>76</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="F19" s="102"/>
-      <c r="G19" s="103" t="s">
-        <v>401</v>
-      </c>
-      <c r="H19" s="66"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="67"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="67"/>
-      <c r="O19" s="67"/>
-      <c r="P19" s="67"/>
-      <c r="Q19" s="66">
+        <v>434</v>
+      </c>
+      <c r="F19" s="109"/>
+      <c r="G19" s="110" t="s">
+        <v>405</v>
+      </c>
+      <c r="H19" s="70"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11188,25 +11234,25 @@
         <v>76</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="F20" s="102"/>
-      <c r="G20" s="103" t="s">
-        <v>401</v>
-      </c>
-      <c r="H20" s="66"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="104"/>
-      <c r="O20" s="104"/>
-      <c r="P20" s="104"/>
-      <c r="Q20" s="66">
+        <v>436</v>
+      </c>
+      <c r="F20" s="109"/>
+      <c r="G20" s="110" t="s">
+        <v>405</v>
+      </c>
+      <c r="H20" s="70"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="111"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11222,16 +11268,16 @@
         <v>76</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="F21" s="40">
+        <v>438</v>
+      </c>
+      <c r="F21" s="42">
         <v>20.0</v>
       </c>
-      <c r="G21" s="41" t="s">
-        <v>435</v>
+      <c r="G21" s="43" t="s">
+        <v>439</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
@@ -11258,13 +11304,13 @@
         <v>86</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>437</v>
-      </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41" t="s">
+        <v>441</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43" t="s">
         <v>309</v>
       </c>
       <c r="H22" s="28"/>
@@ -11292,23 +11338,23 @@
         <v>86</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>439</v>
-      </c>
-      <c r="F23" s="102"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="104"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="104"/>
-      <c r="Q23" s="66">
+        <v>443</v>
+      </c>
+      <c r="F23" s="109"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="111"/>
+      <c r="N23" s="111"/>
+      <c r="O23" s="111"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11324,13 +11370,13 @@
         <v>86</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41" t="s">
+        <v>445</v>
+      </c>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43" t="s">
         <v>75</v>
       </c>
       <c r="H24" s="28"/>
@@ -11358,25 +11404,25 @@
         <v>86</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>406</v>
-      </c>
-      <c r="F25" s="102"/>
-      <c r="G25" s="103" t="s">
+        <v>410</v>
+      </c>
+      <c r="F25" s="109"/>
+      <c r="G25" s="110" t="s">
         <v>75</v>
       </c>
-      <c r="H25" s="66"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="104"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="104"/>
-      <c r="Q25" s="66">
+      <c r="H25" s="70"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="111"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11392,13 +11438,13 @@
         <v>94</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="F26" s="42"/>
+      <c r="G26" s="43" t="s">
         <v>99</v>
       </c>
       <c r="H26" s="28"/>
@@ -11425,15 +11471,15 @@
       <c r="C27" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41" t="s">
-        <v>401</v>
+      <c r="D27" s="44" t="s">
+        <v>449</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>450</v>
+      </c>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43" t="s">
+        <v>405</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
@@ -11460,13 +11506,13 @@
         <v>86</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>447</v>
-      </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
+        <v>452</v>
+      </c>
+      <c r="F28" s="42"/>
+      <c r="G28" s="43"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -11492,14 +11538,14 @@
         <v>94</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>449</v>
-      </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41" t="s">
-        <v>401</v>
+        <v>454</v>
+      </c>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43" t="s">
+        <v>405</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
@@ -11526,14 +11572,14 @@
         <v>76</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>451</v>
-      </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41" t="s">
-        <v>452</v>
+        <v>456</v>
+      </c>
+      <c r="F30" s="42"/>
+      <c r="G30" s="43" t="s">
+        <v>457</v>
       </c>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
@@ -11559,58 +11605,58 @@
       <c r="C31" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="23" t="s">
-        <v>453</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="F31" s="102"/>
-      <c r="G31" s="103" t="s">
-        <v>401</v>
-      </c>
-      <c r="H31" s="66"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="104"/>
-      <c r="N31" s="104"/>
-      <c r="O31" s="104"/>
-      <c r="P31" s="104"/>
-      <c r="Q31" s="66">
+      <c r="D31" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="44" t="s">
+        <v>458</v>
+      </c>
+      <c r="F31" s="109"/>
+      <c r="G31" s="110" t="s">
+        <v>405</v>
+      </c>
+      <c r="H31" s="70"/>
+      <c r="I31" s="111"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="111"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="111"/>
+      <c r="N31" s="111"/>
+      <c r="O31" s="111"/>
+      <c r="P31" s="111"/>
+      <c r="Q31" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="105">
+      <c r="A32" s="112">
         <v>25.0</v>
       </c>
-      <c r="B32" s="106" t="s">
+      <c r="B32" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="107" t="s">
+      <c r="C32" s="114" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="106" t="s">
-        <v>454</v>
-      </c>
-      <c r="E32" s="106" t="s">
-        <v>455</v>
-      </c>
-      <c r="F32" s="102"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="104"/>
-      <c r="N32" s="104"/>
-      <c r="O32" s="104"/>
-      <c r="P32" s="104"/>
-      <c r="Q32" s="66">
+      <c r="D32" s="113" t="s">
+        <v>459</v>
+      </c>
+      <c r="E32" s="113" t="s">
+        <v>460</v>
+      </c>
+      <c r="F32" s="109"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="111"/>
+      <c r="L32" s="111"/>
+      <c r="M32" s="111"/>
+      <c r="N32" s="111"/>
+      <c r="O32" s="111"/>
+      <c r="P32" s="111"/>
+      <c r="Q32" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11626,14 +11672,14 @@
         <v>76</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>457</v>
-      </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41" t="s">
-        <v>458</v>
+        <v>462</v>
+      </c>
+      <c r="F33" s="42"/>
+      <c r="G33" s="43" t="s">
+        <v>463</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
@@ -11712,7 +11758,7 @@
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="115" t="s">
         <v>37</v>
       </c>
       <c r="F1" s="5"/>
@@ -11737,7 +11783,7 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="108"/>
+      <c r="E2" s="115"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="13"/>
@@ -11749,8 +11795,8 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="108" t="s">
-        <v>459</v>
+      <c r="E3" s="115" t="s">
+        <v>464</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
@@ -11763,8 +11809,8 @@
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
-      <c r="E4" s="109" t="s">
-        <v>460</v>
+      <c r="E4" s="116" t="s">
+        <v>465</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
@@ -11777,8 +11823,8 @@
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="108" t="s">
-        <v>461</v>
+      <c r="E5" s="115" t="s">
+        <v>466</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
@@ -11795,10 +11841,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="40" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -11848,23 +11894,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="74">
+      <c r="A8" s="78">
         <v>1.0</v>
       </c>
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="111" t="s">
+      <c r="C8" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="112" t="s">
-        <v>462</v>
-      </c>
-      <c r="E8" s="112" t="s">
-        <v>240</v>
-      </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
+      <c r="D8" s="119" t="s">
+        <v>467</v>
+      </c>
+      <c r="E8" s="119" t="s">
+        <v>468</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -11880,23 +11926,23 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="76">
+      <c r="A9" s="80">
         <v>2.0</v>
       </c>
-      <c r="B9" s="110" t="s">
+      <c r="B9" s="117" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="111" t="s">
+      <c r="C9" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="112" t="s">
-        <v>463</v>
-      </c>
-      <c r="E9" s="112" t="s">
-        <v>464</v>
-      </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
+      <c r="D9" s="119" t="s">
+        <v>469</v>
+      </c>
+      <c r="E9" s="119" t="s">
+        <v>470</v>
+      </c>
+      <c r="F9" s="42"/>
+      <c r="G9" s="43"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -11912,23 +11958,23 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="74">
+      <c r="A10" s="78">
         <v>3.0</v>
       </c>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="111" t="s">
+      <c r="C10" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="113" t="s">
-        <v>465</v>
-      </c>
-      <c r="E10" s="113" t="s">
-        <v>466</v>
-      </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
+      <c r="D10" s="120" t="s">
+        <v>471</v>
+      </c>
+      <c r="E10" s="120" t="s">
+        <v>472</v>
+      </c>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -11944,23 +11990,23 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="76">
+      <c r="A11" s="80">
         <v>4.0</v>
       </c>
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="111" t="s">
+      <c r="C11" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="113" t="s">
-        <v>467</v>
-      </c>
-      <c r="E11" s="113" t="s">
-        <v>468</v>
-      </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
+      <c r="D11" s="120" t="s">
+        <v>473</v>
+      </c>
+      <c r="E11" s="120" t="s">
+        <v>474</v>
+      </c>
+      <c r="F11" s="42"/>
+      <c r="G11" s="43"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -11976,23 +12022,23 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="74">
+      <c r="A12" s="78">
         <v>5.0</v>
       </c>
-      <c r="B12" s="110" t="s">
+      <c r="B12" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="111" t="s">
+      <c r="C12" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="114" t="s">
-        <v>469</v>
-      </c>
-      <c r="E12" s="112" t="s">
-        <v>470</v>
-      </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
+      <c r="D12" s="121" t="s">
+        <v>475</v>
+      </c>
+      <c r="E12" s="119" t="s">
+        <v>476</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="G12" s="43"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -12008,23 +12054,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="76">
+      <c r="A13" s="80">
         <v>6.0</v>
       </c>
-      <c r="B13" s="110" t="s">
+      <c r="B13" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="115" t="s">
+      <c r="C13" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="114" t="s">
-        <v>471</v>
-      </c>
-      <c r="E13" s="114" t="s">
-        <v>472</v>
-      </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41"/>
+      <c r="D13" s="121" t="s">
+        <v>477</v>
+      </c>
+      <c r="E13" s="121" t="s">
+        <v>478</v>
+      </c>
+      <c r="F13" s="42"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -12040,23 +12086,23 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="74">
+      <c r="A14" s="78">
         <v>7.0</v>
       </c>
-      <c r="B14" s="110" t="s">
+      <c r="B14" s="117" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="115" t="s">
+      <c r="C14" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="114" t="s">
-        <v>473</v>
-      </c>
-      <c r="E14" s="114" t="s">
-        <v>474</v>
-      </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
+      <c r="D14" s="121" t="s">
+        <v>479</v>
+      </c>
+      <c r="E14" s="121" t="s">
+        <v>480</v>
+      </c>
+      <c r="F14" s="42"/>
+      <c r="G14" s="43"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -12072,23 +12118,23 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="76">
+      <c r="A15" s="80">
         <v>8.0</v>
       </c>
-      <c r="B15" s="110" t="s">
+      <c r="B15" s="117" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="115" t="s">
+      <c r="C15" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="114" t="s">
-        <v>475</v>
-      </c>
-      <c r="E15" s="114" t="s">
-        <v>476</v>
-      </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
+      <c r="D15" s="121" t="s">
+        <v>481</v>
+      </c>
+      <c r="E15" s="121" t="s">
+        <v>482</v>
+      </c>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -12104,23 +12150,23 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="74">
+      <c r="A16" s="78">
         <v>9.0</v>
       </c>
-      <c r="B16" s="110" t="s">
+      <c r="B16" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="114" t="s">
-        <v>477</v>
-      </c>
-      <c r="E16" s="114" t="s">
-        <v>478</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
+      <c r="D16" s="121" t="s">
+        <v>483</v>
+      </c>
+      <c r="E16" s="121" t="s">
+        <v>484</v>
+      </c>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
       <c r="J16" s="29"/>
@@ -12136,23 +12182,23 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="76">
+      <c r="A17" s="80">
         <v>10.0</v>
       </c>
-      <c r="B17" s="110" t="s">
+      <c r="B17" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="115" t="s">
+      <c r="C17" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="116" t="s">
-        <v>479</v>
-      </c>
-      <c r="E17" s="116" t="s">
-        <v>480</v>
-      </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
+      <c r="D17" s="123" t="s">
+        <v>485</v>
+      </c>
+      <c r="E17" s="123" t="s">
+        <v>476</v>
+      </c>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -12168,23 +12214,23 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="74">
+      <c r="A18" s="78">
         <v>12.0</v>
       </c>
-      <c r="B18" s="110" t="s">
+      <c r="B18" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="115" t="s">
+      <c r="C18" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="114" t="s">
-        <v>481</v>
-      </c>
-      <c r="E18" s="114" t="s">
-        <v>482</v>
-      </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
+      <c r="D18" s="121" t="s">
+        <v>486</v>
+      </c>
+      <c r="E18" s="121" t="s">
+        <v>487</v>
+      </c>
+      <c r="F18" s="42"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -12200,23 +12246,23 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="76">
+      <c r="A19" s="80">
         <v>11.0</v>
       </c>
-      <c r="B19" s="110" t="s">
+      <c r="B19" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="115" t="s">
+      <c r="C19" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="114" t="s">
-        <v>483</v>
-      </c>
-      <c r="E19" s="114" t="s">
-        <v>484</v>
-      </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
+      <c r="D19" s="121" t="s">
+        <v>488</v>
+      </c>
+      <c r="E19" s="121" t="s">
+        <v>489</v>
+      </c>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -12232,23 +12278,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="74">
+      <c r="A20" s="78">
         <v>13.0</v>
       </c>
-      <c r="B20" s="110" t="s">
+      <c r="B20" s="117" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="115" t="s">
+      <c r="C20" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="114" t="s">
+      <c r="D20" s="121" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="114" t="s">
-        <v>485</v>
-      </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41"/>
+      <c r="E20" s="121" t="s">
+        <v>490</v>
+      </c>
+      <c r="F20" s="42"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -12264,23 +12310,23 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="76">
+      <c r="A21" s="80">
         <v>14.0</v>
       </c>
-      <c r="B21" s="110" t="s">
+      <c r="B21" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="115" t="s">
+      <c r="C21" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="114" t="s">
-        <v>473</v>
-      </c>
-      <c r="E21" s="114" t="s">
-        <v>486</v>
-      </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41"/>
+      <c r="D21" s="121" t="s">
+        <v>479</v>
+      </c>
+      <c r="E21" s="121" t="s">
+        <v>491</v>
+      </c>
+      <c r="F21" s="42"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -12296,23 +12342,23 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="74">
+      <c r="A22" s="78">
         <v>15.0</v>
       </c>
-      <c r="B22" s="110" t="s">
+      <c r="B22" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="111" t="s">
+      <c r="C22" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="116" t="s">
-        <v>487</v>
-      </c>
-      <c r="E22" s="116" t="s">
-        <v>374</v>
-      </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41"/>
+      <c r="D22" s="123" t="s">
+        <v>184</v>
+      </c>
+      <c r="E22" s="123" t="s">
+        <v>492</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -12328,23 +12374,23 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="76">
+      <c r="A23" s="80">
         <v>16.0</v>
       </c>
-      <c r="B23" s="110" t="s">
+      <c r="B23" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="111" t="s">
+      <c r="C23" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="116" t="s">
-        <v>488</v>
-      </c>
-      <c r="E23" s="116" t="s">
-        <v>489</v>
-      </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
+      <c r="D23" s="123" t="s">
+        <v>493</v>
+      </c>
+      <c r="E23" s="123" t="s">
+        <v>494</v>
+      </c>
+      <c r="F23" s="42"/>
+      <c r="G23" s="43"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -12360,23 +12406,23 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="74">
+      <c r="A24" s="78">
         <v>17.0</v>
       </c>
-      <c r="B24" s="110" t="s">
+      <c r="B24" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="111" t="s">
+      <c r="C24" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="112" t="s">
-        <v>490</v>
-      </c>
-      <c r="E24" s="112" t="s">
-        <v>491</v>
-      </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
+      <c r="D24" s="119" t="s">
+        <v>495</v>
+      </c>
+      <c r="E24" s="119" t="s">
+        <v>496</v>
+      </c>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -12392,23 +12438,23 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="74">
+      <c r="A25" s="78">
         <v>18.0</v>
       </c>
-      <c r="B25" s="110" t="s">
+      <c r="B25" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="111" t="s">
+      <c r="C25" s="118" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="112" t="s">
-        <v>492</v>
-      </c>
-      <c r="E25" s="112" t="s">
-        <v>493</v>
-      </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
+      <c r="D25" s="124" t="s">
+        <v>497</v>
+      </c>
+      <c r="E25" s="124" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -12424,23 +12470,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="74">
+      <c r="A26" s="78">
         <v>19.0</v>
       </c>
-      <c r="B26" s="110" t="s">
+      <c r="B26" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="111" t="s">
+      <c r="C26" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="112" t="s">
-        <v>494</v>
-      </c>
-      <c r="E26" s="112" t="s">
-        <v>470</v>
-      </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
+      <c r="D26" s="119" t="s">
+        <v>498</v>
+      </c>
+      <c r="E26" s="119" t="s">
+        <v>476</v>
+      </c>
+      <c r="F26" s="42"/>
+      <c r="G26" s="43"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -12456,23 +12502,23 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="74">
+      <c r="A27" s="78">
         <v>20.0</v>
       </c>
-      <c r="B27" s="110" t="s">
+      <c r="B27" s="117" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="111" t="s">
+      <c r="C27" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="112" t="s">
-        <v>495</v>
-      </c>
-      <c r="E27" s="112" t="s">
-        <v>486</v>
-      </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
+      <c r="D27" s="119" t="s">
+        <v>499</v>
+      </c>
+      <c r="E27" s="119" t="s">
+        <v>491</v>
+      </c>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43"/>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
@@ -12488,23 +12534,23 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="74">
+      <c r="A28" s="78">
         <v>21.0</v>
       </c>
-      <c r="B28" s="110" t="s">
+      <c r="B28" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="111" t="s">
+      <c r="C28" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="112" t="s">
-        <v>496</v>
-      </c>
-      <c r="E28" s="112" t="s">
-        <v>497</v>
-      </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
+      <c r="D28" s="124" t="s">
+        <v>500</v>
+      </c>
+      <c r="E28" s="124" t="s">
+        <v>144</v>
+      </c>
+      <c r="F28" s="42"/>
+      <c r="G28" s="43"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -12520,23 +12566,23 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="74">
+      <c r="A29" s="78">
         <v>22.0</v>
       </c>
-      <c r="B29" s="110" t="s">
+      <c r="B29" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="111" t="s">
+      <c r="C29" s="118" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="112" t="s">
-        <v>498</v>
-      </c>
-      <c r="E29" s="112" t="s">
-        <v>181</v>
-      </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41"/>
+      <c r="D29" s="119" t="s">
+        <v>501</v>
+      </c>
+      <c r="E29" s="119" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -12552,23 +12598,23 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="74">
+      <c r="A30" s="78">
         <v>23.0</v>
       </c>
-      <c r="B30" s="110" t="s">
+      <c r="B30" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="111" t="s">
+      <c r="C30" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="112" t="s">
-        <v>499</v>
-      </c>
-      <c r="E30" s="112" t="s">
-        <v>500</v>
-      </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41"/>
+      <c r="D30" s="119" t="s">
+        <v>502</v>
+      </c>
+      <c r="E30" s="119" t="s">
+        <v>503</v>
+      </c>
+      <c r="F30" s="42"/>
+      <c r="G30" s="43"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -12584,23 +12630,23 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="80">
         <v>24.0</v>
       </c>
-      <c r="B31" s="110" t="s">
+      <c r="B31" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="111" t="s">
+      <c r="C31" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="112" t="s">
+      <c r="D31" s="119" t="s">
         <v>282</v>
       </c>
-      <c r="E31" s="112" t="s">
-        <v>501</v>
-      </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
+      <c r="E31" s="119" t="s">
+        <v>504</v>
+      </c>
+      <c r="F31" s="42"/>
+      <c r="G31" s="43"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -12616,23 +12662,23 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="74">
+      <c r="A32" s="78">
         <v>25.0</v>
       </c>
-      <c r="B32" s="110" t="s">
+      <c r="B32" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="111" t="s">
+      <c r="C32" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="112" t="s">
-        <v>502</v>
-      </c>
-      <c r="E32" s="112" t="s">
-        <v>503</v>
-      </c>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41"/>
+      <c r="D32" s="119" t="s">
+        <v>505</v>
+      </c>
+      <c r="E32" s="119" t="s">
+        <v>506</v>
+      </c>
+      <c r="F32" s="42"/>
+      <c r="G32" s="43"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -12648,23 +12694,23 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="80">
         <v>26.0</v>
       </c>
-      <c r="B33" s="110" t="s">
+      <c r="B33" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="111" t="s">
+      <c r="C33" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="116" t="s">
-        <v>181</v>
-      </c>
-      <c r="E33" s="116" t="s">
-        <v>504</v>
-      </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
+      <c r="D33" s="123" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="123" t="s">
+        <v>507</v>
+      </c>
+      <c r="F33" s="42"/>
+      <c r="G33" s="43"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
